--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Reports\Camera Reports\Dashboard\PCS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\DEN Camera System\PCS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E1A3DB8F-A959-4B02-B477-9D6636134DDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2C21E548-DF63-467E-8738-2BEB6276D55B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRIVE-ALERTS" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1132" uniqueCount="468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1201" uniqueCount="491">
   <si>
     <t>DRIVE ALERTS</t>
   </si>
@@ -1384,28 +1384,16 @@
     <t>18.5mi NW of Richfield UT</t>
   </si>
   <si>
-    <t>03/17/26 11:04 EDT</t>
-  </si>
-  <si>
-    <t>1.3mi W of Garden Acres CA</t>
-  </si>
-  <si>
     <t>03/17/26 11:42 EDT</t>
   </si>
   <si>
     <t>1.4mi W of Springville UT</t>
   </si>
   <si>
-    <t>03/17/26 17:46 EDT</t>
-  </si>
-  <si>
-    <t>12.4mi SW of Nephi UT</t>
-  </si>
-  <si>
-    <t>03/17/26 18:32 EDT</t>
-  </si>
-  <si>
-    <t>19.1mi NW of Richfield UT</t>
+    <t>03/17/26 15:10 EDT</t>
+  </si>
+  <si>
+    <t>1.2mi NW of Murray UT</t>
   </si>
   <si>
     <t>03/17/26 18:37 EDT</t>
@@ -1414,16 +1402,97 @@
     <t>8.9mi SW of Cortez CO</t>
   </si>
   <si>
-    <t>9.1mi SW of Cortez CO</t>
-  </si>
-  <si>
-    <t>03/17/26 21:00 EDT</t>
-  </si>
-  <si>
-    <t>14.4mi N of Hurricane UT</t>
-  </si>
-  <si>
-    <t>14.2mi N of Hurricane UT</t>
+    <t>03/18/26 16:05 EDT</t>
+  </si>
+  <si>
+    <t>55.4mi SE of Las Vegas NM</t>
+  </si>
+  <si>
+    <t>03/18/26 17:45 EDT</t>
+  </si>
+  <si>
+    <t>03/19/26 12:56 EDT</t>
+  </si>
+  <si>
+    <t>03/18/26 18:04 EDT</t>
+  </si>
+  <si>
+    <t>20mi W of Amarillo TX</t>
+  </si>
+  <si>
+    <t>03/19/26 08:40 EDT</t>
+  </si>
+  <si>
+    <t>5.8mi S of Edmond OK</t>
+  </si>
+  <si>
+    <t>03/20/26 09:12 EDT</t>
+  </si>
+  <si>
+    <t>4.9mi E of Amarillo TX</t>
+  </si>
+  <si>
+    <t>03/20/26 09:38 EDT</t>
+  </si>
+  <si>
+    <t>1.9mi N of Burley ID</t>
+  </si>
+  <si>
+    <t>03/20/26 10:19 EDT</t>
+  </si>
+  <si>
+    <t>61.5mi E of Black Forest CO</t>
+  </si>
+  <si>
+    <t>03/20/26 10:51 EDT</t>
+  </si>
+  <si>
+    <t>0.9mi S of Tucumcari NM</t>
+  </si>
+  <si>
+    <t>03/20/26 11:52 EDT</t>
+  </si>
+  <si>
+    <t>24.6mi W of Tucumcari NM</t>
+  </si>
+  <si>
+    <t>03/20/26 12:19 EDT</t>
+  </si>
+  <si>
+    <t>55.2mi W of Tucumcari NM</t>
+  </si>
+  <si>
+    <t>03/20/26 12:39 EDT</t>
+  </si>
+  <si>
+    <t>43.8mi S of Las Vegas NM</t>
+  </si>
+  <si>
+    <t>03/20/26 13:00 EDT</t>
+  </si>
+  <si>
+    <t>41.6mi E of Edgewood NM</t>
+  </si>
+  <si>
+    <t>03/20/26 13:26 EDT</t>
+  </si>
+  <si>
+    <t>12.7mi SE of Edgewood NM</t>
+  </si>
+  <si>
+    <t>03/20/26 21:46 EDT</t>
+  </si>
+  <si>
+    <t>10.8mi E of Barstow CA</t>
+  </si>
+  <si>
+    <t>03/21/26 10:52 EDT</t>
+  </si>
+  <si>
+    <t>17.4mi NE of Richfield UT</t>
+  </si>
+  <si>
+    <t>03/21/26 13:00 EDT</t>
   </si>
 </sst>
 </file>
@@ -1785,7 +1854,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M194"/>
+  <dimension ref="A1:M206"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="13" width="15" customWidth="1"/>
@@ -8056,27 +8125,25 @@
         <v>454</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="C187" s="3">
-        <v>926</v>
+        <v>672</v>
       </c>
       <c r="D187" s="3">
-        <v>1494427295</v>
+        <v>1494461959</v>
       </c>
       <c r="E187" s="3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F187" s="3" t="s">
         <v>455</v>
       </c>
       <c r="G187" s="3"/>
       <c r="H187" s="3">
-        <v>52</v>
-      </c>
-      <c r="I187" s="3">
-        <v>65</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="I187" s="3"/>
       <c r="J187" s="3" t="s">
         <v>19</v>
       </c>
@@ -8089,13 +8156,13 @@
         <v>456</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>50</v>
+        <v>418</v>
       </c>
       <c r="C188" s="3">
-        <v>672</v>
+        <v>730</v>
       </c>
       <c r="D188" s="3">
-        <v>1494461959</v>
+        <v>1494655283</v>
       </c>
       <c r="E188" s="3" t="s">
         <v>26</v>
@@ -8105,9 +8172,11 @@
       </c>
       <c r="G188" s="3"/>
       <c r="H188" s="3">
-        <v>53</v>
-      </c>
-      <c r="I188" s="3"/>
+        <v>74</v>
+      </c>
+      <c r="I188" s="3">
+        <v>70</v>
+      </c>
       <c r="J188" s="3" t="s">
         <v>19</v>
       </c>
@@ -8120,13 +8189,13 @@
         <v>458</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="C189" s="3">
-        <v>357</v>
+        <v>672</v>
       </c>
       <c r="D189" s="3">
-        <v>1494790804</v>
+        <v>1494825081</v>
       </c>
       <c r="E189" s="3" t="s">
         <v>26</v>
@@ -8134,14 +8203,12 @@
       <c r="F189" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="G189" s="3" t="s">
-        <v>52</v>
-      </c>
+      <c r="G189" s="3"/>
       <c r="H189" s="3">
+        <v>74</v>
+      </c>
+      <c r="I189" s="3">
         <v>65</v>
-      </c>
-      <c r="I189" s="3">
-        <v>80</v>
       </c>
       <c r="J189" s="3" t="s">
         <v>19</v>
@@ -8155,27 +8222,27 @@
         <v>460</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="C190" s="3">
-        <v>357</v>
+        <v>672</v>
       </c>
       <c r="D190" s="3">
-        <v>1494821911</v>
+        <v>1495493954</v>
       </c>
       <c r="E190" s="3" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="F190" s="3" t="s">
         <v>461</v>
       </c>
-      <c r="G190" s="3" t="s">
-        <v>52</v>
-      </c>
+      <c r="G190" s="3"/>
       <c r="H190" s="3">
-        <v>27</v>
-      </c>
-      <c r="I190" s="3"/>
+        <v>78</v>
+      </c>
+      <c r="I190" s="3">
+        <v>75</v>
+      </c>
       <c r="J190" s="3" t="s">
         <v>19</v>
       </c>
@@ -8188,37 +8255,41 @@
         <v>462</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C191" s="3">
-        <v>672</v>
+        <v>336</v>
       </c>
       <c r="D191" s="3">
-        <v>1494825081</v>
+        <v>1495577870</v>
       </c>
       <c r="E191" s="3" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="F191" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G191" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H191" s="3">
+        <v>20</v>
+      </c>
+      <c r="I191" s="3"/>
+      <c r="J191" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="K191" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="L191" s="3" t="s">
         <v>463</v>
       </c>
-      <c r="G191" s="3"/>
-      <c r="H191" s="3">
-        <v>74</v>
-      </c>
-      <c r="I191" s="3">
-        <v>65</v>
-      </c>
-      <c r="J191" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K191" s="3"/>
-      <c r="L191" s="3"/>
       <c r="M191" s="3"/>
     </row>
     <row r="192" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A192" s="3" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B192" s="3" t="s">
         <v>50</v>
@@ -8227,22 +8298,20 @@
         <v>672</v>
       </c>
       <c r="D192" s="3">
-        <v>1494825070</v>
+        <v>1495591658</v>
       </c>
       <c r="E192" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F192" s="3" t="s">
-        <v>464</v>
-      </c>
-      <c r="G192" s="3" t="s">
-        <v>52</v>
-      </c>
+        <v>465</v>
+      </c>
+      <c r="G192" s="3"/>
       <c r="H192" s="3">
+        <v>77</v>
+      </c>
+      <c r="I192" s="3">
         <v>75</v>
-      </c>
-      <c r="I192" s="3">
-        <v>65</v>
       </c>
       <c r="J192" s="3" t="s">
         <v>19</v>
@@ -8253,31 +8322,29 @@
     </row>
     <row r="193" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A193" s="3" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="C193" s="3">
-        <v>357</v>
+        <v>672</v>
       </c>
       <c r="D193" s="3">
-        <v>1494894175</v>
+        <v>1495878766</v>
       </c>
       <c r="E193" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F193" s="3" t="s">
-        <v>466</v>
-      </c>
-      <c r="G193" s="3" t="s">
-        <v>52</v>
-      </c>
+        <v>467</v>
+      </c>
+      <c r="G193" s="3"/>
       <c r="H193" s="3">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I193" s="3">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="J193" s="3" t="s">
         <v>19</v>
@@ -8288,31 +8355,29 @@
     </row>
     <row r="194" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A194" s="3" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="C194" s="3">
-        <v>357</v>
+        <v>672</v>
       </c>
       <c r="D194" s="3">
-        <v>1494894173</v>
+        <v>1496697474</v>
       </c>
       <c r="E194" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F194" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="G194" s="3" t="s">
-        <v>52</v>
-      </c>
+        <v>469</v>
+      </c>
+      <c r="G194" s="3"/>
       <c r="H194" s="3">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I194" s="3">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="J194" s="3" t="s">
         <v>19</v>
@@ -8320,6 +8385,416 @@
       <c r="K194" s="3"/>
       <c r="L194" s="3"/>
       <c r="M194" s="3"/>
+    </row>
+    <row r="195" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A195" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="B195" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C195" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D195" s="3">
+        <v>1496718268</v>
+      </c>
+      <c r="E195" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F195" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="G195" s="3"/>
+      <c r="H195" s="3">
+        <v>39</v>
+      </c>
+      <c r="I195" s="3"/>
+      <c r="J195" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K195" s="3"/>
+      <c r="L195" s="3"/>
+      <c r="M195" s="3"/>
+    </row>
+    <row r="196" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A196" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="B196" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C196" s="3">
+        <v>926</v>
+      </c>
+      <c r="D196" s="3">
+        <v>1496753224</v>
+      </c>
+      <c r="E196" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F196" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="G196" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H196" s="3">
+        <v>65</v>
+      </c>
+      <c r="I196" s="3">
+        <v>65</v>
+      </c>
+      <c r="J196" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K196" s="3"/>
+      <c r="L196" s="3"/>
+      <c r="M196" s="3"/>
+    </row>
+    <row r="197" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A197" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="B197" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C197" s="3">
+        <v>926</v>
+      </c>
+      <c r="D197" s="3">
+        <v>1496753235</v>
+      </c>
+      <c r="E197" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F197" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="G197" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H197" s="3">
+        <v>65</v>
+      </c>
+      <c r="I197" s="3">
+        <v>65</v>
+      </c>
+      <c r="J197" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K197" s="3"/>
+      <c r="L197" s="3"/>
+      <c r="M197" s="3"/>
+    </row>
+    <row r="198" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A198" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="B198" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C198" s="3">
+        <v>672</v>
+      </c>
+      <c r="D198" s="3">
+        <v>1496780688</v>
+      </c>
+      <c r="E198" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F198" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="G198" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H198" s="3">
+        <v>51</v>
+      </c>
+      <c r="I198" s="3"/>
+      <c r="J198" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K198" s="3"/>
+      <c r="L198" s="3"/>
+      <c r="M198" s="3"/>
+    </row>
+    <row r="199" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A199" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="B199" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C199" s="3">
+        <v>672</v>
+      </c>
+      <c r="D199" s="3">
+        <v>1496835697</v>
+      </c>
+      <c r="E199" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="F199" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="G199" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H199" s="3">
+        <v>71</v>
+      </c>
+      <c r="I199" s="3">
+        <v>75</v>
+      </c>
+      <c r="J199" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K199" s="3"/>
+      <c r="L199" s="3"/>
+      <c r="M199" s="3"/>
+    </row>
+    <row r="200" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A200" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="B200" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C200" s="3">
+        <v>672</v>
+      </c>
+      <c r="D200" s="3">
+        <v>1496859100</v>
+      </c>
+      <c r="E200" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="F200" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="G200" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H200" s="3">
+        <v>73</v>
+      </c>
+      <c r="I200" s="3">
+        <v>75</v>
+      </c>
+      <c r="J200" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K200" s="3"/>
+      <c r="L200" s="3"/>
+      <c r="M200" s="3"/>
+    </row>
+    <row r="201" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A201" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="B201" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C201" s="3">
+        <v>672</v>
+      </c>
+      <c r="D201" s="3">
+        <v>1496877970</v>
+      </c>
+      <c r="E201" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="F201" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="G201" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H201" s="3">
+        <v>73</v>
+      </c>
+      <c r="I201" s="3">
+        <v>75</v>
+      </c>
+      <c r="J201" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K201" s="3"/>
+      <c r="L201" s="3"/>
+      <c r="M201" s="3"/>
+    </row>
+    <row r="202" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A202" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="B202" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C202" s="3">
+        <v>672</v>
+      </c>
+      <c r="D202" s="3">
+        <v>1496896088</v>
+      </c>
+      <c r="E202" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="F202" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="G202" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H202" s="3">
+        <v>76</v>
+      </c>
+      <c r="I202" s="3">
+        <v>75</v>
+      </c>
+      <c r="J202" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K202" s="3"/>
+      <c r="L202" s="3"/>
+      <c r="M202" s="3"/>
+    </row>
+    <row r="203" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A203" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="B203" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C203" s="3">
+        <v>672</v>
+      </c>
+      <c r="D203" s="3">
+        <v>1496919247</v>
+      </c>
+      <c r="E203" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="F203" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="G203" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H203" s="3">
+        <v>71</v>
+      </c>
+      <c r="I203" s="3">
+        <v>75</v>
+      </c>
+      <c r="J203" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K203" s="3"/>
+      <c r="L203" s="3"/>
+      <c r="M203" s="3"/>
+    </row>
+    <row r="204" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A204" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="B204" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C204" s="3">
+        <v>357</v>
+      </c>
+      <c r="D204" s="3">
+        <v>1497234414</v>
+      </c>
+      <c r="E204" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F204" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="G204" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H204" s="3">
+        <v>55</v>
+      </c>
+      <c r="I204" s="3">
+        <v>70</v>
+      </c>
+      <c r="J204" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K204" s="3"/>
+      <c r="L204" s="3"/>
+      <c r="M204" s="3"/>
+    </row>
+    <row r="205" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A205" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="B205" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C205" s="3">
+        <v>672</v>
+      </c>
+      <c r="D205" s="3">
+        <v>1497368467</v>
+      </c>
+      <c r="E205" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F205" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="G205" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H205" s="3">
+        <v>22</v>
+      </c>
+      <c r="I205" s="3"/>
+      <c r="J205" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K205" s="3"/>
+      <c r="L205" s="3"/>
+      <c r="M205" s="3"/>
+    </row>
+    <row r="206" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A206" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="B206" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C206" s="3">
+        <v>672</v>
+      </c>
+      <c r="D206" s="3">
+        <v>1497417014</v>
+      </c>
+      <c r="E206" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F206" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="G206" s="3"/>
+      <c r="H206" s="3">
+        <v>35</v>
+      </c>
+      <c r="I206" s="3">
+        <v>65</v>
+      </c>
+      <c r="J206" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K206" s="3"/>
+      <c r="L206" s="3"/>
+      <c r="M206" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\PCS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{95EA046F-4C57-4E53-8AE0-F5D9D2DCAF45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{618A6DB3-9407-4F9E-A26E-C406B4247D2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4251" uniqueCount="1453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4394" uniqueCount="1502">
   <si>
     <t>DRIVE ALERTS</t>
   </si>
@@ -4339,6 +4339,9 @@
     <t>1.6mi SW of Orem UT</t>
   </si>
   <si>
+    <t>04/06/26 13:10 EDT</t>
+  </si>
+  <si>
     <t>04/03/26 08:25 EDT</t>
   </si>
   <si>
@@ -4351,6 +4354,9 @@
     <t>2.6mi SE of Salt Lake City UT</t>
   </si>
   <si>
+    <t>04/06/26 13:09 EDT</t>
+  </si>
+  <si>
     <t>04/03/26 20:40 EDT</t>
   </si>
   <si>
@@ -4375,10 +4381,151 @@
     <t>10.2mi E of Kearney NE</t>
   </si>
   <si>
+    <t>04/06/26 13:11 EDT</t>
+  </si>
+  <si>
     <t>04/04/26 13:39 EDT</t>
   </si>
   <si>
     <t>8.7mi NW of Barstow CA</t>
+  </si>
+  <si>
+    <t>04/06/26 14:11 EDT</t>
+  </si>
+  <si>
+    <t>04/07/26 10:05 EDT</t>
+  </si>
+  <si>
+    <t>04/06/26 14:14 EDT</t>
+  </si>
+  <si>
+    <t>1.5mi NW of Loma Linda CA</t>
+  </si>
+  <si>
+    <t>04/07/26 10:04 EDT</t>
+  </si>
+  <si>
+    <t>04/06/26 17:27 EDT</t>
+  </si>
+  <si>
+    <t>2.5mi W of Redlands CA</t>
+  </si>
+  <si>
+    <t>04/07/26 06:50 EDT</t>
+  </si>
+  <si>
+    <t>0.6mi SW of Nampa ID</t>
+  </si>
+  <si>
+    <t>04/07/26 16:36 EDT</t>
+  </si>
+  <si>
+    <t>2.8mi SW of Amarillo TX</t>
+  </si>
+  <si>
+    <t>04/08/26 12:08 EDT</t>
+  </si>
+  <si>
+    <t>04/08/26 12:43 EDT</t>
+  </si>
+  <si>
+    <t>04/08/26 13:53 EDT</t>
+  </si>
+  <si>
+    <t>12.5mi N of Ammon ID</t>
+  </si>
+  <si>
+    <t>04/08/26 16:25 EDT</t>
+  </si>
+  <si>
+    <t>20.1mi W of Evergreen CO</t>
+  </si>
+  <si>
+    <t>04/08/26 17:04 EDT</t>
+  </si>
+  <si>
+    <t>04/09/26 14:51 EDT</t>
+  </si>
+  <si>
+    <t>04/08/26 17:09 EDT</t>
+  </si>
+  <si>
+    <t>04/08/26 20:07 EDT</t>
+  </si>
+  <si>
+    <t>15.4mi W of Rawlins WY</t>
+  </si>
+  <si>
+    <t>04/09/26 14:52 EDT</t>
+  </si>
+  <si>
+    <t>04/09/26 00:12 EDT</t>
+  </si>
+  <si>
+    <t>04/09/26 12:17 EDT</t>
+  </si>
+  <si>
+    <t>24.8mi SE of Fort Irwin CA</t>
+  </si>
+  <si>
+    <t>04/09/26 14:53 EDT</t>
+  </si>
+  <si>
+    <t>04/09/26 15:23 EDT</t>
+  </si>
+  <si>
+    <t>04/10/26 16:36 EDT</t>
+  </si>
+  <si>
+    <t>04/09/26 17:14 EDT</t>
+  </si>
+  <si>
+    <t>3.7mi E of Buckeye AZ</t>
+  </si>
+  <si>
+    <t>04/10/26 16:38 EDT</t>
+  </si>
+  <si>
+    <t>04/10/26 02:57 EDT</t>
+  </si>
+  <si>
+    <t>04/10/26 05:24 EDT</t>
+  </si>
+  <si>
+    <t>27.9mi E of Fort Irwin CA</t>
+  </si>
+  <si>
+    <t>04/10/26 13:06 EDT</t>
+  </si>
+  <si>
+    <t>11.9mi SE of Rupert ID</t>
+  </si>
+  <si>
+    <t>04/10/26 15:07 EDT</t>
+  </si>
+  <si>
+    <t>2.8mi N of Golden Hills CA</t>
+  </si>
+  <si>
+    <t>04/10/26 17:51 EDT</t>
+  </si>
+  <si>
+    <t>4.3mi N of West Valley City UT</t>
+  </si>
+  <si>
+    <t>04/11/26 07:08 EDT</t>
+  </si>
+  <si>
+    <t>12mi W of Cheyenne WY</t>
+  </si>
+  <si>
+    <t>04/12/26 06:39 EDT</t>
+  </si>
+  <si>
+    <t>04/12/26 22:17 EDT</t>
+  </si>
+  <si>
+    <t>20.6mi NW of Bowie TX</t>
   </si>
 </sst>
 </file>
@@ -4740,7 +4887,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M660"/>
+  <dimension ref="A1:M684"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="13" width="15" customWidth="1"/>
@@ -27475,15 +27622,19 @@
         <v>70</v>
       </c>
       <c r="J653" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K653" s="3"/>
-      <c r="L653" s="3"/>
+        <v>25</v>
+      </c>
+      <c r="K653" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L653" s="3" t="s">
+        <v>1439</v>
+      </c>
       <c r="M653" s="3"/>
     </row>
     <row r="654" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A654" s="3" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="B654" s="3" t="s">
         <v>60</v>
@@ -27498,7 +27649,7 @@
         <v>40</v>
       </c>
       <c r="F654" s="3" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="G654" s="3"/>
       <c r="H654" s="3">
@@ -27516,7 +27667,7 @@
     </row>
     <row r="655" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A655" s="3" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="B655" s="3"/>
       <c r="C655" s="3">
@@ -27529,7 +27680,7 @@
         <v>40</v>
       </c>
       <c r="F655" s="3" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="G655" s="3" t="s">
         <v>77</v>
@@ -27541,15 +27692,19 @@
         <v>70</v>
       </c>
       <c r="J655" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K655" s="3"/>
-      <c r="L655" s="3"/>
+        <v>25</v>
+      </c>
+      <c r="K655" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L655" s="3" t="s">
+        <v>1444</v>
+      </c>
       <c r="M655" s="3"/>
     </row>
     <row r="656" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A656" s="3" t="s">
-        <v>1443</v>
+        <v>1445</v>
       </c>
       <c r="B656" s="3" t="s">
         <v>269</v>
@@ -27564,7 +27719,7 @@
         <v>22</v>
       </c>
       <c r="F656" s="3" t="s">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="G656" s="3"/>
       <c r="H656" s="3">
@@ -27580,7 +27735,7 @@
     </row>
     <row r="657" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A657" s="3" t="s">
-        <v>1445</v>
+        <v>1447</v>
       </c>
       <c r="B657" s="3" t="s">
         <v>65</v>
@@ -27595,9 +27750,11 @@
         <v>22</v>
       </c>
       <c r="F657" s="3" t="s">
-        <v>1446</v>
-      </c>
-      <c r="G657" s="3"/>
+        <v>1448</v>
+      </c>
+      <c r="G657" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="H657" s="3">
         <v>57</v>
       </c>
@@ -27605,15 +27762,19 @@
         <v>55</v>
       </c>
       <c r="J657" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K657" s="3"/>
-      <c r="L657" s="3"/>
+        <v>25</v>
+      </c>
+      <c r="K657" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L657" s="3" t="s">
+        <v>1439</v>
+      </c>
       <c r="M657" s="3"/>
     </row>
     <row r="658" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A658" s="3" t="s">
-        <v>1447</v>
+        <v>1449</v>
       </c>
       <c r="B658" s="3"/>
       <c r="C658" s="3">
@@ -27626,9 +27787,11 @@
         <v>22</v>
       </c>
       <c r="F658" s="3" t="s">
-        <v>1448</v>
-      </c>
-      <c r="G658" s="3"/>
+        <v>1450</v>
+      </c>
+      <c r="G658" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="H658" s="3">
         <v>53</v>
       </c>
@@ -27636,15 +27799,19 @@
         <v>50</v>
       </c>
       <c r="J658" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K658" s="3"/>
-      <c r="L658" s="3"/>
+        <v>25</v>
+      </c>
+      <c r="K658" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L658" s="3" t="s">
+        <v>1439</v>
+      </c>
       <c r="M658" s="3"/>
     </row>
     <row r="659" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A659" s="3" t="s">
-        <v>1449</v>
+        <v>1451</v>
       </c>
       <c r="B659" s="3" t="s">
         <v>242</v>
@@ -27659,10 +27826,10 @@
         <v>37</v>
       </c>
       <c r="F659" s="3" t="s">
-        <v>1450</v>
+        <v>1452</v>
       </c>
       <c r="G659" s="3" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="H659" s="3">
         <v>64</v>
@@ -27671,15 +27838,19 @@
         <v>75</v>
       </c>
       <c r="J659" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K659" s="3"/>
-      <c r="L659" s="3"/>
+        <v>25</v>
+      </c>
+      <c r="K659" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L659" s="3" t="s">
+        <v>1453</v>
+      </c>
       <c r="M659" s="3"/>
     </row>
     <row r="660" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A660" s="3" t="s">
-        <v>1451</v>
+        <v>1454</v>
       </c>
       <c r="B660" s="3" t="s">
         <v>284</v>
@@ -27694,7 +27865,7 @@
         <v>53</v>
       </c>
       <c r="F660" s="3" t="s">
-        <v>1452</v>
+        <v>1455</v>
       </c>
       <c r="G660" s="3" t="s">
         <v>77</v>
@@ -27704,11 +27875,797 @@
       </c>
       <c r="I660" s="3"/>
       <c r="J660" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K660" s="3"/>
-      <c r="L660" s="3"/>
+        <v>25</v>
+      </c>
+      <c r="K660" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L660" s="3" t="s">
+        <v>1453</v>
+      </c>
       <c r="M660" s="3"/>
+    </row>
+    <row r="661" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A661" s="3" t="s">
+        <v>1456</v>
+      </c>
+      <c r="B661" s="3"/>
+      <c r="C661" s="3">
+        <v>345</v>
+      </c>
+      <c r="D661" s="3">
+        <v>1506989959</v>
+      </c>
+      <c r="E661" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F661" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G661" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H661" s="3">
+        <v>39</v>
+      </c>
+      <c r="I661" s="3">
+        <v>50</v>
+      </c>
+      <c r="J661" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K661" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L661" s="3" t="s">
+        <v>1457</v>
+      </c>
+      <c r="M661" s="3"/>
+    </row>
+    <row r="662" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A662" s="3" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B662" s="3"/>
+      <c r="C662" s="3">
+        <v>926</v>
+      </c>
+      <c r="D662" s="3">
+        <v>1506992884</v>
+      </c>
+      <c r="E662" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F662" s="3" t="s">
+        <v>1459</v>
+      </c>
+      <c r="G662" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H662" s="3">
+        <v>46</v>
+      </c>
+      <c r="I662" s="3"/>
+      <c r="J662" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K662" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L662" s="3" t="s">
+        <v>1460</v>
+      </c>
+      <c r="M662" s="3"/>
+    </row>
+    <row r="663" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A663" s="3" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B663" s="3"/>
+      <c r="C663" s="3">
+        <v>926</v>
+      </c>
+      <c r="D663" s="3">
+        <v>1507160282</v>
+      </c>
+      <c r="E663" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F663" s="3" t="s">
+        <v>1462</v>
+      </c>
+      <c r="G663" s="3"/>
+      <c r="H663" s="3">
+        <v>31</v>
+      </c>
+      <c r="I663" s="3"/>
+      <c r="J663" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K663" s="3"/>
+      <c r="L663" s="3"/>
+      <c r="M663" s="3"/>
+    </row>
+    <row r="664" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A664" s="3" t="s">
+        <v>1463</v>
+      </c>
+      <c r="B664" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C664" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="D664" s="3">
+        <v>1507385487</v>
+      </c>
+      <c r="E664" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F664" s="3" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G664" s="3"/>
+      <c r="H664" s="3">
+        <v>30</v>
+      </c>
+      <c r="I664" s="3"/>
+      <c r="J664" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K664" s="3"/>
+      <c r="L664" s="3"/>
+      <c r="M664" s="3"/>
+    </row>
+    <row r="665" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A665" s="3" t="s">
+        <v>1465</v>
+      </c>
+      <c r="B665" s="3"/>
+      <c r="C665" s="3">
+        <v>730</v>
+      </c>
+      <c r="D665" s="3">
+        <v>1507909775</v>
+      </c>
+      <c r="E665" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F665" s="3" t="s">
+        <v>1466</v>
+      </c>
+      <c r="G665" s="3"/>
+      <c r="H665" s="3">
+        <v>24</v>
+      </c>
+      <c r="I665" s="3"/>
+      <c r="J665" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K665" s="3"/>
+      <c r="L665" s="3"/>
+      <c r="M665" s="3"/>
+    </row>
+    <row r="666" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A666" s="3" t="s">
+        <v>1467</v>
+      </c>
+      <c r="B666" s="3"/>
+      <c r="C666" s="3">
+        <v>344</v>
+      </c>
+      <c r="D666" s="3">
+        <v>1508464921</v>
+      </c>
+      <c r="E666" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F666" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="G666" s="3"/>
+      <c r="H666" s="3">
+        <v>43</v>
+      </c>
+      <c r="I666" s="3"/>
+      <c r="J666" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K666" s="3"/>
+      <c r="L666" s="3"/>
+      <c r="M666" s="3"/>
+    </row>
+    <row r="667" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A667" s="3" t="s">
+        <v>1468</v>
+      </c>
+      <c r="B667" s="3"/>
+      <c r="C667" s="3">
+        <v>344</v>
+      </c>
+      <c r="D667" s="3">
+        <v>1508496690</v>
+      </c>
+      <c r="E667" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F667" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="G667" s="3"/>
+      <c r="H667" s="3">
+        <v>50</v>
+      </c>
+      <c r="I667" s="3"/>
+      <c r="J667" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K667" s="3"/>
+      <c r="L667" s="3"/>
+      <c r="M667" s="3"/>
+    </row>
+    <row r="668" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A668" s="3" t="s">
+        <v>1469</v>
+      </c>
+      <c r="B668" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C668" s="3">
+        <v>336</v>
+      </c>
+      <c r="D668" s="3">
+        <v>1508568447</v>
+      </c>
+      <c r="E668" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F668" s="3" t="s">
+        <v>1470</v>
+      </c>
+      <c r="G668" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H668" s="3">
+        <v>65</v>
+      </c>
+      <c r="I668" s="3">
+        <v>70</v>
+      </c>
+      <c r="J668" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K668" s="3"/>
+      <c r="L668" s="3"/>
+      <c r="M668" s="3"/>
+    </row>
+    <row r="669" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A669" s="3" t="s">
+        <v>1471</v>
+      </c>
+      <c r="B669" s="3"/>
+      <c r="C669" s="3">
+        <v>730</v>
+      </c>
+      <c r="D669" s="3">
+        <v>1508715605</v>
+      </c>
+      <c r="E669" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F669" s="3" t="s">
+        <v>1472</v>
+      </c>
+      <c r="G669" s="3"/>
+      <c r="H669" s="3">
+        <v>61</v>
+      </c>
+      <c r="I669" s="3"/>
+      <c r="J669" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K669" s="3"/>
+      <c r="L669" s="3"/>
+      <c r="M669" s="3"/>
+    </row>
+    <row r="670" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A670" s="3" t="s">
+        <v>1473</v>
+      </c>
+      <c r="B670" s="3"/>
+      <c r="C670" s="3">
+        <v>338</v>
+      </c>
+      <c r="D670" s="3">
+        <v>1508750058</v>
+      </c>
+      <c r="E670" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F670" s="3" t="s">
+        <v>786</v>
+      </c>
+      <c r="G670" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H670" s="3">
+        <v>52</v>
+      </c>
+      <c r="I670" s="3">
+        <v>50</v>
+      </c>
+      <c r="J670" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K670" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L670" s="3" t="s">
+        <v>1474</v>
+      </c>
+      <c r="M670" s="3"/>
+    </row>
+    <row r="671" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A671" s="3" t="s">
+        <v>1475</v>
+      </c>
+      <c r="B671" s="3"/>
+      <c r="C671" s="3">
+        <v>344</v>
+      </c>
+      <c r="D671" s="3">
+        <v>1508754786</v>
+      </c>
+      <c r="E671" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F671" s="3" t="s">
+        <v>1059</v>
+      </c>
+      <c r="G671" s="3"/>
+      <c r="H671" s="3">
+        <v>66</v>
+      </c>
+      <c r="I671" s="3">
+        <v>55</v>
+      </c>
+      <c r="J671" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K671" s="3"/>
+      <c r="L671" s="3"/>
+      <c r="M671" s="3"/>
+    </row>
+    <row r="672" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A672" s="3" t="s">
+        <v>1476</v>
+      </c>
+      <c r="B672" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="C672" s="3">
+        <v>108</v>
+      </c>
+      <c r="D672" s="3">
+        <v>1508867939</v>
+      </c>
+      <c r="E672" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F672" s="3" t="s">
+        <v>1477</v>
+      </c>
+      <c r="G672" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H672" s="3">
+        <v>79</v>
+      </c>
+      <c r="I672" s="3">
+        <v>75</v>
+      </c>
+      <c r="J672" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K672" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L672" s="3" t="s">
+        <v>1478</v>
+      </c>
+      <c r="M672" s="3"/>
+    </row>
+    <row r="673" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A673" s="3" t="s">
+        <v>1479</v>
+      </c>
+      <c r="B673" s="3"/>
+      <c r="C673" s="3">
+        <v>730</v>
+      </c>
+      <c r="D673" s="3">
+        <v>1508936320</v>
+      </c>
+      <c r="E673" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F673" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="G673" s="3"/>
+      <c r="H673" s="3">
+        <v>45</v>
+      </c>
+      <c r="I673" s="3"/>
+      <c r="J673" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K673" s="3"/>
+      <c r="L673" s="3"/>
+      <c r="M673" s="3"/>
+    </row>
+    <row r="674" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A674" s="3" t="s">
+        <v>1480</v>
+      </c>
+      <c r="B674" s="3"/>
+      <c r="C674" s="3">
+        <v>729</v>
+      </c>
+      <c r="D674" s="3">
+        <v>1509291581</v>
+      </c>
+      <c r="E674" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F674" s="3" t="s">
+        <v>1481</v>
+      </c>
+      <c r="G674" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H674" s="3">
+        <v>64</v>
+      </c>
+      <c r="I674" s="3">
+        <v>70</v>
+      </c>
+      <c r="J674" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K674" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L674" s="3" t="s">
+        <v>1482</v>
+      </c>
+      <c r="M674" s="3"/>
+    </row>
+    <row r="675" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A675" s="3" t="s">
+        <v>1483</v>
+      </c>
+      <c r="B675" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C675" s="3">
+        <v>672</v>
+      </c>
+      <c r="D675" s="3">
+        <v>1509472660</v>
+      </c>
+      <c r="E675" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F675" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="G675" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H675" s="3">
+        <v>64</v>
+      </c>
+      <c r="I675" s="3">
+        <v>75</v>
+      </c>
+      <c r="J675" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K675" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L675" s="3" t="s">
+        <v>1484</v>
+      </c>
+      <c r="M675" s="3"/>
+    </row>
+    <row r="676" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A676" s="3" t="s">
+        <v>1485</v>
+      </c>
+      <c r="B676" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C676" s="3">
+        <v>210</v>
+      </c>
+      <c r="D676" s="3">
+        <v>1509571237</v>
+      </c>
+      <c r="E676" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F676" s="3" t="s">
+        <v>1486</v>
+      </c>
+      <c r="G676" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H676" s="3">
+        <v>75</v>
+      </c>
+      <c r="I676" s="3">
+        <v>75</v>
+      </c>
+      <c r="J676" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K676" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L676" s="3" t="s">
+        <v>1487</v>
+      </c>
+      <c r="M676" s="3"/>
+    </row>
+    <row r="677" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A677" s="3" t="s">
+        <v>1488</v>
+      </c>
+      <c r="B677" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C677" s="3">
+        <v>459</v>
+      </c>
+      <c r="D677" s="3">
+        <v>1509766286</v>
+      </c>
+      <c r="E677" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F677" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="G677" s="3"/>
+      <c r="H677" s="3">
+        <v>13</v>
+      </c>
+      <c r="I677" s="3"/>
+      <c r="J677" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K677" s="3"/>
+      <c r="L677" s="3"/>
+      <c r="M677" s="3"/>
+    </row>
+    <row r="678" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A678" s="3" t="s">
+        <v>1489</v>
+      </c>
+      <c r="B678" s="3"/>
+      <c r="C678" s="3">
+        <v>926</v>
+      </c>
+      <c r="D678" s="3">
+        <v>1509787521</v>
+      </c>
+      <c r="E678" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F678" s="3" t="s">
+        <v>1490</v>
+      </c>
+      <c r="G678" s="3"/>
+      <c r="H678" s="3">
+        <v>60</v>
+      </c>
+      <c r="I678" s="3"/>
+      <c r="J678" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K678" s="3"/>
+      <c r="L678" s="3"/>
+      <c r="M678" s="3"/>
+    </row>
+    <row r="679" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A679" s="3" t="s">
+        <v>1491</v>
+      </c>
+      <c r="B679" s="3"/>
+      <c r="C679" s="3">
+        <v>730</v>
+      </c>
+      <c r="D679" s="3">
+        <v>1510130566</v>
+      </c>
+      <c r="E679" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F679" s="3" t="s">
+        <v>1492</v>
+      </c>
+      <c r="G679" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H679" s="3">
+        <v>71</v>
+      </c>
+      <c r="I679" s="3">
+        <v>80</v>
+      </c>
+      <c r="J679" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K679" s="3"/>
+      <c r="L679" s="3"/>
+      <c r="M679" s="3"/>
+    </row>
+    <row r="680" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A680" s="3" t="s">
+        <v>1493</v>
+      </c>
+      <c r="B680" s="3"/>
+      <c r="C680" s="3">
+        <v>926</v>
+      </c>
+      <c r="D680" s="3">
+        <v>1510241668</v>
+      </c>
+      <c r="E680" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="F680" s="3" t="s">
+        <v>1494</v>
+      </c>
+      <c r="G680" s="3"/>
+      <c r="H680" s="3">
+        <v>40</v>
+      </c>
+      <c r="I680" s="3">
+        <v>65</v>
+      </c>
+      <c r="J680" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K680" s="3"/>
+      <c r="L680" s="3"/>
+      <c r="M680" s="3"/>
+    </row>
+    <row r="681" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A681" s="3" t="s">
+        <v>1495</v>
+      </c>
+      <c r="B681" s="3"/>
+      <c r="C681" s="3">
+        <v>338</v>
+      </c>
+      <c r="D681" s="3">
+        <v>1510371416</v>
+      </c>
+      <c r="E681" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F681" s="3" t="s">
+        <v>1496</v>
+      </c>
+      <c r="G681" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H681" s="3">
+        <v>23</v>
+      </c>
+      <c r="I681" s="3"/>
+      <c r="J681" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K681" s="3"/>
+      <c r="L681" s="3"/>
+      <c r="M681" s="3"/>
+    </row>
+    <row r="682" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A682" s="3" t="s">
+        <v>1497</v>
+      </c>
+      <c r="B682" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C682" s="3">
+        <v>839</v>
+      </c>
+      <c r="D682" s="3">
+        <v>1510546997</v>
+      </c>
+      <c r="E682" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F682" s="3" t="s">
+        <v>1498</v>
+      </c>
+      <c r="G682" s="3"/>
+      <c r="H682" s="3">
+        <v>64</v>
+      </c>
+      <c r="I682" s="3">
+        <v>75</v>
+      </c>
+      <c r="J682" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K682" s="3"/>
+      <c r="L682" s="3"/>
+      <c r="M682" s="3"/>
+    </row>
+    <row r="683" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A683" s="3" t="s">
+        <v>1499</v>
+      </c>
+      <c r="B683" s="3"/>
+      <c r="C683" s="3">
+        <v>839</v>
+      </c>
+      <c r="D683" s="3">
+        <v>1510861510</v>
+      </c>
+      <c r="E683" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F683" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="G683" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H683" s="3">
+        <v>23</v>
+      </c>
+      <c r="I683" s="3"/>
+      <c r="J683" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K683" s="3"/>
+      <c r="L683" s="3"/>
+      <c r="M683" s="3"/>
+    </row>
+    <row r="684" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A684" s="3" t="s">
+        <v>1500</v>
+      </c>
+      <c r="B684" s="3"/>
+      <c r="C684" s="3">
+        <v>730</v>
+      </c>
+      <c r="D684" s="3">
+        <v>1511061934</v>
+      </c>
+      <c r="E684" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F684" s="3" t="s">
+        <v>1501</v>
+      </c>
+      <c r="G684" s="3"/>
+      <c r="H684" s="3">
+        <v>66</v>
+      </c>
+      <c r="I684" s="3"/>
+      <c r="J684" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K684" s="3"/>
+      <c r="L684" s="3"/>
+      <c r="M684" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\PCS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{618A6DB3-9407-4F9E-A26E-C406B4247D2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{580EE8E4-B680-42AC-A7FD-221D3F49108F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4394" uniqueCount="1502">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4713" uniqueCount="1611">
   <si>
     <t>DRIVE ALERTS</t>
   </si>
@@ -4489,6 +4489,9 @@
     <t>04/10/26 02:57 EDT</t>
   </si>
   <si>
+    <t>04/13/26 10:22 EDT</t>
+  </si>
+  <si>
     <t>04/10/26 05:24 EDT</t>
   </si>
   <si>
@@ -4501,6 +4504,9 @@
     <t>11.9mi SE of Rupert ID</t>
   </si>
   <si>
+    <t>04/13/26 10:23 EDT</t>
+  </si>
+  <si>
     <t>04/10/26 15:07 EDT</t>
   </si>
   <si>
@@ -4513,6 +4519,9 @@
     <t>4.3mi N of West Valley City UT</t>
   </si>
   <si>
+    <t>04/13/26 10:24 EDT</t>
+  </si>
+  <si>
     <t>04/11/26 07:08 EDT</t>
   </si>
   <si>
@@ -4526,6 +4535,324 @@
   </si>
   <si>
     <t>20.6mi NW of Bowie TX</t>
+  </si>
+  <si>
+    <t>3.5mi NE of West Valley City UT</t>
+  </si>
+  <si>
+    <t>04/13/26 11:49 EDT</t>
+  </si>
+  <si>
+    <t>2.5mi N of West Valley City UT</t>
+  </si>
+  <si>
+    <t>04/13/26 19:02 EDT</t>
+  </si>
+  <si>
+    <t>25mi SE of Price UT</t>
+  </si>
+  <si>
+    <t>04/14/26 01:01 EDT</t>
+  </si>
+  <si>
+    <t>27.5mi W of Fruita CO</t>
+  </si>
+  <si>
+    <t>04/14/26 07:52 EDT</t>
+  </si>
+  <si>
+    <t>15.1mi W of South Valley NM</t>
+  </si>
+  <si>
+    <t>04/15/26 19:09 EDT</t>
+  </si>
+  <si>
+    <t>04/14/26 13:34 EDT</t>
+  </si>
+  <si>
+    <t>0.7mi S of American Fork UT</t>
+  </si>
+  <si>
+    <t>04/15/26 19:08 EDT</t>
+  </si>
+  <si>
+    <t>04/14/26 13:35 EDT</t>
+  </si>
+  <si>
+    <t>1.8mi SE of American Fork UT</t>
+  </si>
+  <si>
+    <t>04/15/26 19:10 EDT</t>
+  </si>
+  <si>
+    <t>04/14/26 13:46 EDT</t>
+  </si>
+  <si>
+    <t>2.7mi NW of Springville UT</t>
+  </si>
+  <si>
+    <t>04/14/26 14:32 EDT</t>
+  </si>
+  <si>
+    <t>04/15/26 19:11 EDT</t>
+  </si>
+  <si>
+    <t>04/14/26 17:38 EDT</t>
+  </si>
+  <si>
+    <t>11.2mi SW of Nephi UT</t>
+  </si>
+  <si>
+    <t>04/14/26 18:48 EDT</t>
+  </si>
+  <si>
+    <t>13.2mi E of Evanston WY</t>
+  </si>
+  <si>
+    <t>04/15/26 19:12 EDT</t>
+  </si>
+  <si>
+    <t>04/15/26 10:58 EDT</t>
+  </si>
+  <si>
+    <t>4.8mi N of West Valley City UT</t>
+  </si>
+  <si>
+    <t>04/15/26 13:36 EDT</t>
+  </si>
+  <si>
+    <t>04/15/26 14:04 EDT</t>
+  </si>
+  <si>
+    <t>4.6mi N of West Valley City UT</t>
+  </si>
+  <si>
+    <t>04/15/26 14:09 EDT</t>
+  </si>
+  <si>
+    <t>0.3mi SE of Farr West UT</t>
+  </si>
+  <si>
+    <t>04/15/26 19:34 EDT</t>
+  </si>
+  <si>
+    <t>1.7mi SE of Bluffdale UT</t>
+  </si>
+  <si>
+    <t>04/16/26 09:36 EDT</t>
+  </si>
+  <si>
+    <t>04/16/26 00:48 EDT</t>
+  </si>
+  <si>
+    <t>2.5mi E of Paradise NV</t>
+  </si>
+  <si>
+    <t>04/17/26 12:11 EDT</t>
+  </si>
+  <si>
+    <t>04/16/26 16:10 EDT</t>
+  </si>
+  <si>
+    <t>23.1mi NW of Lexington NE</t>
+  </si>
+  <si>
+    <t>04/16/26 16:30 EDT</t>
+  </si>
+  <si>
+    <t>2.3mi SW of Lexington NE</t>
+  </si>
+  <si>
+    <t>04/16/26 16:49 EDT</t>
+  </si>
+  <si>
+    <t>13.1mi W of Kearney NE</t>
+  </si>
+  <si>
+    <t>04/16/26 17:37 EDT</t>
+  </si>
+  <si>
+    <t>6.7mi S of Grand Island NE</t>
+  </si>
+  <si>
+    <t>04/16/26 18:05 EDT</t>
+  </si>
+  <si>
+    <t>5.4mi SW of York NE</t>
+  </si>
+  <si>
+    <t>04/16/26 18:22 EDT</t>
+  </si>
+  <si>
+    <t>10.7mi SW of Seward NE</t>
+  </si>
+  <si>
+    <t>04/16/26 18:23 EDT</t>
+  </si>
+  <si>
+    <t>9.7mi SW of Seward NE</t>
+  </si>
+  <si>
+    <t>04/16/26 18:51 EDT</t>
+  </si>
+  <si>
+    <t>5.1mi N of Lincoln NE</t>
+  </si>
+  <si>
+    <t>04/16/26 20:55 EDT</t>
+  </si>
+  <si>
+    <t>16mi NW of Atlantic IA</t>
+  </si>
+  <si>
+    <t>04/16/26 21:27 EDT</t>
+  </si>
+  <si>
+    <t>23.5mi E of Atlantic IA</t>
+  </si>
+  <si>
+    <t>04/17/26 05:14 EDT</t>
+  </si>
+  <si>
+    <t>04/17/26 07:38 EDT</t>
+  </si>
+  <si>
+    <t>0.3mi S of Oak Hills CA</t>
+  </si>
+  <si>
+    <t>0.4mi S of Oak Hills CA</t>
+  </si>
+  <si>
+    <t>04/17/26 16:20 EDT</t>
+  </si>
+  <si>
+    <t>04/17/26 17:24 EDT</t>
+  </si>
+  <si>
+    <t>1.3mi E of Dana Point CA</t>
+  </si>
+  <si>
+    <t>04/17/26 18:02 EDT</t>
+  </si>
+  <si>
+    <t>4.6mi SW of Sun Prairie WI</t>
+  </si>
+  <si>
+    <t>04/17/26 18:03 EDT</t>
+  </si>
+  <si>
+    <t>4.7mi NW of Cottage Grove WI</t>
+  </si>
+  <si>
+    <t>04/18/26 02:04 EDT</t>
+  </si>
+  <si>
+    <t>04/18/26 07:21 EDT</t>
+  </si>
+  <si>
+    <t>3.6mi E of Hesperia CA</t>
+  </si>
+  <si>
+    <t>04/18/26 10:07 EDT</t>
+  </si>
+  <si>
+    <t>4.7mi W of Morris IL</t>
+  </si>
+  <si>
+    <t>5.2mi W of Morris IL</t>
+  </si>
+  <si>
+    <t>04/18/26 10:38 EDT</t>
+  </si>
+  <si>
+    <t>2.3mi N of Spring Valley IL</t>
+  </si>
+  <si>
+    <t>2.6mi NW of Spring Valley IL</t>
+  </si>
+  <si>
+    <t>04/18/26 12:08 EDT</t>
+  </si>
+  <si>
+    <t>22.8mi E of Kingman AZ</t>
+  </si>
+  <si>
+    <t>04/18/26 12:19 EDT</t>
+  </si>
+  <si>
+    <t>33.3mi E of Kingman AZ</t>
+  </si>
+  <si>
+    <t>33.6mi E of Kingman AZ</t>
+  </si>
+  <si>
+    <t>04/18/26 13:23 EDT</t>
+  </si>
+  <si>
+    <t>13.7mi W of Davenport IA</t>
+  </si>
+  <si>
+    <t>04/18/26 13:25 EDT</t>
+  </si>
+  <si>
+    <t>34.1mi N of Chino Valley AZ</t>
+  </si>
+  <si>
+    <t>04/18/26 13:40 EDT</t>
+  </si>
+  <si>
+    <t>15.4mi E of Iowa City IA</t>
+  </si>
+  <si>
+    <t>04/18/26 13:48 EDT</t>
+  </si>
+  <si>
+    <t>6.1mi E of Iowa City IA</t>
+  </si>
+  <si>
+    <t>04/18/26 16:03 EDT</t>
+  </si>
+  <si>
+    <t>12.2mi E of Grinnell IA</t>
+  </si>
+  <si>
+    <t>04/18/26 16:17 EDT</t>
+  </si>
+  <si>
+    <t>5.4mi SW of Grinnell IA</t>
+  </si>
+  <si>
+    <t>04/18/26 17:01 EDT</t>
+  </si>
+  <si>
+    <t>3.9mi SE of Johnston IA</t>
+  </si>
+  <si>
+    <t>04/18/26 17:46 EDT</t>
+  </si>
+  <si>
+    <t>15.8mi N of Hurricane UT</t>
+  </si>
+  <si>
+    <t>04/18/26 18:55 EDT</t>
+  </si>
+  <si>
+    <t>18.1mi W of Atlantic IA</t>
+  </si>
+  <si>
+    <t>18.2mi W of Atlantic IA</t>
+  </si>
+  <si>
+    <t>04/18/26 19:52 EDT</t>
+  </si>
+  <si>
+    <t>4.8mi SW of Gretna NE</t>
+  </si>
+  <si>
+    <t>04/18/26 20:48 EDT</t>
+  </si>
+  <si>
+    <t>12.1mi E of York NE</t>
   </si>
 </sst>
 </file>
@@ -4887,7 +5214,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M684"/>
+  <dimension ref="A1:M739"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="13" width="15" customWidth="1"/>
@@ -28438,21 +28765,27 @@
       <c r="F677" s="3" t="s">
         <v>384</v>
       </c>
-      <c r="G677" s="3"/>
+      <c r="G677" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="H677" s="3">
         <v>13</v>
       </c>
       <c r="I677" s="3"/>
       <c r="J677" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K677" s="3"/>
-      <c r="L677" s="3"/>
+        <v>25</v>
+      </c>
+      <c r="K677" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L677" s="3" t="s">
+        <v>1489</v>
+      </c>
       <c r="M677" s="3"/>
     </row>
     <row r="678" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A678" s="3" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="B678" s="3"/>
       <c r="C678" s="3">
@@ -28465,7 +28798,7 @@
         <v>17</v>
       </c>
       <c r="F678" s="3" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="G678" s="3"/>
       <c r="H678" s="3">
@@ -28481,7 +28814,7 @@
     </row>
     <row r="679" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A679" s="3" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="B679" s="3"/>
       <c r="C679" s="3">
@@ -28494,10 +28827,10 @@
         <v>40</v>
       </c>
       <c r="F679" s="3" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="G679" s="3" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="H679" s="3">
         <v>71</v>
@@ -28506,15 +28839,19 @@
         <v>80</v>
       </c>
       <c r="J679" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K679" s="3"/>
-      <c r="L679" s="3"/>
+        <v>25</v>
+      </c>
+      <c r="K679" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L679" s="3" t="s">
+        <v>1494</v>
+      </c>
       <c r="M679" s="3"/>
     </row>
     <row r="680" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A680" s="3" t="s">
-        <v>1493</v>
+        <v>1495</v>
       </c>
       <c r="B680" s="3"/>
       <c r="C680" s="3">
@@ -28527,9 +28864,11 @@
         <v>277</v>
       </c>
       <c r="F680" s="3" t="s">
-        <v>1494</v>
-      </c>
-      <c r="G680" s="3"/>
+        <v>1496</v>
+      </c>
+      <c r="G680" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="H680" s="3">
         <v>40</v>
       </c>
@@ -28537,15 +28876,19 @@
         <v>65</v>
       </c>
       <c r="J680" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K680" s="3"/>
-      <c r="L680" s="3"/>
+        <v>25</v>
+      </c>
+      <c r="K680" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L680" s="3" t="s">
+        <v>1494</v>
+      </c>
       <c r="M680" s="3"/>
     </row>
     <row r="681" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A681" s="3" t="s">
-        <v>1495</v>
+        <v>1497</v>
       </c>
       <c r="B681" s="3"/>
       <c r="C681" s="3">
@@ -28558,25 +28901,29 @@
         <v>53</v>
       </c>
       <c r="F681" s="3" t="s">
-        <v>1496</v>
+        <v>1498</v>
       </c>
       <c r="G681" s="3" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="H681" s="3">
         <v>23</v>
       </c>
       <c r="I681" s="3"/>
       <c r="J681" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K681" s="3"/>
-      <c r="L681" s="3"/>
+        <v>25</v>
+      </c>
+      <c r="K681" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L681" s="3" t="s">
+        <v>1499</v>
+      </c>
       <c r="M681" s="3"/>
     </row>
     <row r="682" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A682" s="3" t="s">
-        <v>1497</v>
+        <v>1500</v>
       </c>
       <c r="B682" s="3" t="s">
         <v>16</v>
@@ -28591,7 +28938,7 @@
         <v>17</v>
       </c>
       <c r="F682" s="3" t="s">
-        <v>1498</v>
+        <v>1501</v>
       </c>
       <c r="G682" s="3"/>
       <c r="H682" s="3">
@@ -28609,7 +28956,7 @@
     </row>
     <row r="683" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A683" s="3" t="s">
-        <v>1499</v>
+        <v>1502</v>
       </c>
       <c r="B683" s="3"/>
       <c r="C683" s="3">
@@ -28625,22 +28972,26 @@
         <v>567</v>
       </c>
       <c r="G683" s="3" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="H683" s="3">
         <v>23</v>
       </c>
       <c r="I683" s="3"/>
       <c r="J683" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K683" s="3"/>
-      <c r="L683" s="3"/>
+        <v>25</v>
+      </c>
+      <c r="K683" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L683" s="3" t="s">
+        <v>1499</v>
+      </c>
       <c r="M683" s="3"/>
     </row>
     <row r="684" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A684" s="3" t="s">
-        <v>1500</v>
+        <v>1503</v>
       </c>
       <c r="B684" s="3"/>
       <c r="C684" s="3">
@@ -28653,7 +29004,7 @@
         <v>17</v>
       </c>
       <c r="F684" s="3" t="s">
-        <v>1501</v>
+        <v>1504</v>
       </c>
       <c r="G684" s="3"/>
       <c r="H684" s="3">
@@ -28666,6 +29017,1861 @@
       <c r="K684" s="3"/>
       <c r="L684" s="3"/>
       <c r="M684" s="3"/>
+    </row>
+    <row r="685" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A685" s="3" t="s">
+        <v>1489</v>
+      </c>
+      <c r="B685" s="3"/>
+      <c r="C685" s="3">
+        <v>344</v>
+      </c>
+      <c r="D685" s="3">
+        <v>1511297188</v>
+      </c>
+      <c r="E685" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F685" s="3" t="s">
+        <v>1505</v>
+      </c>
+      <c r="G685" s="3"/>
+      <c r="H685" s="3">
+        <v>26</v>
+      </c>
+      <c r="I685" s="3"/>
+      <c r="J685" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K685" s="3"/>
+      <c r="L685" s="3"/>
+      <c r="M685" s="3"/>
+    </row>
+    <row r="686" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A686" s="3" t="s">
+        <v>1506</v>
+      </c>
+      <c r="B686" s="3"/>
+      <c r="C686" s="3">
+        <v>344</v>
+      </c>
+      <c r="D686" s="3">
+        <v>1511375840</v>
+      </c>
+      <c r="E686" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F686" s="3" t="s">
+        <v>1507</v>
+      </c>
+      <c r="G686" s="3"/>
+      <c r="H686" s="3">
+        <v>48</v>
+      </c>
+      <c r="I686" s="3"/>
+      <c r="J686" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K686" s="3"/>
+      <c r="L686" s="3"/>
+      <c r="M686" s="3"/>
+    </row>
+    <row r="687" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A687" s="3" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B687" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C687" s="3">
+        <v>357</v>
+      </c>
+      <c r="D687" s="3">
+        <v>1511742886</v>
+      </c>
+      <c r="E687" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F687" s="3" t="s">
+        <v>1509</v>
+      </c>
+      <c r="G687" s="3"/>
+      <c r="H687" s="3">
+        <v>69</v>
+      </c>
+      <c r="I687" s="3">
+        <v>65</v>
+      </c>
+      <c r="J687" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K687" s="3"/>
+      <c r="L687" s="3"/>
+      <c r="M687" s="3"/>
+    </row>
+    <row r="688" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A688" s="3" t="s">
+        <v>1510</v>
+      </c>
+      <c r="B688" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C688" s="3">
+        <v>839</v>
+      </c>
+      <c r="D688" s="3">
+        <v>1511845398</v>
+      </c>
+      <c r="E688" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F688" s="3" t="s">
+        <v>1511</v>
+      </c>
+      <c r="G688" s="3"/>
+      <c r="H688" s="3">
+        <v>64</v>
+      </c>
+      <c r="I688" s="3">
+        <v>80</v>
+      </c>
+      <c r="J688" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K688" s="3"/>
+      <c r="L688" s="3"/>
+      <c r="M688" s="3"/>
+    </row>
+    <row r="689" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A689" s="3" t="s">
+        <v>1512</v>
+      </c>
+      <c r="B689" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C689" s="3">
+        <v>672</v>
+      </c>
+      <c r="D689" s="3">
+        <v>1511954546</v>
+      </c>
+      <c r="E689" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F689" s="3" t="s">
+        <v>1513</v>
+      </c>
+      <c r="G689" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H689" s="3">
+        <v>18</v>
+      </c>
+      <c r="I689" s="3"/>
+      <c r="J689" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K689" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L689" s="3" t="s">
+        <v>1514</v>
+      </c>
+      <c r="M689" s="3"/>
+    </row>
+    <row r="690" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A690" s="3" t="s">
+        <v>1515</v>
+      </c>
+      <c r="B690" s="3"/>
+      <c r="C690" s="3">
+        <v>357</v>
+      </c>
+      <c r="D690" s="3">
+        <v>1512272474</v>
+      </c>
+      <c r="E690" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F690" s="3" t="s">
+        <v>1516</v>
+      </c>
+      <c r="G690" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H690" s="3">
+        <v>73</v>
+      </c>
+      <c r="I690" s="3">
+        <v>70</v>
+      </c>
+      <c r="J690" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K690" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L690" s="3" t="s">
+        <v>1517</v>
+      </c>
+      <c r="M690" s="3"/>
+    </row>
+    <row r="691" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A691" s="3" t="s">
+        <v>1518</v>
+      </c>
+      <c r="B691" s="3"/>
+      <c r="C691" s="3">
+        <v>357</v>
+      </c>
+      <c r="D691" s="3">
+        <v>1512274026</v>
+      </c>
+      <c r="E691" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F691" s="3" t="s">
+        <v>1519</v>
+      </c>
+      <c r="G691" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H691" s="3">
+        <v>75</v>
+      </c>
+      <c r="I691" s="3">
+        <v>70</v>
+      </c>
+      <c r="J691" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K691" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L691" s="3" t="s">
+        <v>1520</v>
+      </c>
+      <c r="M691" s="3"/>
+    </row>
+    <row r="692" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A692" s="3" t="s">
+        <v>1521</v>
+      </c>
+      <c r="B692" s="3"/>
+      <c r="C692" s="3">
+        <v>357</v>
+      </c>
+      <c r="D692" s="3">
+        <v>1512284661</v>
+      </c>
+      <c r="E692" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F692" s="3" t="s">
+        <v>1522</v>
+      </c>
+      <c r="G692" s="3"/>
+      <c r="H692" s="3">
+        <v>71</v>
+      </c>
+      <c r="I692" s="3"/>
+      <c r="J692" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K692" s="3"/>
+      <c r="L692" s="3"/>
+      <c r="M692" s="3"/>
+    </row>
+    <row r="693" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A693" s="3" t="s">
+        <v>1523</v>
+      </c>
+      <c r="B693" s="3"/>
+      <c r="C693" s="3">
+        <v>338</v>
+      </c>
+      <c r="D693" s="3">
+        <v>1512329715</v>
+      </c>
+      <c r="E693" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F693" s="3" t="s">
+        <v>1498</v>
+      </c>
+      <c r="G693" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H693" s="3">
+        <v>19</v>
+      </c>
+      <c r="I693" s="3"/>
+      <c r="J693" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K693" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L693" s="3" t="s">
+        <v>1524</v>
+      </c>
+      <c r="M693" s="3"/>
+    </row>
+    <row r="694" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A694" s="3" t="s">
+        <v>1525</v>
+      </c>
+      <c r="B694" s="3"/>
+      <c r="C694" s="3">
+        <v>375</v>
+      </c>
+      <c r="D694" s="3">
+        <v>1512502260</v>
+      </c>
+      <c r="E694" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F694" s="3" t="s">
+        <v>1526</v>
+      </c>
+      <c r="G694" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H694" s="3">
+        <v>67</v>
+      </c>
+      <c r="I694" s="3">
+        <v>80</v>
+      </c>
+      <c r="J694" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K694" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L694" s="3" t="s">
+        <v>1517</v>
+      </c>
+      <c r="M694" s="3"/>
+    </row>
+    <row r="695" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A695" s="3" t="s">
+        <v>1527</v>
+      </c>
+      <c r="B695" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="C695" s="3">
+        <v>108</v>
+      </c>
+      <c r="D695" s="3">
+        <v>1512550635</v>
+      </c>
+      <c r="E695" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F695" s="3" t="s">
+        <v>1528</v>
+      </c>
+      <c r="G695" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H695" s="3">
+        <v>68</v>
+      </c>
+      <c r="I695" s="3">
+        <v>75</v>
+      </c>
+      <c r="J695" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K695" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L695" s="3" t="s">
+        <v>1529</v>
+      </c>
+      <c r="M695" s="3"/>
+    </row>
+    <row r="696" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A696" s="3" t="s">
+        <v>1530</v>
+      </c>
+      <c r="B696" s="3"/>
+      <c r="C696" s="3">
+        <v>344</v>
+      </c>
+      <c r="D696" s="3">
+        <v>1512940195</v>
+      </c>
+      <c r="E696" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F696" s="3" t="s">
+        <v>1531</v>
+      </c>
+      <c r="G696" s="3"/>
+      <c r="H696" s="3">
+        <v>36</v>
+      </c>
+      <c r="I696" s="3"/>
+      <c r="J696" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K696" s="3"/>
+      <c r="L696" s="3"/>
+      <c r="M696" s="3"/>
+    </row>
+    <row r="697" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A697" s="3" t="s">
+        <v>1532</v>
+      </c>
+      <c r="B697" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C697" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="D697" s="3">
+        <v>1513094980</v>
+      </c>
+      <c r="E697" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F697" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="G697" s="3"/>
+      <c r="H697" s="3">
+        <v>36</v>
+      </c>
+      <c r="I697" s="3">
+        <v>35</v>
+      </c>
+      <c r="J697" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K697" s="3"/>
+      <c r="L697" s="3"/>
+      <c r="M697" s="3"/>
+    </row>
+    <row r="698" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A698" s="3" t="s">
+        <v>1533</v>
+      </c>
+      <c r="B698" s="3"/>
+      <c r="C698" s="3">
+        <v>344</v>
+      </c>
+      <c r="D698" s="3">
+        <v>1513121341</v>
+      </c>
+      <c r="E698" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F698" s="3" t="s">
+        <v>1534</v>
+      </c>
+      <c r="G698" s="3"/>
+      <c r="H698" s="3">
+        <v>49</v>
+      </c>
+      <c r="I698" s="3"/>
+      <c r="J698" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K698" s="3"/>
+      <c r="L698" s="3"/>
+      <c r="M698" s="3"/>
+    </row>
+    <row r="699" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A699" s="3" t="s">
+        <v>1535</v>
+      </c>
+      <c r="B699" s="3"/>
+      <c r="C699" s="3">
+        <v>375</v>
+      </c>
+      <c r="D699" s="3">
+        <v>1513128765</v>
+      </c>
+      <c r="E699" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F699" s="3" t="s">
+        <v>1536</v>
+      </c>
+      <c r="G699" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H699" s="3">
+        <v>70</v>
+      </c>
+      <c r="I699" s="3">
+        <v>75</v>
+      </c>
+      <c r="J699" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K699" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L699" s="3" t="s">
+        <v>1514</v>
+      </c>
+      <c r="M699" s="3"/>
+    </row>
+    <row r="700" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A700" s="3" t="s">
+        <v>1537</v>
+      </c>
+      <c r="B700" s="3"/>
+      <c r="C700" s="3">
+        <v>375</v>
+      </c>
+      <c r="D700" s="3">
+        <v>1513397922</v>
+      </c>
+      <c r="E700" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F700" s="3" t="s">
+        <v>1538</v>
+      </c>
+      <c r="G700" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H700" s="3">
+        <v>64</v>
+      </c>
+      <c r="I700" s="3">
+        <v>70</v>
+      </c>
+      <c r="J700" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K700" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L700" s="3" t="s">
+        <v>1539</v>
+      </c>
+      <c r="M700" s="3"/>
+    </row>
+    <row r="701" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A701" s="3" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B701" s="3"/>
+      <c r="C701" s="3">
+        <v>729</v>
+      </c>
+      <c r="D701" s="3">
+        <v>1513490676</v>
+      </c>
+      <c r="E701" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F701" s="3" t="s">
+        <v>1541</v>
+      </c>
+      <c r="G701" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H701" s="3">
+        <v>29</v>
+      </c>
+      <c r="I701" s="3"/>
+      <c r="J701" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K701" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L701" s="3" t="s">
+        <v>1542</v>
+      </c>
+      <c r="M701" s="3"/>
+    </row>
+    <row r="702" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A702" s="3" t="s">
+        <v>1543</v>
+      </c>
+      <c r="B702" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C702" s="3">
+        <v>357</v>
+      </c>
+      <c r="D702" s="3">
+        <v>1514103935</v>
+      </c>
+      <c r="E702" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F702" s="3" t="s">
+        <v>1544</v>
+      </c>
+      <c r="G702" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H702" s="3">
+        <v>71</v>
+      </c>
+      <c r="I702" s="3">
+        <v>75</v>
+      </c>
+      <c r="J702" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K702" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L702" s="3" t="s">
+        <v>1542</v>
+      </c>
+      <c r="M702" s="3"/>
+    </row>
+    <row r="703" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A703" s="3" t="s">
+        <v>1545</v>
+      </c>
+      <c r="B703" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C703" s="3">
+        <v>357</v>
+      </c>
+      <c r="D703" s="3">
+        <v>1514123635</v>
+      </c>
+      <c r="E703" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F703" s="3" t="s">
+        <v>1546</v>
+      </c>
+      <c r="G703" s="3"/>
+      <c r="H703" s="3">
+        <v>76</v>
+      </c>
+      <c r="I703" s="3">
+        <v>75</v>
+      </c>
+      <c r="J703" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K703" s="3"/>
+      <c r="L703" s="3"/>
+      <c r="M703" s="3"/>
+    </row>
+    <row r="704" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A704" s="3" t="s">
+        <v>1547</v>
+      </c>
+      <c r="B704" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C704" s="3">
+        <v>357</v>
+      </c>
+      <c r="D704" s="3">
+        <v>1514141301</v>
+      </c>
+      <c r="E704" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F704" s="3" t="s">
+        <v>1548</v>
+      </c>
+      <c r="G704" s="3"/>
+      <c r="H704" s="3">
+        <v>77</v>
+      </c>
+      <c r="I704" s="3">
+        <v>75</v>
+      </c>
+      <c r="J704" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K704" s="3"/>
+      <c r="L704" s="3"/>
+      <c r="M704" s="3"/>
+    </row>
+    <row r="705" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A705" s="3" t="s">
+        <v>1549</v>
+      </c>
+      <c r="B705" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C705" s="3">
+        <v>357</v>
+      </c>
+      <c r="D705" s="3">
+        <v>1514184908</v>
+      </c>
+      <c r="E705" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F705" s="3" t="s">
+        <v>1550</v>
+      </c>
+      <c r="G705" s="3"/>
+      <c r="H705" s="3">
+        <v>63</v>
+      </c>
+      <c r="I705" s="3">
+        <v>75</v>
+      </c>
+      <c r="J705" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K705" s="3"/>
+      <c r="L705" s="3"/>
+      <c r="M705" s="3"/>
+    </row>
+    <row r="706" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A706" s="3" t="s">
+        <v>1551</v>
+      </c>
+      <c r="B706" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C706" s="3">
+        <v>357</v>
+      </c>
+      <c r="D706" s="3">
+        <v>1514208086</v>
+      </c>
+      <c r="E706" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F706" s="3" t="s">
+        <v>1552</v>
+      </c>
+      <c r="G706" s="3"/>
+      <c r="H706" s="3">
+        <v>77</v>
+      </c>
+      <c r="I706" s="3">
+        <v>75</v>
+      </c>
+      <c r="J706" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K706" s="3"/>
+      <c r="L706" s="3"/>
+      <c r="M706" s="3"/>
+    </row>
+    <row r="707" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A707" s="3" t="s">
+        <v>1553</v>
+      </c>
+      <c r="B707" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C707" s="3">
+        <v>357</v>
+      </c>
+      <c r="D707" s="3">
+        <v>1514221828</v>
+      </c>
+      <c r="E707" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F707" s="3" t="s">
+        <v>1554</v>
+      </c>
+      <c r="G707" s="3"/>
+      <c r="H707" s="3">
+        <v>72</v>
+      </c>
+      <c r="I707" s="3">
+        <v>75</v>
+      </c>
+      <c r="J707" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K707" s="3"/>
+      <c r="L707" s="3"/>
+      <c r="M707" s="3"/>
+    </row>
+    <row r="708" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A708" s="3" t="s">
+        <v>1555</v>
+      </c>
+      <c r="B708" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C708" s="3">
+        <v>357</v>
+      </c>
+      <c r="D708" s="3">
+        <v>1514221837</v>
+      </c>
+      <c r="E708" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F708" s="3" t="s">
+        <v>1556</v>
+      </c>
+      <c r="G708" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H708" s="3">
+        <v>74</v>
+      </c>
+      <c r="I708" s="3">
+        <v>75</v>
+      </c>
+      <c r="J708" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K708" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L708" s="3" t="s">
+        <v>1542</v>
+      </c>
+      <c r="M708" s="3"/>
+    </row>
+    <row r="709" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A709" s="3" t="s">
+        <v>1557</v>
+      </c>
+      <c r="B709" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C709" s="3">
+        <v>357</v>
+      </c>
+      <c r="D709" s="3">
+        <v>1514241084</v>
+      </c>
+      <c r="E709" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F709" s="3" t="s">
+        <v>1558</v>
+      </c>
+      <c r="G709" s="3"/>
+      <c r="H709" s="3">
+        <v>72</v>
+      </c>
+      <c r="I709" s="3">
+        <v>65</v>
+      </c>
+      <c r="J709" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K709" s="3"/>
+      <c r="L709" s="3"/>
+      <c r="M709" s="3"/>
+    </row>
+    <row r="710" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A710" s="3" t="s">
+        <v>1559</v>
+      </c>
+      <c r="B710" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C710" s="3">
+        <v>357</v>
+      </c>
+      <c r="D710" s="3">
+        <v>1514308501</v>
+      </c>
+      <c r="E710" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F710" s="3" t="s">
+        <v>1560</v>
+      </c>
+      <c r="G710" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H710" s="3">
+        <v>74</v>
+      </c>
+      <c r="I710" s="3">
+        <v>70</v>
+      </c>
+      <c r="J710" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K710" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L710" s="3" t="s">
+        <v>1542</v>
+      </c>
+      <c r="M710" s="3"/>
+    </row>
+    <row r="711" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A711" s="3" t="s">
+        <v>1561</v>
+      </c>
+      <c r="B711" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C711" s="3">
+        <v>357</v>
+      </c>
+      <c r="D711" s="3">
+        <v>1514321018</v>
+      </c>
+      <c r="E711" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F711" s="3" t="s">
+        <v>1562</v>
+      </c>
+      <c r="G711" s="3"/>
+      <c r="H711" s="3">
+        <v>72</v>
+      </c>
+      <c r="I711" s="3">
+        <v>70</v>
+      </c>
+      <c r="J711" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K711" s="3"/>
+      <c r="L711" s="3"/>
+      <c r="M711" s="3"/>
+    </row>
+    <row r="712" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A712" s="3" t="s">
+        <v>1563</v>
+      </c>
+      <c r="B712" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C712" s="3">
+        <v>839</v>
+      </c>
+      <c r="D712" s="3">
+        <v>1514409122</v>
+      </c>
+      <c r="E712" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F712" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="G712" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H712" s="3">
+        <v>27</v>
+      </c>
+      <c r="I712" s="3"/>
+      <c r="J712" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K712" s="3"/>
+      <c r="L712" s="3"/>
+      <c r="M712" s="3"/>
+    </row>
+    <row r="713" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A713" s="3" t="s">
+        <v>1564</v>
+      </c>
+      <c r="B713" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C713" s="3">
+        <v>672</v>
+      </c>
+      <c r="D713" s="3">
+        <v>1514477643</v>
+      </c>
+      <c r="E713" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F713" s="3" t="s">
+        <v>1565</v>
+      </c>
+      <c r="G713" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H713" s="3">
+        <v>64</v>
+      </c>
+      <c r="I713" s="3">
+        <v>70</v>
+      </c>
+      <c r="J713" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K713" s="3"/>
+      <c r="L713" s="3"/>
+      <c r="M713" s="3"/>
+    </row>
+    <row r="714" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A714" s="3" t="s">
+        <v>1564</v>
+      </c>
+      <c r="B714" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C714" s="3">
+        <v>672</v>
+      </c>
+      <c r="D714" s="3">
+        <v>1514477635</v>
+      </c>
+      <c r="E714" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F714" s="3" t="s">
+        <v>1566</v>
+      </c>
+      <c r="G714" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H714" s="3">
+        <v>64</v>
+      </c>
+      <c r="I714" s="3">
+        <v>70</v>
+      </c>
+      <c r="J714" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K714" s="3"/>
+      <c r="L714" s="3"/>
+      <c r="M714" s="3"/>
+    </row>
+    <row r="715" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A715" s="3" t="s">
+        <v>1567</v>
+      </c>
+      <c r="B715" s="3"/>
+      <c r="C715" s="3">
+        <v>344</v>
+      </c>
+      <c r="D715" s="3">
+        <v>1514981526</v>
+      </c>
+      <c r="E715" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F715" s="3" t="s">
+        <v>1531</v>
+      </c>
+      <c r="G715" s="3"/>
+      <c r="H715" s="3">
+        <v>42</v>
+      </c>
+      <c r="I715" s="3">
+        <v>50</v>
+      </c>
+      <c r="J715" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K715" s="3"/>
+      <c r="L715" s="3"/>
+      <c r="M715" s="3"/>
+    </row>
+    <row r="716" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A716" s="3" t="s">
+        <v>1568</v>
+      </c>
+      <c r="B716" s="3"/>
+      <c r="C716" s="3">
+        <v>926</v>
+      </c>
+      <c r="D716" s="3">
+        <v>1515036414</v>
+      </c>
+      <c r="E716" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F716" s="3" t="s">
+        <v>1569</v>
+      </c>
+      <c r="G716" s="3"/>
+      <c r="H716" s="3">
+        <v>62</v>
+      </c>
+      <c r="I716" s="3">
+        <v>65</v>
+      </c>
+      <c r="J716" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K716" s="3"/>
+      <c r="L716" s="3"/>
+      <c r="M716" s="3"/>
+    </row>
+    <row r="717" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A717" s="3" t="s">
+        <v>1570</v>
+      </c>
+      <c r="B717" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C717" s="3">
+        <v>357</v>
+      </c>
+      <c r="D717" s="3">
+        <v>1515065709</v>
+      </c>
+      <c r="E717" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F717" s="3" t="s">
+        <v>1571</v>
+      </c>
+      <c r="G717" s="3"/>
+      <c r="H717" s="3">
+        <v>65</v>
+      </c>
+      <c r="I717" s="3">
+        <v>70</v>
+      </c>
+      <c r="J717" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K717" s="3"/>
+      <c r="L717" s="3"/>
+      <c r="M717" s="3"/>
+    </row>
+    <row r="718" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A718" s="3" t="s">
+        <v>1572</v>
+      </c>
+      <c r="B718" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C718" s="3">
+        <v>357</v>
+      </c>
+      <c r="D718" s="3">
+        <v>1515065714</v>
+      </c>
+      <c r="E718" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F718" s="3" t="s">
+        <v>1573</v>
+      </c>
+      <c r="G718" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H718" s="3">
+        <v>68</v>
+      </c>
+      <c r="I718" s="3">
+        <v>70</v>
+      </c>
+      <c r="J718" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K718" s="3"/>
+      <c r="L718" s="3"/>
+      <c r="M718" s="3"/>
+    </row>
+    <row r="719" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A719" s="3" t="s">
+        <v>1574</v>
+      </c>
+      <c r="B719" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C719" s="3">
+        <v>107</v>
+      </c>
+      <c r="D719" s="3">
+        <v>1515216562</v>
+      </c>
+      <c r="E719" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F719" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="G719" s="3"/>
+      <c r="H719" s="3">
+        <v>40</v>
+      </c>
+      <c r="I719" s="3"/>
+      <c r="J719" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K719" s="3"/>
+      <c r="L719" s="3"/>
+      <c r="M719" s="3"/>
+    </row>
+    <row r="720" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A720" s="3" t="s">
+        <v>1575</v>
+      </c>
+      <c r="B720" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C720" s="3">
+        <v>672</v>
+      </c>
+      <c r="D720" s="3">
+        <v>1515256535</v>
+      </c>
+      <c r="E720" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F720" s="3" t="s">
+        <v>1576</v>
+      </c>
+      <c r="G720" s="3"/>
+      <c r="H720" s="3">
+        <v>37</v>
+      </c>
+      <c r="I720" s="3"/>
+      <c r="J720" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K720" s="3"/>
+      <c r="L720" s="3"/>
+      <c r="M720" s="3"/>
+    </row>
+    <row r="721" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A721" s="3" t="s">
+        <v>1577</v>
+      </c>
+      <c r="B721" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C721" s="3">
+        <v>357</v>
+      </c>
+      <c r="D721" s="3">
+        <v>1515308148</v>
+      </c>
+      <c r="E721" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F721" s="3" t="s">
+        <v>1578</v>
+      </c>
+      <c r="G721" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H721" s="3">
+        <v>67</v>
+      </c>
+      <c r="I721" s="3">
+        <v>70</v>
+      </c>
+      <c r="J721" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K721" s="3"/>
+      <c r="L721" s="3"/>
+      <c r="M721" s="3"/>
+    </row>
+    <row r="722" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A722" s="3" t="s">
+        <v>1577</v>
+      </c>
+      <c r="B722" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C722" s="3">
+        <v>357</v>
+      </c>
+      <c r="D722" s="3">
+        <v>1515308144</v>
+      </c>
+      <c r="E722" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F722" s="3" t="s">
+        <v>1579</v>
+      </c>
+      <c r="G722" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H722" s="3">
+        <v>67</v>
+      </c>
+      <c r="I722" s="3">
+        <v>70</v>
+      </c>
+      <c r="J722" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K722" s="3"/>
+      <c r="L722" s="3"/>
+      <c r="M722" s="3"/>
+    </row>
+    <row r="723" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A723" s="3" t="s">
+        <v>1580</v>
+      </c>
+      <c r="B723" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C723" s="3">
+        <v>357</v>
+      </c>
+      <c r="D723" s="3">
+        <v>1515320127</v>
+      </c>
+      <c r="E723" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F723" s="3" t="s">
+        <v>1581</v>
+      </c>
+      <c r="G723" s="3"/>
+      <c r="H723" s="3">
+        <v>74</v>
+      </c>
+      <c r="I723" s="3">
+        <v>70</v>
+      </c>
+      <c r="J723" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K723" s="3"/>
+      <c r="L723" s="3"/>
+      <c r="M723" s="3"/>
+    </row>
+    <row r="724" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A724" s="3" t="s">
+        <v>1580</v>
+      </c>
+      <c r="B724" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C724" s="3">
+        <v>357</v>
+      </c>
+      <c r="D724" s="3">
+        <v>1515320122</v>
+      </c>
+      <c r="E724" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F724" s="3" t="s">
+        <v>1582</v>
+      </c>
+      <c r="G724" s="3"/>
+      <c r="H724" s="3">
+        <v>74</v>
+      </c>
+      <c r="I724" s="3">
+        <v>70</v>
+      </c>
+      <c r="J724" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K724" s="3"/>
+      <c r="L724" s="3"/>
+      <c r="M724" s="3"/>
+    </row>
+    <row r="725" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A725" s="3" t="s">
+        <v>1583</v>
+      </c>
+      <c r="B725" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C725" s="3">
+        <v>672</v>
+      </c>
+      <c r="D725" s="3">
+        <v>1515357021</v>
+      </c>
+      <c r="E725" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F725" s="3" t="s">
+        <v>1584</v>
+      </c>
+      <c r="G725" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H725" s="3">
+        <v>58</v>
+      </c>
+      <c r="I725" s="3">
+        <v>75</v>
+      </c>
+      <c r="J725" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K725" s="3"/>
+      <c r="L725" s="3"/>
+      <c r="M725" s="3"/>
+    </row>
+    <row r="726" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A726" s="3" t="s">
+        <v>1585</v>
+      </c>
+      <c r="B726" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C726" s="3">
+        <v>672</v>
+      </c>
+      <c r="D726" s="3">
+        <v>1515361958</v>
+      </c>
+      <c r="E726" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F726" s="3" t="s">
+        <v>1586</v>
+      </c>
+      <c r="G726" s="3"/>
+      <c r="H726" s="3">
+        <v>57</v>
+      </c>
+      <c r="I726" s="3">
+        <v>75</v>
+      </c>
+      <c r="J726" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K726" s="3"/>
+      <c r="L726" s="3"/>
+      <c r="M726" s="3"/>
+    </row>
+    <row r="727" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A727" s="3" t="s">
+        <v>1585</v>
+      </c>
+      <c r="B727" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C727" s="3">
+        <v>672</v>
+      </c>
+      <c r="D727" s="3">
+        <v>1515361950</v>
+      </c>
+      <c r="E727" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F727" s="3" t="s">
+        <v>1587</v>
+      </c>
+      <c r="G727" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H727" s="3">
+        <v>56</v>
+      </c>
+      <c r="I727" s="3">
+        <v>75</v>
+      </c>
+      <c r="J727" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K727" s="3"/>
+      <c r="L727" s="3"/>
+      <c r="M727" s="3"/>
+    </row>
+    <row r="728" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A728" s="3" t="s">
+        <v>1588</v>
+      </c>
+      <c r="B728" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C728" s="3">
+        <v>357</v>
+      </c>
+      <c r="D728" s="3">
+        <v>1515388627</v>
+      </c>
+      <c r="E728" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F728" s="3" t="s">
+        <v>1589</v>
+      </c>
+      <c r="G728" s="3"/>
+      <c r="H728" s="3">
+        <v>71</v>
+      </c>
+      <c r="I728" s="3">
+        <v>70</v>
+      </c>
+      <c r="J728" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K728" s="3"/>
+      <c r="L728" s="3"/>
+      <c r="M728" s="3"/>
+    </row>
+    <row r="729" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A729" s="3" t="s">
+        <v>1590</v>
+      </c>
+      <c r="B729" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C729" s="3">
+        <v>672</v>
+      </c>
+      <c r="D729" s="3">
+        <v>1515389394</v>
+      </c>
+      <c r="E729" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F729" s="3" t="s">
+        <v>1591</v>
+      </c>
+      <c r="G729" s="3"/>
+      <c r="H729" s="3">
+        <v>70</v>
+      </c>
+      <c r="I729" s="3">
+        <v>75</v>
+      </c>
+      <c r="J729" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K729" s="3"/>
+      <c r="L729" s="3"/>
+      <c r="M729" s="3"/>
+    </row>
+    <row r="730" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A730" s="3" t="s">
+        <v>1592</v>
+      </c>
+      <c r="B730" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C730" s="3">
+        <v>357</v>
+      </c>
+      <c r="D730" s="3">
+        <v>1515395554</v>
+      </c>
+      <c r="E730" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F730" s="3" t="s">
+        <v>1593</v>
+      </c>
+      <c r="G730" s="3"/>
+      <c r="H730" s="3">
+        <v>65</v>
+      </c>
+      <c r="I730" s="3">
+        <v>70</v>
+      </c>
+      <c r="J730" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K730" s="3"/>
+      <c r="L730" s="3"/>
+      <c r="M730" s="3"/>
+    </row>
+    <row r="731" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A731" s="3" t="s">
+        <v>1594</v>
+      </c>
+      <c r="B731" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C731" s="3">
+        <v>357</v>
+      </c>
+      <c r="D731" s="3">
+        <v>1515398851</v>
+      </c>
+      <c r="E731" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F731" s="3" t="s">
+        <v>1595</v>
+      </c>
+      <c r="G731" s="3"/>
+      <c r="H731" s="3">
+        <v>73</v>
+      </c>
+      <c r="I731" s="3">
+        <v>70</v>
+      </c>
+      <c r="J731" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K731" s="3"/>
+      <c r="L731" s="3"/>
+      <c r="M731" s="3"/>
+    </row>
+    <row r="732" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A732" s="3" t="s">
+        <v>1596</v>
+      </c>
+      <c r="B732" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C732" s="3">
+        <v>357</v>
+      </c>
+      <c r="D732" s="3">
+        <v>1515450591</v>
+      </c>
+      <c r="E732" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F732" s="3" t="s">
+        <v>1597</v>
+      </c>
+      <c r="G732" s="3"/>
+      <c r="H732" s="3">
+        <v>72</v>
+      </c>
+      <c r="I732" s="3">
+        <v>70</v>
+      </c>
+      <c r="J732" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K732" s="3"/>
+      <c r="L732" s="3"/>
+      <c r="M732" s="3"/>
+    </row>
+    <row r="733" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A733" s="3" t="s">
+        <v>1598</v>
+      </c>
+      <c r="B733" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C733" s="3">
+        <v>357</v>
+      </c>
+      <c r="D733" s="3">
+        <v>1515455736</v>
+      </c>
+      <c r="E733" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F733" s="3" t="s">
+        <v>1599</v>
+      </c>
+      <c r="G733" s="3"/>
+      <c r="H733" s="3">
+        <v>75</v>
+      </c>
+      <c r="I733" s="3">
+        <v>70</v>
+      </c>
+      <c r="J733" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K733" s="3"/>
+      <c r="L733" s="3"/>
+      <c r="M733" s="3"/>
+    </row>
+    <row r="734" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A734" s="3" t="s">
+        <v>1600</v>
+      </c>
+      <c r="B734" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C734" s="3">
+        <v>357</v>
+      </c>
+      <c r="D734" s="3">
+        <v>1515470736</v>
+      </c>
+      <c r="E734" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F734" s="3" t="s">
+        <v>1601</v>
+      </c>
+      <c r="G734" s="3"/>
+      <c r="H734" s="3">
+        <v>69</v>
+      </c>
+      <c r="I734" s="3">
+        <v>65</v>
+      </c>
+      <c r="J734" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K734" s="3"/>
+      <c r="L734" s="3"/>
+      <c r="M734" s="3"/>
+    </row>
+    <row r="735" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A735" s="3" t="s">
+        <v>1602</v>
+      </c>
+      <c r="B735" s="3"/>
+      <c r="C735" s="3">
+        <v>729</v>
+      </c>
+      <c r="D735" s="3">
+        <v>1515484813</v>
+      </c>
+      <c r="E735" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F735" s="3" t="s">
+        <v>1603</v>
+      </c>
+      <c r="G735" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H735" s="3">
+        <v>88</v>
+      </c>
+      <c r="I735" s="3">
+        <v>80</v>
+      </c>
+      <c r="J735" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K735" s="3"/>
+      <c r="L735" s="3"/>
+      <c r="M735" s="3"/>
+    </row>
+    <row r="736" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A736" s="3" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B736" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C736" s="3">
+        <v>357</v>
+      </c>
+      <c r="D736" s="3">
+        <v>1515504408</v>
+      </c>
+      <c r="E736" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F736" s="3" t="s">
+        <v>1605</v>
+      </c>
+      <c r="G736" s="3"/>
+      <c r="H736" s="3">
+        <v>73</v>
+      </c>
+      <c r="I736" s="3">
+        <v>70</v>
+      </c>
+      <c r="J736" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K736" s="3"/>
+      <c r="L736" s="3"/>
+      <c r="M736" s="3"/>
+    </row>
+    <row r="737" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A737" s="3" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B737" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C737" s="3">
+        <v>357</v>
+      </c>
+      <c r="D737" s="3">
+        <v>1515504403</v>
+      </c>
+      <c r="E737" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F737" s="3" t="s">
+        <v>1606</v>
+      </c>
+      <c r="G737" s="3"/>
+      <c r="H737" s="3">
+        <v>72</v>
+      </c>
+      <c r="I737" s="3">
+        <v>70</v>
+      </c>
+      <c r="J737" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K737" s="3"/>
+      <c r="L737" s="3"/>
+      <c r="M737" s="3"/>
+    </row>
+    <row r="738" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A738" s="3" t="s">
+        <v>1607</v>
+      </c>
+      <c r="B738" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C738" s="3">
+        <v>357</v>
+      </c>
+      <c r="D738" s="3">
+        <v>1515518591</v>
+      </c>
+      <c r="E738" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F738" s="3" t="s">
+        <v>1608</v>
+      </c>
+      <c r="G738" s="3"/>
+      <c r="H738" s="3">
+        <v>68</v>
+      </c>
+      <c r="I738" s="3">
+        <v>75</v>
+      </c>
+      <c r="J738" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K738" s="3"/>
+      <c r="L738" s="3"/>
+      <c r="M738" s="3"/>
+    </row>
+    <row r="739" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A739" s="3" t="s">
+        <v>1609</v>
+      </c>
+      <c r="B739" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C739" s="3">
+        <v>357</v>
+      </c>
+      <c r="D739" s="3">
+        <v>1515531786</v>
+      </c>
+      <c r="E739" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F739" s="3" t="s">
+        <v>1610</v>
+      </c>
+      <c r="G739" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H739" s="3">
+        <v>75</v>
+      </c>
+      <c r="I739" s="3">
+        <v>75</v>
+      </c>
+      <c r="J739" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K739" s="3"/>
+      <c r="L739" s="3"/>
+      <c r="M739" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\PCS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6316538F-02AE-44FC-A369-A0EC4E0B4C52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7A345196-316B-40F4-9502-88927704B96B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3930" yWindow="3930" windowWidth="43200" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRIVE-ALERTS" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5815" uniqueCount="2496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6144" uniqueCount="2628">
   <si>
     <t>DRIVE ALERTS</t>
   </si>
@@ -7339,6 +7339,9 @@
     <t>40.190182, -111.646874</t>
   </si>
   <si>
+    <t>04/26/26 16:29 EDT</t>
+  </si>
+  <si>
     <t>04/23/26 16:58 EDT</t>
   </si>
   <si>
@@ -7357,6 +7360,9 @@
     <t>38.542292, -112.608951</t>
   </si>
   <si>
+    <t>04/26/26 17:23 EDT</t>
+  </si>
+  <si>
     <t>04/23/26 20:11 EDT</t>
   </si>
   <si>
@@ -7366,6 +7372,9 @@
     <t>35.471797, -108.417010</t>
   </si>
   <si>
+    <t>04/26/26 17:24 EDT</t>
+  </si>
+  <si>
     <t>04/23/26 20:24 EDT</t>
   </si>
   <si>
@@ -7402,6 +7411,9 @@
     <t>36.031760, -115.209335</t>
   </si>
   <si>
+    <t>04/27/26 12:55 EDT</t>
+  </si>
+  <si>
     <t>04/24/26 10:03 EDT</t>
   </si>
   <si>
@@ -7411,12 +7423,18 @@
     <t>40.416526, -111.873158</t>
   </si>
   <si>
+    <t>04/27/26 12:58 EDT</t>
+  </si>
+  <si>
     <t>0.4mi NW of Lehi UT</t>
   </si>
   <si>
     <t>40.418802, -111.875761</t>
   </si>
   <si>
+    <t>04/27/26 12:56 EDT</t>
+  </si>
+  <si>
     <t>04/24/26 11:34 EDT</t>
   </si>
   <si>
@@ -7450,6 +7468,9 @@
     <t>36.331722, -102.073010</t>
   </si>
   <si>
+    <t>04/27/26 12:57 EDT</t>
+  </si>
+  <si>
     <t>04/24/26 18:21 EDT</t>
   </si>
   <si>
@@ -7508,6 +7529,381 @@
   </si>
   <si>
     <t>40.639596, -111.903779</t>
+  </si>
+  <si>
+    <t>04/26/26 15:31 EDT</t>
+  </si>
+  <si>
+    <t>1.4mi S of Chalco NE</t>
+  </si>
+  <si>
+    <t>41.161795, -96.142400</t>
+  </si>
+  <si>
+    <t>04/26/26 15:50 EDT</t>
+  </si>
+  <si>
+    <t>33.2mi SW of Richfield UT</t>
+  </si>
+  <si>
+    <t>38.507566, -112.614642</t>
+  </si>
+  <si>
+    <t>04/27/26 12:59 EDT</t>
+  </si>
+  <si>
+    <t>04/26/26 16:02 EDT</t>
+  </si>
+  <si>
+    <t>35.3mi SE of Price UT</t>
+  </si>
+  <si>
+    <t>39.237896, -110.338797</t>
+  </si>
+  <si>
+    <t>04/26/26 18:02 EDT</t>
+  </si>
+  <si>
+    <t>27.6mi SE of Mapleton UT</t>
+  </si>
+  <si>
+    <t>39.933693, -111.111993</t>
+  </si>
+  <si>
+    <t>04/26/26 20:23 EDT</t>
+  </si>
+  <si>
+    <t>2.4mi NW of Draper UT</t>
+  </si>
+  <si>
+    <t>40.520487, -111.891362</t>
+  </si>
+  <si>
+    <t>04/27/26 13:01 EDT</t>
+  </si>
+  <si>
+    <t>04/27/26 15:36 EDT</t>
+  </si>
+  <si>
+    <t>1.9mi SW of Murray UT</t>
+  </si>
+  <si>
+    <t>40.637346, -111.919530</t>
+  </si>
+  <si>
+    <t>04/28/26 09:32 EDT</t>
+  </si>
+  <si>
+    <t>04/27/26 21:12 EDT</t>
+  </si>
+  <si>
+    <t>3.8mi SE of Calipatria CA</t>
+  </si>
+  <si>
+    <t>33.120299, -115.449756</t>
+  </si>
+  <si>
+    <t>04/27/26 21:34 EDT</t>
+  </si>
+  <si>
+    <t>12.2mi NE of Holtville CA</t>
+  </si>
+  <si>
+    <t>32.972028, -115.288338</t>
+  </si>
+  <si>
+    <t>04/27/26 21:54 EDT</t>
+  </si>
+  <si>
+    <t>29.1mi NE of Holtville CA</t>
+  </si>
+  <si>
+    <t>33.040950, -114.956429</t>
+  </si>
+  <si>
+    <t>04/27/26 23:00 EDT</t>
+  </si>
+  <si>
+    <t>39mi NE of Enoch UT</t>
+  </si>
+  <si>
+    <t>38.238138, -112.649990</t>
+  </si>
+  <si>
+    <t>04/28/26 08:01 EDT</t>
+  </si>
+  <si>
+    <t>39.741687, -104.435241</t>
+  </si>
+  <si>
+    <t>04/29/26 19:28 EDT</t>
+  </si>
+  <si>
+    <t>04/28/26 10:23 EDT</t>
+  </si>
+  <si>
+    <t>2.8mi NW of South Salt Lake UT</t>
+  </si>
+  <si>
+    <t>40.724631, -111.946112</t>
+  </si>
+  <si>
+    <t>04/28/26 10:24 EDT</t>
+  </si>
+  <si>
+    <t>3.6mi NW of South Salt Lake UT</t>
+  </si>
+  <si>
+    <t>40.726040, -111.960970</t>
+  </si>
+  <si>
+    <t>04/28/26 12:53 EDT</t>
+  </si>
+  <si>
+    <t>13.7mi S of Enterprise NV</t>
+  </si>
+  <si>
+    <t>35.819355, -115.299755</t>
+  </si>
+  <si>
+    <t>04/29/26 19:29 EDT</t>
+  </si>
+  <si>
+    <t>04/28/26 16:07 EDT</t>
+  </si>
+  <si>
+    <t>19mi NE of Enoch UT</t>
+  </si>
+  <si>
+    <t>37.931035, -112.764926</t>
+  </si>
+  <si>
+    <t>04/29/26 19:30 EDT</t>
+  </si>
+  <si>
+    <t>04/28/26 16:19 EDT</t>
+  </si>
+  <si>
+    <t>4.7mi E of Enoch UT</t>
+  </si>
+  <si>
+    <t>37.791588, -112.964741</t>
+  </si>
+  <si>
+    <t>04/28/26 16:20 EDT</t>
+  </si>
+  <si>
+    <t>4.4mi E of Enoch UT</t>
+  </si>
+  <si>
+    <t>37.788504, -112.969806</t>
+  </si>
+  <si>
+    <t>04/28/26 18:29 EDT</t>
+  </si>
+  <si>
+    <t>51.4mi SE of Las Vegas NM</t>
+  </si>
+  <si>
+    <t>34.964807, -104.749776</t>
+  </si>
+  <si>
+    <t>51.5mi SE of Las Vegas NM</t>
+  </si>
+  <si>
+    <t>34.964297, -104.745190</t>
+  </si>
+  <si>
+    <t>04/28/26 18:58 EDT</t>
+  </si>
+  <si>
+    <t>11.5mi NE of Moapa Valley NV</t>
+  </si>
+  <si>
+    <t>36.759536, -114.370412</t>
+  </si>
+  <si>
+    <t>04/28/26 22:24 EDT</t>
+  </si>
+  <si>
+    <t>36.128516, -115.180770</t>
+  </si>
+  <si>
+    <t>04/29/26 00:07 EDT</t>
+  </si>
+  <si>
+    <t>32.7mi W of Colby KS</t>
+  </si>
+  <si>
+    <t>39.329734, -101.652947</t>
+  </si>
+  <si>
+    <t>04/29/26 13:09 EDT</t>
+  </si>
+  <si>
+    <t>40.742061, -111.984395</t>
+  </si>
+  <si>
+    <t>04/29/26 17:07 EDT</t>
+  </si>
+  <si>
+    <t>Pcs Exempt</t>
+  </si>
+  <si>
+    <t>1mi N of Bakersfield CA</t>
+  </si>
+  <si>
+    <t>35.367106, -119.041488</t>
+  </si>
+  <si>
+    <t>04/29/26 20:00 EDT</t>
+  </si>
+  <si>
+    <t>36.381637, -114.892882</t>
+  </si>
+  <si>
+    <t>04/30/26 11:27 EDT</t>
+  </si>
+  <si>
+    <t>04/29/26 20:01 EDT</t>
+  </si>
+  <si>
+    <t>1.8mi SE of Bluffdale UT</t>
+  </si>
+  <si>
+    <t>40.456008, -111.914034</t>
+  </si>
+  <si>
+    <t>04/30/26 11:28 EDT</t>
+  </si>
+  <si>
+    <t>04/29/26 22:19 EDT</t>
+  </si>
+  <si>
+    <t>35.3mi W of Guymon OK</t>
+  </si>
+  <si>
+    <t>36.762415, -102.108201</t>
+  </si>
+  <si>
+    <t>04/29/26 22:32 EDT</t>
+  </si>
+  <si>
+    <t>13.3mi NE of Enoch UT</t>
+  </si>
+  <si>
+    <t>37.855176, -112.829116</t>
+  </si>
+  <si>
+    <t>04/30/26 01:43 EDT</t>
+  </si>
+  <si>
+    <t>7.1mi N of Moapa Valley NV</t>
+  </si>
+  <si>
+    <t>36.709575, -114.476978</t>
+  </si>
+  <si>
+    <t>04/30/26 04:54 EDT</t>
+  </si>
+  <si>
+    <t>40.644293, -111.902910</t>
+  </si>
+  <si>
+    <t>05/01/26 14:57 EDT</t>
+  </si>
+  <si>
+    <t>04/30/26 15:21 EDT</t>
+  </si>
+  <si>
+    <t>2mi SW of Pleasant Grove UT</t>
+  </si>
+  <si>
+    <t>40.345515, -111.759643</t>
+  </si>
+  <si>
+    <t>05/01/26 15:00 EDT</t>
+  </si>
+  <si>
+    <t>04/30/26 20:55 EDT</t>
+  </si>
+  <si>
+    <t>37.857267, -112.828587</t>
+  </si>
+  <si>
+    <t>05/01/26 12:35 EDT</t>
+  </si>
+  <si>
+    <t>5.6mi NW of Moapa Valley NV</t>
+  </si>
+  <si>
+    <t>36.671369, -114.519982</t>
+  </si>
+  <si>
+    <t>05/04/26 11:43 EDT</t>
+  </si>
+  <si>
+    <t>05/01/26 17:12 EDT</t>
+  </si>
+  <si>
+    <t>39.951960, -111.962855</t>
+  </si>
+  <si>
+    <t>05/04/26 11:44 EDT</t>
+  </si>
+  <si>
+    <t>05/01/26 17:50 EDT</t>
+  </si>
+  <si>
+    <t>0.5mi NW of St. George UT</t>
+  </si>
+  <si>
+    <t>37.081501, -113.580701</t>
+  </si>
+  <si>
+    <t>05/02/26 03:22 EDT</t>
+  </si>
+  <si>
+    <t>37.8mi E of Evanston WY</t>
+  </si>
+  <si>
+    <t>41.373527, -110.252002</t>
+  </si>
+  <si>
+    <t>05/02/26 04:03 EDT</t>
+  </si>
+  <si>
+    <t>2.7mi W of Evanston WY</t>
+  </si>
+  <si>
+    <t>41.248180, -111.014678</t>
+  </si>
+  <si>
+    <t>05/02/26 21:55 EDT</t>
+  </si>
+  <si>
+    <t>36.317630, -114.986735</t>
+  </si>
+  <si>
+    <t>05/03/26 13:02 EDT</t>
+  </si>
+  <si>
+    <t>2.4mi NW of La Vista NE</t>
+  </si>
+  <si>
+    <t>41.211113, -96.091816</t>
+  </si>
+  <si>
+    <t>05/03/26 21:02 EDT</t>
+  </si>
+  <si>
+    <t>31.2mi N of Hereford TX</t>
+  </si>
+  <si>
+    <t>35.262125, -102.522355</t>
+  </si>
+  <si>
+    <t>05/04/26 11:46 EDT</t>
   </si>
 </sst>
 </file>
@@ -7869,7 +8265,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N788"/>
+  <dimension ref="A1:N828"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="14" width="15" customWidth="1"/>
@@ -36898,22 +37294,26 @@
         <v>2438</v>
       </c>
       <c r="H768" s="3" t="s">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="I768" s="3">
         <v>73</v>
       </c>
       <c r="J768" s="3"/>
       <c r="K768" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L768" s="3"/>
-      <c r="M768" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L768" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M768" s="3" t="s">
+        <v>2439</v>
+      </c>
       <c r="N768" s="3"/>
     </row>
     <row r="769" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A769" s="3" t="s">
-        <v>2439</v>
+        <v>2440</v>
       </c>
       <c r="B769" s="3" t="s">
         <v>74</v>
@@ -36928,10 +37328,10 @@
         <v>47</v>
       </c>
       <c r="F769" s="3" t="s">
-        <v>2440</v>
+        <v>2441</v>
       </c>
       <c r="G769" s="3" t="s">
-        <v>2441</v>
+        <v>2442</v>
       </c>
       <c r="H769" s="3" t="s">
         <v>98</v>
@@ -36941,15 +37341,19 @@
       </c>
       <c r="J769" s="3"/>
       <c r="K769" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L769" s="3"/>
-      <c r="M769" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L769" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M769" s="3" t="s">
+        <v>2439</v>
+      </c>
       <c r="N769" s="3"/>
     </row>
     <row r="770" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A770" s="3" t="s">
-        <v>2442</v>
+        <v>2443</v>
       </c>
       <c r="B770" s="3" t="s">
         <v>339</v>
@@ -36964,13 +37368,13 @@
         <v>47</v>
       </c>
       <c r="F770" s="3" t="s">
-        <v>2443</v>
+        <v>2444</v>
       </c>
       <c r="G770" s="3" t="s">
-        <v>2444</v>
+        <v>2445</v>
       </c>
       <c r="H770" s="3" t="s">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="I770" s="3">
         <v>75</v>
@@ -36979,15 +37383,19 @@
         <v>80</v>
       </c>
       <c r="K770" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L770" s="3"/>
-      <c r="M770" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L770" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M770" s="3" t="s">
+        <v>2446</v>
+      </c>
       <c r="N770" s="3"/>
     </row>
     <row r="771" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A771" s="3" t="s">
-        <v>2445</v>
+        <v>2447</v>
       </c>
       <c r="B771" s="3"/>
       <c r="C771" s="3">
@@ -37000,13 +37408,13 @@
         <v>47</v>
       </c>
       <c r="F771" s="3" t="s">
-        <v>2446</v>
+        <v>2448</v>
       </c>
       <c r="G771" s="3" t="s">
-        <v>2447</v>
+        <v>2449</v>
       </c>
       <c r="H771" s="3" t="s">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="I771" s="3">
         <v>68</v>
@@ -37015,15 +37423,19 @@
         <v>75</v>
       </c>
       <c r="K771" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L771" s="3"/>
-      <c r="M771" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L771" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M771" s="3" t="s">
+        <v>2450</v>
+      </c>
       <c r="N771" s="3"/>
     </row>
     <row r="772" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A772" s="3" t="s">
-        <v>2448</v>
+        <v>2451</v>
       </c>
       <c r="B772" s="3"/>
       <c r="C772" s="3">
@@ -37036,10 +37448,10 @@
         <v>47</v>
       </c>
       <c r="F772" s="3" t="s">
-        <v>2449</v>
+        <v>2452</v>
       </c>
       <c r="G772" s="3" t="s">
-        <v>2450</v>
+        <v>2453</v>
       </c>
       <c r="H772" s="3"/>
       <c r="I772" s="3">
@@ -37057,7 +37469,7 @@
     </row>
     <row r="773" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A773" s="3" t="s">
-        <v>2451</v>
+        <v>2454</v>
       </c>
       <c r="B773" s="3" t="s">
         <v>74</v>
@@ -37072,28 +37484,32 @@
         <v>65</v>
       </c>
       <c r="F773" s="3" t="s">
-        <v>2452</v>
+        <v>2455</v>
       </c>
       <c r="G773" s="3" t="s">
-        <v>2453</v>
+        <v>2456</v>
       </c>
       <c r="H773" s="3" t="s">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="I773" s="3">
         <v>26</v>
       </c>
       <c r="J773" s="3"/>
       <c r="K773" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L773" s="3"/>
-      <c r="M773" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L773" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M773" s="3" t="s">
+        <v>2450</v>
+      </c>
       <c r="N773" s="3"/>
     </row>
     <row r="774" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A774" s="3" t="s">
-        <v>2454</v>
+        <v>2457</v>
       </c>
       <c r="B774" s="3" t="s">
         <v>132</v>
@@ -37108,10 +37524,10 @@
         <v>18</v>
       </c>
       <c r="F774" s="3" t="s">
-        <v>2455</v>
+        <v>2458</v>
       </c>
       <c r="G774" s="3" t="s">
-        <v>2456</v>
+        <v>2459</v>
       </c>
       <c r="H774" s="3"/>
       <c r="I774" s="3">
@@ -37129,7 +37545,7 @@
     </row>
     <row r="775" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A775" s="3" t="s">
-        <v>2457</v>
+        <v>2460</v>
       </c>
       <c r="B775" s="3"/>
       <c r="C775" s="3">
@@ -37142,12 +37558,14 @@
         <v>24</v>
       </c>
       <c r="F775" s="3" t="s">
-        <v>2458</v>
+        <v>2461</v>
       </c>
       <c r="G775" s="3" t="s">
-        <v>2459</v>
-      </c>
-      <c r="H775" s="3"/>
+        <v>2462</v>
+      </c>
+      <c r="H775" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="I775" s="3">
         <v>50</v>
       </c>
@@ -37155,15 +37573,19 @@
         <v>55</v>
       </c>
       <c r="K775" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L775" s="3"/>
-      <c r="M775" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L775" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M775" s="3" t="s">
+        <v>2463</v>
+      </c>
       <c r="N775" s="3"/>
     </row>
     <row r="776" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A776" s="3" t="s">
-        <v>2460</v>
+        <v>2464</v>
       </c>
       <c r="B776" s="3"/>
       <c r="C776" s="3">
@@ -37176,13 +37598,13 @@
         <v>47</v>
       </c>
       <c r="F776" s="3" t="s">
-        <v>2461</v>
+        <v>2465</v>
       </c>
       <c r="G776" s="3" t="s">
-        <v>2462</v>
+        <v>2466</v>
       </c>
       <c r="H776" s="3" t="s">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="I776" s="3">
         <v>67</v>
@@ -37191,15 +37613,19 @@
         <v>70</v>
       </c>
       <c r="K776" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L776" s="3"/>
-      <c r="M776" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L776" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M776" s="3" t="s">
+        <v>2467</v>
+      </c>
       <c r="N776" s="3"/>
     </row>
     <row r="777" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A777" s="3" t="s">
-        <v>2460</v>
+        <v>2464</v>
       </c>
       <c r="B777" s="3"/>
       <c r="C777" s="3">
@@ -37212,13 +37638,13 @@
         <v>43</v>
       </c>
       <c r="F777" s="3" t="s">
-        <v>2463</v>
+        <v>2468</v>
       </c>
       <c r="G777" s="3" t="s">
-        <v>2464</v>
+        <v>2469</v>
       </c>
       <c r="H777" s="3" t="s">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="I777" s="3">
         <v>61</v>
@@ -37227,15 +37653,19 @@
         <v>70</v>
       </c>
       <c r="K777" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L777" s="3"/>
-      <c r="M777" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L777" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M777" s="3" t="s">
+        <v>2470</v>
+      </c>
       <c r="N777" s="3"/>
     </row>
     <row r="778" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A778" s="3" t="s">
-        <v>2465</v>
+        <v>2471</v>
       </c>
       <c r="B778" s="3" t="s">
         <v>349</v>
@@ -37250,10 +37680,10 @@
         <v>47</v>
       </c>
       <c r="F778" s="3" t="s">
-        <v>2466</v>
+        <v>2472</v>
       </c>
       <c r="G778" s="3" t="s">
-        <v>2467</v>
+        <v>2473</v>
       </c>
       <c r="H778" s="3"/>
       <c r="I778" s="3">
@@ -37269,7 +37699,7 @@
     </row>
     <row r="779" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A779" s="3" t="s">
-        <v>2468</v>
+        <v>2474</v>
       </c>
       <c r="B779" s="3"/>
       <c r="C779" s="3">
@@ -37282,10 +37712,10 @@
         <v>47</v>
       </c>
       <c r="F779" s="3" t="s">
-        <v>2469</v>
+        <v>2475</v>
       </c>
       <c r="G779" s="3" t="s">
-        <v>2470</v>
+        <v>2476</v>
       </c>
       <c r="H779" s="3"/>
       <c r="I779" s="3">
@@ -37303,7 +37733,7 @@
     </row>
     <row r="780" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A780" s="3" t="s">
-        <v>2471</v>
+        <v>2477</v>
       </c>
       <c r="B780" s="3"/>
       <c r="C780" s="3">
@@ -37316,10 +37746,10 @@
         <v>47</v>
       </c>
       <c r="F780" s="3" t="s">
-        <v>2472</v>
+        <v>2478</v>
       </c>
       <c r="G780" s="3" t="s">
-        <v>2473</v>
+        <v>2479</v>
       </c>
       <c r="H780" s="3"/>
       <c r="I780" s="3">
@@ -37337,7 +37767,7 @@
     </row>
     <row r="781" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A781" s="3" t="s">
-        <v>2474</v>
+        <v>2480</v>
       </c>
       <c r="B781" s="3"/>
       <c r="C781" s="3">
@@ -37353,25 +37783,29 @@
         <v>299</v>
       </c>
       <c r="G781" s="3" t="s">
-        <v>2475</v>
+        <v>2481</v>
       </c>
       <c r="H781" s="3" t="s">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="I781" s="3">
         <v>23</v>
       </c>
       <c r="J781" s="3"/>
       <c r="K781" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L781" s="3"/>
-      <c r="M781" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L781" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M781" s="3" t="s">
+        <v>2482</v>
+      </c>
       <c r="N781" s="3"/>
     </row>
     <row r="782" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A782" s="3" t="s">
-        <v>2476</v>
+        <v>2483</v>
       </c>
       <c r="B782" s="3"/>
       <c r="C782" s="3">
@@ -37384,12 +37818,14 @@
         <v>24</v>
       </c>
       <c r="F782" s="3" t="s">
-        <v>2477</v>
+        <v>2484</v>
       </c>
       <c r="G782" s="3" t="s">
-        <v>2478</v>
-      </c>
-      <c r="H782" s="3"/>
+        <v>2485</v>
+      </c>
+      <c r="H782" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="I782" s="3">
         <v>28</v>
       </c>
@@ -37397,15 +37833,19 @@
         <v>55</v>
       </c>
       <c r="K782" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L782" s="3"/>
-      <c r="M782" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L782" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M782" s="3" t="s">
+        <v>2463</v>
+      </c>
       <c r="N782" s="3"/>
     </row>
     <row r="783" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A783" s="3" t="s">
-        <v>2479</v>
+        <v>2486</v>
       </c>
       <c r="B783" s="3"/>
       <c r="C783" s="3">
@@ -37418,10 +37858,10 @@
         <v>85</v>
       </c>
       <c r="F783" s="3" t="s">
-        <v>2480</v>
+        <v>2487</v>
       </c>
       <c r="G783" s="3" t="s">
-        <v>2481</v>
+        <v>2488</v>
       </c>
       <c r="H783" s="3" t="s">
         <v>98</v>
@@ -37441,7 +37881,7 @@
     </row>
     <row r="784" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A784" s="3" t="s">
-        <v>2482</v>
+        <v>2489</v>
       </c>
       <c r="B784" s="3" t="s">
         <v>17</v>
@@ -37456,12 +37896,14 @@
         <v>24</v>
       </c>
       <c r="F784" s="3" t="s">
-        <v>2483</v>
+        <v>2490</v>
       </c>
       <c r="G784" s="3" t="s">
-        <v>2484</v>
-      </c>
-      <c r="H784" s="3"/>
+        <v>2491</v>
+      </c>
+      <c r="H784" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="I784" s="3">
         <v>52</v>
       </c>
@@ -37469,15 +37911,19 @@
         <v>55</v>
       </c>
       <c r="K784" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L784" s="3"/>
-      <c r="M784" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L784" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M784" s="3" t="s">
+        <v>2470</v>
+      </c>
       <c r="N784" s="3"/>
     </row>
     <row r="785" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A785" s="3" t="s">
-        <v>2485</v>
+        <v>2492</v>
       </c>
       <c r="B785" s="3" t="s">
         <v>81</v>
@@ -37492,13 +37938,13 @@
         <v>47</v>
       </c>
       <c r="F785" s="3" t="s">
-        <v>2486</v>
+        <v>2493</v>
       </c>
       <c r="G785" s="3" t="s">
-        <v>2487</v>
+        <v>2494</v>
       </c>
       <c r="H785" s="3" t="s">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="I785" s="3">
         <v>65</v>
@@ -37507,15 +37953,19 @@
         <v>75</v>
       </c>
       <c r="K785" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L785" s="3"/>
-      <c r="M785" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L785" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M785" s="3" t="s">
+        <v>2467</v>
+      </c>
       <c r="N785" s="3"/>
     </row>
     <row r="786" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A786" s="3" t="s">
-        <v>2488</v>
+        <v>2495</v>
       </c>
       <c r="B786" s="3" t="s">
         <v>81</v>
@@ -37533,25 +37983,29 @@
         <v>129</v>
       </c>
       <c r="G786" s="3" t="s">
-        <v>2489</v>
+        <v>2496</v>
       </c>
       <c r="H786" s="3" t="s">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="I786" s="3">
         <v>27</v>
       </c>
       <c r="J786" s="3"/>
       <c r="K786" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L786" s="3"/>
-      <c r="M786" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L786" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M786" s="3" t="s">
+        <v>2482</v>
+      </c>
       <c r="N786" s="3"/>
     </row>
     <row r="787" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A787" s="3" t="s">
-        <v>2490</v>
+        <v>2497</v>
       </c>
       <c r="B787" s="3" t="s">
         <v>628</v>
@@ -37566,10 +38020,10 @@
         <v>18</v>
       </c>
       <c r="F787" s="3" t="s">
-        <v>2491</v>
+        <v>2498</v>
       </c>
       <c r="G787" s="3" t="s">
-        <v>2492</v>
+        <v>2499</v>
       </c>
       <c r="H787" s="3"/>
       <c r="I787" s="3">
@@ -37587,7 +38041,7 @@
     </row>
     <row r="788" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A788" s="3" t="s">
-        <v>2493</v>
+        <v>2500</v>
       </c>
       <c r="B788" s="3"/>
       <c r="C788" s="3">
@@ -37600,10 +38054,10 @@
         <v>24</v>
       </c>
       <c r="F788" s="3" t="s">
-        <v>2494</v>
+        <v>2501</v>
       </c>
       <c r="G788" s="3" t="s">
-        <v>2495</v>
+        <v>2502</v>
       </c>
       <c r="H788" s="3"/>
       <c r="I788" s="3">
@@ -37616,6 +38070,1532 @@
       <c r="L788" s="3"/>
       <c r="M788" s="3"/>
       <c r="N788" s="3"/>
+    </row>
+    <row r="789" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A789" s="3" t="s">
+        <v>2503</v>
+      </c>
+      <c r="B789" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="C789" s="3">
+        <v>208</v>
+      </c>
+      <c r="D789" s="3">
+        <v>1520464138</v>
+      </c>
+      <c r="E789" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F789" s="3" t="s">
+        <v>2504</v>
+      </c>
+      <c r="G789" s="3" t="s">
+        <v>2505</v>
+      </c>
+      <c r="H789" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I789" s="3">
+        <v>25</v>
+      </c>
+      <c r="J789" s="3"/>
+      <c r="K789" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L789" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M789" s="3" t="s">
+        <v>2482</v>
+      </c>
+      <c r="N789" s="3"/>
+    </row>
+    <row r="790" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A790" s="3" t="s">
+        <v>2506</v>
+      </c>
+      <c r="B790" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="C790" s="3">
+        <v>838</v>
+      </c>
+      <c r="D790" s="3">
+        <v>1520469467</v>
+      </c>
+      <c r="E790" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F790" s="3" t="s">
+        <v>2507</v>
+      </c>
+      <c r="G790" s="3" t="s">
+        <v>2508</v>
+      </c>
+      <c r="H790" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I790" s="3">
+        <v>69</v>
+      </c>
+      <c r="J790" s="3">
+        <v>80</v>
+      </c>
+      <c r="K790" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L790" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M790" s="3" t="s">
+        <v>2509</v>
+      </c>
+      <c r="N790" s="3"/>
+    </row>
+    <row r="791" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A791" s="3" t="s">
+        <v>2510</v>
+      </c>
+      <c r="B791" s="3"/>
+      <c r="C791" s="3">
+        <v>375</v>
+      </c>
+      <c r="D791" s="3">
+        <v>1520473005</v>
+      </c>
+      <c r="E791" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F791" s="3" t="s">
+        <v>2511</v>
+      </c>
+      <c r="G791" s="3" t="s">
+        <v>2512</v>
+      </c>
+      <c r="H791" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I791" s="3">
+        <v>69</v>
+      </c>
+      <c r="J791" s="3">
+        <v>65</v>
+      </c>
+      <c r="K791" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L791" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M791" s="3" t="s">
+        <v>2509</v>
+      </c>
+      <c r="N791" s="3"/>
+    </row>
+    <row r="792" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A792" s="3" t="s">
+        <v>2513</v>
+      </c>
+      <c r="B792" s="3"/>
+      <c r="C792" s="3">
+        <v>375</v>
+      </c>
+      <c r="D792" s="3">
+        <v>1520506382</v>
+      </c>
+      <c r="E792" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F792" s="3" t="s">
+        <v>2514</v>
+      </c>
+      <c r="G792" s="3" t="s">
+        <v>2515</v>
+      </c>
+      <c r="H792" s="3"/>
+      <c r="I792" s="3">
+        <v>54</v>
+      </c>
+      <c r="J792" s="3">
+        <v>65</v>
+      </c>
+      <c r="K792" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L792" s="3"/>
+      <c r="M792" s="3"/>
+      <c r="N792" s="3"/>
+    </row>
+    <row r="793" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A793" s="3" t="s">
+        <v>2516</v>
+      </c>
+      <c r="B793" s="3"/>
+      <c r="C793" s="3">
+        <v>375</v>
+      </c>
+      <c r="D793" s="3">
+        <v>1520542197</v>
+      </c>
+      <c r="E793" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F793" s="3" t="s">
+        <v>2517</v>
+      </c>
+      <c r="G793" s="3" t="s">
+        <v>2518</v>
+      </c>
+      <c r="H793" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I793" s="3">
+        <v>62</v>
+      </c>
+      <c r="J793" s="3">
+        <v>70</v>
+      </c>
+      <c r="K793" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L793" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M793" s="3" t="s">
+        <v>2519</v>
+      </c>
+      <c r="N793" s="3"/>
+    </row>
+    <row r="794" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A794" s="3" t="s">
+        <v>2520</v>
+      </c>
+      <c r="B794" s="3"/>
+      <c r="C794" s="3">
+        <v>340</v>
+      </c>
+      <c r="D794" s="3">
+        <v>1521112051</v>
+      </c>
+      <c r="E794" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F794" s="3" t="s">
+        <v>2521</v>
+      </c>
+      <c r="G794" s="3" t="s">
+        <v>2522</v>
+      </c>
+      <c r="H794" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I794" s="3"/>
+      <c r="J794" s="3"/>
+      <c r="K794" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L794" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M794" s="3" t="s">
+        <v>2523</v>
+      </c>
+      <c r="N794" s="3"/>
+    </row>
+    <row r="795" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A795" s="3" t="s">
+        <v>2524</v>
+      </c>
+      <c r="B795" s="3"/>
+      <c r="C795" s="3">
+        <v>926</v>
+      </c>
+      <c r="D795" s="3">
+        <v>1521333053</v>
+      </c>
+      <c r="E795" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F795" s="3" t="s">
+        <v>2525</v>
+      </c>
+      <c r="G795" s="3" t="s">
+        <v>2526</v>
+      </c>
+      <c r="H795" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I795" s="3">
+        <v>55</v>
+      </c>
+      <c r="J795" s="3"/>
+      <c r="K795" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L795" s="3"/>
+      <c r="M795" s="3"/>
+      <c r="N795" s="3"/>
+    </row>
+    <row r="796" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A796" s="3" t="s">
+        <v>2527</v>
+      </c>
+      <c r="B796" s="3"/>
+      <c r="C796" s="3">
+        <v>926</v>
+      </c>
+      <c r="D796" s="3">
+        <v>1521339680</v>
+      </c>
+      <c r="E796" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F796" s="3" t="s">
+        <v>2528</v>
+      </c>
+      <c r="G796" s="3" t="s">
+        <v>2529</v>
+      </c>
+      <c r="H796" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I796" s="3">
+        <v>61</v>
+      </c>
+      <c r="J796" s="3"/>
+      <c r="K796" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L796" s="3"/>
+      <c r="M796" s="3"/>
+      <c r="N796" s="3"/>
+    </row>
+    <row r="797" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A797" s="3" t="s">
+        <v>2530</v>
+      </c>
+      <c r="B797" s="3"/>
+      <c r="C797" s="3">
+        <v>926</v>
+      </c>
+      <c r="D797" s="3">
+        <v>1521345602</v>
+      </c>
+      <c r="E797" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F797" s="3" t="s">
+        <v>2531</v>
+      </c>
+      <c r="G797" s="3" t="s">
+        <v>2532</v>
+      </c>
+      <c r="H797" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I797" s="3">
+        <v>58</v>
+      </c>
+      <c r="J797" s="3"/>
+      <c r="K797" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L797" s="3"/>
+      <c r="M797" s="3"/>
+      <c r="N797" s="3"/>
+    </row>
+    <row r="798" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A798" s="3" t="s">
+        <v>2533</v>
+      </c>
+      <c r="B798" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="C798" s="3">
+        <v>108</v>
+      </c>
+      <c r="D798" s="3">
+        <v>1521361102</v>
+      </c>
+      <c r="E798" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F798" s="3" t="s">
+        <v>2534</v>
+      </c>
+      <c r="G798" s="3" t="s">
+        <v>2535</v>
+      </c>
+      <c r="H798" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I798" s="3">
+        <v>82</v>
+      </c>
+      <c r="J798" s="3">
+        <v>80</v>
+      </c>
+      <c r="K798" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L798" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M798" s="3" t="s">
+        <v>2523</v>
+      </c>
+      <c r="N798" s="3"/>
+    </row>
+    <row r="799" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A799" s="3" t="s">
+        <v>2536</v>
+      </c>
+      <c r="B799" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C799" s="3">
+        <v>839</v>
+      </c>
+      <c r="D799" s="3">
+        <v>1521506701</v>
+      </c>
+      <c r="E799" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F799" s="3" t="s">
+        <v>1366</v>
+      </c>
+      <c r="G799" s="3" t="s">
+        <v>2537</v>
+      </c>
+      <c r="H799" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I799" s="3">
+        <v>17</v>
+      </c>
+      <c r="J799" s="3"/>
+      <c r="K799" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L799" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M799" s="3" t="s">
+        <v>2538</v>
+      </c>
+      <c r="N799" s="3"/>
+    </row>
+    <row r="800" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A800" s="3" t="s">
+        <v>2539</v>
+      </c>
+      <c r="B800" s="3"/>
+      <c r="C800" s="3">
+        <v>344</v>
+      </c>
+      <c r="D800" s="3">
+        <v>1521635096</v>
+      </c>
+      <c r="E800" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F800" s="3" t="s">
+        <v>2540</v>
+      </c>
+      <c r="G800" s="3" t="s">
+        <v>2541</v>
+      </c>
+      <c r="H800" s="3"/>
+      <c r="I800" s="3">
+        <v>66</v>
+      </c>
+      <c r="J800" s="3">
+        <v>65</v>
+      </c>
+      <c r="K800" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L800" s="3"/>
+      <c r="M800" s="3"/>
+      <c r="N800" s="3"/>
+    </row>
+    <row r="801" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A801" s="3" t="s">
+        <v>2542</v>
+      </c>
+      <c r="B801" s="3"/>
+      <c r="C801" s="3">
+        <v>344</v>
+      </c>
+      <c r="D801" s="3">
+        <v>1521635098</v>
+      </c>
+      <c r="E801" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F801" s="3" t="s">
+        <v>2543</v>
+      </c>
+      <c r="G801" s="3" t="s">
+        <v>2544</v>
+      </c>
+      <c r="H801" s="3"/>
+      <c r="I801" s="3">
+        <v>57</v>
+      </c>
+      <c r="J801" s="3"/>
+      <c r="K801" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L801" s="3"/>
+      <c r="M801" s="3"/>
+      <c r="N801" s="3"/>
+    </row>
+    <row r="802" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A802" s="3" t="s">
+        <v>2545</v>
+      </c>
+      <c r="B802" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C802" s="3">
+        <v>672</v>
+      </c>
+      <c r="D802" s="3">
+        <v>1521783503</v>
+      </c>
+      <c r="E802" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F802" s="3" t="s">
+        <v>2546</v>
+      </c>
+      <c r="G802" s="3" t="s">
+        <v>2547</v>
+      </c>
+      <c r="H802" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I802" s="3">
+        <v>70</v>
+      </c>
+      <c r="J802" s="3"/>
+      <c r="K802" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L802" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M802" s="3" t="s">
+        <v>2548</v>
+      </c>
+      <c r="N802" s="3"/>
+    </row>
+    <row r="803" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A803" s="3" t="s">
+        <v>2549</v>
+      </c>
+      <c r="B803" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C803" s="3">
+        <v>357</v>
+      </c>
+      <c r="D803" s="3">
+        <v>1521983580</v>
+      </c>
+      <c r="E803" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F803" s="3" t="s">
+        <v>2550</v>
+      </c>
+      <c r="G803" s="3" t="s">
+        <v>2551</v>
+      </c>
+      <c r="H803" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I803" s="3">
+        <v>73</v>
+      </c>
+      <c r="J803" s="3">
+        <v>80</v>
+      </c>
+      <c r="K803" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L803" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M803" s="3" t="s">
+        <v>2552</v>
+      </c>
+      <c r="N803" s="3"/>
+    </row>
+    <row r="804" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A804" s="3" t="s">
+        <v>2553</v>
+      </c>
+      <c r="B804" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C804" s="3">
+        <v>357</v>
+      </c>
+      <c r="D804" s="3">
+        <v>1521995222</v>
+      </c>
+      <c r="E804" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F804" s="3" t="s">
+        <v>2554</v>
+      </c>
+      <c r="G804" s="3" t="s">
+        <v>2555</v>
+      </c>
+      <c r="H804" s="3"/>
+      <c r="I804" s="3">
+        <v>72</v>
+      </c>
+      <c r="J804" s="3">
+        <v>80</v>
+      </c>
+      <c r="K804" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L804" s="3"/>
+      <c r="M804" s="3"/>
+      <c r="N804" s="3"/>
+    </row>
+    <row r="805" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A805" s="3" t="s">
+        <v>2556</v>
+      </c>
+      <c r="B805" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C805" s="3">
+        <v>357</v>
+      </c>
+      <c r="D805" s="3">
+        <v>1521995187</v>
+      </c>
+      <c r="E805" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F805" s="3" t="s">
+        <v>2557</v>
+      </c>
+      <c r="G805" s="3" t="s">
+        <v>2558</v>
+      </c>
+      <c r="H805" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I805" s="3">
+        <v>69</v>
+      </c>
+      <c r="J805" s="3">
+        <v>80</v>
+      </c>
+      <c r="K805" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L805" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M805" s="3" t="s">
+        <v>2538</v>
+      </c>
+      <c r="N805" s="3"/>
+    </row>
+    <row r="806" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A806" s="3" t="s">
+        <v>2559</v>
+      </c>
+      <c r="B806" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C806" s="3">
+        <v>336</v>
+      </c>
+      <c r="D806" s="3">
+        <v>1522102765</v>
+      </c>
+      <c r="E806" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F806" s="3" t="s">
+        <v>2560</v>
+      </c>
+      <c r="G806" s="3" t="s">
+        <v>2561</v>
+      </c>
+      <c r="H806" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I806" s="3">
+        <v>67</v>
+      </c>
+      <c r="J806" s="3">
+        <v>75</v>
+      </c>
+      <c r="K806" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L806" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M806" s="3" t="s">
+        <v>2552</v>
+      </c>
+      <c r="N806" s="3"/>
+    </row>
+    <row r="807" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A807" s="3" t="s">
+        <v>2559</v>
+      </c>
+      <c r="B807" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C807" s="3">
+        <v>336</v>
+      </c>
+      <c r="D807" s="3">
+        <v>1522102772</v>
+      </c>
+      <c r="E807" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F807" s="3" t="s">
+        <v>2562</v>
+      </c>
+      <c r="G807" s="3" t="s">
+        <v>2563</v>
+      </c>
+      <c r="H807" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I807" s="3">
+        <v>67</v>
+      </c>
+      <c r="J807" s="3">
+        <v>75</v>
+      </c>
+      <c r="K807" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L807" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M807" s="3" t="s">
+        <v>2538</v>
+      </c>
+      <c r="N807" s="3"/>
+    </row>
+    <row r="808" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A808" s="3" t="s">
+        <v>2564</v>
+      </c>
+      <c r="B808" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C808" s="3">
+        <v>357</v>
+      </c>
+      <c r="D808" s="3">
+        <v>1522122107</v>
+      </c>
+      <c r="E808" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F808" s="3" t="s">
+        <v>2565</v>
+      </c>
+      <c r="G808" s="3" t="s">
+        <v>2566</v>
+      </c>
+      <c r="H808" s="3"/>
+      <c r="I808" s="3">
+        <v>77</v>
+      </c>
+      <c r="J808" s="3">
+        <v>75</v>
+      </c>
+      <c r="K808" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L808" s="3"/>
+      <c r="M808" s="3"/>
+      <c r="N808" s="3"/>
+    </row>
+    <row r="809" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A809" s="3" t="s">
+        <v>2567</v>
+      </c>
+      <c r="B809" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C809" s="3">
+        <v>357</v>
+      </c>
+      <c r="D809" s="3">
+        <v>1522208915</v>
+      </c>
+      <c r="E809" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F809" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="G809" s="3" t="s">
+        <v>2568</v>
+      </c>
+      <c r="H809" s="3"/>
+      <c r="I809" s="3">
+        <v>66</v>
+      </c>
+      <c r="J809" s="3">
+        <v>65</v>
+      </c>
+      <c r="K809" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L809" s="3"/>
+      <c r="M809" s="3"/>
+      <c r="N809" s="3"/>
+    </row>
+    <row r="810" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A810" s="3" t="s">
+        <v>2569</v>
+      </c>
+      <c r="B810" s="3"/>
+      <c r="C810" s="3">
+        <v>729</v>
+      </c>
+      <c r="D810" s="3">
+        <v>1522231117</v>
+      </c>
+      <c r="E810" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F810" s="3" t="s">
+        <v>2570</v>
+      </c>
+      <c r="G810" s="3" t="s">
+        <v>2571</v>
+      </c>
+      <c r="H810" s="3"/>
+      <c r="I810" s="3">
+        <v>64</v>
+      </c>
+      <c r="J810" s="3">
+        <v>75</v>
+      </c>
+      <c r="K810" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L810" s="3"/>
+      <c r="M810" s="3"/>
+      <c r="N810" s="3"/>
+    </row>
+    <row r="811" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A811" s="3" t="s">
+        <v>2572</v>
+      </c>
+      <c r="B811" s="3"/>
+      <c r="C811" s="3">
+        <v>338</v>
+      </c>
+      <c r="D811" s="3">
+        <v>1522658684</v>
+      </c>
+      <c r="E811" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F811" s="3" t="s">
+        <v>1517</v>
+      </c>
+      <c r="G811" s="3" t="s">
+        <v>2573</v>
+      </c>
+      <c r="H811" s="3"/>
+      <c r="I811" s="3">
+        <v>40</v>
+      </c>
+      <c r="J811" s="3"/>
+      <c r="K811" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L811" s="3"/>
+      <c r="M811" s="3"/>
+      <c r="N811" s="3"/>
+    </row>
+    <row r="812" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A812" s="3" t="s">
+        <v>2574</v>
+      </c>
+      <c r="B812" s="3" t="s">
+        <v>2575</v>
+      </c>
+      <c r="C812" s="3">
+        <v>357</v>
+      </c>
+      <c r="D812" s="3">
+        <v>1522894512</v>
+      </c>
+      <c r="E812" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F812" s="3" t="s">
+        <v>2576</v>
+      </c>
+      <c r="G812" s="3" t="s">
+        <v>2577</v>
+      </c>
+      <c r="H812" s="3"/>
+      <c r="I812" s="3">
+        <v>65</v>
+      </c>
+      <c r="J812" s="3">
+        <v>65</v>
+      </c>
+      <c r="K812" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L812" s="3"/>
+      <c r="M812" s="3"/>
+      <c r="N812" s="3"/>
+    </row>
+    <row r="813" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A813" s="3" t="s">
+        <v>2578</v>
+      </c>
+      <c r="B813" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C813" s="3">
+        <v>672</v>
+      </c>
+      <c r="D813" s="3">
+        <v>1523008254</v>
+      </c>
+      <c r="E813" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F813" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="G813" s="3" t="s">
+        <v>2579</v>
+      </c>
+      <c r="H813" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I813" s="3">
+        <v>29</v>
+      </c>
+      <c r="J813" s="3">
+        <v>70</v>
+      </c>
+      <c r="K813" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L813" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M813" s="3" t="s">
+        <v>2580</v>
+      </c>
+      <c r="N813" s="3"/>
+    </row>
+    <row r="814" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A814" s="3" t="s">
+        <v>2581</v>
+      </c>
+      <c r="B814" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="C814" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="D814" s="3">
+        <v>1523007901</v>
+      </c>
+      <c r="E814" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F814" s="3" t="s">
+        <v>2582</v>
+      </c>
+      <c r="G814" s="3" t="s">
+        <v>2583</v>
+      </c>
+      <c r="H814" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I814" s="3">
+        <v>45</v>
+      </c>
+      <c r="J814" s="3">
+        <v>70</v>
+      </c>
+      <c r="K814" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L814" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M814" s="3" t="s">
+        <v>2584</v>
+      </c>
+      <c r="N814" s="3"/>
+    </row>
+    <row r="815" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A815" s="3" t="s">
+        <v>2585</v>
+      </c>
+      <c r="B815" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C815" s="3">
+        <v>336</v>
+      </c>
+      <c r="D815" s="3">
+        <v>1523061841</v>
+      </c>
+      <c r="E815" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F815" s="3" t="s">
+        <v>2586</v>
+      </c>
+      <c r="G815" s="3" t="s">
+        <v>2587</v>
+      </c>
+      <c r="H815" s="3"/>
+      <c r="I815" s="3">
+        <v>65</v>
+      </c>
+      <c r="J815" s="3">
+        <v>65</v>
+      </c>
+      <c r="K815" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L815" s="3"/>
+      <c r="M815" s="3"/>
+      <c r="N815" s="3"/>
+    </row>
+    <row r="816" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A816" s="3" t="s">
+        <v>2588</v>
+      </c>
+      <c r="B816" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C816" s="3">
+        <v>459</v>
+      </c>
+      <c r="D816" s="3">
+        <v>1523064588</v>
+      </c>
+      <c r="E816" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F816" s="3" t="s">
+        <v>2589</v>
+      </c>
+      <c r="G816" s="3" t="s">
+        <v>2590</v>
+      </c>
+      <c r="H816" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I816" s="3">
+        <v>16</v>
+      </c>
+      <c r="J816" s="3"/>
+      <c r="K816" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L816" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M816" s="3" t="s">
+        <v>2584</v>
+      </c>
+      <c r="N816" s="3"/>
+    </row>
+    <row r="817" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A817" s="3" t="s">
+        <v>2591</v>
+      </c>
+      <c r="B817" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C817" s="3">
+        <v>357</v>
+      </c>
+      <c r="D817" s="3">
+        <v>1523100080</v>
+      </c>
+      <c r="E817" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F817" s="3" t="s">
+        <v>2592</v>
+      </c>
+      <c r="G817" s="3" t="s">
+        <v>2593</v>
+      </c>
+      <c r="H817" s="3"/>
+      <c r="I817" s="3">
+        <v>78</v>
+      </c>
+      <c r="J817" s="3">
+        <v>75</v>
+      </c>
+      <c r="K817" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L817" s="3"/>
+      <c r="M817" s="3"/>
+      <c r="N817" s="3"/>
+    </row>
+    <row r="818" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A818" s="3" t="s">
+        <v>2594</v>
+      </c>
+      <c r="B818" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="C818" s="3">
+        <v>108</v>
+      </c>
+      <c r="D818" s="3">
+        <v>1523125531</v>
+      </c>
+      <c r="E818" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F818" s="3" t="s">
+        <v>1703</v>
+      </c>
+      <c r="G818" s="3" t="s">
+        <v>2595</v>
+      </c>
+      <c r="H818" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I818" s="3">
+        <v>75</v>
+      </c>
+      <c r="J818" s="3">
+        <v>70</v>
+      </c>
+      <c r="K818" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L818" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M818" s="3" t="s">
+        <v>2596</v>
+      </c>
+      <c r="N818" s="3"/>
+    </row>
+    <row r="819" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A819" s="3" t="s">
+        <v>2597</v>
+      </c>
+      <c r="B819" s="3" t="s">
+        <v>1742</v>
+      </c>
+      <c r="C819" s="3">
+        <v>375</v>
+      </c>
+      <c r="D819" s="3">
+        <v>1523656024</v>
+      </c>
+      <c r="E819" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F819" s="3" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G819" s="3" t="s">
+        <v>2599</v>
+      </c>
+      <c r="H819" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I819" s="3">
+        <v>23</v>
+      </c>
+      <c r="J819" s="3"/>
+      <c r="K819" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L819" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M819" s="3" t="s">
+        <v>2600</v>
+      </c>
+      <c r="N819" s="3"/>
+    </row>
+    <row r="820" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A820" s="3" t="s">
+        <v>2601</v>
+      </c>
+      <c r="B820" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C820" s="3">
+        <v>459</v>
+      </c>
+      <c r="D820" s="3">
+        <v>1523900784</v>
+      </c>
+      <c r="E820" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F820" s="3" t="s">
+        <v>1873</v>
+      </c>
+      <c r="G820" s="3" t="s">
+        <v>2602</v>
+      </c>
+      <c r="H820" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I820" s="3">
+        <v>43</v>
+      </c>
+      <c r="J820" s="3"/>
+      <c r="K820" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L820" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M820" s="3" t="s">
+        <v>2600</v>
+      </c>
+      <c r="N820" s="3"/>
+    </row>
+    <row r="821" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A821" s="3" t="s">
+        <v>2603</v>
+      </c>
+      <c r="B821" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C821" s="3">
+        <v>672</v>
+      </c>
+      <c r="D821" s="3">
+        <v>1524320995</v>
+      </c>
+      <c r="E821" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F821" s="3" t="s">
+        <v>2604</v>
+      </c>
+      <c r="G821" s="3" t="s">
+        <v>2605</v>
+      </c>
+      <c r="H821" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I821" s="3">
+        <v>56</v>
+      </c>
+      <c r="J821" s="3">
+        <v>75</v>
+      </c>
+      <c r="K821" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L821" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M821" s="3" t="s">
+        <v>2606</v>
+      </c>
+      <c r="N821" s="3"/>
+    </row>
+    <row r="822" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A822" s="3" t="s">
+        <v>2607</v>
+      </c>
+      <c r="B822" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="C822" s="3">
+        <v>357</v>
+      </c>
+      <c r="D822" s="3">
+        <v>1524568838</v>
+      </c>
+      <c r="E822" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F822" s="3" t="s">
+        <v>2102</v>
+      </c>
+      <c r="G822" s="3" t="s">
+        <v>2608</v>
+      </c>
+      <c r="H822" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I822" s="3">
+        <v>40</v>
+      </c>
+      <c r="J822" s="3">
+        <v>65</v>
+      </c>
+      <c r="K822" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L822" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M822" s="3" t="s">
+        <v>2609</v>
+      </c>
+      <c r="N822" s="3"/>
+    </row>
+    <row r="823" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A823" s="3" t="s">
+        <v>2610</v>
+      </c>
+      <c r="B823" s="3"/>
+      <c r="C823" s="3">
+        <v>926</v>
+      </c>
+      <c r="D823" s="3">
+        <v>1524594997</v>
+      </c>
+      <c r="E823" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F823" s="3" t="s">
+        <v>2611</v>
+      </c>
+      <c r="G823" s="3" t="s">
+        <v>2612</v>
+      </c>
+      <c r="H823" s="3"/>
+      <c r="I823" s="3">
+        <v>22</v>
+      </c>
+      <c r="J823" s="3"/>
+      <c r="K823" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L823" s="3"/>
+      <c r="M823" s="3"/>
+      <c r="N823" s="3"/>
+    </row>
+    <row r="824" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A824" s="3" t="s">
+        <v>2613</v>
+      </c>
+      <c r="B824" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C824" s="3">
+        <v>336</v>
+      </c>
+      <c r="D824" s="3">
+        <v>1524748755</v>
+      </c>
+      <c r="E824" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F824" s="3" t="s">
+        <v>2614</v>
+      </c>
+      <c r="G824" s="3" t="s">
+        <v>2615</v>
+      </c>
+      <c r="H824" s="3"/>
+      <c r="I824" s="3">
+        <v>64</v>
+      </c>
+      <c r="J824" s="3">
+        <v>75</v>
+      </c>
+      <c r="K824" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L824" s="3"/>
+      <c r="M824" s="3"/>
+      <c r="N824" s="3"/>
+    </row>
+    <row r="825" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A825" s="3" t="s">
+        <v>2616</v>
+      </c>
+      <c r="B825" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C825" s="3">
+        <v>336</v>
+      </c>
+      <c r="D825" s="3">
+        <v>1524752331</v>
+      </c>
+      <c r="E825" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F825" s="3" t="s">
+        <v>2617</v>
+      </c>
+      <c r="G825" s="3" t="s">
+        <v>2618</v>
+      </c>
+      <c r="H825" s="3"/>
+      <c r="I825" s="3">
+        <v>63</v>
+      </c>
+      <c r="J825" s="3">
+        <v>75</v>
+      </c>
+      <c r="K825" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L825" s="3"/>
+      <c r="M825" s="3"/>
+      <c r="N825" s="3"/>
+    </row>
+    <row r="826" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A826" s="3" t="s">
+        <v>2619</v>
+      </c>
+      <c r="B826" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C826" s="3">
+        <v>107</v>
+      </c>
+      <c r="D826" s="3">
+        <v>1525060749</v>
+      </c>
+      <c r="E826" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F826" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="G826" s="3" t="s">
+        <v>2620</v>
+      </c>
+      <c r="H826" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I826" s="3">
+        <v>16</v>
+      </c>
+      <c r="J826" s="3"/>
+      <c r="K826" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L826" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M826" s="3" t="s">
+        <v>2609</v>
+      </c>
+      <c r="N826" s="3"/>
+    </row>
+    <row r="827" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A827" s="3" t="s">
+        <v>2621</v>
+      </c>
+      <c r="B827" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C827" s="3">
+        <v>672</v>
+      </c>
+      <c r="D827" s="3">
+        <v>1525179648</v>
+      </c>
+      <c r="E827" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F827" s="3" t="s">
+        <v>2622</v>
+      </c>
+      <c r="G827" s="3" t="s">
+        <v>2623</v>
+      </c>
+      <c r="H827" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I827" s="3">
+        <v>63</v>
+      </c>
+      <c r="J827" s="3"/>
+      <c r="K827" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L827" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M827" s="3" t="s">
+        <v>2609</v>
+      </c>
+      <c r="N827" s="3"/>
+    </row>
+    <row r="828" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A828" s="3" t="s">
+        <v>2624</v>
+      </c>
+      <c r="B828" s="3"/>
+      <c r="C828" s="3">
+        <v>730</v>
+      </c>
+      <c r="D828" s="3">
+        <v>1525309356</v>
+      </c>
+      <c r="E828" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F828" s="3" t="s">
+        <v>2625</v>
+      </c>
+      <c r="G828" s="3" t="s">
+        <v>2626</v>
+      </c>
+      <c r="H828" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I828" s="3">
+        <v>75</v>
+      </c>
+      <c r="J828" s="3">
+        <v>75</v>
+      </c>
+      <c r="K828" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L828" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M828" s="3" t="s">
+        <v>2627</v>
+      </c>
+      <c r="N828" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\PCS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7A345196-316B-40F4-9502-88927704B96B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{03BF7DF7-C7C8-4E42-9422-BBC01BFFFDFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6144" uniqueCount="2628">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6346" uniqueCount="2722">
   <si>
     <t>DRIVE ALERTS</t>
   </si>
@@ -7904,6 +7904,288 @@
   </si>
   <si>
     <t>05/04/26 11:46 EDT</t>
+  </si>
+  <si>
+    <t>05/04/26 18:31 EDT</t>
+  </si>
+  <si>
+    <t>34.992309, -116.578765</t>
+  </si>
+  <si>
+    <t>05/05/26 12:13 EDT</t>
+  </si>
+  <si>
+    <t>05/05/26 10:44 EDT</t>
+  </si>
+  <si>
+    <t>1.3mi SW of Midvale UT</t>
+  </si>
+  <si>
+    <t>40.597790, -111.903659</t>
+  </si>
+  <si>
+    <t>05/06/26 10:13 EDT</t>
+  </si>
+  <si>
+    <t>05/05/26 10:45 EDT</t>
+  </si>
+  <si>
+    <t>1.8mi S of Midvale UT</t>
+  </si>
+  <si>
+    <t>40.589421, -111.900989</t>
+  </si>
+  <si>
+    <t>05/06/26 10:06 EDT</t>
+  </si>
+  <si>
+    <t>05/05/26 12:27 EDT</t>
+  </si>
+  <si>
+    <t>1.8mi N of Salt Lake City UT</t>
+  </si>
+  <si>
+    <t>40.802136, -111.921127</t>
+  </si>
+  <si>
+    <t>05/06/26 10:10 EDT</t>
+  </si>
+  <si>
+    <t>05/05/26 12:55 EDT</t>
+  </si>
+  <si>
+    <t>2.3mi W of American Fork UT</t>
+  </si>
+  <si>
+    <t>40.390917, -111.835035</t>
+  </si>
+  <si>
+    <t>05/05/26 13:56 EDT</t>
+  </si>
+  <si>
+    <t>2.5mi W of Provo UT</t>
+  </si>
+  <si>
+    <t>40.241746, -111.692980</t>
+  </si>
+  <si>
+    <t>05/05/26 18:03 EDT</t>
+  </si>
+  <si>
+    <t>0.5mi SE of Lehi UT</t>
+  </si>
+  <si>
+    <t>40.410328, -111.863146</t>
+  </si>
+  <si>
+    <t>05/05/26 18:34 EDT</t>
+  </si>
+  <si>
+    <t>2.9mi W of South Salt Lake UT</t>
+  </si>
+  <si>
+    <t>40.708397, -111.953155</t>
+  </si>
+  <si>
+    <t>05/05/26 20:45 EDT</t>
+  </si>
+  <si>
+    <t>9.1mi E of North Las Vegas NV</t>
+  </si>
+  <si>
+    <t>36.324561, -114.931317</t>
+  </si>
+  <si>
+    <t>05/06/26 10:08 EDT</t>
+  </si>
+  <si>
+    <t>9mi E of North Las Vegas NV</t>
+  </si>
+  <si>
+    <t>36.323610, -114.933105</t>
+  </si>
+  <si>
+    <t>05/05/26 22:32 EDT</t>
+  </si>
+  <si>
+    <t>19.9mi W of Fruita CO</t>
+  </si>
+  <si>
+    <t>39.189148, -109.099721</t>
+  </si>
+  <si>
+    <t>05/06/26 01:26 EDT</t>
+  </si>
+  <si>
+    <t>2.3mi NW of Rialto CA</t>
+  </si>
+  <si>
+    <t>34.136698, -117.422527</t>
+  </si>
+  <si>
+    <t>05/06/26 20:47 EDT</t>
+  </si>
+  <si>
+    <t>28.3mi NW of Lexington NE</t>
+  </si>
+  <si>
+    <t>40.947850, -100.238141</t>
+  </si>
+  <si>
+    <t>05/07/26 09:24 EDT</t>
+  </si>
+  <si>
+    <t>05/06/26 21:50 EDT</t>
+  </si>
+  <si>
+    <t>18.7mi SE of Laramie WY</t>
+  </si>
+  <si>
+    <t>41.129585, -105.341294</t>
+  </si>
+  <si>
+    <t>05/07/26 08:43 EDT</t>
+  </si>
+  <si>
+    <t>0.1mi S of Kaysville UT</t>
+  </si>
+  <si>
+    <t>41.027243, -111.945786</t>
+  </si>
+  <si>
+    <t>05/08/26 14:07 EDT</t>
+  </si>
+  <si>
+    <t>05/07/26 11:18 EDT</t>
+  </si>
+  <si>
+    <t>0.4mi N of Sunset UT</t>
+  </si>
+  <si>
+    <t>41.145130, -112.025633</t>
+  </si>
+  <si>
+    <t>05/07/26 11:27 EDT</t>
+  </si>
+  <si>
+    <t>1.1mi NW of Murray UT</t>
+  </si>
+  <si>
+    <t>40.662069, -111.901158</t>
+  </si>
+  <si>
+    <t>05/07/26 11:39 EDT</t>
+  </si>
+  <si>
+    <t>0.6mi S of North Salt Lake UT</t>
+  </si>
+  <si>
+    <t>40.835269, -111.915732</t>
+  </si>
+  <si>
+    <t>05/07/26 12:18 EDT</t>
+  </si>
+  <si>
+    <t>1.4mi SE of Salt Lake City UT</t>
+  </si>
+  <si>
+    <t>40.760636, -111.915240</t>
+  </si>
+  <si>
+    <t>05/07/26 13:01 EDT</t>
+  </si>
+  <si>
+    <t>1.5mi SW of Springville UT</t>
+  </si>
+  <si>
+    <t>40.154297, -111.647000</t>
+  </si>
+  <si>
+    <t>05/07/26 19:29 EDT</t>
+  </si>
+  <si>
+    <t>2.5mi SW of Pleasant Grove UT</t>
+  </si>
+  <si>
+    <t>40.344143, -111.770891</t>
+  </si>
+  <si>
+    <t>05/08/26 10:44 EDT</t>
+  </si>
+  <si>
+    <t>0.3mi NW of South Salt Lake UT</t>
+  </si>
+  <si>
+    <t>40.707786, -111.903614</t>
+  </si>
+  <si>
+    <t>05/08/26 13:53 EDT</t>
+  </si>
+  <si>
+    <t>1.1mi NW of San Dimas CA</t>
+  </si>
+  <si>
+    <t>34.118167, -117.824776</t>
+  </si>
+  <si>
+    <t>05/08/26 13:54 EDT</t>
+  </si>
+  <si>
+    <t>1mi SW of San Dimas CA</t>
+  </si>
+  <si>
+    <t>34.095828, -117.819587</t>
+  </si>
+  <si>
+    <t>05/08/26 14:22 EDT</t>
+  </si>
+  <si>
+    <t>0.9mi W of West Valley City UT</t>
+  </si>
+  <si>
+    <t>40.690895, -112.029194</t>
+  </si>
+  <si>
+    <t>05/08/26 14:36 EDT</t>
+  </si>
+  <si>
+    <t>3.3mi NW of Temescal Valley CA</t>
+  </si>
+  <si>
+    <t>33.796382, -117.501342</t>
+  </si>
+  <si>
+    <t>3.2mi NW of Temescal Valley CA</t>
+  </si>
+  <si>
+    <t>33.795832, -117.500975</t>
+  </si>
+  <si>
+    <t>05/08/26 14:58 EDT</t>
+  </si>
+  <si>
+    <t>2.2mi SW of Provo UT</t>
+  </si>
+  <si>
+    <t>40.226278, -111.677744</t>
+  </si>
+  <si>
+    <t>05/08/26 16:36 EDT</t>
+  </si>
+  <si>
+    <t>10.1mi W of Green River WY</t>
+  </si>
+  <si>
+    <t>41.543450, -109.661388</t>
+  </si>
+  <si>
+    <t>05/08/26 20:25 EDT</t>
+  </si>
+  <si>
+    <t>1.4mi W of Orem UT</t>
+  </si>
+  <si>
+    <t>40.302933, -111.725986</t>
   </si>
 </sst>
 </file>
@@ -8265,7 +8547,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N828"/>
+  <dimension ref="A1:N858"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="14" width="15" customWidth="1"/>
@@ -39597,6 +39879,1126 @@
       </c>
       <c r="N828" s="3"/>
     </row>
+    <row r="829" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A829" s="3" t="s">
+        <v>2628</v>
+      </c>
+      <c r="B829" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C829" s="3">
+        <v>731</v>
+      </c>
+      <c r="D829" s="3">
+        <v>1526027579</v>
+      </c>
+      <c r="E829" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F829" s="3" t="s">
+        <v>1965</v>
+      </c>
+      <c r="G829" s="3" t="s">
+        <v>2629</v>
+      </c>
+      <c r="H829" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I829" s="3">
+        <v>65</v>
+      </c>
+      <c r="J829" s="3">
+        <v>70</v>
+      </c>
+      <c r="K829" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L829" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M829" s="3" t="s">
+        <v>2630</v>
+      </c>
+      <c r="N829" s="3"/>
+    </row>
+    <row r="830" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A830" s="3" t="s">
+        <v>2631</v>
+      </c>
+      <c r="B830" s="3"/>
+      <c r="C830" s="3">
+        <v>840</v>
+      </c>
+      <c r="D830" s="3">
+        <v>1526434783</v>
+      </c>
+      <c r="E830" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F830" s="3" t="s">
+        <v>2632</v>
+      </c>
+      <c r="G830" s="3" t="s">
+        <v>2633</v>
+      </c>
+      <c r="H830" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I830" s="3">
+        <v>63</v>
+      </c>
+      <c r="J830" s="3">
+        <v>70</v>
+      </c>
+      <c r="K830" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L830" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M830" s="3" t="s">
+        <v>2634</v>
+      </c>
+      <c r="N830" s="3"/>
+    </row>
+    <row r="831" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A831" s="3" t="s">
+        <v>2635</v>
+      </c>
+      <c r="B831" s="3"/>
+      <c r="C831" s="3">
+        <v>840</v>
+      </c>
+      <c r="D831" s="3">
+        <v>1526434770</v>
+      </c>
+      <c r="E831" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F831" s="3" t="s">
+        <v>2636</v>
+      </c>
+      <c r="G831" s="3" t="s">
+        <v>2637</v>
+      </c>
+      <c r="H831" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I831" s="3">
+        <v>61</v>
+      </c>
+      <c r="J831" s="3">
+        <v>70</v>
+      </c>
+      <c r="K831" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L831" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M831" s="3" t="s">
+        <v>2638</v>
+      </c>
+      <c r="N831" s="3"/>
+    </row>
+    <row r="832" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A832" s="3" t="s">
+        <v>2639</v>
+      </c>
+      <c r="B832" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="C832" s="3">
+        <v>375</v>
+      </c>
+      <c r="D832" s="3">
+        <v>1526536959</v>
+      </c>
+      <c r="E832" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F832" s="3" t="s">
+        <v>2640</v>
+      </c>
+      <c r="G832" s="3" t="s">
+        <v>2641</v>
+      </c>
+      <c r="H832" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I832" s="3">
+        <v>57</v>
+      </c>
+      <c r="J832" s="3">
+        <v>70</v>
+      </c>
+      <c r="K832" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L832" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M832" s="3" t="s">
+        <v>2642</v>
+      </c>
+      <c r="N832" s="3"/>
+    </row>
+    <row r="833" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A833" s="3" t="s">
+        <v>2643</v>
+      </c>
+      <c r="B833" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="C833" s="3">
+        <v>375</v>
+      </c>
+      <c r="D833" s="3">
+        <v>1526565872</v>
+      </c>
+      <c r="E833" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F833" s="3" t="s">
+        <v>2644</v>
+      </c>
+      <c r="G833" s="3" t="s">
+        <v>2645</v>
+      </c>
+      <c r="H833" s="3"/>
+      <c r="I833" s="3">
+        <v>71</v>
+      </c>
+      <c r="J833" s="3">
+        <v>70</v>
+      </c>
+      <c r="K833" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L833" s="3"/>
+      <c r="M833" s="3"/>
+      <c r="N833" s="3"/>
+    </row>
+    <row r="834" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A834" s="3" t="s">
+        <v>2646</v>
+      </c>
+      <c r="B834" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="C834" s="3">
+        <v>375</v>
+      </c>
+      <c r="D834" s="3">
+        <v>1526628324</v>
+      </c>
+      <c r="E834" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F834" s="3" t="s">
+        <v>2647</v>
+      </c>
+      <c r="G834" s="3" t="s">
+        <v>2648</v>
+      </c>
+      <c r="H834" s="3"/>
+      <c r="I834" s="3">
+        <v>70</v>
+      </c>
+      <c r="J834" s="3">
+        <v>70</v>
+      </c>
+      <c r="K834" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L834" s="3"/>
+      <c r="M834" s="3"/>
+      <c r="N834" s="3"/>
+    </row>
+    <row r="835" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A835" s="3" t="s">
+        <v>2649</v>
+      </c>
+      <c r="B835" s="3"/>
+      <c r="C835" s="3">
+        <v>338</v>
+      </c>
+      <c r="D835" s="3">
+        <v>1526860721</v>
+      </c>
+      <c r="E835" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F835" s="3" t="s">
+        <v>2650</v>
+      </c>
+      <c r="G835" s="3" t="s">
+        <v>2651</v>
+      </c>
+      <c r="H835" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I835" s="3">
+        <v>81</v>
+      </c>
+      <c r="J835" s="3">
+        <v>70</v>
+      </c>
+      <c r="K835" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L835" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M835" s="3" t="s">
+        <v>2642</v>
+      </c>
+      <c r="N835" s="3"/>
+    </row>
+    <row r="836" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A836" s="3" t="s">
+        <v>2652</v>
+      </c>
+      <c r="B836" s="3"/>
+      <c r="C836" s="3">
+        <v>338</v>
+      </c>
+      <c r="D836" s="3">
+        <v>1526883467</v>
+      </c>
+      <c r="E836" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F836" s="3" t="s">
+        <v>2653</v>
+      </c>
+      <c r="G836" s="3" t="s">
+        <v>2654</v>
+      </c>
+      <c r="H836" s="3"/>
+      <c r="I836" s="3">
+        <v>64</v>
+      </c>
+      <c r="J836" s="3">
+        <v>70</v>
+      </c>
+      <c r="K836" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L836" s="3"/>
+      <c r="M836" s="3"/>
+      <c r="N836" s="3"/>
+    </row>
+    <row r="837" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A837" s="3" t="s">
+        <v>2655</v>
+      </c>
+      <c r="B837" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C837" s="3">
+        <v>210</v>
+      </c>
+      <c r="D837" s="3">
+        <v>1526953556</v>
+      </c>
+      <c r="E837" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F837" s="3" t="s">
+        <v>2656</v>
+      </c>
+      <c r="G837" s="3" t="s">
+        <v>2657</v>
+      </c>
+      <c r="H837" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I837" s="3">
+        <v>75</v>
+      </c>
+      <c r="J837" s="3">
+        <v>75</v>
+      </c>
+      <c r="K837" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L837" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M837" s="3" t="s">
+        <v>2658</v>
+      </c>
+      <c r="N837" s="3"/>
+    </row>
+    <row r="838" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A838" s="3" t="s">
+        <v>2655</v>
+      </c>
+      <c r="B838" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C838" s="3">
+        <v>210</v>
+      </c>
+      <c r="D838" s="3">
+        <v>1526953548</v>
+      </c>
+      <c r="E838" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F838" s="3" t="s">
+        <v>2659</v>
+      </c>
+      <c r="G838" s="3" t="s">
+        <v>2660</v>
+      </c>
+      <c r="H838" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I838" s="3">
+        <v>75</v>
+      </c>
+      <c r="J838" s="3">
+        <v>75</v>
+      </c>
+      <c r="K838" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L838" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M838" s="3" t="s">
+        <v>2638</v>
+      </c>
+      <c r="N838" s="3"/>
+    </row>
+    <row r="839" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A839" s="3" t="s">
+        <v>2661</v>
+      </c>
+      <c r="B839" s="3"/>
+      <c r="C839" s="3">
+        <v>459</v>
+      </c>
+      <c r="D839" s="3">
+        <v>1526989429</v>
+      </c>
+      <c r="E839" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F839" s="3" t="s">
+        <v>2662</v>
+      </c>
+      <c r="G839" s="3" t="s">
+        <v>2663</v>
+      </c>
+      <c r="H839" s="3"/>
+      <c r="I839" s="3">
+        <v>72</v>
+      </c>
+      <c r="J839" s="3">
+        <v>80</v>
+      </c>
+      <c r="K839" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L839" s="3"/>
+      <c r="M839" s="3"/>
+      <c r="N839" s="3"/>
+    </row>
+    <row r="840" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A840" s="3" t="s">
+        <v>2664</v>
+      </c>
+      <c r="B840" s="3"/>
+      <c r="C840" s="3">
+        <v>926</v>
+      </c>
+      <c r="D840" s="3">
+        <v>1527020957</v>
+      </c>
+      <c r="E840" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F840" s="3" t="s">
+        <v>2665</v>
+      </c>
+      <c r="G840" s="3" t="s">
+        <v>2666</v>
+      </c>
+      <c r="H840" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I840" s="3">
+        <v>62</v>
+      </c>
+      <c r="J840" s="3">
+        <v>65</v>
+      </c>
+      <c r="K840" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L840" s="3"/>
+      <c r="M840" s="3"/>
+      <c r="N840" s="3"/>
+    </row>
+    <row r="841" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A841" s="3" t="s">
+        <v>2667</v>
+      </c>
+      <c r="B841" s="3"/>
+      <c r="C841" s="3">
+        <v>459</v>
+      </c>
+      <c r="D841" s="3">
+        <v>1527810190</v>
+      </c>
+      <c r="E841" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F841" s="3" t="s">
+        <v>2668</v>
+      </c>
+      <c r="G841" s="3" t="s">
+        <v>2669</v>
+      </c>
+      <c r="H841" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I841" s="3">
+        <v>71</v>
+      </c>
+      <c r="J841" s="3">
+        <v>75</v>
+      </c>
+      <c r="K841" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L841" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M841" s="3" t="s">
+        <v>2670</v>
+      </c>
+      <c r="N841" s="3"/>
+    </row>
+    <row r="842" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A842" s="3" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B842" s="3"/>
+      <c r="C842" s="3">
+        <v>209</v>
+      </c>
+      <c r="D842" s="3">
+        <v>1527833709</v>
+      </c>
+      <c r="E842" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F842" s="3" t="s">
+        <v>2672</v>
+      </c>
+      <c r="G842" s="3" t="s">
+        <v>2673</v>
+      </c>
+      <c r="H842" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I842" s="3">
+        <v>73</v>
+      </c>
+      <c r="J842" s="3">
+        <v>75</v>
+      </c>
+      <c r="K842" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L842" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M842" s="3" t="s">
+        <v>2670</v>
+      </c>
+      <c r="N842" s="3"/>
+    </row>
+    <row r="843" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A843" s="3" t="s">
+        <v>2674</v>
+      </c>
+      <c r="B843" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="C843" s="3">
+        <v>375</v>
+      </c>
+      <c r="D843" s="3">
+        <v>1528048280</v>
+      </c>
+      <c r="E843" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F843" s="3" t="s">
+        <v>2675</v>
+      </c>
+      <c r="G843" s="3" t="s">
+        <v>2676</v>
+      </c>
+      <c r="H843" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I843" s="3">
+        <v>68</v>
+      </c>
+      <c r="J843" s="3">
+        <v>70</v>
+      </c>
+      <c r="K843" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L843" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M843" s="3" t="s">
+        <v>2677</v>
+      </c>
+      <c r="N843" s="3"/>
+    </row>
+    <row r="844" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A844" s="3" t="s">
+        <v>2678</v>
+      </c>
+      <c r="B844" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="C844" s="3">
+        <v>375</v>
+      </c>
+      <c r="D844" s="3">
+        <v>1528203266</v>
+      </c>
+      <c r="E844" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F844" s="3" t="s">
+        <v>2679</v>
+      </c>
+      <c r="G844" s="3" t="s">
+        <v>2680</v>
+      </c>
+      <c r="H844" s="3"/>
+      <c r="I844" s="3">
+        <v>69</v>
+      </c>
+      <c r="J844" s="3">
+        <v>70</v>
+      </c>
+      <c r="K844" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L844" s="3"/>
+      <c r="M844" s="3"/>
+      <c r="N844" s="3"/>
+    </row>
+    <row r="845" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A845" s="3" t="s">
+        <v>2681</v>
+      </c>
+      <c r="B845" s="3"/>
+      <c r="C845" s="3">
+        <v>344</v>
+      </c>
+      <c r="D845" s="3">
+        <v>1528211571</v>
+      </c>
+      <c r="E845" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F845" s="3" t="s">
+        <v>2682</v>
+      </c>
+      <c r="G845" s="3" t="s">
+        <v>2683</v>
+      </c>
+      <c r="H845" s="3"/>
+      <c r="I845" s="3">
+        <v>65</v>
+      </c>
+      <c r="J845" s="3">
+        <v>70</v>
+      </c>
+      <c r="K845" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L845" s="3"/>
+      <c r="M845" s="3"/>
+      <c r="N845" s="3"/>
+    </row>
+    <row r="846" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A846" s="3" t="s">
+        <v>2684</v>
+      </c>
+      <c r="B846" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="C846" s="3">
+        <v>375</v>
+      </c>
+      <c r="D846" s="3">
+        <v>1528225514</v>
+      </c>
+      <c r="E846" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F846" s="3" t="s">
+        <v>2685</v>
+      </c>
+      <c r="G846" s="3" t="s">
+        <v>2686</v>
+      </c>
+      <c r="H846" s="3"/>
+      <c r="I846" s="3">
+        <v>59</v>
+      </c>
+      <c r="J846" s="3">
+        <v>70</v>
+      </c>
+      <c r="K846" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L846" s="3"/>
+      <c r="M846" s="3"/>
+      <c r="N846" s="3"/>
+    </row>
+    <row r="847" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A847" s="3" t="s">
+        <v>2687</v>
+      </c>
+      <c r="B847" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="C847" s="3">
+        <v>375</v>
+      </c>
+      <c r="D847" s="3">
+        <v>1528268409</v>
+      </c>
+      <c r="E847" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F847" s="3" t="s">
+        <v>2688</v>
+      </c>
+      <c r="G847" s="3" t="s">
+        <v>2689</v>
+      </c>
+      <c r="H847" s="3"/>
+      <c r="I847" s="3">
+        <v>58</v>
+      </c>
+      <c r="J847" s="3"/>
+      <c r="K847" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L847" s="3"/>
+      <c r="M847" s="3"/>
+      <c r="N847" s="3"/>
+    </row>
+    <row r="848" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A848" s="3" t="s">
+        <v>2690</v>
+      </c>
+      <c r="B848" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="C848" s="3">
+        <v>375</v>
+      </c>
+      <c r="D848" s="3">
+        <v>1528313816</v>
+      </c>
+      <c r="E848" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F848" s="3" t="s">
+        <v>2691</v>
+      </c>
+      <c r="G848" s="3" t="s">
+        <v>2692</v>
+      </c>
+      <c r="H848" s="3"/>
+      <c r="I848" s="3">
+        <v>61</v>
+      </c>
+      <c r="J848" s="3">
+        <v>70</v>
+      </c>
+      <c r="K848" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L848" s="3"/>
+      <c r="M848" s="3"/>
+      <c r="N848" s="3"/>
+    </row>
+    <row r="849" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A849" s="3" t="s">
+        <v>2693</v>
+      </c>
+      <c r="B849" s="3"/>
+      <c r="C849" s="3">
+        <v>926</v>
+      </c>
+      <c r="D849" s="3">
+        <v>1528666896</v>
+      </c>
+      <c r="E849" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F849" s="3" t="s">
+        <v>2694</v>
+      </c>
+      <c r="G849" s="3" t="s">
+        <v>2695</v>
+      </c>
+      <c r="H849" s="3"/>
+      <c r="I849" s="3">
+        <v>35</v>
+      </c>
+      <c r="J849" s="3"/>
+      <c r="K849" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L849" s="3"/>
+      <c r="M849" s="3"/>
+      <c r="N849" s="3"/>
+    </row>
+    <row r="850" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A850" s="3" t="s">
+        <v>2696</v>
+      </c>
+      <c r="B850" s="3"/>
+      <c r="C850" s="3">
+        <v>344</v>
+      </c>
+      <c r="D850" s="3">
+        <v>1529044819</v>
+      </c>
+      <c r="E850" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F850" s="3" t="s">
+        <v>2697</v>
+      </c>
+      <c r="G850" s="3" t="s">
+        <v>2698</v>
+      </c>
+      <c r="H850" s="3"/>
+      <c r="I850" s="3">
+        <v>66</v>
+      </c>
+      <c r="J850" s="3">
+        <v>70</v>
+      </c>
+      <c r="K850" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L850" s="3"/>
+      <c r="M850" s="3"/>
+      <c r="N850" s="3"/>
+    </row>
+    <row r="851" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A851" s="3" t="s">
+        <v>2699</v>
+      </c>
+      <c r="B851" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C851" s="3">
+        <v>840</v>
+      </c>
+      <c r="D851" s="3">
+        <v>1529233544</v>
+      </c>
+      <c r="E851" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F851" s="3" t="s">
+        <v>2700</v>
+      </c>
+      <c r="G851" s="3" t="s">
+        <v>2701</v>
+      </c>
+      <c r="H851" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I851" s="3">
+        <v>58</v>
+      </c>
+      <c r="J851" s="3">
+        <v>65</v>
+      </c>
+      <c r="K851" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L851" s="3"/>
+      <c r="M851" s="3"/>
+      <c r="N851" s="3"/>
+    </row>
+    <row r="852" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A852" s="3" t="s">
+        <v>2702</v>
+      </c>
+      <c r="B852" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C852" s="3">
+        <v>840</v>
+      </c>
+      <c r="D852" s="3">
+        <v>1529235207</v>
+      </c>
+      <c r="E852" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F852" s="3" t="s">
+        <v>2703</v>
+      </c>
+      <c r="G852" s="3" t="s">
+        <v>2704</v>
+      </c>
+      <c r="H852" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I852" s="3">
+        <v>62</v>
+      </c>
+      <c r="J852" s="3">
+        <v>65</v>
+      </c>
+      <c r="K852" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L852" s="3"/>
+      <c r="M852" s="3"/>
+      <c r="N852" s="3"/>
+    </row>
+    <row r="853" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A853" s="3" t="s">
+        <v>2705</v>
+      </c>
+      <c r="B853" s="3"/>
+      <c r="C853" s="3">
+        <v>344</v>
+      </c>
+      <c r="D853" s="3">
+        <v>1529263574</v>
+      </c>
+      <c r="E853" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F853" s="3" t="s">
+        <v>2706</v>
+      </c>
+      <c r="G853" s="3" t="s">
+        <v>2707</v>
+      </c>
+      <c r="H853" s="3"/>
+      <c r="I853" s="3">
+        <v>56</v>
+      </c>
+      <c r="J853" s="3">
+        <v>65</v>
+      </c>
+      <c r="K853" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L853" s="3"/>
+      <c r="M853" s="3"/>
+      <c r="N853" s="3"/>
+    </row>
+    <row r="854" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A854" s="3" t="s">
+        <v>2708</v>
+      </c>
+      <c r="B854" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C854" s="3">
+        <v>840</v>
+      </c>
+      <c r="D854" s="3">
+        <v>1529276951</v>
+      </c>
+      <c r="E854" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F854" s="3" t="s">
+        <v>2709</v>
+      </c>
+      <c r="G854" s="3" t="s">
+        <v>2710</v>
+      </c>
+      <c r="H854" s="3"/>
+      <c r="I854" s="3">
+        <v>55</v>
+      </c>
+      <c r="J854" s="3">
+        <v>70</v>
+      </c>
+      <c r="K854" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L854" s="3"/>
+      <c r="M854" s="3"/>
+      <c r="N854" s="3"/>
+    </row>
+    <row r="855" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A855" s="3" t="s">
+        <v>2708</v>
+      </c>
+      <c r="B855" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C855" s="3">
+        <v>840</v>
+      </c>
+      <c r="D855" s="3">
+        <v>1529276966</v>
+      </c>
+      <c r="E855" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F855" s="3" t="s">
+        <v>2711</v>
+      </c>
+      <c r="G855" s="3" t="s">
+        <v>2712</v>
+      </c>
+      <c r="H855" s="3"/>
+      <c r="I855" s="3">
+        <v>56</v>
+      </c>
+      <c r="J855" s="3">
+        <v>70</v>
+      </c>
+      <c r="K855" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L855" s="3"/>
+      <c r="M855" s="3"/>
+      <c r="N855" s="3"/>
+    </row>
+    <row r="856" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A856" s="3" t="s">
+        <v>2713</v>
+      </c>
+      <c r="B856" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C856" s="3">
+        <v>375</v>
+      </c>
+      <c r="D856" s="3">
+        <v>1529298138</v>
+      </c>
+      <c r="E856" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F856" s="3" t="s">
+        <v>2714</v>
+      </c>
+      <c r="G856" s="3" t="s">
+        <v>2715</v>
+      </c>
+      <c r="H856" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I856" s="3">
+        <v>64</v>
+      </c>
+      <c r="J856" s="3">
+        <v>70</v>
+      </c>
+      <c r="K856" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L856" s="3"/>
+      <c r="M856" s="3"/>
+      <c r="N856" s="3"/>
+    </row>
+    <row r="857" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A857" s="3" t="s">
+        <v>2716</v>
+      </c>
+      <c r="B857" s="3"/>
+      <c r="C857" s="3">
+        <v>459</v>
+      </c>
+      <c r="D857" s="3">
+        <v>1529391018</v>
+      </c>
+      <c r="E857" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F857" s="3" t="s">
+        <v>2717</v>
+      </c>
+      <c r="G857" s="3" t="s">
+        <v>2718</v>
+      </c>
+      <c r="H857" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I857" s="3">
+        <v>70</v>
+      </c>
+      <c r="J857" s="3">
+        <v>75</v>
+      </c>
+      <c r="K857" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L857" s="3"/>
+      <c r="M857" s="3"/>
+      <c r="N857" s="3"/>
+    </row>
+    <row r="858" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A858" s="3" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B858" s="3"/>
+      <c r="C858" s="3">
+        <v>672</v>
+      </c>
+      <c r="D858" s="3">
+        <v>1529533048</v>
+      </c>
+      <c r="E858" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F858" s="3" t="s">
+        <v>2720</v>
+      </c>
+      <c r="G858" s="3" t="s">
+        <v>2721</v>
+      </c>
+      <c r="H858" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I858" s="3">
+        <v>72</v>
+      </c>
+      <c r="J858" s="3">
+        <v>70</v>
+      </c>
+      <c r="K858" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L858" s="3"/>
+      <c r="M858" s="3"/>
+      <c r="N858" s="3"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\PCS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6B2AB86F-13E1-4405-9346-1852C879566F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{05AA246D-06B9-478D-BD4B-4C7CC1A6D907}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6726" uniqueCount="2885">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7162" uniqueCount="3060">
   <si>
     <t>DRIVE ALERTS</t>
   </si>
@@ -8542,6 +8542,9 @@
     <t>40.723447, -111.531975</t>
   </si>
   <si>
+    <t>05/18/26 11:01 EDT</t>
+  </si>
+  <si>
     <t>0.7mi S of Lamar CO</t>
   </si>
   <si>
@@ -8578,6 +8581,9 @@
     <t>40.747298, -112.006390</t>
   </si>
   <si>
+    <t>05/18/26 11:17 EDT</t>
+  </si>
+  <si>
     <t>05/15/26 17:22 EDT</t>
   </si>
   <si>
@@ -8668,6 +8674,9 @@
     <t>41.782660, -107.213821</t>
   </si>
   <si>
+    <t>05/18/26 11:12 EDT</t>
+  </si>
+  <si>
     <t>05/17/26 06:55 EDT</t>
   </si>
   <si>
@@ -8675,6 +8684,522 @@
   </si>
   <si>
     <t>37.203951, -108.684845</t>
+  </si>
+  <si>
+    <t>05/18/26 11:06 EDT</t>
+  </si>
+  <si>
+    <t>05/17/26 12:55 EDT</t>
+  </si>
+  <si>
+    <t>1.7mi SW of Orem UT</t>
+  </si>
+  <si>
+    <t>40.283336, -111.725317</t>
+  </si>
+  <si>
+    <t>05/18/26 11:15 EDT</t>
+  </si>
+  <si>
+    <t>05/17/26 16:18 EDT</t>
+  </si>
+  <si>
+    <t>1.4mi SW of Payson UT</t>
+  </si>
+  <si>
+    <t>40.026118, -111.761536</t>
+  </si>
+  <si>
+    <t>05/17/26 16:34 EDT</t>
+  </si>
+  <si>
+    <t>2.9mi N of Nephi UT</t>
+  </si>
+  <si>
+    <t>39.748506, -111.835459</t>
+  </si>
+  <si>
+    <t>05/17/26 19:24 EDT</t>
+  </si>
+  <si>
+    <t>38.948079, -112.353215</t>
+  </si>
+  <si>
+    <t>05/17/26 21:46 EDT</t>
+  </si>
+  <si>
+    <t>42.5mi NW of Richfield UT</t>
+  </si>
+  <si>
+    <t>39.301596, -112.472268</t>
+  </si>
+  <si>
+    <t>05/17/26 22:22 EDT</t>
+  </si>
+  <si>
+    <t>21mi W of Richfield UT</t>
+  </si>
+  <si>
+    <t>38.848317, -112.466430</t>
+  </si>
+  <si>
+    <t>05/18/26 00:18 EDT</t>
+  </si>
+  <si>
+    <t>1.2mi NE of Cedar City UT</t>
+  </si>
+  <si>
+    <t>37.692620, -113.078042</t>
+  </si>
+  <si>
+    <t>05/18/26 00:28 EDT</t>
+  </si>
+  <si>
+    <t>6.7mi SW of Cedar City UT</t>
+  </si>
+  <si>
+    <t>37.601909, -113.162096</t>
+  </si>
+  <si>
+    <t>05/18/26 09:41 EDT</t>
+  </si>
+  <si>
+    <t>2.5mi SW of Salt Lake City UT</t>
+  </si>
+  <si>
+    <t>40.758085, -111.972055</t>
+  </si>
+  <si>
+    <t>05/19/26 10:56 EDT</t>
+  </si>
+  <si>
+    <t>05/18/26 09:51 EDT</t>
+  </si>
+  <si>
+    <t>18.7mi NW of Richfield UT</t>
+  </si>
+  <si>
+    <t>38.939127, -112.355348</t>
+  </si>
+  <si>
+    <t>05/18/26 10:19 EDT</t>
+  </si>
+  <si>
+    <t>1.1mi N of Charter Oak CA</t>
+  </si>
+  <si>
+    <t>34.117495, -117.850370</t>
+  </si>
+  <si>
+    <t>05/19/26 10:59 EDT</t>
+  </si>
+  <si>
+    <t>05/18/26 13:24 EDT</t>
+  </si>
+  <si>
+    <t>41.9mi SW of Richfield UT</t>
+  </si>
+  <si>
+    <t>38.348063, -112.659722</t>
+  </si>
+  <si>
+    <t>05/19/26 10:55 EDT</t>
+  </si>
+  <si>
+    <t>05/18/26 15:16 EDT</t>
+  </si>
+  <si>
+    <t>2.6mi NW of South Salt Lake UT</t>
+  </si>
+  <si>
+    <t>40.724148, -111.941473</t>
+  </si>
+  <si>
+    <t>05/18/26 15:50 EDT</t>
+  </si>
+  <si>
+    <t>10.8mi W of Kearney NE</t>
+  </si>
+  <si>
+    <t>40.680746, -99.286836</t>
+  </si>
+  <si>
+    <t>05/18/26 16:31 EDT</t>
+  </si>
+  <si>
+    <t>40.743226, -111.991552</t>
+  </si>
+  <si>
+    <t>05/18/26 16:38 EDT</t>
+  </si>
+  <si>
+    <t>3mi W of South Salt Lake UT</t>
+  </si>
+  <si>
+    <t>40.715461, -111.953990</t>
+  </si>
+  <si>
+    <t>05/18/26 16:49 EDT</t>
+  </si>
+  <si>
+    <t>40.566729, -111.899925</t>
+  </si>
+  <si>
+    <t>05/18/26 16:59 EDT</t>
+  </si>
+  <si>
+    <t>0.8mi NW of Lehi UT</t>
+  </si>
+  <si>
+    <t>40.423209, -111.881833</t>
+  </si>
+  <si>
+    <t>05/18/26 20:49 EDT</t>
+  </si>
+  <si>
+    <t>2.5mi NE of Payson UT</t>
+  </si>
+  <si>
+    <t>40.068734, -111.719464</t>
+  </si>
+  <si>
+    <t>05/19/26 10:58 EDT</t>
+  </si>
+  <si>
+    <t>05/18/26 20:51 EDT</t>
+  </si>
+  <si>
+    <t>2.8mi NW of Salem UT</t>
+  </si>
+  <si>
+    <t>40.089004, -111.698535</t>
+  </si>
+  <si>
+    <t>05/19/26 10:57 EDT</t>
+  </si>
+  <si>
+    <t>05/19/26 02:30 EDT</t>
+  </si>
+  <si>
+    <t>1.9mi W of Washington UT</t>
+  </si>
+  <si>
+    <t>37.120307, -113.520624</t>
+  </si>
+  <si>
+    <t>05/19/26 02:51 EDT</t>
+  </si>
+  <si>
+    <t>13.2mi N of Hurricane UT</t>
+  </si>
+  <si>
+    <t>37.330960, -113.282043</t>
+  </si>
+  <si>
+    <t>05/19/26 03:11 EDT</t>
+  </si>
+  <si>
+    <t>9.2mi SW of Cedar City UT</t>
+  </si>
+  <si>
+    <t>37.570145, -113.183717</t>
+  </si>
+  <si>
+    <t>05/19/26 09:06 EDT</t>
+  </si>
+  <si>
+    <t>7.1mi NW of Evergreen CO</t>
+  </si>
+  <si>
+    <t>39.720703, -105.407978</t>
+  </si>
+  <si>
+    <t>40.713510, -111.953959</t>
+  </si>
+  <si>
+    <t>05/19/26 09:32 EDT</t>
+  </si>
+  <si>
+    <t>40.114569, -111.731761</t>
+  </si>
+  <si>
+    <t>05/20/26 17:43 EDT</t>
+  </si>
+  <si>
+    <t>05/19/26 11:33 EDT</t>
+  </si>
+  <si>
+    <t>11.7mi S of Richland Center WI</t>
+  </si>
+  <si>
+    <t>43.182469, -90.301863</t>
+  </si>
+  <si>
+    <t>05/19/26 17:24 EDT</t>
+  </si>
+  <si>
+    <t>35.926301, -115.195602</t>
+  </si>
+  <si>
+    <t>05/20/26 17:42 EDT</t>
+  </si>
+  <si>
+    <t>05/19/26 17:27 EDT</t>
+  </si>
+  <si>
+    <t>1.2mi NW of Salt Lake City UT</t>
+  </si>
+  <si>
+    <t>40.788196, -111.949317</t>
+  </si>
+  <si>
+    <t>05/20/26 17:48 EDT</t>
+  </si>
+  <si>
+    <t>05/19/26 21:31 EDT</t>
+  </si>
+  <si>
+    <t>3.2mi NE of Enterprise NV</t>
+  </si>
+  <si>
+    <t>36.034851, -115.180636</t>
+  </si>
+  <si>
+    <t>05/20/26 17:41 EDT</t>
+  </si>
+  <si>
+    <t>05/19/26 21:44 EDT</t>
+  </si>
+  <si>
+    <t>5mi NW of Sunrise Manor NV</t>
+  </si>
+  <si>
+    <t>36.212688, -115.127598</t>
+  </si>
+  <si>
+    <t>05/19/26 21:49 EDT</t>
+  </si>
+  <si>
+    <t>37.910278, -112.778212</t>
+  </si>
+  <si>
+    <t>05/20/26 17:46 EDT</t>
+  </si>
+  <si>
+    <t>05/20/26 14:32 EDT</t>
+  </si>
+  <si>
+    <t>20.7mi W of Richfield UT</t>
+  </si>
+  <si>
+    <t>38.855820, -112.457512</t>
+  </si>
+  <si>
+    <t>05/21/26 09:20 EDT</t>
+  </si>
+  <si>
+    <t>05/20/26 15:09 EDT</t>
+  </si>
+  <si>
+    <t>12.3mi SE of Castle Rock CO</t>
+  </si>
+  <si>
+    <t>39.244414, -104.697735</t>
+  </si>
+  <si>
+    <t>05/21/26 09:19 EDT</t>
+  </si>
+  <si>
+    <t>05/20/26 18:22 EDT</t>
+  </si>
+  <si>
+    <t>17.6mi N of Hurricane UT</t>
+  </si>
+  <si>
+    <t>37.388235, -113.245497</t>
+  </si>
+  <si>
+    <t>05/20/26 22:20 EDT</t>
+  </si>
+  <si>
+    <t>38.949650, -112.352962</t>
+  </si>
+  <si>
+    <t>05/21/26 09:09 EDT</t>
+  </si>
+  <si>
+    <t>2mi N of Four Corners MT</t>
+  </si>
+  <si>
+    <t>45.698047, -111.185290</t>
+  </si>
+  <si>
+    <t>05/21/26 13:05 EDT</t>
+  </si>
+  <si>
+    <t>36.1mi S of Enterprise NV</t>
+  </si>
+  <si>
+    <t>35.514615, -115.432570</t>
+  </si>
+  <si>
+    <t>05/22/26 21:46 EDT</t>
+  </si>
+  <si>
+    <t>05/21/26 14:14 EDT</t>
+  </si>
+  <si>
+    <t>21.3mi S of Arvin CA</t>
+  </si>
+  <si>
+    <t>34.895235, -118.918923</t>
+  </si>
+  <si>
+    <t>05/22/26 10:05 EDT</t>
+  </si>
+  <si>
+    <t>1.5mi NE of Oak Hills CA</t>
+  </si>
+  <si>
+    <t>34.407858, -117.396365</t>
+  </si>
+  <si>
+    <t>05/22/26 15:11 EDT</t>
+  </si>
+  <si>
+    <t>2mi NE of St. George UT</t>
+  </si>
+  <si>
+    <t>37.102470, -113.560743</t>
+  </si>
+  <si>
+    <t>05/22/26 19:20 EDT</t>
+  </si>
+  <si>
+    <t>1.7mi NW of South Salt Lake UT</t>
+  </si>
+  <si>
+    <t>40.724346, -111.918962</t>
+  </si>
+  <si>
+    <t>05/22/26 19:21 EDT</t>
+  </si>
+  <si>
+    <t>1.8mi NW of South Salt Lake UT</t>
+  </si>
+  <si>
+    <t>40.724446, -111.922227</t>
+  </si>
+  <si>
+    <t>05/22/26 21:45 EDT</t>
+  </si>
+  <si>
+    <t>05/23/26 04:18 EDT</t>
+  </si>
+  <si>
+    <t>50.9mi W of Tucumcari NM</t>
+  </si>
+  <si>
+    <t>34.978815, -104.574395</t>
+  </si>
+  <si>
+    <t>05/23/26 08:54 EDT</t>
+  </si>
+  <si>
+    <t>2.1mi NW of Lehi UT</t>
+  </si>
+  <si>
+    <t>40.437135, -111.896649</t>
+  </si>
+  <si>
+    <t>1.9mi NW of Lehi UT</t>
+  </si>
+  <si>
+    <t>40.435520, -111.895107</t>
+  </si>
+  <si>
+    <t>05/23/26 12:05 EDT</t>
+  </si>
+  <si>
+    <t>1.9mi SW of Payson UT</t>
+  </si>
+  <si>
+    <t>40.014026, -111.762348</t>
+  </si>
+  <si>
+    <t>05/23/26 13:35 EDT</t>
+  </si>
+  <si>
+    <t>0.6mi S of Santaquin UT</t>
+  </si>
+  <si>
+    <t>39.962616, -111.789863</t>
+  </si>
+  <si>
+    <t>05/23/26 13:44 EDT</t>
+  </si>
+  <si>
+    <t>3.8mi SW of Salt Lake City UT</t>
+  </si>
+  <si>
+    <t>40.744391, -111.989220</t>
+  </si>
+  <si>
+    <t>05/23/26 18:47 EDT</t>
+  </si>
+  <si>
+    <t>40.091048, -111.597141</t>
+  </si>
+  <si>
+    <t>05/24/26 00:43 EDT</t>
+  </si>
+  <si>
+    <t>36.706798, -101.446363</t>
+  </si>
+  <si>
+    <t>05/24/26 02:40 EDT</t>
+  </si>
+  <si>
+    <t>64.8mi S of Lamar CO</t>
+  </si>
+  <si>
+    <t>37.136927, -102.603867</t>
+  </si>
+  <si>
+    <t>05/24/26 03:01 EDT</t>
+  </si>
+  <si>
+    <t>44.8mi S of Lamar CO</t>
+  </si>
+  <si>
+    <t>37.425056, -102.616641</t>
+  </si>
+  <si>
+    <t>05/24/26 03:21 EDT</t>
+  </si>
+  <si>
+    <t>23.1mi S of Lamar CO</t>
+  </si>
+  <si>
+    <t>37.739408, -102.602364</t>
+  </si>
+  <si>
+    <t>05/24/26 03:42 EDT</t>
+  </si>
+  <si>
+    <t>1.3mi S of Lamar CO</t>
+  </si>
+  <si>
+    <t>38.055868, -102.616589</t>
+  </si>
+  <si>
+    <t>05/24/26 04:02 EDT</t>
+  </si>
+  <si>
+    <t>12.6mi NW of Lamar CO</t>
+  </si>
+  <si>
+    <t>38.235447, -102.723983</t>
   </si>
 </sst>
 </file>
@@ -9036,7 +9561,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N912"/>
+  <dimension ref="A1:N968"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="14" width="15" customWidth="1"/>
@@ -42916,7 +43441,9 @@
       <c r="G896" s="3" t="s">
         <v>2839</v>
       </c>
-      <c r="H896" s="3"/>
+      <c r="H896" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="I896" s="3">
         <v>64</v>
       </c>
@@ -42924,10 +43451,14 @@
         <v>70</v>
       </c>
       <c r="K896" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L896" s="3"/>
-      <c r="M896" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L896" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M896" s="3" t="s">
+        <v>2840</v>
+      </c>
       <c r="N896" s="3"/>
     </row>
     <row r="897" spans="1:14" x14ac:dyDescent="0.3">
@@ -42945,10 +43476,10 @@
         <v>85</v>
       </c>
       <c r="F897" s="3" t="s">
-        <v>2840</v>
+        <v>2841</v>
       </c>
       <c r="G897" s="3" t="s">
-        <v>2841</v>
+        <v>2842</v>
       </c>
       <c r="H897" s="3" t="s">
         <v>98</v>
@@ -42968,7 +43499,7 @@
     </row>
     <row r="898" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A898" s="3" t="s">
-        <v>2842</v>
+        <v>2843</v>
       </c>
       <c r="B898" s="3"/>
       <c r="C898" s="3">
@@ -42984,23 +43515,29 @@
         <v>75</v>
       </c>
       <c r="G898" s="3" t="s">
-        <v>2843</v>
-      </c>
-      <c r="H898" s="3"/>
+        <v>2844</v>
+      </c>
+      <c r="H898" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="I898" s="3">
         <v>37</v>
       </c>
       <c r="J898" s="3"/>
       <c r="K898" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L898" s="3"/>
-      <c r="M898" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L898" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M898" s="3" t="s">
+        <v>2840</v>
+      </c>
       <c r="N898" s="3"/>
     </row>
     <row r="899" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A899" s="3" t="s">
-        <v>2844</v>
+        <v>2845</v>
       </c>
       <c r="B899" s="3"/>
       <c r="C899" s="3">
@@ -43013,10 +43550,10 @@
         <v>85</v>
       </c>
       <c r="F899" s="3" t="s">
-        <v>2845</v>
+        <v>2846</v>
       </c>
       <c r="G899" s="3" t="s">
-        <v>2846</v>
+        <v>2847</v>
       </c>
       <c r="H899" s="3" t="s">
         <v>98</v>
@@ -43036,7 +43573,7 @@
     </row>
     <row r="900" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A900" s="3" t="s">
-        <v>2847</v>
+        <v>2848</v>
       </c>
       <c r="B900" s="3"/>
       <c r="C900" s="3">
@@ -43049,10 +43586,10 @@
         <v>85</v>
       </c>
       <c r="F900" s="3" t="s">
-        <v>2848</v>
+        <v>2849</v>
       </c>
       <c r="G900" s="3" t="s">
-        <v>2849</v>
+        <v>2850</v>
       </c>
       <c r="H900" s="3" t="s">
         <v>98</v>
@@ -43072,7 +43609,7 @@
     </row>
     <row r="901" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A901" s="3" t="s">
-        <v>2850</v>
+        <v>2851</v>
       </c>
       <c r="B901" s="3"/>
       <c r="C901" s="3">
@@ -43088,25 +43625,29 @@
         <v>107</v>
       </c>
       <c r="G901" s="3" t="s">
-        <v>2851</v>
+        <v>2852</v>
       </c>
       <c r="H901" s="3" t="s">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="I901" s="3">
         <v>29</v>
       </c>
       <c r="J901" s="3"/>
       <c r="K901" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L901" s="3"/>
-      <c r="M901" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L901" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M901" s="3" t="s">
+        <v>2853</v>
+      </c>
       <c r="N901" s="3"/>
     </row>
     <row r="902" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A902" s="3" t="s">
-        <v>2852</v>
+        <v>2854</v>
       </c>
       <c r="B902" s="3"/>
       <c r="C902" s="3">
@@ -43119,10 +43660,10 @@
         <v>85</v>
       </c>
       <c r="F902" s="3" t="s">
-        <v>2853</v>
+        <v>2855</v>
       </c>
       <c r="G902" s="3" t="s">
-        <v>2854</v>
+        <v>2856</v>
       </c>
       <c r="H902" s="3" t="s">
         <v>98</v>
@@ -43142,7 +43683,7 @@
     </row>
     <row r="903" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A903" s="3" t="s">
-        <v>2855</v>
+        <v>2857</v>
       </c>
       <c r="B903" s="3"/>
       <c r="C903" s="3">
@@ -43155,10 +43696,10 @@
         <v>85</v>
       </c>
       <c r="F903" s="3" t="s">
-        <v>2856</v>
+        <v>2858</v>
       </c>
       <c r="G903" s="3" t="s">
-        <v>2857</v>
+        <v>2859</v>
       </c>
       <c r="H903" s="3" t="s">
         <v>98</v>
@@ -43178,7 +43719,7 @@
     </row>
     <row r="904" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A904" s="3" t="s">
-        <v>2858</v>
+        <v>2860</v>
       </c>
       <c r="B904" s="3" t="s">
         <v>339</v>
@@ -43193,28 +43734,32 @@
         <v>24</v>
       </c>
       <c r="F904" s="3" t="s">
-        <v>2859</v>
+        <v>2861</v>
       </c>
       <c r="G904" s="3" t="s">
-        <v>2860</v>
+        <v>2862</v>
       </c>
       <c r="H904" s="3" t="s">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="I904" s="3">
         <v>56</v>
       </c>
       <c r="J904" s="3"/>
       <c r="K904" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L904" s="3"/>
-      <c r="M904" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L904" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M904" s="3" t="s">
+        <v>2840</v>
+      </c>
       <c r="N904" s="3"/>
     </row>
     <row r="905" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A905" s="3" t="s">
-        <v>2861</v>
+        <v>2863</v>
       </c>
       <c r="B905" s="3"/>
       <c r="C905" s="3">
@@ -43227,10 +43772,10 @@
         <v>85</v>
       </c>
       <c r="F905" s="3" t="s">
-        <v>2862</v>
+        <v>2864</v>
       </c>
       <c r="G905" s="3" t="s">
-        <v>2863</v>
+        <v>2865</v>
       </c>
       <c r="H905" s="3"/>
       <c r="I905" s="3">
@@ -43246,7 +43791,7 @@
     </row>
     <row r="906" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A906" s="3" t="s">
-        <v>2864</v>
+        <v>2866</v>
       </c>
       <c r="B906" s="3"/>
       <c r="C906" s="3">
@@ -43259,10 +43804,10 @@
         <v>85</v>
       </c>
       <c r="F906" s="3" t="s">
-        <v>2865</v>
+        <v>2867</v>
       </c>
       <c r="G906" s="3" t="s">
-        <v>2866</v>
+        <v>2868</v>
       </c>
       <c r="H906" s="3" t="s">
         <v>98</v>
@@ -43282,7 +43827,7 @@
     </row>
     <row r="907" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A907" s="3" t="s">
-        <v>2867</v>
+        <v>2869</v>
       </c>
       <c r="B907" s="3"/>
       <c r="C907" s="3">
@@ -43295,10 +43840,10 @@
         <v>85</v>
       </c>
       <c r="F907" s="3" t="s">
-        <v>2868</v>
+        <v>2870</v>
       </c>
       <c r="G907" s="3" t="s">
-        <v>2869</v>
+        <v>2871</v>
       </c>
       <c r="H907" s="3" t="s">
         <v>98</v>
@@ -43318,7 +43863,7 @@
     </row>
     <row r="908" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A908" s="3" t="s">
-        <v>2870</v>
+        <v>2872</v>
       </c>
       <c r="B908" s="3"/>
       <c r="C908" s="3">
@@ -43331,10 +43876,10 @@
         <v>85</v>
       </c>
       <c r="F908" s="3" t="s">
-        <v>2871</v>
+        <v>2873</v>
       </c>
       <c r="G908" s="3" t="s">
-        <v>2872</v>
+        <v>2874</v>
       </c>
       <c r="H908" s="3" t="s">
         <v>98</v>
@@ -43354,7 +43899,7 @@
     </row>
     <row r="909" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A909" s="3" t="s">
-        <v>2873</v>
+        <v>2875</v>
       </c>
       <c r="B909" s="3"/>
       <c r="C909" s="3">
@@ -43367,10 +43912,10 @@
         <v>85</v>
       </c>
       <c r="F909" s="3" t="s">
-        <v>2874</v>
+        <v>2876</v>
       </c>
       <c r="G909" s="3" t="s">
-        <v>2875</v>
+        <v>2877</v>
       </c>
       <c r="H909" s="3" t="s">
         <v>98</v>
@@ -43390,7 +43935,7 @@
     </row>
     <row r="910" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A910" s="3" t="s">
-        <v>2876</v>
+        <v>2878</v>
       </c>
       <c r="B910" s="3"/>
       <c r="C910" s="3">
@@ -43403,12 +43948,14 @@
         <v>24</v>
       </c>
       <c r="F910" s="3" t="s">
-        <v>2877</v>
+        <v>2879</v>
       </c>
       <c r="G910" s="3" t="s">
-        <v>2878</v>
-      </c>
-      <c r="H910" s="3"/>
+        <v>2880</v>
+      </c>
+      <c r="H910" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="I910" s="3">
         <v>45</v>
       </c>
@@ -43416,15 +43963,19 @@
         <v>55</v>
       </c>
       <c r="K910" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L910" s="3"/>
-      <c r="M910" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L910" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M910" s="3" t="s">
+        <v>2840</v>
+      </c>
       <c r="N910" s="3"/>
     </row>
     <row r="911" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A911" s="3" t="s">
-        <v>2879</v>
+        <v>2881</v>
       </c>
       <c r="B911" s="3" t="s">
         <v>42</v>
@@ -43439,10 +43990,10 @@
         <v>47</v>
       </c>
       <c r="F911" s="3" t="s">
-        <v>2880</v>
+        <v>2882</v>
       </c>
       <c r="G911" s="3" t="s">
-        <v>2881</v>
+        <v>2883</v>
       </c>
       <c r="H911" s="3" t="s">
         <v>98</v>
@@ -43454,15 +44005,19 @@
         <v>75</v>
       </c>
       <c r="K911" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L911" s="3"/>
-      <c r="M911" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L911" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M911" s="3" t="s">
+        <v>2884</v>
+      </c>
       <c r="N911" s="3"/>
     </row>
     <row r="912" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A912" s="3" t="s">
-        <v>2882</v>
+        <v>2885</v>
       </c>
       <c r="B912" s="3" t="s">
         <v>335</v>
@@ -43477,12 +44032,14 @@
         <v>344</v>
       </c>
       <c r="F912" s="3" t="s">
-        <v>2883</v>
+        <v>2886</v>
       </c>
       <c r="G912" s="3" t="s">
-        <v>2884</v>
-      </c>
-      <c r="H912" s="3"/>
+        <v>2887</v>
+      </c>
+      <c r="H912" s="3" t="s">
+        <v>98</v>
+      </c>
       <c r="I912" s="3">
         <v>40</v>
       </c>
@@ -43490,11 +44047,2147 @@
         <v>45</v>
       </c>
       <c r="K912" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L912" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M912" s="3" t="s">
+        <v>2888</v>
+      </c>
+      <c r="N912" s="3"/>
+    </row>
+    <row r="913" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A913" s="3" t="s">
+        <v>2889</v>
+      </c>
+      <c r="B913" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C913" s="3">
+        <v>96</v>
+      </c>
+      <c r="D913" s="3">
+        <v>1534919977</v>
+      </c>
+      <c r="E913" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F913" s="3" t="s">
+        <v>2890</v>
+      </c>
+      <c r="G913" s="3" t="s">
+        <v>2891</v>
+      </c>
+      <c r="H913" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I913" s="3">
+        <v>70</v>
+      </c>
+      <c r="J913" s="3"/>
+      <c r="K913" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L913" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M913" s="3" t="s">
+        <v>2892</v>
+      </c>
+      <c r="N913" s="3"/>
+    </row>
+    <row r="914" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A914" s="3" t="s">
+        <v>2893</v>
+      </c>
+      <c r="B914" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C914" s="3">
+        <v>357</v>
+      </c>
+      <c r="D914" s="3">
+        <v>1534980617</v>
+      </c>
+      <c r="E914" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F914" s="3" t="s">
+        <v>2894</v>
+      </c>
+      <c r="G914" s="3" t="s">
+        <v>2895</v>
+      </c>
+      <c r="H914" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I914" s="3">
+        <v>73</v>
+      </c>
+      <c r="J914" s="3">
+        <v>75</v>
+      </c>
+      <c r="K914" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L914" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M914" s="3" t="s">
+        <v>2853</v>
+      </c>
+      <c r="N914" s="3"/>
+    </row>
+    <row r="915" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A915" s="3" t="s">
+        <v>2896</v>
+      </c>
+      <c r="B915" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C915" s="3">
+        <v>357</v>
+      </c>
+      <c r="D915" s="3">
+        <v>1534985603</v>
+      </c>
+      <c r="E915" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F915" s="3" t="s">
+        <v>2897</v>
+      </c>
+      <c r="G915" s="3" t="s">
+        <v>2898</v>
+      </c>
+      <c r="H915" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I915" s="3">
+        <v>56</v>
+      </c>
+      <c r="J915" s="3"/>
+      <c r="K915" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L915" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M915" s="3" t="s">
+        <v>2853</v>
+      </c>
+      <c r="N915" s="3"/>
+    </row>
+    <row r="916" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A916" s="3" t="s">
+        <v>2899</v>
+      </c>
+      <c r="B916" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C916" s="3">
+        <v>357</v>
+      </c>
+      <c r="D916" s="3">
+        <v>1535034020</v>
+      </c>
+      <c r="E916" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F916" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="G916" s="3" t="s">
+        <v>2900</v>
+      </c>
+      <c r="H916" s="3"/>
+      <c r="I916" s="3">
+        <v>15</v>
+      </c>
+      <c r="J916" s="3"/>
+      <c r="K916" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L912" s="3"/>
-      <c r="M912" s="3"/>
-      <c r="N912" s="3"/>
+      <c r="L916" s="3"/>
+      <c r="M916" s="3"/>
+      <c r="N916" s="3"/>
+    </row>
+    <row r="917" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A917" s="3" t="s">
+        <v>2901</v>
+      </c>
+      <c r="B917" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C917" s="3">
+        <v>375</v>
+      </c>
+      <c r="D917" s="3">
+        <v>1535068205</v>
+      </c>
+      <c r="E917" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F917" s="3" t="s">
+        <v>2902</v>
+      </c>
+      <c r="G917" s="3" t="s">
+        <v>2903</v>
+      </c>
+      <c r="H917" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I917" s="3">
+        <v>62</v>
+      </c>
+      <c r="J917" s="3">
+        <v>65</v>
+      </c>
+      <c r="K917" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L917" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M917" s="3" t="s">
+        <v>2892</v>
+      </c>
+      <c r="N917" s="3"/>
+    </row>
+    <row r="918" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A918" s="3" t="s">
+        <v>2904</v>
+      </c>
+      <c r="B918" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C918" s="3">
+        <v>375</v>
+      </c>
+      <c r="D918" s="3">
+        <v>1535074746</v>
+      </c>
+      <c r="E918" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F918" s="3" t="s">
+        <v>2905</v>
+      </c>
+      <c r="G918" s="3" t="s">
+        <v>2906</v>
+      </c>
+      <c r="H918" s="3"/>
+      <c r="I918" s="3">
+        <v>70</v>
+      </c>
+      <c r="J918" s="3">
+        <v>70</v>
+      </c>
+      <c r="K918" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L918" s="3"/>
+      <c r="M918" s="3"/>
+      <c r="N918" s="3"/>
+    </row>
+    <row r="919" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A919" s="3" t="s">
+        <v>2907</v>
+      </c>
+      <c r="B919" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C919" s="3">
+        <v>375</v>
+      </c>
+      <c r="D919" s="3">
+        <v>1535090557</v>
+      </c>
+      <c r="E919" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F919" s="3" t="s">
+        <v>2908</v>
+      </c>
+      <c r="G919" s="3" t="s">
+        <v>2909</v>
+      </c>
+      <c r="H919" s="3"/>
+      <c r="I919" s="3">
+        <v>62</v>
+      </c>
+      <c r="J919" s="3">
+        <v>75</v>
+      </c>
+      <c r="K919" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L919" s="3"/>
+      <c r="M919" s="3"/>
+      <c r="N919" s="3"/>
+    </row>
+    <row r="920" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A920" s="3" t="s">
+        <v>2910</v>
+      </c>
+      <c r="B920" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C920" s="3">
+        <v>375</v>
+      </c>
+      <c r="D920" s="3">
+        <v>1535091640</v>
+      </c>
+      <c r="E920" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F920" s="3" t="s">
+        <v>2911</v>
+      </c>
+      <c r="G920" s="3" t="s">
+        <v>2912</v>
+      </c>
+      <c r="H920" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I920" s="3">
+        <v>51</v>
+      </c>
+      <c r="J920" s="3">
+        <v>80</v>
+      </c>
+      <c r="K920" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L920" s="3"/>
+      <c r="M920" s="3"/>
+      <c r="N920" s="3"/>
+    </row>
+    <row r="921" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A921" s="3" t="s">
+        <v>2913</v>
+      </c>
+      <c r="B921" s="3"/>
+      <c r="C921" s="3">
+        <v>339</v>
+      </c>
+      <c r="D921" s="3">
+        <v>1535292985</v>
+      </c>
+      <c r="E921" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F921" s="3" t="s">
+        <v>2914</v>
+      </c>
+      <c r="G921" s="3" t="s">
+        <v>2915</v>
+      </c>
+      <c r="H921" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I921" s="3">
+        <v>26</v>
+      </c>
+      <c r="J921" s="3"/>
+      <c r="K921" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L921" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M921" s="3" t="s">
+        <v>2916</v>
+      </c>
+      <c r="N921" s="3"/>
+    </row>
+    <row r="922" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A922" s="3" t="s">
+        <v>2917</v>
+      </c>
+      <c r="B922" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C922" s="3">
+        <v>357</v>
+      </c>
+      <c r="D922" s="3">
+        <v>1535302026</v>
+      </c>
+      <c r="E922" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F922" s="3" t="s">
+        <v>2918</v>
+      </c>
+      <c r="G922" s="3" t="s">
+        <v>2919</v>
+      </c>
+      <c r="H922" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I922" s="3">
+        <v>21</v>
+      </c>
+      <c r="J922" s="3"/>
+      <c r="K922" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L922" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M922" s="3" t="s">
+        <v>2916</v>
+      </c>
+      <c r="N922" s="3"/>
+    </row>
+    <row r="923" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A923" s="3" t="s">
+        <v>2920</v>
+      </c>
+      <c r="B923" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C923" s="3">
+        <v>672</v>
+      </c>
+      <c r="D923" s="3">
+        <v>1535327206</v>
+      </c>
+      <c r="E923" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F923" s="3" t="s">
+        <v>2921</v>
+      </c>
+      <c r="G923" s="3" t="s">
+        <v>2922</v>
+      </c>
+      <c r="H923" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I923" s="3">
+        <v>62</v>
+      </c>
+      <c r="J923" s="3">
+        <v>65</v>
+      </c>
+      <c r="K923" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L923" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M923" s="3" t="s">
+        <v>2923</v>
+      </c>
+      <c r="N923" s="3"/>
+    </row>
+    <row r="924" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A924" s="3" t="s">
+        <v>2924</v>
+      </c>
+      <c r="B924" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="C924" s="3">
+        <v>108</v>
+      </c>
+      <c r="D924" s="3">
+        <v>1535499549</v>
+      </c>
+      <c r="E924" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F924" s="3" t="s">
+        <v>2925</v>
+      </c>
+      <c r="G924" s="3" t="s">
+        <v>2926</v>
+      </c>
+      <c r="H924" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I924" s="3">
+        <v>81</v>
+      </c>
+      <c r="J924" s="3">
+        <v>80</v>
+      </c>
+      <c r="K924" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L924" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M924" s="3" t="s">
+        <v>2927</v>
+      </c>
+      <c r="N924" s="3"/>
+    </row>
+    <row r="925" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A925" s="3" t="s">
+        <v>2928</v>
+      </c>
+      <c r="B925" s="3"/>
+      <c r="C925" s="3">
+        <v>339</v>
+      </c>
+      <c r="D925" s="3">
+        <v>1535608261</v>
+      </c>
+      <c r="E925" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F925" s="3" t="s">
+        <v>2929</v>
+      </c>
+      <c r="G925" s="3" t="s">
+        <v>2930</v>
+      </c>
+      <c r="H925" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I925" s="3">
+        <v>60</v>
+      </c>
+      <c r="J925" s="3">
+        <v>65</v>
+      </c>
+      <c r="K925" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L925" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M925" s="3" t="s">
+        <v>2923</v>
+      </c>
+      <c r="N925" s="3"/>
+    </row>
+    <row r="926" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A926" s="3" t="s">
+        <v>2931</v>
+      </c>
+      <c r="B926" s="3"/>
+      <c r="C926" s="3">
+        <v>459</v>
+      </c>
+      <c r="D926" s="3">
+        <v>1535640860</v>
+      </c>
+      <c r="E926" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F926" s="3" t="s">
+        <v>2932</v>
+      </c>
+      <c r="G926" s="3" t="s">
+        <v>2933</v>
+      </c>
+      <c r="H926" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I926" s="3">
+        <v>71</v>
+      </c>
+      <c r="J926" s="3">
+        <v>75</v>
+      </c>
+      <c r="K926" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L926" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M926" s="3" t="s">
+        <v>2923</v>
+      </c>
+      <c r="N926" s="3"/>
+    </row>
+    <row r="927" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A927" s="3" t="s">
+        <v>2934</v>
+      </c>
+      <c r="B927" s="3" t="s">
+        <v>801</v>
+      </c>
+      <c r="C927" s="3">
+        <v>344</v>
+      </c>
+      <c r="D927" s="3">
+        <v>1535677730</v>
+      </c>
+      <c r="E927" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F927" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="G927" s="3" t="s">
+        <v>2935</v>
+      </c>
+      <c r="H927" s="3"/>
+      <c r="I927" s="3">
+        <v>48</v>
+      </c>
+      <c r="J927" s="3"/>
+      <c r="K927" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L927" s="3"/>
+      <c r="M927" s="3"/>
+      <c r="N927" s="3"/>
+    </row>
+    <row r="928" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A928" s="3" t="s">
+        <v>2936</v>
+      </c>
+      <c r="B928" s="3"/>
+      <c r="C928" s="3">
+        <v>338</v>
+      </c>
+      <c r="D928" s="3">
+        <v>1535685242</v>
+      </c>
+      <c r="E928" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F928" s="3" t="s">
+        <v>2937</v>
+      </c>
+      <c r="G928" s="3" t="s">
+        <v>2938</v>
+      </c>
+      <c r="H928" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I928" s="3"/>
+      <c r="J928" s="3"/>
+      <c r="K928" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L928" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M928" s="3" t="s">
+        <v>2923</v>
+      </c>
+      <c r="N928" s="3"/>
+    </row>
+    <row r="929" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A929" s="3" t="s">
+        <v>2939</v>
+      </c>
+      <c r="B929" s="3"/>
+      <c r="C929" s="3">
+        <v>338</v>
+      </c>
+      <c r="D929" s="3">
+        <v>1535694826</v>
+      </c>
+      <c r="E929" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F929" s="3" t="s">
+        <v>1469</v>
+      </c>
+      <c r="G929" s="3" t="s">
+        <v>2940</v>
+      </c>
+      <c r="H929" s="3"/>
+      <c r="I929" s="3"/>
+      <c r="J929" s="3"/>
+      <c r="K929" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L929" s="3"/>
+      <c r="M929" s="3"/>
+      <c r="N929" s="3"/>
+    </row>
+    <row r="930" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A930" s="3" t="s">
+        <v>2941</v>
+      </c>
+      <c r="B930" s="3"/>
+      <c r="C930" s="3">
+        <v>338</v>
+      </c>
+      <c r="D930" s="3">
+        <v>1535703607</v>
+      </c>
+      <c r="E930" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F930" s="3" t="s">
+        <v>2942</v>
+      </c>
+      <c r="G930" s="3" t="s">
+        <v>2943</v>
+      </c>
+      <c r="H930" s="3"/>
+      <c r="I930" s="3"/>
+      <c r="J930" s="3"/>
+      <c r="K930" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L930" s="3"/>
+      <c r="M930" s="3"/>
+      <c r="N930" s="3"/>
+    </row>
+    <row r="931" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A931" s="3" t="s">
+        <v>2944</v>
+      </c>
+      <c r="B931" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="C931" s="3">
+        <v>840</v>
+      </c>
+      <c r="D931" s="3">
+        <v>1535845953</v>
+      </c>
+      <c r="E931" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="F931" s="3" t="s">
+        <v>2945</v>
+      </c>
+      <c r="G931" s="3" t="s">
+        <v>2946</v>
+      </c>
+      <c r="H931" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I931" s="3">
+        <v>68</v>
+      </c>
+      <c r="J931" s="3">
+        <v>75</v>
+      </c>
+      <c r="K931" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L931" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M931" s="3" t="s">
+        <v>2947</v>
+      </c>
+      <c r="N931" s="3"/>
+    </row>
+    <row r="932" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A932" s="3" t="s">
+        <v>2948</v>
+      </c>
+      <c r="B932" s="3" t="s">
+        <v>1742</v>
+      </c>
+      <c r="C932" s="3">
+        <v>840</v>
+      </c>
+      <c r="D932" s="3">
+        <v>1535846624</v>
+      </c>
+      <c r="E932" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F932" s="3" t="s">
+        <v>2949</v>
+      </c>
+      <c r="G932" s="3" t="s">
+        <v>2950</v>
+      </c>
+      <c r="H932" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I932" s="3">
+        <v>69</v>
+      </c>
+      <c r="J932" s="3">
+        <v>75</v>
+      </c>
+      <c r="K932" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L932" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M932" s="3" t="s">
+        <v>2951</v>
+      </c>
+      <c r="N932" s="3"/>
+    </row>
+    <row r="933" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A933" s="3" t="s">
+        <v>2952</v>
+      </c>
+      <c r="B933" s="3"/>
+      <c r="C933" s="3">
+        <v>926</v>
+      </c>
+      <c r="D933" s="3">
+        <v>1535919185</v>
+      </c>
+      <c r="E933" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F933" s="3" t="s">
+        <v>2953</v>
+      </c>
+      <c r="G933" s="3" t="s">
+        <v>2954</v>
+      </c>
+      <c r="H933" s="3"/>
+      <c r="I933" s="3">
+        <v>40</v>
+      </c>
+      <c r="J933" s="3"/>
+      <c r="K933" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L933" s="3"/>
+      <c r="M933" s="3"/>
+      <c r="N933" s="3"/>
+    </row>
+    <row r="934" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A934" s="3" t="s">
+        <v>2955</v>
+      </c>
+      <c r="B934" s="3"/>
+      <c r="C934" s="3">
+        <v>926</v>
+      </c>
+      <c r="D934" s="3">
+        <v>1535921672</v>
+      </c>
+      <c r="E934" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F934" s="3" t="s">
+        <v>2956</v>
+      </c>
+      <c r="G934" s="3" t="s">
+        <v>2957</v>
+      </c>
+      <c r="H934" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I934" s="3">
+        <v>65</v>
+      </c>
+      <c r="J934" s="3">
+        <v>80</v>
+      </c>
+      <c r="K934" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L934" s="3"/>
+      <c r="M934" s="3"/>
+      <c r="N934" s="3"/>
+    </row>
+    <row r="935" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A935" s="3" t="s">
+        <v>2958</v>
+      </c>
+      <c r="B935" s="3"/>
+      <c r="C935" s="3">
+        <v>926</v>
+      </c>
+      <c r="D935" s="3">
+        <v>1535924691</v>
+      </c>
+      <c r="E935" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F935" s="3" t="s">
+        <v>2959</v>
+      </c>
+      <c r="G935" s="3" t="s">
+        <v>2960</v>
+      </c>
+      <c r="H935" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I935" s="3">
+        <v>65</v>
+      </c>
+      <c r="J935" s="3">
+        <v>80</v>
+      </c>
+      <c r="K935" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L935" s="3"/>
+      <c r="M935" s="3"/>
+      <c r="N935" s="3"/>
+    </row>
+    <row r="936" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A936" s="3" t="s">
+        <v>2961</v>
+      </c>
+      <c r="B936" s="3" t="s">
+        <v>1742</v>
+      </c>
+      <c r="C936" s="3">
+        <v>840</v>
+      </c>
+      <c r="D936" s="3">
+        <v>1536099937</v>
+      </c>
+      <c r="E936" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F936" s="3" t="s">
+        <v>2962</v>
+      </c>
+      <c r="G936" s="3" t="s">
+        <v>2963</v>
+      </c>
+      <c r="H936" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I936" s="3">
+        <v>46</v>
+      </c>
+      <c r="J936" s="3">
+        <v>65</v>
+      </c>
+      <c r="K936" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L936" s="3"/>
+      <c r="M936" s="3"/>
+      <c r="N936" s="3"/>
+    </row>
+    <row r="937" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A937" s="3" t="s">
+        <v>2961</v>
+      </c>
+      <c r="B937" s="3"/>
+      <c r="C937" s="3">
+        <v>344</v>
+      </c>
+      <c r="D937" s="3">
+        <v>1536100415</v>
+      </c>
+      <c r="E937" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F937" s="3" t="s">
+        <v>2653</v>
+      </c>
+      <c r="G937" s="3" t="s">
+        <v>2964</v>
+      </c>
+      <c r="H937" s="3"/>
+      <c r="I937" s="3">
+        <v>73</v>
+      </c>
+      <c r="J937" s="3">
+        <v>70</v>
+      </c>
+      <c r="K937" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L937" s="3"/>
+      <c r="M937" s="3"/>
+      <c r="N937" s="3"/>
+    </row>
+    <row r="938" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A938" s="3" t="s">
+        <v>2965</v>
+      </c>
+      <c r="B938" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="C938" s="3">
+        <v>357</v>
+      </c>
+      <c r="D938" s="3">
+        <v>1536124238</v>
+      </c>
+      <c r="E938" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F938" s="3" t="s">
+        <v>1559</v>
+      </c>
+      <c r="G938" s="3" t="s">
+        <v>2966</v>
+      </c>
+      <c r="H938" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I938" s="3">
+        <v>33</v>
+      </c>
+      <c r="J938" s="3"/>
+      <c r="K938" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L938" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M938" s="3" t="s">
+        <v>2967</v>
+      </c>
+      <c r="N938" s="3"/>
+    </row>
+    <row r="939" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A939" s="3" t="s">
+        <v>2968</v>
+      </c>
+      <c r="B939" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="C939" s="3">
+        <v>208</v>
+      </c>
+      <c r="D939" s="3">
+        <v>1536251149</v>
+      </c>
+      <c r="E939" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F939" s="3" t="s">
+        <v>2969</v>
+      </c>
+      <c r="G939" s="3" t="s">
+        <v>2970</v>
+      </c>
+      <c r="H939" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I939" s="3">
+        <v>57</v>
+      </c>
+      <c r="J939" s="3"/>
+      <c r="K939" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L939" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M939" s="3" t="s">
+        <v>2967</v>
+      </c>
+      <c r="N939" s="3"/>
+    </row>
+    <row r="940" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A940" s="3" t="s">
+        <v>2971</v>
+      </c>
+      <c r="B940" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C940" s="3">
+        <v>839</v>
+      </c>
+      <c r="D940" s="3">
+        <v>1536595792</v>
+      </c>
+      <c r="E940" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F940" s="3" t="s">
+        <v>2795</v>
+      </c>
+      <c r="G940" s="3" t="s">
+        <v>2972</v>
+      </c>
+      <c r="H940" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I940" s="3">
+        <v>18</v>
+      </c>
+      <c r="J940" s="3"/>
+      <c r="K940" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L940" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M940" s="3" t="s">
+        <v>2973</v>
+      </c>
+      <c r="N940" s="3"/>
+    </row>
+    <row r="941" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A941" s="3" t="s">
+        <v>2974</v>
+      </c>
+      <c r="B941" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="C941" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="D941" s="3">
+        <v>1536629627</v>
+      </c>
+      <c r="E941" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F941" s="3" t="s">
+        <v>2975</v>
+      </c>
+      <c r="G941" s="3" t="s">
+        <v>2976</v>
+      </c>
+      <c r="H941" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I941" s="3">
+        <v>59</v>
+      </c>
+      <c r="J941" s="3">
+        <v>70</v>
+      </c>
+      <c r="K941" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L941" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M941" s="3" t="s">
+        <v>2977</v>
+      </c>
+      <c r="N941" s="3"/>
+    </row>
+    <row r="942" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A942" s="3" t="s">
+        <v>2978</v>
+      </c>
+      <c r="B942" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C942" s="3">
+        <v>375</v>
+      </c>
+      <c r="D942" s="3">
+        <v>1536746334</v>
+      </c>
+      <c r="E942" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F942" s="3" t="s">
+        <v>2979</v>
+      </c>
+      <c r="G942" s="3" t="s">
+        <v>2980</v>
+      </c>
+      <c r="H942" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I942" s="3">
+        <v>70</v>
+      </c>
+      <c r="J942" s="3">
+        <v>65</v>
+      </c>
+      <c r="K942" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L942" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M942" s="3" t="s">
+        <v>2981</v>
+      </c>
+      <c r="N942" s="3"/>
+    </row>
+    <row r="943" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A943" s="3" t="s">
+        <v>2982</v>
+      </c>
+      <c r="B943" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C943" s="3">
+        <v>375</v>
+      </c>
+      <c r="D943" s="3">
+        <v>1536750816</v>
+      </c>
+      <c r="E943" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F943" s="3" t="s">
+        <v>2983</v>
+      </c>
+      <c r="G943" s="3" t="s">
+        <v>2984</v>
+      </c>
+      <c r="H943" s="3"/>
+      <c r="I943" s="3">
+        <v>70</v>
+      </c>
+      <c r="J943" s="3">
+        <v>65</v>
+      </c>
+      <c r="K943" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L943" s="3"/>
+      <c r="M943" s="3"/>
+      <c r="N943" s="3"/>
+    </row>
+    <row r="944" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A944" s="3" t="s">
+        <v>2985</v>
+      </c>
+      <c r="B944" s="3"/>
+      <c r="C944" s="3">
+        <v>339</v>
+      </c>
+      <c r="D944" s="3">
+        <v>1536752458</v>
+      </c>
+      <c r="E944" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F944" s="3" t="s">
+        <v>629</v>
+      </c>
+      <c r="G944" s="3" t="s">
+        <v>2986</v>
+      </c>
+      <c r="H944" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I944" s="3">
+        <v>21</v>
+      </c>
+      <c r="J944" s="3"/>
+      <c r="K944" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L944" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M944" s="3" t="s">
+        <v>2987</v>
+      </c>
+      <c r="N944" s="3"/>
+    </row>
+    <row r="945" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A945" s="3" t="s">
+        <v>2988</v>
+      </c>
+      <c r="B945" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="C945" s="3">
+        <v>108</v>
+      </c>
+      <c r="D945" s="3">
+        <v>1537318681</v>
+      </c>
+      <c r="E945" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F945" s="3" t="s">
+        <v>2989</v>
+      </c>
+      <c r="G945" s="3" t="s">
+        <v>2990</v>
+      </c>
+      <c r="H945" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I945" s="3">
+        <v>82</v>
+      </c>
+      <c r="J945" s="3">
+        <v>70</v>
+      </c>
+      <c r="K945" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L945" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M945" s="3" t="s">
+        <v>2991</v>
+      </c>
+      <c r="N945" s="3"/>
+    </row>
+    <row r="946" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A946" s="3" t="s">
+        <v>2992</v>
+      </c>
+      <c r="B946" s="3"/>
+      <c r="C946" s="3">
+        <v>729</v>
+      </c>
+      <c r="D946" s="3">
+        <v>1537355627</v>
+      </c>
+      <c r="E946" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F946" s="3" t="s">
+        <v>2993</v>
+      </c>
+      <c r="G946" s="3" t="s">
+        <v>2994</v>
+      </c>
+      <c r="H946" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I946" s="3">
+        <v>64</v>
+      </c>
+      <c r="J946" s="3">
+        <v>65</v>
+      </c>
+      <c r="K946" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L946" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M946" s="3" t="s">
+        <v>2995</v>
+      </c>
+      <c r="N946" s="3"/>
+    </row>
+    <row r="947" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A947" s="3" t="s">
+        <v>2996</v>
+      </c>
+      <c r="B947" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="C947" s="3">
+        <v>108</v>
+      </c>
+      <c r="D947" s="3">
+        <v>1537529361</v>
+      </c>
+      <c r="E947" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F947" s="3" t="s">
+        <v>2997</v>
+      </c>
+      <c r="G947" s="3" t="s">
+        <v>2998</v>
+      </c>
+      <c r="H947" s="3"/>
+      <c r="I947" s="3">
+        <v>77</v>
+      </c>
+      <c r="J947" s="3">
+        <v>80</v>
+      </c>
+      <c r="K947" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L947" s="3"/>
+      <c r="M947" s="3"/>
+      <c r="N947" s="3"/>
+    </row>
+    <row r="948" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A948" s="3" t="s">
+        <v>2999</v>
+      </c>
+      <c r="B948" s="3"/>
+      <c r="C948" s="3">
+        <v>375</v>
+      </c>
+      <c r="D948" s="3">
+        <v>1537650945</v>
+      </c>
+      <c r="E948" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F948" s="3" t="s">
+        <v>1773</v>
+      </c>
+      <c r="G948" s="3" t="s">
+        <v>3000</v>
+      </c>
+      <c r="H948" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I948" s="3">
+        <v>33</v>
+      </c>
+      <c r="J948" s="3"/>
+      <c r="K948" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L948" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M948" s="3" t="s">
+        <v>2991</v>
+      </c>
+      <c r="N948" s="3"/>
+    </row>
+    <row r="949" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A949" s="3" t="s">
+        <v>3001</v>
+      </c>
+      <c r="B949" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="C949" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="D949" s="3">
+        <v>1537880709</v>
+      </c>
+      <c r="E949" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F949" s="3" t="s">
+        <v>3002</v>
+      </c>
+      <c r="G949" s="3" t="s">
+        <v>3003</v>
+      </c>
+      <c r="H949" s="3"/>
+      <c r="I949" s="3">
+        <v>54</v>
+      </c>
+      <c r="J949" s="3">
+        <v>70</v>
+      </c>
+      <c r="K949" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L949" s="3"/>
+      <c r="M949" s="3"/>
+      <c r="N949" s="3"/>
+    </row>
+    <row r="950" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A950" s="3" t="s">
+        <v>3004</v>
+      </c>
+      <c r="B950" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C950" s="3">
+        <v>839</v>
+      </c>
+      <c r="D950" s="3">
+        <v>1538115834</v>
+      </c>
+      <c r="E950" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F950" s="3" t="s">
+        <v>3005</v>
+      </c>
+      <c r="G950" s="3" t="s">
+        <v>3006</v>
+      </c>
+      <c r="H950" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I950" s="3">
+        <v>14</v>
+      </c>
+      <c r="J950" s="3">
+        <v>35</v>
+      </c>
+      <c r="K950" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L950" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M950" s="3" t="s">
+        <v>3007</v>
+      </c>
+      <c r="N950" s="3"/>
+    </row>
+    <row r="951" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A951" s="3" t="s">
+        <v>3008</v>
+      </c>
+      <c r="B951" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C951" s="3">
+        <v>672</v>
+      </c>
+      <c r="D951" s="3">
+        <v>1538187418</v>
+      </c>
+      <c r="E951" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F951" s="3" t="s">
+        <v>3009</v>
+      </c>
+      <c r="G951" s="3" t="s">
+        <v>3010</v>
+      </c>
+      <c r="H951" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I951" s="3">
+        <v>48</v>
+      </c>
+      <c r="J951" s="3">
+        <v>65</v>
+      </c>
+      <c r="K951" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L951" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M951" s="3" t="s">
+        <v>3007</v>
+      </c>
+      <c r="N951" s="3"/>
+    </row>
+    <row r="952" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A952" s="3" t="s">
+        <v>3011</v>
+      </c>
+      <c r="B952" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C952" s="3">
+        <v>839</v>
+      </c>
+      <c r="D952" s="3">
+        <v>1538800041</v>
+      </c>
+      <c r="E952" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F952" s="3" t="s">
+        <v>3012</v>
+      </c>
+      <c r="G952" s="3" t="s">
+        <v>3013</v>
+      </c>
+      <c r="H952" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I952" s="3">
+        <v>53</v>
+      </c>
+      <c r="J952" s="3"/>
+      <c r="K952" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L952" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M952" s="3" t="s">
+        <v>3007</v>
+      </c>
+      <c r="N952" s="3"/>
+    </row>
+    <row r="953" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A953" s="3" t="s">
+        <v>3014</v>
+      </c>
+      <c r="B953" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C953" s="3">
+        <v>672</v>
+      </c>
+      <c r="D953" s="3">
+        <v>1539087124</v>
+      </c>
+      <c r="E953" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F953" s="3" t="s">
+        <v>3015</v>
+      </c>
+      <c r="G953" s="3" t="s">
+        <v>3016</v>
+      </c>
+      <c r="H953" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I953" s="3">
+        <v>64</v>
+      </c>
+      <c r="J953" s="3">
+        <v>70</v>
+      </c>
+      <c r="K953" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L953" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M953" s="3" t="s">
+        <v>3007</v>
+      </c>
+      <c r="N953" s="3"/>
+    </row>
+    <row r="954" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A954" s="3" t="s">
+        <v>3017</v>
+      </c>
+      <c r="B954" s="3"/>
+      <c r="C954" s="3">
+        <v>345</v>
+      </c>
+      <c r="D954" s="3">
+        <v>1539260004</v>
+      </c>
+      <c r="E954" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F954" s="3" t="s">
+        <v>3018</v>
+      </c>
+      <c r="G954" s="3" t="s">
+        <v>3019</v>
+      </c>
+      <c r="H954" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I954" s="3">
+        <v>64</v>
+      </c>
+      <c r="J954" s="3">
+        <v>65</v>
+      </c>
+      <c r="K954" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L954" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M954" s="3" t="s">
+        <v>3007</v>
+      </c>
+      <c r="N954" s="3"/>
+    </row>
+    <row r="955" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A955" s="3" t="s">
+        <v>3020</v>
+      </c>
+      <c r="B955" s="3"/>
+      <c r="C955" s="3">
+        <v>345</v>
+      </c>
+      <c r="D955" s="3">
+        <v>1539260009</v>
+      </c>
+      <c r="E955" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F955" s="3" t="s">
+        <v>3021</v>
+      </c>
+      <c r="G955" s="3" t="s">
+        <v>3022</v>
+      </c>
+      <c r="H955" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I955" s="3">
+        <v>65</v>
+      </c>
+      <c r="J955" s="3">
+        <v>65</v>
+      </c>
+      <c r="K955" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L955" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M955" s="3" t="s">
+        <v>3023</v>
+      </c>
+      <c r="N955" s="3"/>
+    </row>
+    <row r="956" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A956" s="3" t="s">
+        <v>3024</v>
+      </c>
+      <c r="B956" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C956" s="3">
+        <v>336</v>
+      </c>
+      <c r="D956" s="3">
+        <v>1539376012</v>
+      </c>
+      <c r="E956" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F956" s="3" t="s">
+        <v>3025</v>
+      </c>
+      <c r="G956" s="3" t="s">
+        <v>3026</v>
+      </c>
+      <c r="H956" s="3"/>
+      <c r="I956" s="3">
+        <v>65</v>
+      </c>
+      <c r="J956" s="3">
+        <v>75</v>
+      </c>
+      <c r="K956" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L956" s="3"/>
+      <c r="M956" s="3"/>
+      <c r="N956" s="3"/>
+    </row>
+    <row r="957" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A957" s="3" t="s">
+        <v>3027</v>
+      </c>
+      <c r="B957" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C957" s="3">
+        <v>672</v>
+      </c>
+      <c r="D957" s="3">
+        <v>1539423990</v>
+      </c>
+      <c r="E957" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F957" s="3" t="s">
+        <v>3028</v>
+      </c>
+      <c r="G957" s="3" t="s">
+        <v>3029</v>
+      </c>
+      <c r="H957" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I957" s="3">
+        <v>75</v>
+      </c>
+      <c r="J957" s="3">
+        <v>70</v>
+      </c>
+      <c r="K957" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L957" s="3"/>
+      <c r="M957" s="3"/>
+      <c r="N957" s="3"/>
+    </row>
+    <row r="958" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A958" s="3" t="s">
+        <v>3027</v>
+      </c>
+      <c r="B958" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C958" s="3">
+        <v>672</v>
+      </c>
+      <c r="D958" s="3">
+        <v>1539423996</v>
+      </c>
+      <c r="E958" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F958" s="3" t="s">
+        <v>3030</v>
+      </c>
+      <c r="G958" s="3" t="s">
+        <v>3031</v>
+      </c>
+      <c r="H958" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I958" s="3">
+        <v>75</v>
+      </c>
+      <c r="J958" s="3">
+        <v>70</v>
+      </c>
+      <c r="K958" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L958" s="3"/>
+      <c r="M958" s="3"/>
+      <c r="N958" s="3"/>
+    </row>
+    <row r="959" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A959" s="3" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B959" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="C959" s="3">
+        <v>63</v>
+      </c>
+      <c r="D959" s="3">
+        <v>1539488977</v>
+      </c>
+      <c r="E959" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F959" s="3" t="s">
+        <v>3033</v>
+      </c>
+      <c r="G959" s="3" t="s">
+        <v>3034</v>
+      </c>
+      <c r="H959" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I959" s="3">
+        <v>79</v>
+      </c>
+      <c r="J959" s="3">
+        <v>75</v>
+      </c>
+      <c r="K959" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L959" s="3"/>
+      <c r="M959" s="3"/>
+      <c r="N959" s="3"/>
+    </row>
+    <row r="960" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A960" s="3" t="s">
+        <v>3035</v>
+      </c>
+      <c r="B960" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="C960" s="3">
+        <v>63</v>
+      </c>
+      <c r="D960" s="3">
+        <v>1539522130</v>
+      </c>
+      <c r="E960" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F960" s="3" t="s">
+        <v>3036</v>
+      </c>
+      <c r="G960" s="3" t="s">
+        <v>3037</v>
+      </c>
+      <c r="H960" s="3"/>
+      <c r="I960" s="3">
+        <v>79</v>
+      </c>
+      <c r="J960" s="3">
+        <v>75</v>
+      </c>
+      <c r="K960" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L960" s="3"/>
+      <c r="M960" s="3"/>
+      <c r="N960" s="3"/>
+    </row>
+    <row r="961" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A961" s="3" t="s">
+        <v>3038</v>
+      </c>
+      <c r="B961" s="3"/>
+      <c r="C961" s="3">
+        <v>344</v>
+      </c>
+      <c r="D961" s="3">
+        <v>1539525219</v>
+      </c>
+      <c r="E961" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F961" s="3" t="s">
+        <v>3039</v>
+      </c>
+      <c r="G961" s="3" t="s">
+        <v>3040</v>
+      </c>
+      <c r="H961" s="3"/>
+      <c r="I961" s="3">
+        <v>40</v>
+      </c>
+      <c r="J961" s="3"/>
+      <c r="K961" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L961" s="3"/>
+      <c r="M961" s="3"/>
+      <c r="N961" s="3"/>
+    </row>
+    <row r="962" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A962" s="3" t="s">
+        <v>3041</v>
+      </c>
+      <c r="B962" s="3"/>
+      <c r="C962" s="3">
+        <v>840</v>
+      </c>
+      <c r="D962" s="3">
+        <v>1539622105</v>
+      </c>
+      <c r="E962" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F962" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G962" s="3" t="s">
+        <v>3042</v>
+      </c>
+      <c r="H962" s="3"/>
+      <c r="I962" s="3">
+        <v>53</v>
+      </c>
+      <c r="J962" s="3"/>
+      <c r="K962" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L962" s="3"/>
+      <c r="M962" s="3"/>
+      <c r="N962" s="3"/>
+    </row>
+    <row r="963" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A963" s="3" t="s">
+        <v>3043</v>
+      </c>
+      <c r="B963" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C963" s="3">
+        <v>336</v>
+      </c>
+      <c r="D963" s="3">
+        <v>1539684234</v>
+      </c>
+      <c r="E963" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F963" s="3" t="s">
+        <v>1507</v>
+      </c>
+      <c r="G963" s="3" t="s">
+        <v>3044</v>
+      </c>
+      <c r="H963" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I963" s="3">
+        <v>26</v>
+      </c>
+      <c r="J963" s="3"/>
+      <c r="K963" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L963" s="3"/>
+      <c r="M963" s="3"/>
+      <c r="N963" s="3"/>
+    </row>
+    <row r="964" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A964" s="3" t="s">
+        <v>3045</v>
+      </c>
+      <c r="B964" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C964" s="3">
+        <v>336</v>
+      </c>
+      <c r="D964" s="3">
+        <v>1539693243</v>
+      </c>
+      <c r="E964" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F964" s="3" t="s">
+        <v>3046</v>
+      </c>
+      <c r="G964" s="3" t="s">
+        <v>3047</v>
+      </c>
+      <c r="H964" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I964" s="3">
+        <v>65</v>
+      </c>
+      <c r="J964" s="3">
+        <v>65</v>
+      </c>
+      <c r="K964" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L964" s="3"/>
+      <c r="M964" s="3"/>
+      <c r="N964" s="3"/>
+    </row>
+    <row r="965" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A965" s="3" t="s">
+        <v>3048</v>
+      </c>
+      <c r="B965" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C965" s="3">
+        <v>336</v>
+      </c>
+      <c r="D965" s="3">
+        <v>1539694459</v>
+      </c>
+      <c r="E965" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F965" s="3" t="s">
+        <v>3049</v>
+      </c>
+      <c r="G965" s="3" t="s">
+        <v>3050</v>
+      </c>
+      <c r="H965" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I965" s="3">
+        <v>66</v>
+      </c>
+      <c r="J965" s="3">
+        <v>65</v>
+      </c>
+      <c r="K965" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L965" s="3"/>
+      <c r="M965" s="3"/>
+      <c r="N965" s="3"/>
+    </row>
+    <row r="966" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A966" s="3" t="s">
+        <v>3051</v>
+      </c>
+      <c r="B966" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C966" s="3">
+        <v>336</v>
+      </c>
+      <c r="D966" s="3">
+        <v>1539695608</v>
+      </c>
+      <c r="E966" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F966" s="3" t="s">
+        <v>3052</v>
+      </c>
+      <c r="G966" s="3" t="s">
+        <v>3053</v>
+      </c>
+      <c r="H966" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I966" s="3">
+        <v>66</v>
+      </c>
+      <c r="J966" s="3">
+        <v>65</v>
+      </c>
+      <c r="K966" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L966" s="3"/>
+      <c r="M966" s="3"/>
+      <c r="N966" s="3"/>
+    </row>
+    <row r="967" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A967" s="3" t="s">
+        <v>3054</v>
+      </c>
+      <c r="B967" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C967" s="3">
+        <v>336</v>
+      </c>
+      <c r="D967" s="3">
+        <v>1539696748</v>
+      </c>
+      <c r="E967" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F967" s="3" t="s">
+        <v>3055</v>
+      </c>
+      <c r="G967" s="3" t="s">
+        <v>3056</v>
+      </c>
+      <c r="H967" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I967" s="3">
+        <v>58</v>
+      </c>
+      <c r="J967" s="3">
+        <v>55</v>
+      </c>
+      <c r="K967" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L967" s="3"/>
+      <c r="M967" s="3"/>
+      <c r="N967" s="3"/>
+    </row>
+    <row r="968" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A968" s="3" t="s">
+        <v>3057</v>
+      </c>
+      <c r="B968" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C968" s="3">
+        <v>336</v>
+      </c>
+      <c r="D968" s="3">
+        <v>1539698015</v>
+      </c>
+      <c r="E968" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F968" s="3" t="s">
+        <v>3058</v>
+      </c>
+      <c r="G968" s="3" t="s">
+        <v>3059</v>
+      </c>
+      <c r="H968" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I968" s="3">
+        <v>65</v>
+      </c>
+      <c r="J968" s="3">
+        <v>65</v>
+      </c>
+      <c r="K968" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L968" s="3"/>
+      <c r="M968" s="3"/>
+      <c r="N968" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\PCS- TS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\PCS-Trucking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2D30233B-41E8-4DD5-8127-E252F0061BAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{72419570-1BCB-4A89-ADA7-F8F92EAB2A44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="1215" windowWidth="21930" windowHeight="14985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3420" yWindow="3420" windowWidth="43200" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRIVE-ALERTS" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8046" uniqueCount="3432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8452" uniqueCount="3588">
   <si>
     <t>DRIVE ALERTS</t>
   </si>
@@ -10171,6 +10171,9 @@
     <t>41.792172, -110.576470</t>
   </si>
   <si>
+    <t>06/15/26 09:32 EDT</t>
+  </si>
+  <si>
     <t>06/12/26 13:18 EDT</t>
   </si>
   <si>
@@ -10189,6 +10192,9 @@
     <t>41.242031, -112.015483</t>
   </si>
   <si>
+    <t>06/15/26 09:33 EDT</t>
+  </si>
+  <si>
     <t>06/12/26 16:04 EDT</t>
   </si>
   <si>
@@ -10261,6 +10267,9 @@
     <t>35.061209, -106.452247</t>
   </si>
   <si>
+    <t>06/15/26 09:34 EDT</t>
+  </si>
+  <si>
     <t>06/13/26 20:45 EDT</t>
   </si>
   <si>
@@ -10270,6 +10279,9 @@
     <t>41.497843, -95.317461</t>
   </si>
   <si>
+    <t>06/15/26 09:35 EDT</t>
+  </si>
+  <si>
     <t>06/14/26 02:20 EDT</t>
   </si>
   <si>
@@ -10316,6 +10328,462 @@
   </si>
   <si>
     <t>37.290053, -113.301389</t>
+  </si>
+  <si>
+    <t>06/15/26 01:14 EDT</t>
+  </si>
+  <si>
+    <t>56.8mi NE of Woodlake CA</t>
+  </si>
+  <si>
+    <t>36.848534, -118.231448</t>
+  </si>
+  <si>
+    <t>06/15/26 12:50 EDT</t>
+  </si>
+  <si>
+    <t>0.9mi N of Rancho Cucamonga CA</t>
+  </si>
+  <si>
+    <t>34.136823, -117.561836</t>
+  </si>
+  <si>
+    <t>06/16/26 09:15 EDT</t>
+  </si>
+  <si>
+    <t>06/15/26 17:41 EDT</t>
+  </si>
+  <si>
+    <t>1.4mi S of Layton UT</t>
+  </si>
+  <si>
+    <t>41.056594, -111.961122</t>
+  </si>
+  <si>
+    <t>1.5mi S of Layton UT</t>
+  </si>
+  <si>
+    <t>41.055935, -111.961062</t>
+  </si>
+  <si>
+    <t>06/15/26 19:23 EDT</t>
+  </si>
+  <si>
+    <t>2.2mi NW of Pleasant View UT</t>
+  </si>
+  <si>
+    <t>41.341149, -112.037052</t>
+  </si>
+  <si>
+    <t>06/15/26 19:45 EDT</t>
+  </si>
+  <si>
+    <t>3.7mi SE of Tremonton UT</t>
+  </si>
+  <si>
+    <t>41.679574, -112.140066</t>
+  </si>
+  <si>
+    <t>06/15/26 20:23 EDT</t>
+  </si>
+  <si>
+    <t>18.6mi W of Preston ID</t>
+  </si>
+  <si>
+    <t>42.177425, -112.228227</t>
+  </si>
+  <si>
+    <t>06/15/26 20:49 EDT</t>
+  </si>
+  <si>
+    <t>3.5mi S of Perry UT</t>
+  </si>
+  <si>
+    <t>41.414081, -112.050738</t>
+  </si>
+  <si>
+    <t>06/15/26 22:16 EDT</t>
+  </si>
+  <si>
+    <t>40.163770, -111.650896</t>
+  </si>
+  <si>
+    <t>06/16/26 09:16 EDT</t>
+  </si>
+  <si>
+    <t>5.5mi SW of Idaho Falls ID</t>
+  </si>
+  <si>
+    <t>43.436096, -112.121061</t>
+  </si>
+  <si>
+    <t>06/16/26 09:17 EDT</t>
+  </si>
+  <si>
+    <t>06/16/26 14:18 EDT</t>
+  </si>
+  <si>
+    <t>3.7mi SE of Belgrade MT</t>
+  </si>
+  <si>
+    <t>45.743109, -111.115811</t>
+  </si>
+  <si>
+    <t>06/17/26 09:47 EDT</t>
+  </si>
+  <si>
+    <t>06/16/26 16:05 EDT</t>
+  </si>
+  <si>
+    <t>2.6mi SW of Salt Lake City UT</t>
+  </si>
+  <si>
+    <t>40.755896, -111.972181</t>
+  </si>
+  <si>
+    <t>06/16/26 16:49 EDT</t>
+  </si>
+  <si>
+    <t>2.1mi NE of Chubbuck ID</t>
+  </si>
+  <si>
+    <t>42.950083, -112.435235</t>
+  </si>
+  <si>
+    <t>06/16/26 17:08 EDT</t>
+  </si>
+  <si>
+    <t>7.4mi E of Evanston WY</t>
+  </si>
+  <si>
+    <t>41.272327, -110.822325</t>
+  </si>
+  <si>
+    <t>06/16/26 17:10 EDT</t>
+  </si>
+  <si>
+    <t>15mi SE of Pocatello ID</t>
+  </si>
+  <si>
+    <t>42.743924, -112.226203</t>
+  </si>
+  <si>
+    <t>06/16/26 17:17 EDT</t>
+  </si>
+  <si>
+    <t>21.2mi SE of Pocatello ID</t>
+  </si>
+  <si>
+    <t>42.632507, -112.203791</t>
+  </si>
+  <si>
+    <t>06/16/26 17:30 EDT</t>
+  </si>
+  <si>
+    <t>42.422300, -112.186623</t>
+  </si>
+  <si>
+    <t>06/16/26 17:51 EDT</t>
+  </si>
+  <si>
+    <t>17.5mi W of Preston ID</t>
+  </si>
+  <si>
+    <t>42.125445, -112.219355</t>
+  </si>
+  <si>
+    <t>06/16/26 21:08 EDT</t>
+  </si>
+  <si>
+    <t>1.9mi NW of Winchester NV</t>
+  </si>
+  <si>
+    <t>36.148561, -115.166984</t>
+  </si>
+  <si>
+    <t>06/17/26 05:33 EDT</t>
+  </si>
+  <si>
+    <t>3.6mi SE of Waynesboro VA</t>
+  </si>
+  <si>
+    <t>38.034081, -78.849641</t>
+  </si>
+  <si>
+    <t>06/17/26 15:38 EDT</t>
+  </si>
+  <si>
+    <t>3.7mi SE of Waynesboro VA</t>
+  </si>
+  <si>
+    <t>38.034431, -78.848251</t>
+  </si>
+  <si>
+    <t>06/17/26 12:40 EDT</t>
+  </si>
+  <si>
+    <t>0.4mi NE of Santaquin UT</t>
+  </si>
+  <si>
+    <t>39.975571, -111.790892</t>
+  </si>
+  <si>
+    <t>06/17/26 15:18 EDT</t>
+  </si>
+  <si>
+    <t>4.5mi SE of Kearney NE</t>
+  </si>
+  <si>
+    <t>40.674946, -99.003927</t>
+  </si>
+  <si>
+    <t>06/17/26 15:21 EDT</t>
+  </si>
+  <si>
+    <t>8mi E of Kearney NE</t>
+  </si>
+  <si>
+    <t>40.690867, -98.931687</t>
+  </si>
+  <si>
+    <t>06/18/26 09:11 EDT</t>
+  </si>
+  <si>
+    <t>06/17/26 15:41 EDT</t>
+  </si>
+  <si>
+    <t>16.1mi NW of Hastings NE</t>
+  </si>
+  <si>
+    <t>40.743083, -98.627682</t>
+  </si>
+  <si>
+    <t>16mi NW of Hastings NE</t>
+  </si>
+  <si>
+    <t>40.748033, -98.619763</t>
+  </si>
+  <si>
+    <t>06/17/26 16:18 EDT</t>
+  </si>
+  <si>
+    <t>11mi W of York NE</t>
+  </si>
+  <si>
+    <t>40.821018, -97.793265</t>
+  </si>
+  <si>
+    <t>06/17/26 17:53 EDT</t>
+  </si>
+  <si>
+    <t>10.8mi W of Lincoln NE</t>
+  </si>
+  <si>
+    <t>40.820468, -96.885282</t>
+  </si>
+  <si>
+    <t>06/17/26 18:04 EDT</t>
+  </si>
+  <si>
+    <t>2.3mi NW of West Valley City UT</t>
+  </si>
+  <si>
+    <t>40.718362, -112.031298</t>
+  </si>
+  <si>
+    <t>06/17/26 18:19 EDT</t>
+  </si>
+  <si>
+    <t>40.725737, -112.013243</t>
+  </si>
+  <si>
+    <t>06/17/26 18:31 EDT</t>
+  </si>
+  <si>
+    <t>4.9mi SW of York NE</t>
+  </si>
+  <si>
+    <t>40.821405, -97.661536</t>
+  </si>
+  <si>
+    <t>06/17/26 19:42 EDT</t>
+  </si>
+  <si>
+    <t>1mi S of Shiprock NM</t>
+  </si>
+  <si>
+    <t>36.777896, -108.696591</t>
+  </si>
+  <si>
+    <t>06/17/26 20:27 EDT</t>
+  </si>
+  <si>
+    <t>10.5mi W of Breckenridge CO</t>
+  </si>
+  <si>
+    <t>39.554393, -106.226690</t>
+  </si>
+  <si>
+    <t>06/17/26 22:35 EDT</t>
+  </si>
+  <si>
+    <t>36.308601, -114.950265</t>
+  </si>
+  <si>
+    <t>06/18/26 09:12 EDT</t>
+  </si>
+  <si>
+    <t>06/17/26 23:15 EDT</t>
+  </si>
+  <si>
+    <t>1.3mi NE of Nephi UT</t>
+  </si>
+  <si>
+    <t>39.722108, -111.819483</t>
+  </si>
+  <si>
+    <t>06/18/26 03:16 EDT</t>
+  </si>
+  <si>
+    <t>21.6mi SW of Nephi UT</t>
+  </si>
+  <si>
+    <t>39.435593, -112.032653</t>
+  </si>
+  <si>
+    <t>06/18/26 08:00 EDT</t>
+  </si>
+  <si>
+    <t>1.5mi E of Clearfield UT</t>
+  </si>
+  <si>
+    <t>41.095043, -111.996350</t>
+  </si>
+  <si>
+    <t>06/19/26 08:53 EDT</t>
+  </si>
+  <si>
+    <t>06/18/26 09:39 EDT</t>
+  </si>
+  <si>
+    <t>7.7mi W of Plain City UT</t>
+  </si>
+  <si>
+    <t>41.278892, -112.231167</t>
+  </si>
+  <si>
+    <t>06/18/26 20:06 EDT</t>
+  </si>
+  <si>
+    <t>06/18/26 10:11 EDT</t>
+  </si>
+  <si>
+    <t>3.6mi NE of West Valley City UT</t>
+  </si>
+  <si>
+    <t>40.728056, -111.968023</t>
+  </si>
+  <si>
+    <t>06/18/26 15:05 EDT</t>
+  </si>
+  <si>
+    <t>40.741302, -111.981420</t>
+  </si>
+  <si>
+    <t>06/18/26 15:33 EDT</t>
+  </si>
+  <si>
+    <t>40.743173, -111.988624</t>
+  </si>
+  <si>
+    <t>06/18/26 17:33 EDT</t>
+  </si>
+  <si>
+    <t>2.1mi SE of Charlottesville VA</t>
+  </si>
+  <si>
+    <t>38.016066, -78.458198</t>
+  </si>
+  <si>
+    <t>06/19/26 08:55 EDT</t>
+  </si>
+  <si>
+    <t>06/19/26 01:53 EDT</t>
+  </si>
+  <si>
+    <t>23.7mi SW of Nephi UT</t>
+  </si>
+  <si>
+    <t>39.408715, -112.052110</t>
+  </si>
+  <si>
+    <t>06/19/26 12:10 EDT</t>
+  </si>
+  <si>
+    <t>2.1mi NE of Franklin PA</t>
+  </si>
+  <si>
+    <t>39.901192, -80.146194</t>
+  </si>
+  <si>
+    <t>06/19/26 14:22 EDT</t>
+  </si>
+  <si>
+    <t>1.6mi SW of Salt Lake City UT</t>
+  </si>
+  <si>
+    <t>40.760431, -111.952162</t>
+  </si>
+  <si>
+    <t>19mi N of Hurricane UT</t>
+  </si>
+  <si>
+    <t>37.408439, -113.236784</t>
+  </si>
+  <si>
+    <t>06/19/26 16:31 EDT</t>
+  </si>
+  <si>
+    <t>0.5mi NW of Brush CO</t>
+  </si>
+  <si>
+    <t>40.265291, -103.639822</t>
+  </si>
+  <si>
+    <t>06/19/26 18:18 EDT</t>
+  </si>
+  <si>
+    <t>1.6mi S of Gary IN</t>
+  </si>
+  <si>
+    <t>41.567576, -87.341573</t>
+  </si>
+  <si>
+    <t>06/19/26 22:07 EDT</t>
+  </si>
+  <si>
+    <t>0.9mi S of North Platte NE</t>
+  </si>
+  <si>
+    <t>41.113928, -100.763787</t>
+  </si>
+  <si>
+    <t>06/20/26 19:06 EDT</t>
+  </si>
+  <si>
+    <t>35.1mi E of Rock Springs WY</t>
+  </si>
+  <si>
+    <t>41.643831, -108.544886</t>
+  </si>
+  <si>
+    <t>06/20/26 19:48 EDT</t>
+  </si>
+  <si>
+    <t>10mi SE of Lexington NE</t>
+  </si>
+  <si>
+    <t>40.695899, -99.588162</t>
   </si>
 </sst>
 </file>
@@ -10677,7 +11145,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N1086"/>
+  <dimension ref="A1:N1137"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="14" width="15" customWidth="1"/>
@@ -51219,15 +51687,19 @@
       </c>
       <c r="J1069" s="3"/>
       <c r="K1069" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1069" s="3"/>
-      <c r="M1069" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L1069" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1069" s="3" t="s">
+        <v>3383</v>
+      </c>
       <c r="N1069" s="3"/>
     </row>
     <row r="1070" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1070" s="3" t="s">
-        <v>3383</v>
+        <v>3384</v>
       </c>
       <c r="B1070" s="3" t="s">
         <v>32</v>
@@ -51242,12 +51714,14 @@
         <v>24</v>
       </c>
       <c r="F1070" s="3" t="s">
-        <v>3384</v>
+        <v>3385</v>
       </c>
       <c r="G1070" s="3" t="s">
-        <v>3385</v>
-      </c>
-      <c r="H1070" s="3"/>
+        <v>3386</v>
+      </c>
+      <c r="H1070" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="I1070" s="3">
         <v>41</v>
       </c>
@@ -51255,15 +51729,19 @@
         <v>45</v>
       </c>
       <c r="K1070" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1070" s="3"/>
-      <c r="M1070" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L1070" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1070" s="3" t="s">
+        <v>3383</v>
+      </c>
       <c r="N1070" s="3"/>
     </row>
     <row r="1071" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1071" s="3" t="s">
-        <v>3386</v>
+        <v>3387</v>
       </c>
       <c r="B1071" s="3" t="s">
         <v>32</v>
@@ -51278,13 +51756,13 @@
         <v>47</v>
       </c>
       <c r="F1071" s="3" t="s">
-        <v>3387</v>
+        <v>3388</v>
       </c>
       <c r="G1071" s="3" t="s">
-        <v>3388</v>
+        <v>3389</v>
       </c>
       <c r="H1071" s="3" t="s">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="I1071" s="3">
         <v>77</v>
@@ -51293,15 +51771,19 @@
         <v>70</v>
       </c>
       <c r="K1071" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1071" s="3"/>
-      <c r="M1071" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L1071" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1071" s="3" t="s">
+        <v>3390</v>
+      </c>
       <c r="N1071" s="3"/>
     </row>
     <row r="1072" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1072" s="3" t="s">
-        <v>3389</v>
+        <v>3391</v>
       </c>
       <c r="B1072" s="3"/>
       <c r="C1072" s="3">
@@ -51314,10 +51796,10 @@
         <v>24</v>
       </c>
       <c r="F1072" s="3" t="s">
-        <v>3390</v>
+        <v>3392</v>
       </c>
       <c r="G1072" s="3" t="s">
-        <v>3391</v>
+        <v>3393</v>
       </c>
       <c r="H1072" s="3"/>
       <c r="I1072" s="3">
@@ -51333,7 +51815,7 @@
     </row>
     <row r="1073" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1073" s="3" t="s">
-        <v>3392</v>
+        <v>3394</v>
       </c>
       <c r="B1073" s="3" t="s">
         <v>74</v>
@@ -51348,13 +51830,13 @@
         <v>43</v>
       </c>
       <c r="F1073" s="3" t="s">
-        <v>3393</v>
+        <v>3395</v>
       </c>
       <c r="G1073" s="3" t="s">
-        <v>3394</v>
+        <v>3396</v>
       </c>
       <c r="H1073" s="3" t="s">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="I1073" s="3">
         <v>55</v>
@@ -51363,15 +51845,19 @@
         <v>75</v>
       </c>
       <c r="K1073" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1073" s="3"/>
-      <c r="M1073" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L1073" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1073" s="3" t="s">
+        <v>3390</v>
+      </c>
       <c r="N1073" s="3"/>
     </row>
     <row r="1074" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1074" s="3" t="s">
-        <v>3395</v>
+        <v>3397</v>
       </c>
       <c r="B1074" s="3"/>
       <c r="C1074" s="3">
@@ -51384,10 +51870,10 @@
         <v>18</v>
       </c>
       <c r="F1074" s="3" t="s">
-        <v>3396</v>
+        <v>3398</v>
       </c>
       <c r="G1074" s="3" t="s">
-        <v>3397</v>
+        <v>3399</v>
       </c>
       <c r="H1074" s="3"/>
       <c r="I1074" s="3">
@@ -51405,9 +51891,11 @@
     </row>
     <row r="1075" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1075" s="3" t="s">
-        <v>3398</v>
-      </c>
-      <c r="B1075" s="3"/>
+        <v>3400</v>
+      </c>
+      <c r="B1075" s="3" t="s">
+        <v>149</v>
+      </c>
       <c r="C1075" s="3">
         <v>339</v>
       </c>
@@ -51418,10 +51906,10 @@
         <v>18</v>
       </c>
       <c r="F1075" s="3" t="s">
-        <v>3399</v>
+        <v>3401</v>
       </c>
       <c r="G1075" s="3" t="s">
-        <v>3400</v>
+        <v>3402</v>
       </c>
       <c r="H1075" s="3"/>
       <c r="I1075" s="3">
@@ -51439,7 +51927,7 @@
     </row>
     <row r="1076" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1076" s="3" t="s">
-        <v>3401</v>
+        <v>3403</v>
       </c>
       <c r="B1076" s="3"/>
       <c r="C1076" s="3">
@@ -51452,26 +51940,32 @@
         <v>24</v>
       </c>
       <c r="F1076" s="3" t="s">
-        <v>3402</v>
+        <v>3404</v>
       </c>
       <c r="G1076" s="3" t="s">
-        <v>3403</v>
-      </c>
-      <c r="H1076" s="3"/>
+        <v>3405</v>
+      </c>
+      <c r="H1076" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="I1076" s="3">
         <v>43</v>
       </c>
       <c r="J1076" s="3"/>
       <c r="K1076" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1076" s="3"/>
-      <c r="M1076" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L1076" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1076" s="3" t="s">
+        <v>3390</v>
+      </c>
       <c r="N1076" s="3"/>
     </row>
     <row r="1077" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1077" s="3" t="s">
-        <v>3404</v>
+        <v>3406</v>
       </c>
       <c r="B1077" s="3" t="s">
         <v>74</v>
@@ -51486,26 +51980,32 @@
         <v>65</v>
       </c>
       <c r="F1077" s="3" t="s">
-        <v>3405</v>
+        <v>3407</v>
       </c>
       <c r="G1077" s="3" t="s">
-        <v>3406</v>
-      </c>
-      <c r="H1077" s="3"/>
+        <v>3408</v>
+      </c>
+      <c r="H1077" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="I1077" s="3">
         <v>28</v>
       </c>
       <c r="J1077" s="3"/>
       <c r="K1077" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1077" s="3"/>
-      <c r="M1077" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L1077" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1077" s="3" t="s">
+        <v>3390</v>
+      </c>
       <c r="N1077" s="3"/>
     </row>
     <row r="1078" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1078" s="3" t="s">
-        <v>3407</v>
+        <v>3409</v>
       </c>
       <c r="B1078" s="3" t="s">
         <v>74</v>
@@ -51520,13 +52020,13 @@
         <v>43</v>
       </c>
       <c r="F1078" s="3" t="s">
-        <v>3408</v>
+        <v>3410</v>
       </c>
       <c r="G1078" s="3" t="s">
-        <v>3409</v>
+        <v>3411</v>
       </c>
       <c r="H1078" s="3" t="s">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="I1078" s="3">
         <v>70</v>
@@ -51535,15 +52035,19 @@
         <v>75</v>
       </c>
       <c r="K1078" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1078" s="3"/>
-      <c r="M1078" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L1078" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1078" s="3" t="s">
+        <v>3390</v>
+      </c>
       <c r="N1078" s="3"/>
     </row>
     <row r="1079" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1079" s="3" t="s">
-        <v>3410</v>
+        <v>3412</v>
       </c>
       <c r="B1079" s="3" t="s">
         <v>74</v>
@@ -51558,10 +52062,10 @@
         <v>47</v>
       </c>
       <c r="F1079" s="3" t="s">
-        <v>3411</v>
+        <v>3413</v>
       </c>
       <c r="G1079" s="3" t="s">
-        <v>3412</v>
+        <v>3414</v>
       </c>
       <c r="H1079" s="3" t="s">
         <v>98</v>
@@ -51573,15 +52077,19 @@
         <v>65</v>
       </c>
       <c r="K1079" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1079" s="3"/>
-      <c r="M1079" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L1079" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1079" s="3" t="s">
+        <v>3415</v>
+      </c>
       <c r="N1079" s="3"/>
     </row>
     <row r="1080" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1080" s="3" t="s">
-        <v>3413</v>
+        <v>3416</v>
       </c>
       <c r="B1080" s="3"/>
       <c r="C1080" s="3">
@@ -51594,10 +52102,10 @@
         <v>47</v>
       </c>
       <c r="F1080" s="3" t="s">
-        <v>3414</v>
+        <v>3417</v>
       </c>
       <c r="G1080" s="3" t="s">
-        <v>3415</v>
+        <v>3418</v>
       </c>
       <c r="H1080" s="3" t="s">
         <v>98</v>
@@ -51609,15 +52117,19 @@
         <v>70</v>
       </c>
       <c r="K1080" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1080" s="3"/>
-      <c r="M1080" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L1080" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1080" s="3" t="s">
+        <v>3419</v>
+      </c>
       <c r="N1080" s="3"/>
     </row>
     <row r="1081" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1081" s="3" t="s">
-        <v>3416</v>
+        <v>3420</v>
       </c>
       <c r="B1081" s="3" t="s">
         <v>339</v>
@@ -51632,12 +52144,14 @@
         <v>24</v>
       </c>
       <c r="F1081" s="3" t="s">
-        <v>3417</v>
+        <v>3421</v>
       </c>
       <c r="G1081" s="3" t="s">
-        <v>3418</v>
-      </c>
-      <c r="H1081" s="3"/>
+        <v>3422</v>
+      </c>
+      <c r="H1081" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="I1081" s="3">
         <v>33</v>
       </c>
@@ -51645,15 +52159,19 @@
         <v>55</v>
       </c>
       <c r="K1081" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1081" s="3"/>
-      <c r="M1081" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L1081" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1081" s="3" t="s">
+        <v>3419</v>
+      </c>
       <c r="N1081" s="3"/>
     </row>
     <row r="1082" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1082" s="3" t="s">
-        <v>3419</v>
+        <v>3423</v>
       </c>
       <c r="B1082" s="3" t="s">
         <v>74</v>
@@ -51668,10 +52186,10 @@
         <v>47</v>
       </c>
       <c r="F1082" s="3" t="s">
-        <v>3420</v>
+        <v>3424</v>
       </c>
       <c r="G1082" s="3" t="s">
-        <v>3421</v>
+        <v>3425</v>
       </c>
       <c r="H1082" s="3"/>
       <c r="I1082" s="3">
@@ -51687,7 +52205,7 @@
     </row>
     <row r="1083" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1083" s="3" t="s">
-        <v>3419</v>
+        <v>3423</v>
       </c>
       <c r="B1083" s="3" t="s">
         <v>74</v>
@@ -51702,28 +52220,32 @@
         <v>43</v>
       </c>
       <c r="F1083" s="3" t="s">
-        <v>3422</v>
+        <v>3426</v>
       </c>
       <c r="G1083" s="3" t="s">
-        <v>3423</v>
+        <v>3427</v>
       </c>
       <c r="H1083" s="3" t="s">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="I1083" s="3">
         <v>66</v>
       </c>
       <c r="J1083" s="3"/>
       <c r="K1083" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1083" s="3"/>
-      <c r="M1083" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L1083" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1083" s="3" t="s">
+        <v>3419</v>
+      </c>
       <c r="N1083" s="3"/>
     </row>
     <row r="1084" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1084" s="3" t="s">
-        <v>3424</v>
+        <v>3428</v>
       </c>
       <c r="B1084" s="3" t="s">
         <v>424</v>
@@ -51738,13 +52260,13 @@
         <v>24</v>
       </c>
       <c r="F1084" s="3" t="s">
-        <v>3425</v>
+        <v>3429</v>
       </c>
       <c r="G1084" s="3" t="s">
-        <v>3426</v>
+        <v>3430</v>
       </c>
       <c r="H1084" s="3" t="s">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="I1084" s="3">
         <v>66</v>
@@ -51753,15 +52275,19 @@
         <v>80</v>
       </c>
       <c r="K1084" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1084" s="3"/>
-      <c r="M1084" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L1084" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1084" s="3" t="s">
+        <v>3419</v>
+      </c>
       <c r="N1084" s="3"/>
     </row>
     <row r="1085" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1085" s="3" t="s">
-        <v>3427</v>
+        <v>3431</v>
       </c>
       <c r="B1085" s="3" t="s">
         <v>424</v>
@@ -51776,13 +52302,13 @@
         <v>47</v>
       </c>
       <c r="F1085" s="3" t="s">
-        <v>3428</v>
+        <v>3432</v>
       </c>
       <c r="G1085" s="3" t="s">
-        <v>3429</v>
+        <v>3433</v>
       </c>
       <c r="H1085" s="3" t="s">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="I1085" s="3">
         <v>72</v>
@@ -51791,15 +52317,19 @@
         <v>80</v>
       </c>
       <c r="K1085" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1085" s="3"/>
-      <c r="M1085" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L1085" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1085" s="3" t="s">
+        <v>3419</v>
+      </c>
       <c r="N1085" s="3"/>
     </row>
     <row r="1086" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1086" s="3" t="s">
-        <v>3427</v>
+        <v>3431</v>
       </c>
       <c r="B1086" s="3" t="s">
         <v>424</v>
@@ -51814,13 +52344,13 @@
         <v>43</v>
       </c>
       <c r="F1086" s="3" t="s">
-        <v>3430</v>
+        <v>3434</v>
       </c>
       <c r="G1086" s="3" t="s">
-        <v>3431</v>
+        <v>3435</v>
       </c>
       <c r="H1086" s="3" t="s">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="I1086" s="3">
         <v>72</v>
@@ -51829,11 +52359,1945 @@
         <v>80</v>
       </c>
       <c r="K1086" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1086" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1086" s="3" t="s">
+        <v>3419</v>
+      </c>
+      <c r="N1086" s="3"/>
+    </row>
+    <row r="1087" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1087" s="3" t="s">
+        <v>3436</v>
+      </c>
+      <c r="B1087" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1087" s="3">
+        <v>210</v>
+      </c>
+      <c r="D1087" s="3">
+        <v>1554454137</v>
+      </c>
+      <c r="E1087" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1087" s="3" t="s">
+        <v>3437</v>
+      </c>
+      <c r="G1087" s="3" t="s">
+        <v>3438</v>
+      </c>
+      <c r="H1087" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1087" s="3">
+        <v>60</v>
+      </c>
+      <c r="J1087" s="3"/>
+      <c r="K1087" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1087" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1087" s="3" t="s">
+        <v>3419</v>
+      </c>
+      <c r="N1087" s="3"/>
+    </row>
+    <row r="1088" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1088" s="3" t="s">
+        <v>3439</v>
+      </c>
+      <c r="B1088" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1088" s="3">
+        <v>839</v>
+      </c>
+      <c r="D1088" s="3">
+        <v>1554838220</v>
+      </c>
+      <c r="E1088" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1088" s="3" t="s">
+        <v>3440</v>
+      </c>
+      <c r="G1088" s="3" t="s">
+        <v>3441</v>
+      </c>
+      <c r="H1088" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1088" s="3">
+        <v>65</v>
+      </c>
+      <c r="J1088" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1088" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1088" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1088" s="3" t="s">
+        <v>3442</v>
+      </c>
+      <c r="N1088" s="3"/>
+    </row>
+    <row r="1089" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1089" s="3" t="s">
+        <v>3443</v>
+      </c>
+      <c r="B1089" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1089" s="3">
+        <v>86</v>
+      </c>
+      <c r="D1089" s="3">
+        <v>1555114158</v>
+      </c>
+      <c r="E1089" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1089" s="3" t="s">
+        <v>3444</v>
+      </c>
+      <c r="G1089" s="3" t="s">
+        <v>3445</v>
+      </c>
+      <c r="H1089" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1089" s="3">
+        <v>73</v>
+      </c>
+      <c r="J1089" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1089" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1089" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1089" s="3" t="s">
+        <v>3442</v>
+      </c>
+      <c r="N1089" s="3"/>
+    </row>
+    <row r="1090" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1090" s="3" t="s">
+        <v>3443</v>
+      </c>
+      <c r="B1090" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1090" s="3">
+        <v>86</v>
+      </c>
+      <c r="D1090" s="3">
+        <v>1555114168</v>
+      </c>
+      <c r="E1090" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1090" s="3" t="s">
+        <v>3446</v>
+      </c>
+      <c r="G1090" s="3" t="s">
+        <v>3447</v>
+      </c>
+      <c r="H1090" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1090" s="3">
+        <v>73</v>
+      </c>
+      <c r="J1090" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1090" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1090" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1090" s="3" t="s">
+        <v>3442</v>
+      </c>
+      <c r="N1090" s="3"/>
+    </row>
+    <row r="1091" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1091" s="3" t="s">
+        <v>3448</v>
+      </c>
+      <c r="B1091" s="3"/>
+      <c r="C1091" s="3">
+        <v>209</v>
+      </c>
+      <c r="D1091" s="3">
+        <v>1555183824</v>
+      </c>
+      <c r="E1091" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1091" s="3" t="s">
+        <v>3449</v>
+      </c>
+      <c r="G1091" s="3" t="s">
+        <v>3450</v>
+      </c>
+      <c r="H1091" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1091" s="3">
+        <v>67</v>
+      </c>
+      <c r="J1091" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1091" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1091" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1091" s="3" t="s">
+        <v>3442</v>
+      </c>
+      <c r="N1091" s="3"/>
+    </row>
+    <row r="1092" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1092" s="3" t="s">
+        <v>3451</v>
+      </c>
+      <c r="B1092" s="3"/>
+      <c r="C1092" s="3">
+        <v>209</v>
+      </c>
+      <c r="D1092" s="3">
+        <v>1555195802</v>
+      </c>
+      <c r="E1092" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1092" s="3" t="s">
+        <v>3452</v>
+      </c>
+      <c r="G1092" s="3" t="s">
+        <v>3453</v>
+      </c>
+      <c r="H1092" s="3"/>
+      <c r="I1092" s="3">
+        <v>67</v>
+      </c>
+      <c r="J1092" s="3">
+        <v>80</v>
+      </c>
+      <c r="K1092" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L1086" s="3"/>
-      <c r="M1086" s="3"/>
-      <c r="N1086" s="3"/>
+      <c r="L1092" s="3"/>
+      <c r="M1092" s="3"/>
+      <c r="N1092" s="3"/>
+    </row>
+    <row r="1093" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1093" s="3" t="s">
+        <v>3454</v>
+      </c>
+      <c r="B1093" s="3"/>
+      <c r="C1093" s="3">
+        <v>209</v>
+      </c>
+      <c r="D1093" s="3">
+        <v>1555216083</v>
+      </c>
+      <c r="E1093" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F1093" s="3" t="s">
+        <v>3455</v>
+      </c>
+      <c r="G1093" s="3" t="s">
+        <v>3456</v>
+      </c>
+      <c r="H1093" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1093" s="3">
+        <v>68</v>
+      </c>
+      <c r="J1093" s="3">
+        <v>80</v>
+      </c>
+      <c r="K1093" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1093" s="3"/>
+      <c r="M1093" s="3"/>
+      <c r="N1093" s="3"/>
+    </row>
+    <row r="1094" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1094" s="3" t="s">
+        <v>3457</v>
+      </c>
+      <c r="B1094" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C1094" s="3">
+        <v>339</v>
+      </c>
+      <c r="D1094" s="3">
+        <v>1555228135</v>
+      </c>
+      <c r="E1094" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1094" s="3" t="s">
+        <v>3458</v>
+      </c>
+      <c r="G1094" s="3" t="s">
+        <v>3459</v>
+      </c>
+      <c r="H1094" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1094" s="3">
+        <v>70</v>
+      </c>
+      <c r="J1094" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1094" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1094" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1094" s="3" t="s">
+        <v>3442</v>
+      </c>
+      <c r="N1094" s="3"/>
+    </row>
+    <row r="1095" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1095" s="3" t="s">
+        <v>3460</v>
+      </c>
+      <c r="B1095" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C1095" s="3">
+        <v>339</v>
+      </c>
+      <c r="D1095" s="3">
+        <v>1555259805</v>
+      </c>
+      <c r="E1095" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1095" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="G1095" s="3" t="s">
+        <v>3461</v>
+      </c>
+      <c r="H1095" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1095" s="3">
+        <v>20</v>
+      </c>
+      <c r="J1095" s="3"/>
+      <c r="K1095" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1095" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1095" s="3" t="s">
+        <v>3462</v>
+      </c>
+      <c r="N1095" s="3"/>
+    </row>
+    <row r="1096" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1096" s="3" t="s">
+        <v>3460</v>
+      </c>
+      <c r="B1096" s="3"/>
+      <c r="C1096" s="3">
+        <v>209</v>
+      </c>
+      <c r="D1096" s="3">
+        <v>1555260049</v>
+      </c>
+      <c r="E1096" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="F1096" s="3" t="s">
+        <v>3463</v>
+      </c>
+      <c r="G1096" s="3" t="s">
+        <v>3464</v>
+      </c>
+      <c r="H1096" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1096" s="3"/>
+      <c r="J1096" s="3"/>
+      <c r="K1096" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1096" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1096" s="3" t="s">
+        <v>3465</v>
+      </c>
+      <c r="N1096" s="3"/>
+    </row>
+    <row r="1097" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1097" s="3" t="s">
+        <v>3466</v>
+      </c>
+      <c r="B1097" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="C1097" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="D1097" s="3">
+        <v>1555830211</v>
+      </c>
+      <c r="E1097" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1097" s="3" t="s">
+        <v>3467</v>
+      </c>
+      <c r="G1097" s="3" t="s">
+        <v>3468</v>
+      </c>
+      <c r="H1097" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1097" s="3">
+        <v>68</v>
+      </c>
+      <c r="J1097" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1097" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1097" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1097" s="3" t="s">
+        <v>3469</v>
+      </c>
+      <c r="N1097" s="3"/>
+    </row>
+    <row r="1098" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1098" s="3" t="s">
+        <v>3470</v>
+      </c>
+      <c r="B1098" s="3"/>
+      <c r="C1098" s="3">
+        <v>340</v>
+      </c>
+      <c r="D1098" s="3">
+        <v>1555945224</v>
+      </c>
+      <c r="E1098" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1098" s="3" t="s">
+        <v>3471</v>
+      </c>
+      <c r="G1098" s="3" t="s">
+        <v>3472</v>
+      </c>
+      <c r="H1098" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1098" s="3">
+        <v>39</v>
+      </c>
+      <c r="J1098" s="3"/>
+      <c r="K1098" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1098" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1098" s="3" t="s">
+        <v>3469</v>
+      </c>
+      <c r="N1098" s="3"/>
+    </row>
+    <row r="1099" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1099" s="3" t="s">
+        <v>3473</v>
+      </c>
+      <c r="B1099" s="3"/>
+      <c r="C1099" s="3">
+        <v>209</v>
+      </c>
+      <c r="D1099" s="3">
+        <v>1555991087</v>
+      </c>
+      <c r="E1099" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F1099" s="3" t="s">
+        <v>3474</v>
+      </c>
+      <c r="G1099" s="3" t="s">
+        <v>3475</v>
+      </c>
+      <c r="H1099" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1099" s="3">
+        <v>66</v>
+      </c>
+      <c r="J1099" s="3"/>
+      <c r="K1099" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1099" s="3"/>
+      <c r="M1099" s="3"/>
+      <c r="N1099" s="3"/>
+    </row>
+    <row r="1100" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1100" s="3" t="s">
+        <v>3476</v>
+      </c>
+      <c r="B1100" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C1100" s="3">
+        <v>339</v>
+      </c>
+      <c r="D1100" s="3">
+        <v>1556009852</v>
+      </c>
+      <c r="E1100" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1100" s="3" t="s">
+        <v>3477</v>
+      </c>
+      <c r="G1100" s="3" t="s">
+        <v>3478</v>
+      </c>
+      <c r="H1100" s="3"/>
+      <c r="I1100" s="3">
+        <v>64</v>
+      </c>
+      <c r="J1100" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1100" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1100" s="3"/>
+      <c r="M1100" s="3"/>
+      <c r="N1100" s="3"/>
+    </row>
+    <row r="1101" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1101" s="3" t="s">
+        <v>3479</v>
+      </c>
+      <c r="B1101" s="3"/>
+      <c r="C1101" s="3">
+        <v>209</v>
+      </c>
+      <c r="D1101" s="3">
+        <v>1556010645</v>
+      </c>
+      <c r="E1101" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F1101" s="3" t="s">
+        <v>3480</v>
+      </c>
+      <c r="G1101" s="3" t="s">
+        <v>3481</v>
+      </c>
+      <c r="H1101" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1101" s="3">
+        <v>65</v>
+      </c>
+      <c r="J1101" s="3"/>
+      <c r="K1101" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1101" s="3"/>
+      <c r="M1101" s="3"/>
+      <c r="N1101" s="3"/>
+    </row>
+    <row r="1102" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1102" s="3" t="s">
+        <v>3482</v>
+      </c>
+      <c r="B1102" s="3"/>
+      <c r="C1102" s="3">
+        <v>209</v>
+      </c>
+      <c r="D1102" s="3">
+        <v>1556017360</v>
+      </c>
+      <c r="E1102" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="F1102" s="3" t="s">
+        <v>3483</v>
+      </c>
+      <c r="G1102" s="3" t="s">
+        <v>3484</v>
+      </c>
+      <c r="H1102" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1102" s="3">
+        <v>66</v>
+      </c>
+      <c r="J1102" s="3">
+        <v>80</v>
+      </c>
+      <c r="K1102" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1102" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1102" s="3" t="s">
+        <v>3469</v>
+      </c>
+      <c r="N1102" s="3"/>
+    </row>
+    <row r="1103" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1103" s="3" t="s">
+        <v>3485</v>
+      </c>
+      <c r="B1103" s="3"/>
+      <c r="C1103" s="3">
+        <v>209</v>
+      </c>
+      <c r="D1103" s="3">
+        <v>1556029736</v>
+      </c>
+      <c r="E1103" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F1103" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="G1103" s="3" t="s">
+        <v>3486</v>
+      </c>
+      <c r="H1103" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1103" s="3">
+        <v>73</v>
+      </c>
+      <c r="J1103" s="3">
+        <v>80</v>
+      </c>
+      <c r="K1103" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1103" s="3"/>
+      <c r="M1103" s="3"/>
+      <c r="N1103" s="3"/>
+    </row>
+    <row r="1104" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1104" s="3" t="s">
+        <v>3487</v>
+      </c>
+      <c r="B1104" s="3"/>
+      <c r="C1104" s="3">
+        <v>209</v>
+      </c>
+      <c r="D1104" s="3">
+        <v>1556047789</v>
+      </c>
+      <c r="E1104" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F1104" s="3" t="s">
+        <v>3488</v>
+      </c>
+      <c r="G1104" s="3" t="s">
+        <v>3489</v>
+      </c>
+      <c r="H1104" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1104" s="3">
+        <v>69</v>
+      </c>
+      <c r="J1104" s="3"/>
+      <c r="K1104" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1104" s="3"/>
+      <c r="M1104" s="3"/>
+      <c r="N1104" s="3"/>
+    </row>
+    <row r="1105" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1105" s="3" t="s">
+        <v>3490</v>
+      </c>
+      <c r="B1105" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C1105" s="3">
+        <v>731</v>
+      </c>
+      <c r="D1105" s="3">
+        <v>1556173223</v>
+      </c>
+      <c r="E1105" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1105" s="3" t="s">
+        <v>3491</v>
+      </c>
+      <c r="G1105" s="3" t="s">
+        <v>3492</v>
+      </c>
+      <c r="H1105" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1105" s="3">
+        <v>66</v>
+      </c>
+      <c r="J1105" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1105" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1105" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1105" s="3" t="s">
+        <v>3469</v>
+      </c>
+      <c r="N1105" s="3"/>
+    </row>
+    <row r="1106" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1106" s="3" t="s">
+        <v>3493</v>
+      </c>
+      <c r="B1106" s="3"/>
+      <c r="C1106" s="3">
+        <v>672</v>
+      </c>
+      <c r="D1106" s="3">
+        <v>1556290888</v>
+      </c>
+      <c r="E1106" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1106" s="3" t="s">
+        <v>3494</v>
+      </c>
+      <c r="G1106" s="3" t="s">
+        <v>3495</v>
+      </c>
+      <c r="H1106" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1106" s="3">
+        <v>70</v>
+      </c>
+      <c r="J1106" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1106" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1106" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1106" s="3" t="s">
+        <v>3496</v>
+      </c>
+      <c r="N1106" s="3"/>
+    </row>
+    <row r="1107" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1107" s="3" t="s">
+        <v>3493</v>
+      </c>
+      <c r="B1107" s="3" t="s">
+        <v>1641</v>
+      </c>
+      <c r="C1107" s="3">
+        <v>672</v>
+      </c>
+      <c r="D1107" s="3">
+        <v>1556290892</v>
+      </c>
+      <c r="E1107" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1107" s="3" t="s">
+        <v>3497</v>
+      </c>
+      <c r="G1107" s="3" t="s">
+        <v>3498</v>
+      </c>
+      <c r="H1107" s="3"/>
+      <c r="I1107" s="3">
+        <v>70</v>
+      </c>
+      <c r="J1107" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1107" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1107" s="3"/>
+      <c r="M1107" s="3"/>
+      <c r="N1107" s="3"/>
+    </row>
+    <row r="1108" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1108" s="3" t="s">
+        <v>3499</v>
+      </c>
+      <c r="B1108" s="3"/>
+      <c r="C1108" s="3">
+        <v>840</v>
+      </c>
+      <c r="D1108" s="3">
+        <v>1556675988</v>
+      </c>
+      <c r="E1108" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1108" s="3" t="s">
+        <v>3500</v>
+      </c>
+      <c r="G1108" s="3" t="s">
+        <v>3501</v>
+      </c>
+      <c r="H1108" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1108" s="3">
+        <v>32</v>
+      </c>
+      <c r="J1108" s="3"/>
+      <c r="K1108" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1108" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1108" s="3" t="s">
+        <v>3496</v>
+      </c>
+      <c r="N1108" s="3"/>
+    </row>
+    <row r="1109" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1109" s="3" t="s">
+        <v>3502</v>
+      </c>
+      <c r="B1109" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C1109" s="3">
+        <v>339</v>
+      </c>
+      <c r="D1109" s="3">
+        <v>1556851523</v>
+      </c>
+      <c r="E1109" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1109" s="3" t="s">
+        <v>3503</v>
+      </c>
+      <c r="G1109" s="3" t="s">
+        <v>3504</v>
+      </c>
+      <c r="H1109" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1109" s="3">
+        <v>70</v>
+      </c>
+      <c r="J1109" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1109" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1109" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1109" s="3" t="s">
+        <v>3496</v>
+      </c>
+      <c r="N1109" s="3"/>
+    </row>
+    <row r="1110" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1110" s="3" t="s">
+        <v>3505</v>
+      </c>
+      <c r="B1110" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C1110" s="3">
+        <v>339</v>
+      </c>
+      <c r="D1110" s="3">
+        <v>1556854971</v>
+      </c>
+      <c r="E1110" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1110" s="3" t="s">
+        <v>3506</v>
+      </c>
+      <c r="G1110" s="3" t="s">
+        <v>3507</v>
+      </c>
+      <c r="H1110" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1110" s="3">
+        <v>74</v>
+      </c>
+      <c r="J1110" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1110" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1110" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1110" s="3" t="s">
+        <v>3508</v>
+      </c>
+      <c r="N1110" s="3"/>
+    </row>
+    <row r="1111" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1111" s="3" t="s">
+        <v>3509</v>
+      </c>
+      <c r="B1111" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C1111" s="3">
+        <v>339</v>
+      </c>
+      <c r="D1111" s="3">
+        <v>1556877434</v>
+      </c>
+      <c r="E1111" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1111" s="3" t="s">
+        <v>3510</v>
+      </c>
+      <c r="G1111" s="3" t="s">
+        <v>3511</v>
+      </c>
+      <c r="H1111" s="3"/>
+      <c r="I1111" s="3">
+        <v>74</v>
+      </c>
+      <c r="J1111" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1111" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1111" s="3"/>
+      <c r="M1111" s="3"/>
+      <c r="N1111" s="3"/>
+    </row>
+    <row r="1112" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1112" s="3" t="s">
+        <v>3509</v>
+      </c>
+      <c r="B1112" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C1112" s="3">
+        <v>339</v>
+      </c>
+      <c r="D1112" s="3">
+        <v>1556877429</v>
+      </c>
+      <c r="E1112" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1112" s="3" t="s">
+        <v>3512</v>
+      </c>
+      <c r="G1112" s="3" t="s">
+        <v>3513</v>
+      </c>
+      <c r="H1112" s="3"/>
+      <c r="I1112" s="3">
+        <v>69</v>
+      </c>
+      <c r="J1112" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1112" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1112" s="3"/>
+      <c r="M1112" s="3"/>
+      <c r="N1112" s="3"/>
+    </row>
+    <row r="1113" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1113" s="3" t="s">
+        <v>3514</v>
+      </c>
+      <c r="B1113" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C1113" s="3">
+        <v>339</v>
+      </c>
+      <c r="D1113" s="3">
+        <v>1556916212</v>
+      </c>
+      <c r="E1113" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1113" s="3" t="s">
+        <v>3515</v>
+      </c>
+      <c r="G1113" s="3" t="s">
+        <v>3516</v>
+      </c>
+      <c r="H1113" s="3"/>
+      <c r="I1113" s="3">
+        <v>73</v>
+      </c>
+      <c r="J1113" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1113" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1113" s="3"/>
+      <c r="M1113" s="3"/>
+      <c r="N1113" s="3"/>
+    </row>
+    <row r="1114" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1114" s="3" t="s">
+        <v>3517</v>
+      </c>
+      <c r="B1114" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1114" s="3">
+        <v>336</v>
+      </c>
+      <c r="D1114" s="3">
+        <v>1557005441</v>
+      </c>
+      <c r="E1114" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1114" s="3" t="s">
+        <v>3518</v>
+      </c>
+      <c r="G1114" s="3" t="s">
+        <v>3519</v>
+      </c>
+      <c r="H1114" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1114" s="3">
+        <v>65</v>
+      </c>
+      <c r="J1114" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1114" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1114" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1114" s="3" t="s">
+        <v>3508</v>
+      </c>
+      <c r="N1114" s="3"/>
+    </row>
+    <row r="1115" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1115" s="3" t="s">
+        <v>3520</v>
+      </c>
+      <c r="B1115" s="3"/>
+      <c r="C1115" s="3">
+        <v>340</v>
+      </c>
+      <c r="D1115" s="3">
+        <v>1557014291</v>
+      </c>
+      <c r="E1115" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1115" s="3" t="s">
+        <v>3521</v>
+      </c>
+      <c r="G1115" s="3" t="s">
+        <v>3522</v>
+      </c>
+      <c r="H1115" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1115" s="3">
+        <v>33</v>
+      </c>
+      <c r="J1115" s="3"/>
+      <c r="K1115" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1115" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1115" s="3" t="s">
+        <v>3508</v>
+      </c>
+      <c r="N1115" s="3"/>
+    </row>
+    <row r="1116" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1116" s="3" t="s">
+        <v>3523</v>
+      </c>
+      <c r="B1116" s="3"/>
+      <c r="C1116" s="3">
+        <v>340</v>
+      </c>
+      <c r="D1116" s="3">
+        <v>1557026144</v>
+      </c>
+      <c r="E1116" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1116" s="3" t="s">
+        <v>1309</v>
+      </c>
+      <c r="G1116" s="3" t="s">
+        <v>3524</v>
+      </c>
+      <c r="H1116" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1116" s="3">
+        <v>63</v>
+      </c>
+      <c r="J1116" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1116" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1116" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1116" s="3" t="s">
+        <v>3508</v>
+      </c>
+      <c r="N1116" s="3"/>
+    </row>
+    <row r="1117" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1117" s="3" t="s">
+        <v>3525</v>
+      </c>
+      <c r="B1117" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1117" s="3">
+        <v>336</v>
+      </c>
+      <c r="D1117" s="3">
+        <v>1557036309</v>
+      </c>
+      <c r="E1117" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1117" s="3" t="s">
+        <v>3526</v>
+      </c>
+      <c r="G1117" s="3" t="s">
+        <v>3527</v>
+      </c>
+      <c r="H1117" s="3"/>
+      <c r="I1117" s="3">
+        <v>65</v>
+      </c>
+      <c r="J1117" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1117" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1117" s="3"/>
+      <c r="M1117" s="3"/>
+      <c r="N1117" s="3"/>
+    </row>
+    <row r="1118" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1118" s="3" t="s">
+        <v>3528</v>
+      </c>
+      <c r="B1118" s="3"/>
+      <c r="C1118" s="3">
+        <v>209</v>
+      </c>
+      <c r="D1118" s="3">
+        <v>1557086813</v>
+      </c>
+      <c r="E1118" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1118" s="3" t="s">
+        <v>3529</v>
+      </c>
+      <c r="G1118" s="3" t="s">
+        <v>3530</v>
+      </c>
+      <c r="H1118" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1118" s="3">
+        <v>25</v>
+      </c>
+      <c r="J1118" s="3"/>
+      <c r="K1118" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1118" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1118" s="3" t="s">
+        <v>3508</v>
+      </c>
+      <c r="N1118" s="3"/>
+    </row>
+    <row r="1119" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1119" s="3" t="s">
+        <v>3531</v>
+      </c>
+      <c r="B1119" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C1119" s="3">
+        <v>731</v>
+      </c>
+      <c r="D1119" s="3">
+        <v>1557109265</v>
+      </c>
+      <c r="E1119" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1119" s="3" t="s">
+        <v>3532</v>
+      </c>
+      <c r="G1119" s="3" t="s">
+        <v>3533</v>
+      </c>
+      <c r="H1119" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1119" s="3">
+        <v>44</v>
+      </c>
+      <c r="J1119" s="3"/>
+      <c r="K1119" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1119" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1119" s="3" t="s">
+        <v>3508</v>
+      </c>
+      <c r="N1119" s="3"/>
+    </row>
+    <row r="1120" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1120" s="3" t="s">
+        <v>3534</v>
+      </c>
+      <c r="B1120" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1120" s="3">
+        <v>839</v>
+      </c>
+      <c r="D1120" s="3">
+        <v>1557161846</v>
+      </c>
+      <c r="E1120" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1120" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="G1120" s="3" t="s">
+        <v>3535</v>
+      </c>
+      <c r="H1120" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1120" s="3">
+        <v>21</v>
+      </c>
+      <c r="J1120" s="3"/>
+      <c r="K1120" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1120" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1120" s="3" t="s">
+        <v>3536</v>
+      </c>
+      <c r="N1120" s="3"/>
+    </row>
+    <row r="1121" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1121" s="3" t="s">
+        <v>3537</v>
+      </c>
+      <c r="B1121" s="3"/>
+      <c r="C1121" s="3">
+        <v>375</v>
+      </c>
+      <c r="D1121" s="3">
+        <v>1557173266</v>
+      </c>
+      <c r="E1121" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1121" s="3" t="s">
+        <v>3538</v>
+      </c>
+      <c r="G1121" s="3" t="s">
+        <v>3539</v>
+      </c>
+      <c r="H1121" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1121" s="3">
+        <v>60</v>
+      </c>
+      <c r="J1121" s="3">
+        <v>80</v>
+      </c>
+      <c r="K1121" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1121" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1121" s="3" t="s">
+        <v>3536</v>
+      </c>
+      <c r="N1121" s="3"/>
+    </row>
+    <row r="1122" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1122" s="3" t="s">
+        <v>3540</v>
+      </c>
+      <c r="B1122" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1122" s="3">
+        <v>839</v>
+      </c>
+      <c r="D1122" s="3">
+        <v>1557220190</v>
+      </c>
+      <c r="E1122" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1122" s="3" t="s">
+        <v>3541</v>
+      </c>
+      <c r="G1122" s="3" t="s">
+        <v>3542</v>
+      </c>
+      <c r="H1122" s="3"/>
+      <c r="I1122" s="3">
+        <v>64</v>
+      </c>
+      <c r="J1122" s="3">
+        <v>80</v>
+      </c>
+      <c r="K1122" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1122" s="3"/>
+      <c r="M1122" s="3"/>
+      <c r="N1122" s="3"/>
+    </row>
+    <row r="1123" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1123" s="3" t="s">
+        <v>3543</v>
+      </c>
+      <c r="B1123" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1123" s="3">
+        <v>86</v>
+      </c>
+      <c r="D1123" s="3">
+        <v>1557343636</v>
+      </c>
+      <c r="E1123" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1123" s="3" t="s">
+        <v>3544</v>
+      </c>
+      <c r="G1123" s="3" t="s">
+        <v>3545</v>
+      </c>
+      <c r="H1123" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1123" s="3">
+        <v>81</v>
+      </c>
+      <c r="J1123" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1123" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1123" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1123" s="3" t="s">
+        <v>3546</v>
+      </c>
+      <c r="N1123" s="3"/>
+    </row>
+    <row r="1124" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1124" s="3" t="s">
+        <v>3547</v>
+      </c>
+      <c r="B1124" s="3"/>
+      <c r="C1124" s="3">
+        <v>338</v>
+      </c>
+      <c r="D1124" s="3">
+        <v>1557438427</v>
+      </c>
+      <c r="E1124" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1124" s="3" t="s">
+        <v>3548</v>
+      </c>
+      <c r="G1124" s="3" t="s">
+        <v>3549</v>
+      </c>
+      <c r="H1124" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1124" s="3">
+        <v>11</v>
+      </c>
+      <c r="J1124" s="3"/>
+      <c r="K1124" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1124" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1124" s="3" t="s">
+        <v>3550</v>
+      </c>
+      <c r="N1124" s="3"/>
+    </row>
+    <row r="1125" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1125" s="3" t="s">
+        <v>3551</v>
+      </c>
+      <c r="B1125" s="3"/>
+      <c r="C1125" s="3">
+        <v>345</v>
+      </c>
+      <c r="D1125" s="3">
+        <v>1557470627</v>
+      </c>
+      <c r="E1125" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1125" s="3" t="s">
+        <v>3552</v>
+      </c>
+      <c r="G1125" s="3" t="s">
+        <v>3553</v>
+      </c>
+      <c r="H1125" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1125" s="3">
+        <v>23</v>
+      </c>
+      <c r="J1125" s="3"/>
+      <c r="K1125" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1125" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1125" s="3" t="s">
+        <v>3550</v>
+      </c>
+      <c r="N1125" s="3"/>
+    </row>
+    <row r="1126" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1126" s="3" t="s">
+        <v>3554</v>
+      </c>
+      <c r="B1126" s="3"/>
+      <c r="C1126" s="3">
+        <v>340</v>
+      </c>
+      <c r="D1126" s="3">
+        <v>1557791907</v>
+      </c>
+      <c r="E1126" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1126" s="3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="G1126" s="3" t="s">
+        <v>3555</v>
+      </c>
+      <c r="H1126" s="3"/>
+      <c r="I1126" s="3">
+        <v>45</v>
+      </c>
+      <c r="J1126" s="3"/>
+      <c r="K1126" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1126" s="3"/>
+      <c r="M1126" s="3"/>
+      <c r="N1126" s="3"/>
+    </row>
+    <row r="1127" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1127" s="3" t="s">
+        <v>3556</v>
+      </c>
+      <c r="B1127" s="3"/>
+      <c r="C1127" s="3">
+        <v>340</v>
+      </c>
+      <c r="D1127" s="3">
+        <v>1557822031</v>
+      </c>
+      <c r="E1127" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1127" s="3" t="s">
+        <v>3042</v>
+      </c>
+      <c r="G1127" s="3" t="s">
+        <v>3557</v>
+      </c>
+      <c r="H1127" s="3"/>
+      <c r="I1127" s="3">
+        <v>32</v>
+      </c>
+      <c r="J1127" s="3"/>
+      <c r="K1127" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1127" s="3"/>
+      <c r="M1127" s="3"/>
+      <c r="N1127" s="3"/>
+    </row>
+    <row r="1128" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1128" s="3" t="s">
+        <v>3558</v>
+      </c>
+      <c r="B1128" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1128" s="3">
+        <v>672</v>
+      </c>
+      <c r="D1128" s="3">
+        <v>1557940698</v>
+      </c>
+      <c r="E1128" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1128" s="3" t="s">
+        <v>3559</v>
+      </c>
+      <c r="G1128" s="3" t="s">
+        <v>3560</v>
+      </c>
+      <c r="H1128" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1128" s="3">
+        <v>70</v>
+      </c>
+      <c r="J1128" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1128" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1128" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1128" s="3" t="s">
+        <v>3561</v>
+      </c>
+      <c r="N1128" s="3"/>
+    </row>
+    <row r="1129" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1129" s="3" t="s">
+        <v>3562</v>
+      </c>
+      <c r="B1129" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1129" s="3">
+        <v>839</v>
+      </c>
+      <c r="D1129" s="3">
+        <v>1558160599</v>
+      </c>
+      <c r="E1129" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1129" s="3" t="s">
+        <v>3563</v>
+      </c>
+      <c r="G1129" s="3" t="s">
+        <v>3564</v>
+      </c>
+      <c r="H1129" s="3"/>
+      <c r="I1129" s="3">
+        <v>64</v>
+      </c>
+      <c r="J1129" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1129" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1129" s="3"/>
+      <c r="M1129" s="3"/>
+      <c r="N1129" s="3"/>
+    </row>
+    <row r="1130" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1130" s="3" t="s">
+        <v>3565</v>
+      </c>
+      <c r="B1130" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1130" s="3">
+        <v>672</v>
+      </c>
+      <c r="D1130" s="3">
+        <v>1558522254</v>
+      </c>
+      <c r="E1130" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1130" s="3" t="s">
+        <v>3566</v>
+      </c>
+      <c r="G1130" s="3" t="s">
+        <v>3567</v>
+      </c>
+      <c r="H1130" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1130" s="3">
+        <v>34</v>
+      </c>
+      <c r="J1130" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1130" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1130" s="3"/>
+      <c r="M1130" s="3"/>
+      <c r="N1130" s="3"/>
+    </row>
+    <row r="1131" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1131" s="3" t="s">
+        <v>3568</v>
+      </c>
+      <c r="B1131" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C1131" s="3">
+        <v>339</v>
+      </c>
+      <c r="D1131" s="3">
+        <v>1558653218</v>
+      </c>
+      <c r="E1131" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1131" s="3" t="s">
+        <v>3569</v>
+      </c>
+      <c r="G1131" s="3" t="s">
+        <v>3570</v>
+      </c>
+      <c r="H1131" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1131" s="3">
+        <v>54</v>
+      </c>
+      <c r="J1131" s="3"/>
+      <c r="K1131" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1131" s="3"/>
+      <c r="M1131" s="3"/>
+      <c r="N1131" s="3"/>
+    </row>
+    <row r="1132" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1132" s="3" t="s">
+        <v>3568</v>
+      </c>
+      <c r="B1132" s="3"/>
+      <c r="C1132" s="3">
+        <v>926</v>
+      </c>
+      <c r="D1132" s="3">
+        <v>1558652928</v>
+      </c>
+      <c r="E1132" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1132" s="3" t="s">
+        <v>3571</v>
+      </c>
+      <c r="G1132" s="3" t="s">
+        <v>3572</v>
+      </c>
+      <c r="H1132" s="3"/>
+      <c r="I1132" s="3">
+        <v>59</v>
+      </c>
+      <c r="J1132" s="3">
+        <v>80</v>
+      </c>
+      <c r="K1132" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1132" s="3"/>
+      <c r="M1132" s="3"/>
+      <c r="N1132" s="3"/>
+    </row>
+    <row r="1133" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1133" s="3" t="s">
+        <v>3573</v>
+      </c>
+      <c r="B1133" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1133" s="3">
+        <v>459</v>
+      </c>
+      <c r="D1133" s="3">
+        <v>1558773706</v>
+      </c>
+      <c r="E1133" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1133" s="3" t="s">
+        <v>3574</v>
+      </c>
+      <c r="G1133" s="3" t="s">
+        <v>3575</v>
+      </c>
+      <c r="H1133" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1133" s="3">
+        <v>23</v>
+      </c>
+      <c r="J1133" s="3"/>
+      <c r="K1133" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1133" s="3"/>
+      <c r="M1133" s="3"/>
+      <c r="N1133" s="3"/>
+    </row>
+    <row r="1134" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1134" s="3" t="s">
+        <v>3576</v>
+      </c>
+      <c r="B1134" s="3"/>
+      <c r="C1134" s="3">
+        <v>837</v>
+      </c>
+      <c r="D1134" s="3">
+        <v>1558854022</v>
+      </c>
+      <c r="E1134" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1134" s="3" t="s">
+        <v>3577</v>
+      </c>
+      <c r="G1134" s="3" t="s">
+        <v>3578</v>
+      </c>
+      <c r="H1134" s="3"/>
+      <c r="I1134" s="3">
+        <v>71</v>
+      </c>
+      <c r="J1134" s="3">
+        <v>55</v>
+      </c>
+      <c r="K1134" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1134" s="3"/>
+      <c r="M1134" s="3"/>
+      <c r="N1134" s="3"/>
+    </row>
+    <row r="1135" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1135" s="3" t="s">
+        <v>3579</v>
+      </c>
+      <c r="B1135" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1135" s="3">
+        <v>459</v>
+      </c>
+      <c r="D1135" s="3">
+        <v>1558960858</v>
+      </c>
+      <c r="E1135" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1135" s="3" t="s">
+        <v>3580</v>
+      </c>
+      <c r="G1135" s="3" t="s">
+        <v>3581</v>
+      </c>
+      <c r="H1135" s="3"/>
+      <c r="I1135" s="3">
+        <v>48</v>
+      </c>
+      <c r="J1135" s="3">
+        <v>40</v>
+      </c>
+      <c r="K1135" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1135" s="3"/>
+      <c r="M1135" s="3"/>
+      <c r="N1135" s="3"/>
+    </row>
+    <row r="1136" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1136" s="3" t="s">
+        <v>3582</v>
+      </c>
+      <c r="B1136" s="3"/>
+      <c r="C1136" s="3">
+        <v>209</v>
+      </c>
+      <c r="D1136" s="3">
+        <v>1559324144</v>
+      </c>
+      <c r="E1136" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1136" s="3" t="s">
+        <v>3583</v>
+      </c>
+      <c r="G1136" s="3" t="s">
+        <v>3584</v>
+      </c>
+      <c r="H1136" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1136" s="3">
+        <v>58</v>
+      </c>
+      <c r="J1136" s="3">
+        <v>80</v>
+      </c>
+      <c r="K1136" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1136" s="3"/>
+      <c r="M1136" s="3"/>
+      <c r="N1136" s="3"/>
+    </row>
+    <row r="1137" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1137" s="3" t="s">
+        <v>3585</v>
+      </c>
+      <c r="B1137" s="3"/>
+      <c r="C1137" s="3">
+        <v>837</v>
+      </c>
+      <c r="D1137" s="3">
+        <v>1559336258</v>
+      </c>
+      <c r="E1137" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1137" s="3" t="s">
+        <v>3586</v>
+      </c>
+      <c r="G1137" s="3" t="s">
+        <v>3587</v>
+      </c>
+      <c r="H1137" s="3"/>
+      <c r="I1137" s="3">
+        <v>77</v>
+      </c>
+      <c r="J1137" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1137" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1137" s="3"/>
+      <c r="M1137" s="3"/>
+      <c r="N1137" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\PCS-Trucking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{72419570-1BCB-4A89-ADA7-F8F92EAB2A44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{323FF9D7-C282-4EA3-A388-E62E33C82810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3420" yWindow="3420" windowWidth="43200" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRIVE-ALERTS" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8452" uniqueCount="3588">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8829" uniqueCount="3750">
   <si>
     <t>DRIVE ALERTS</t>
   </si>
@@ -10726,6 +10726,9 @@
     <t>39.901192, -80.146194</t>
   </si>
   <si>
+    <t>06/22/26 11:32 EDT</t>
+  </si>
+  <si>
     <t>06/19/26 14:22 EDT</t>
   </si>
   <si>
@@ -10768,6 +10771,9 @@
     <t>41.113928, -100.763787</t>
   </si>
   <si>
+    <t>06/22/26 11:47 EDT</t>
+  </si>
+  <si>
     <t>06/20/26 19:06 EDT</t>
   </si>
   <si>
@@ -10777,6 +10783,9 @@
     <t>41.643831, -108.544886</t>
   </si>
   <si>
+    <t>06/22/26 11:48 EDT</t>
+  </si>
+  <si>
     <t>06/20/26 19:48 EDT</t>
   </si>
   <si>
@@ -10784,6 +10793,483 @@
   </si>
   <si>
     <t>40.695899, -99.588162</t>
+  </si>
+  <si>
+    <t>06/21/26 18:08 EDT</t>
+  </si>
+  <si>
+    <t>21.6mi NW of Laramie WY</t>
+  </si>
+  <si>
+    <t>41.456718, -105.977037</t>
+  </si>
+  <si>
+    <t>06/21/26 21:56 EDT</t>
+  </si>
+  <si>
+    <t>36.037351, -115.197505</t>
+  </si>
+  <si>
+    <t>06/22/26 02:09 EDT</t>
+  </si>
+  <si>
+    <t>6.8mi NW of Moapa Valley NV</t>
+  </si>
+  <si>
+    <t>36.665703, -114.555827</t>
+  </si>
+  <si>
+    <t>06/22/26 02:14 EDT</t>
+  </si>
+  <si>
+    <t>4.5mi E of River Road OR</t>
+  </si>
+  <si>
+    <t>44.100515, -123.044570</t>
+  </si>
+  <si>
+    <t>06/23/26 12:19 EDT</t>
+  </si>
+  <si>
+    <t>06/22/26 10:35 EDT</t>
+  </si>
+  <si>
+    <t>2.4mi S of Chalco NE</t>
+  </si>
+  <si>
+    <t>41.146477, -96.140441</t>
+  </si>
+  <si>
+    <t>06/23/26 11:03 EDT</t>
+  </si>
+  <si>
+    <t>06/22/26 12:36 EDT</t>
+  </si>
+  <si>
+    <t>0.6mi NW of Payson UT</t>
+  </si>
+  <si>
+    <t>40.042841, -111.745829</t>
+  </si>
+  <si>
+    <t>06/23/26 12:20 EDT</t>
+  </si>
+  <si>
+    <t>06/22/26 14:31 EDT</t>
+  </si>
+  <si>
+    <t>1.9mi SE of Idaho Falls ID</t>
+  </si>
+  <si>
+    <t>43.468069, -112.009119</t>
+  </si>
+  <si>
+    <t>06/23/26 11:02 EDT</t>
+  </si>
+  <si>
+    <t>06/22/26 16:37 EDT</t>
+  </si>
+  <si>
+    <t>3.1mi S of Cedar City UT</t>
+  </si>
+  <si>
+    <t>37.638707, -113.095738</t>
+  </si>
+  <si>
+    <t>06/22/26 17:46 EDT</t>
+  </si>
+  <si>
+    <t>15.9mi E of Barstow CA</t>
+  </si>
+  <si>
+    <t>34.844614, -116.768207</t>
+  </si>
+  <si>
+    <t>06/23/26 12:21 EDT</t>
+  </si>
+  <si>
+    <t>06/22/26 21:15 EDT</t>
+  </si>
+  <si>
+    <t>35.514732, -115.432500</t>
+  </si>
+  <si>
+    <t>06/22/26 21:16 EDT</t>
+  </si>
+  <si>
+    <t>0.6mi SW of American Fork UT</t>
+  </si>
+  <si>
+    <t>40.371550, -111.802581</t>
+  </si>
+  <si>
+    <t>06/23/26 12:22 EDT</t>
+  </si>
+  <si>
+    <t>06/22/26 21:45 EDT</t>
+  </si>
+  <si>
+    <t>0.7mi S of Centerville UT</t>
+  </si>
+  <si>
+    <t>40.918353, -111.884806</t>
+  </si>
+  <si>
+    <t>06/23/26 11:01 EDT</t>
+  </si>
+  <si>
+    <t>06/22/26 21:57 EDT</t>
+  </si>
+  <si>
+    <t>5.9mi W of Lodi CA</t>
+  </si>
+  <si>
+    <t>38.117297, -121.400720</t>
+  </si>
+  <si>
+    <t>06/22/26 22:50 EDT</t>
+  </si>
+  <si>
+    <t>8.2mi N of Tremonton UT</t>
+  </si>
+  <si>
+    <t>41.837667, -112.176626</t>
+  </si>
+  <si>
+    <t>06/23/26 04:51 EDT</t>
+  </si>
+  <si>
+    <t>1.6mi NW of Brigham City UT</t>
+  </si>
+  <si>
+    <t>41.521665, -112.064192</t>
+  </si>
+  <si>
+    <t>06/23/26 12:10 EDT</t>
+  </si>
+  <si>
+    <t>3mi S of Salt Lake City UT</t>
+  </si>
+  <si>
+    <t>40.736846, -111.949075</t>
+  </si>
+  <si>
+    <t>06/23/26 14:57 EDT</t>
+  </si>
+  <si>
+    <t>2.2mi E of Marion IA</t>
+  </si>
+  <si>
+    <t>42.035755, -91.543350</t>
+  </si>
+  <si>
+    <t>06/23/26 19:29 EDT</t>
+  </si>
+  <si>
+    <t>0.9mi N of West Bountiful UT</t>
+  </si>
+  <si>
+    <t>40.910793, -111.912599</t>
+  </si>
+  <si>
+    <t>06/24/26 01:07 EDT</t>
+  </si>
+  <si>
+    <t>36.151196, -115.164479</t>
+  </si>
+  <si>
+    <t>06/25/26 08:57 EDT</t>
+  </si>
+  <si>
+    <t>06/24/26 02:17 EDT</t>
+  </si>
+  <si>
+    <t>2.4mi E of Mesquite NV</t>
+  </si>
+  <si>
+    <t>36.808511, -114.090995</t>
+  </si>
+  <si>
+    <t>06/24/26 09:34 EDT</t>
+  </si>
+  <si>
+    <t>40.517369, -111.903025</t>
+  </si>
+  <si>
+    <t>06/24/26 09:48 EDT</t>
+  </si>
+  <si>
+    <t>1.4mi SE of West Jordan UT</t>
+  </si>
+  <si>
+    <t>40.592506, -111.977069</t>
+  </si>
+  <si>
+    <t>06/25/26 09:11 EDT</t>
+  </si>
+  <si>
+    <t>06/24/26 12:30 EDT</t>
+  </si>
+  <si>
+    <t>0.9mi W of American Fork UT</t>
+  </si>
+  <si>
+    <t>40.374007, -111.810592</t>
+  </si>
+  <si>
+    <t>06/24/26 13:49 EDT</t>
+  </si>
+  <si>
+    <t>4.3mi W of Salt Lake City UT</t>
+  </si>
+  <si>
+    <t>40.754945, -112.007930</t>
+  </si>
+  <si>
+    <t>06/25/26 09:12 EDT</t>
+  </si>
+  <si>
+    <t>06/24/26 16:49 EDT</t>
+  </si>
+  <si>
+    <t>1.8mi NW of Denver CO</t>
+  </si>
+  <si>
+    <t>39.778486, -104.901181</t>
+  </si>
+  <si>
+    <t>06/24/26 18:23 EDT</t>
+  </si>
+  <si>
+    <t>2.8mi SE of Berkley CO</t>
+  </si>
+  <si>
+    <t>39.768266, -105.005266</t>
+  </si>
+  <si>
+    <t>06/25/26 08:58 EDT</t>
+  </si>
+  <si>
+    <t>06/24/26 22:05 EDT</t>
+  </si>
+  <si>
+    <t>8.2mi SW of Cortez CO</t>
+  </si>
+  <si>
+    <t>37.246733, -108.650952</t>
+  </si>
+  <si>
+    <t>06/25/26 09:13 EDT</t>
+  </si>
+  <si>
+    <t>06/25/26 00:24 EDT</t>
+  </si>
+  <si>
+    <t>29.6mi E of Evanston WY</t>
+  </si>
+  <si>
+    <t>41.339335, -110.403370</t>
+  </si>
+  <si>
+    <t>06/25/26 00:32 EDT</t>
+  </si>
+  <si>
+    <t>37.3mi E of Evanston WY</t>
+  </si>
+  <si>
+    <t>41.371577, -110.261441</t>
+  </si>
+  <si>
+    <t>06/25/26 08:22 EDT</t>
+  </si>
+  <si>
+    <t>2.5mi NW of Ogden UT</t>
+  </si>
+  <si>
+    <t>41.244614, -112.011718</t>
+  </si>
+  <si>
+    <t>06/25/26 09:04 EDT</t>
+  </si>
+  <si>
+    <t>2.1mi SE of Bluffdale UT</t>
+  </si>
+  <si>
+    <t>40.451051, -111.912939</t>
+  </si>
+  <si>
+    <t>06/25/26 18:46 EDT</t>
+  </si>
+  <si>
+    <t>06/25/26 15:39 EDT</t>
+  </si>
+  <si>
+    <t>40.747983, -111.973875</t>
+  </si>
+  <si>
+    <t>06/25/26 19:46 EDT</t>
+  </si>
+  <si>
+    <t>18.4mi SW of Cedar City UT</t>
+  </si>
+  <si>
+    <t>37.440095, -113.232244</t>
+  </si>
+  <si>
+    <t>06/25/26 23:40 EDT</t>
+  </si>
+  <si>
+    <t>06/25/26 19:51 EDT</t>
+  </si>
+  <si>
+    <t>15.2mi N of Hurricane UT</t>
+  </si>
+  <si>
+    <t>37.358016, -113.264580</t>
+  </si>
+  <si>
+    <t>06/25/26 23:46 EDT</t>
+  </si>
+  <si>
+    <t>2.3mi SE of Decatur TX</t>
+  </si>
+  <si>
+    <t>33.199907, -97.563853</t>
+  </si>
+  <si>
+    <t>06/26/26 09:44 EDT</t>
+  </si>
+  <si>
+    <t>40.451986, -111.913208</t>
+  </si>
+  <si>
+    <t>06/26/26 11:06 EDT</t>
+  </si>
+  <si>
+    <t>1.8mi E of Bluffdale UT</t>
+  </si>
+  <si>
+    <t>40.478562, -111.903785</t>
+  </si>
+  <si>
+    <t>06/26/26 12:59 EDT</t>
+  </si>
+  <si>
+    <t>40.293767, -111.725896</t>
+  </si>
+  <si>
+    <t>1.5mi W of Orem UT</t>
+  </si>
+  <si>
+    <t>40.290806, -111.725843</t>
+  </si>
+  <si>
+    <t>06/26/26 14:04 EDT</t>
+  </si>
+  <si>
+    <t>4.2mi SE of Air Force Academy CO</t>
+  </si>
+  <si>
+    <t>38.954870, -104.803854</t>
+  </si>
+  <si>
+    <t>06/26/26 14:57 EDT</t>
+  </si>
+  <si>
+    <t>3.3mi W of Colorado Springs CO</t>
+  </si>
+  <si>
+    <t>38.874498, -104.821427</t>
+  </si>
+  <si>
+    <t>06/26/26 15:10 EDT</t>
+  </si>
+  <si>
+    <t>58.6mi E of Black Forest CO</t>
+  </si>
+  <si>
+    <t>39.213572, -103.600612</t>
+  </si>
+  <si>
+    <t>06/26/26 15:19 EDT</t>
+  </si>
+  <si>
+    <t>8.1mi S of Pueblo CO</t>
+  </si>
+  <si>
+    <t>38.156548, -104.647831</t>
+  </si>
+  <si>
+    <t>06/26/26 16:13 EDT</t>
+  </si>
+  <si>
+    <t>27.7mi NW of Price UT</t>
+  </si>
+  <si>
+    <t>39.933828, -111.098160</t>
+  </si>
+  <si>
+    <t>06/26/26 18:42 EDT</t>
+  </si>
+  <si>
+    <t>2.7mi SW of White City UT</t>
+  </si>
+  <si>
+    <t>40.534300, -111.892651</t>
+  </si>
+  <si>
+    <t>06/26/26 19:03 EDT</t>
+  </si>
+  <si>
+    <t>23.9mi NE of Rexburg ID</t>
+  </si>
+  <si>
+    <t>44.069741, -111.456003</t>
+  </si>
+  <si>
+    <t>06/26/26 19:17 EDT</t>
+  </si>
+  <si>
+    <t>2.8mi S of Provo UT</t>
+  </si>
+  <si>
+    <t>40.205716, -111.657494</t>
+  </si>
+  <si>
+    <t>06/27/26 14:31 EDT</t>
+  </si>
+  <si>
+    <t>6.3mi S of Lamar CO</t>
+  </si>
+  <si>
+    <t>37.982734, -102.613164</t>
+  </si>
+  <si>
+    <t>06/27/26 16:27 EDT</t>
+  </si>
+  <si>
+    <t>80.6mi W of Pecos TX</t>
+  </si>
+  <si>
+    <t>31.040958, -104.819336</t>
+  </si>
+  <si>
+    <t>06/27/26 16:35 EDT</t>
+  </si>
+  <si>
+    <t>0.1mi N of Auburn CA</t>
+  </si>
+  <si>
+    <t>38.896935, -121.078679</t>
+  </si>
+  <si>
+    <t>06/27/26 20:31 EDT</t>
+  </si>
+  <si>
+    <t>23.2mi E of Winslow AZ</t>
+  </si>
+  <si>
+    <t>34.952489, -110.309137</t>
   </si>
 </sst>
 </file>
@@ -11145,7 +11631,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N1137"/>
+  <dimension ref="A1:N1188"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="14" width="15" customWidth="1"/>
@@ -54038,7 +54524,7 @@
         <v>3567</v>
       </c>
       <c r="H1130" s="3" t="s">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="I1130" s="3">
         <v>34</v>
@@ -54047,15 +54533,19 @@
         <v>70</v>
       </c>
       <c r="K1130" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1130" s="3"/>
-      <c r="M1130" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L1130" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1130" s="3" t="s">
+        <v>3568</v>
+      </c>
       <c r="N1130" s="3"/>
     </row>
     <row r="1131" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1131" s="3" t="s">
-        <v>3568</v>
+        <v>3569</v>
       </c>
       <c r="B1131" s="3" t="s">
         <v>311</v>
@@ -54070,28 +54560,32 @@
         <v>43</v>
       </c>
       <c r="F1131" s="3" t="s">
-        <v>3569</v>
+        <v>3570</v>
       </c>
       <c r="G1131" s="3" t="s">
-        <v>3570</v>
+        <v>3571</v>
       </c>
       <c r="H1131" s="3" t="s">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="I1131" s="3">
         <v>54</v>
       </c>
       <c r="J1131" s="3"/>
       <c r="K1131" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1131" s="3"/>
-      <c r="M1131" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L1131" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1131" s="3" t="s">
+        <v>3568</v>
+      </c>
       <c r="N1131" s="3"/>
     </row>
     <row r="1132" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1132" s="3" t="s">
-        <v>3568</v>
+        <v>3569</v>
       </c>
       <c r="B1132" s="3"/>
       <c r="C1132" s="3">
@@ -54104,12 +54598,14 @@
         <v>24</v>
       </c>
       <c r="F1132" s="3" t="s">
-        <v>3571</v>
+        <v>3572</v>
       </c>
       <c r="G1132" s="3" t="s">
-        <v>3572</v>
-      </c>
-      <c r="H1132" s="3"/>
+        <v>3573</v>
+      </c>
+      <c r="H1132" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="I1132" s="3">
         <v>59</v>
       </c>
@@ -54117,15 +54613,19 @@
         <v>80</v>
       </c>
       <c r="K1132" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1132" s="3"/>
-      <c r="M1132" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L1132" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1132" s="3" t="s">
+        <v>3568</v>
+      </c>
       <c r="N1132" s="3"/>
     </row>
     <row r="1133" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1133" s="3" t="s">
-        <v>3573</v>
+        <v>3574</v>
       </c>
       <c r="B1133" s="3" t="s">
         <v>42</v>
@@ -54140,28 +54640,32 @@
         <v>65</v>
       </c>
       <c r="F1133" s="3" t="s">
-        <v>3574</v>
+        <v>3575</v>
       </c>
       <c r="G1133" s="3" t="s">
-        <v>3575</v>
+        <v>3576</v>
       </c>
       <c r="H1133" s="3" t="s">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="I1133" s="3">
         <v>23</v>
       </c>
       <c r="J1133" s="3"/>
       <c r="K1133" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1133" s="3"/>
-      <c r="M1133" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L1133" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1133" s="3" t="s">
+        <v>3568</v>
+      </c>
       <c r="N1133" s="3"/>
     </row>
     <row r="1134" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1134" s="3" t="s">
-        <v>3576</v>
+        <v>3577</v>
       </c>
       <c r="B1134" s="3"/>
       <c r="C1134" s="3">
@@ -54174,12 +54678,14 @@
         <v>24</v>
       </c>
       <c r="F1134" s="3" t="s">
-        <v>3577</v>
+        <v>3578</v>
       </c>
       <c r="G1134" s="3" t="s">
-        <v>3578</v>
-      </c>
-      <c r="H1134" s="3"/>
+        <v>3579</v>
+      </c>
+      <c r="H1134" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="I1134" s="3">
         <v>71</v>
       </c>
@@ -54187,15 +54693,19 @@
         <v>55</v>
       </c>
       <c r="K1134" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1134" s="3"/>
-      <c r="M1134" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L1134" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1134" s="3" t="s">
+        <v>3568</v>
+      </c>
       <c r="N1134" s="3"/>
     </row>
     <row r="1135" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1135" s="3" t="s">
-        <v>3579</v>
+        <v>3580</v>
       </c>
       <c r="B1135" s="3" t="s">
         <v>42</v>
@@ -54210,12 +54720,14 @@
         <v>24</v>
       </c>
       <c r="F1135" s="3" t="s">
-        <v>3580</v>
+        <v>3581</v>
       </c>
       <c r="G1135" s="3" t="s">
-        <v>3581</v>
-      </c>
-      <c r="H1135" s="3"/>
+        <v>3582</v>
+      </c>
+      <c r="H1135" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="I1135" s="3">
         <v>48</v>
       </c>
@@ -54223,15 +54735,19 @@
         <v>40</v>
       </c>
       <c r="K1135" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1135" s="3"/>
-      <c r="M1135" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L1135" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1135" s="3" t="s">
+        <v>3583</v>
+      </c>
       <c r="N1135" s="3"/>
     </row>
     <row r="1136" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1136" s="3" t="s">
-        <v>3582</v>
+        <v>3584</v>
       </c>
       <c r="B1136" s="3"/>
       <c r="C1136" s="3">
@@ -54244,13 +54760,13 @@
         <v>24</v>
       </c>
       <c r="F1136" s="3" t="s">
-        <v>3583</v>
+        <v>3585</v>
       </c>
       <c r="G1136" s="3" t="s">
-        <v>3584</v>
+        <v>3586</v>
       </c>
       <c r="H1136" s="3" t="s">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="I1136" s="3">
         <v>58</v>
@@ -54259,15 +54775,19 @@
         <v>80</v>
       </c>
       <c r="K1136" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1136" s="3"/>
-      <c r="M1136" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L1136" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1136" s="3" t="s">
+        <v>3587</v>
+      </c>
       <c r="N1136" s="3"/>
     </row>
     <row r="1137" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1137" s="3" t="s">
-        <v>3585</v>
+        <v>3588</v>
       </c>
       <c r="B1137" s="3"/>
       <c r="C1137" s="3">
@@ -54280,10 +54800,10 @@
         <v>18</v>
       </c>
       <c r="F1137" s="3" t="s">
-        <v>3586</v>
+        <v>3589</v>
       </c>
       <c r="G1137" s="3" t="s">
-        <v>3587</v>
+        <v>3590</v>
       </c>
       <c r="H1137" s="3"/>
       <c r="I1137" s="3">
@@ -54298,6 +54818,1914 @@
       <c r="L1137" s="3"/>
       <c r="M1137" s="3"/>
       <c r="N1137" s="3"/>
+    </row>
+    <row r="1138" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1138" s="3" t="s">
+        <v>3591</v>
+      </c>
+      <c r="B1138" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1138" s="3">
+        <v>459</v>
+      </c>
+      <c r="D1138" s="3">
+        <v>1559592482</v>
+      </c>
+      <c r="E1138" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1138" s="3" t="s">
+        <v>3592</v>
+      </c>
+      <c r="G1138" s="3" t="s">
+        <v>3593</v>
+      </c>
+      <c r="H1138" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1138" s="3">
+        <v>72</v>
+      </c>
+      <c r="J1138" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1138" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1138" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1138" s="3" t="s">
+        <v>3587</v>
+      </c>
+      <c r="N1138" s="3"/>
+    </row>
+    <row r="1139" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1139" s="3" t="s">
+        <v>3594</v>
+      </c>
+      <c r="B1139" s="3"/>
+      <c r="C1139" s="3">
+        <v>840</v>
+      </c>
+      <c r="D1139" s="3">
+        <v>1559651475</v>
+      </c>
+      <c r="E1139" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1139" s="3" t="s">
+        <v>3173</v>
+      </c>
+      <c r="G1139" s="3" t="s">
+        <v>3595</v>
+      </c>
+      <c r="H1139" s="3"/>
+      <c r="I1139" s="3">
+        <v>51</v>
+      </c>
+      <c r="J1139" s="3">
+        <v>55</v>
+      </c>
+      <c r="K1139" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1139" s="3"/>
+      <c r="M1139" s="3"/>
+      <c r="N1139" s="3"/>
+    </row>
+    <row r="1140" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1140" s="3" t="s">
+        <v>3596</v>
+      </c>
+      <c r="B1140" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1140" s="3">
+        <v>336</v>
+      </c>
+      <c r="D1140" s="3">
+        <v>1559687641</v>
+      </c>
+      <c r="E1140" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1140" s="3" t="s">
+        <v>3597</v>
+      </c>
+      <c r="G1140" s="3" t="s">
+        <v>3598</v>
+      </c>
+      <c r="H1140" s="3"/>
+      <c r="I1140" s="3">
+        <v>65</v>
+      </c>
+      <c r="J1140" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1140" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1140" s="3"/>
+      <c r="M1140" s="3"/>
+      <c r="N1140" s="3"/>
+    </row>
+    <row r="1141" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1141" s="3" t="s">
+        <v>3599</v>
+      </c>
+      <c r="B1141" s="3"/>
+      <c r="C1141" s="3">
+        <v>729</v>
+      </c>
+      <c r="D1141" s="3">
+        <v>1559687971</v>
+      </c>
+      <c r="E1141" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="F1141" s="3" t="s">
+        <v>3600</v>
+      </c>
+      <c r="G1141" s="3" t="s">
+        <v>3601</v>
+      </c>
+      <c r="H1141" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1141" s="3">
+        <v>64</v>
+      </c>
+      <c r="J1141" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1141" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1141" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1141" s="3" t="s">
+        <v>3602</v>
+      </c>
+      <c r="N1141" s="3"/>
+    </row>
+    <row r="1142" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1142" s="3" t="s">
+        <v>3603</v>
+      </c>
+      <c r="B1142" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C1142" s="3">
+        <v>731</v>
+      </c>
+      <c r="D1142" s="3">
+        <v>1559945091</v>
+      </c>
+      <c r="E1142" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1142" s="3" t="s">
+        <v>3604</v>
+      </c>
+      <c r="G1142" s="3" t="s">
+        <v>3605</v>
+      </c>
+      <c r="H1142" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1142" s="3">
+        <v>39</v>
+      </c>
+      <c r="J1142" s="3"/>
+      <c r="K1142" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1142" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1142" s="3" t="s">
+        <v>3606</v>
+      </c>
+      <c r="N1142" s="3"/>
+    </row>
+    <row r="1143" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1143" s="3" t="s">
+        <v>3607</v>
+      </c>
+      <c r="B1143" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C1143" s="3">
+        <v>375</v>
+      </c>
+      <c r="D1143" s="3">
+        <v>1560067641</v>
+      </c>
+      <c r="E1143" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1143" s="3" t="s">
+        <v>3608</v>
+      </c>
+      <c r="G1143" s="3" t="s">
+        <v>3609</v>
+      </c>
+      <c r="H1143" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1143" s="3">
+        <v>70</v>
+      </c>
+      <c r="J1143" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1143" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1143" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1143" s="3" t="s">
+        <v>3610</v>
+      </c>
+      <c r="N1143" s="3"/>
+    </row>
+    <row r="1144" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1144" s="3" t="s">
+        <v>3611</v>
+      </c>
+      <c r="B1144" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C1144" s="3">
+        <v>96</v>
+      </c>
+      <c r="D1144" s="3">
+        <v>1560185788</v>
+      </c>
+      <c r="E1144" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1144" s="3" t="s">
+        <v>3612</v>
+      </c>
+      <c r="G1144" s="3" t="s">
+        <v>3613</v>
+      </c>
+      <c r="H1144" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1144" s="3">
+        <v>41</v>
+      </c>
+      <c r="J1144" s="3"/>
+      <c r="K1144" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1144" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1144" s="3" t="s">
+        <v>3614</v>
+      </c>
+      <c r="N1144" s="3"/>
+    </row>
+    <row r="1145" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1145" s="3" t="s">
+        <v>3615</v>
+      </c>
+      <c r="B1145" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C1145" s="3">
+        <v>375</v>
+      </c>
+      <c r="D1145" s="3">
+        <v>1560310626</v>
+      </c>
+      <c r="E1145" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1145" s="3" t="s">
+        <v>3616</v>
+      </c>
+      <c r="G1145" s="3" t="s">
+        <v>3617</v>
+      </c>
+      <c r="H1145" s="3"/>
+      <c r="I1145" s="3">
+        <v>71</v>
+      </c>
+      <c r="J1145" s="3">
+        <v>80</v>
+      </c>
+      <c r="K1145" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1145" s="3"/>
+      <c r="M1145" s="3"/>
+      <c r="N1145" s="3"/>
+    </row>
+    <row r="1146" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1146" s="3" t="s">
+        <v>3618</v>
+      </c>
+      <c r="B1146" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="C1146" s="3">
+        <v>63</v>
+      </c>
+      <c r="D1146" s="3">
+        <v>1560371395</v>
+      </c>
+      <c r="E1146" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1146" s="3" t="s">
+        <v>3619</v>
+      </c>
+      <c r="G1146" s="3" t="s">
+        <v>3620</v>
+      </c>
+      <c r="H1146" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1146" s="3">
+        <v>20</v>
+      </c>
+      <c r="J1146" s="3"/>
+      <c r="K1146" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1146" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1146" s="3" t="s">
+        <v>3621</v>
+      </c>
+      <c r="N1146" s="3"/>
+    </row>
+    <row r="1147" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1147" s="3" t="s">
+        <v>3622</v>
+      </c>
+      <c r="B1147" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C1147" s="3">
+        <v>375</v>
+      </c>
+      <c r="D1147" s="3">
+        <v>1560495402</v>
+      </c>
+      <c r="E1147" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1147" s="3" t="s">
+        <v>3180</v>
+      </c>
+      <c r="G1147" s="3" t="s">
+        <v>3623</v>
+      </c>
+      <c r="H1147" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1147" s="3">
+        <v>21</v>
+      </c>
+      <c r="J1147" s="3">
+        <v>35</v>
+      </c>
+      <c r="K1147" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1147" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1147" s="3" t="s">
+        <v>3614</v>
+      </c>
+      <c r="N1147" s="3"/>
+    </row>
+    <row r="1148" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1148" s="3" t="s">
+        <v>3624</v>
+      </c>
+      <c r="B1148" s="3"/>
+      <c r="C1148" s="3">
+        <v>459</v>
+      </c>
+      <c r="D1148" s="3">
+        <v>1560496148</v>
+      </c>
+      <c r="E1148" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1148" s="3" t="s">
+        <v>3625</v>
+      </c>
+      <c r="G1148" s="3" t="s">
+        <v>3626</v>
+      </c>
+      <c r="H1148" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1148" s="3">
+        <v>69</v>
+      </c>
+      <c r="J1148" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1148" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1148" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1148" s="3" t="s">
+        <v>3627</v>
+      </c>
+      <c r="N1148" s="3"/>
+    </row>
+    <row r="1149" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1149" s="3" t="s">
+        <v>3628</v>
+      </c>
+      <c r="B1149" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1149" s="3">
+        <v>336</v>
+      </c>
+      <c r="D1149" s="3">
+        <v>1560507047</v>
+      </c>
+      <c r="E1149" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="F1149" s="3" t="s">
+        <v>3629</v>
+      </c>
+      <c r="G1149" s="3" t="s">
+        <v>3630</v>
+      </c>
+      <c r="H1149" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1149" s="3"/>
+      <c r="J1149" s="3"/>
+      <c r="K1149" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1149" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1149" s="3" t="s">
+        <v>3631</v>
+      </c>
+      <c r="N1149" s="3"/>
+    </row>
+    <row r="1150" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1150" s="3" t="s">
+        <v>3632</v>
+      </c>
+      <c r="B1150" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1150" s="3">
+        <v>210</v>
+      </c>
+      <c r="D1150" s="3">
+        <v>1560511202</v>
+      </c>
+      <c r="E1150" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1150" s="3" t="s">
+        <v>3633</v>
+      </c>
+      <c r="G1150" s="3" t="s">
+        <v>3634</v>
+      </c>
+      <c r="H1150" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1150" s="3">
+        <v>40</v>
+      </c>
+      <c r="J1150" s="3"/>
+      <c r="K1150" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1150" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1150" s="3" t="s">
+        <v>3631</v>
+      </c>
+      <c r="N1150" s="3"/>
+    </row>
+    <row r="1151" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1151" s="3" t="s">
+        <v>3635</v>
+      </c>
+      <c r="B1151" s="3"/>
+      <c r="C1151" s="3">
+        <v>459</v>
+      </c>
+      <c r="D1151" s="3">
+        <v>1560527594</v>
+      </c>
+      <c r="E1151" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1151" s="3" t="s">
+        <v>3636</v>
+      </c>
+      <c r="G1151" s="3" t="s">
+        <v>3637</v>
+      </c>
+      <c r="H1151" s="3"/>
+      <c r="I1151" s="3">
+        <v>72</v>
+      </c>
+      <c r="J1151" s="3">
+        <v>80</v>
+      </c>
+      <c r="K1151" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1151" s="3"/>
+      <c r="M1151" s="3"/>
+      <c r="N1151" s="3"/>
+    </row>
+    <row r="1152" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1152" s="3" t="s">
+        <v>3638</v>
+      </c>
+      <c r="B1152" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1152" s="3">
+        <v>336</v>
+      </c>
+      <c r="D1152" s="3">
+        <v>1560594437</v>
+      </c>
+      <c r="E1152" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1152" s="3" t="s">
+        <v>3639</v>
+      </c>
+      <c r="G1152" s="3" t="s">
+        <v>3640</v>
+      </c>
+      <c r="H1152" s="3"/>
+      <c r="I1152" s="3">
+        <v>65</v>
+      </c>
+      <c r="J1152" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1152" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1152" s="3"/>
+      <c r="M1152" s="3"/>
+      <c r="N1152" s="3"/>
+    </row>
+    <row r="1153" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1153" s="3" t="s">
+        <v>3641</v>
+      </c>
+      <c r="B1153" s="3"/>
+      <c r="C1153" s="3">
+        <v>338</v>
+      </c>
+      <c r="D1153" s="3">
+        <v>1560960806</v>
+      </c>
+      <c r="E1153" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F1153" s="3" t="s">
+        <v>3642</v>
+      </c>
+      <c r="G1153" s="3" t="s">
+        <v>3643</v>
+      </c>
+      <c r="H1153" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1153" s="3">
+        <v>67</v>
+      </c>
+      <c r="J1153" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1153" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1153" s="3"/>
+      <c r="M1153" s="3"/>
+      <c r="N1153" s="3"/>
+    </row>
+    <row r="1154" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1154" s="3" t="s">
+        <v>3644</v>
+      </c>
+      <c r="B1154" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C1154" s="3">
+        <v>731</v>
+      </c>
+      <c r="D1154" s="3">
+        <v>1561144972</v>
+      </c>
+      <c r="E1154" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1154" s="3" t="s">
+        <v>3645</v>
+      </c>
+      <c r="G1154" s="3" t="s">
+        <v>3646</v>
+      </c>
+      <c r="H1154" s="3"/>
+      <c r="I1154" s="3">
+        <v>50</v>
+      </c>
+      <c r="J1154" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1154" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1154" s="3"/>
+      <c r="M1154" s="3"/>
+      <c r="N1154" s="3"/>
+    </row>
+    <row r="1155" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1155" s="3" t="s">
+        <v>3647</v>
+      </c>
+      <c r="B1155" s="3"/>
+      <c r="C1155" s="3">
+        <v>338</v>
+      </c>
+      <c r="D1155" s="3">
+        <v>1561394010</v>
+      </c>
+      <c r="E1155" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1155" s="3" t="s">
+        <v>3648</v>
+      </c>
+      <c r="G1155" s="3" t="s">
+        <v>3649</v>
+      </c>
+      <c r="H1155" s="3"/>
+      <c r="I1155" s="3">
+        <v>55</v>
+      </c>
+      <c r="J1155" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1155" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1155" s="3"/>
+      <c r="M1155" s="3"/>
+      <c r="N1155" s="3"/>
+    </row>
+    <row r="1156" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1156" s="3" t="s">
+        <v>3650</v>
+      </c>
+      <c r="B1156" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C1156" s="3">
+        <v>375</v>
+      </c>
+      <c r="D1156" s="3">
+        <v>1561519458</v>
+      </c>
+      <c r="E1156" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1156" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="G1156" s="3" t="s">
+        <v>3651</v>
+      </c>
+      <c r="H1156" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1156" s="3">
+        <v>70</v>
+      </c>
+      <c r="J1156" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1156" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1156" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1156" s="3" t="s">
+        <v>3652</v>
+      </c>
+      <c r="N1156" s="3"/>
+    </row>
+    <row r="1157" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1157" s="3" t="s">
+        <v>3653</v>
+      </c>
+      <c r="B1157" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C1157" s="3">
+        <v>375</v>
+      </c>
+      <c r="D1157" s="3">
+        <v>1561531738</v>
+      </c>
+      <c r="E1157" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1157" s="3" t="s">
+        <v>3654</v>
+      </c>
+      <c r="G1157" s="3" t="s">
+        <v>3655</v>
+      </c>
+      <c r="H1157" s="3"/>
+      <c r="I1157" s="3">
+        <v>70</v>
+      </c>
+      <c r="J1157" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1157" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1157" s="3"/>
+      <c r="M1157" s="3"/>
+      <c r="N1157" s="3"/>
+    </row>
+    <row r="1158" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1158" s="3" t="s">
+        <v>3656</v>
+      </c>
+      <c r="B1158" s="3"/>
+      <c r="C1158" s="3">
+        <v>338</v>
+      </c>
+      <c r="D1158" s="3">
+        <v>1561762633</v>
+      </c>
+      <c r="E1158" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="F1158" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1158" s="3" t="s">
+        <v>3657</v>
+      </c>
+      <c r="H1158" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1158" s="3"/>
+      <c r="J1158" s="3"/>
+      <c r="K1158" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1158" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1158" s="3" t="s">
+        <v>3652</v>
+      </c>
+      <c r="N1158" s="3"/>
+    </row>
+    <row r="1159" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1159" s="3" t="s">
+        <v>3658</v>
+      </c>
+      <c r="B1159" s="3"/>
+      <c r="C1159" s="3">
+        <v>342</v>
+      </c>
+      <c r="D1159" s="3">
+        <v>1561777478</v>
+      </c>
+      <c r="E1159" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1159" s="3" t="s">
+        <v>3659</v>
+      </c>
+      <c r="G1159" s="3" t="s">
+        <v>3660</v>
+      </c>
+      <c r="H1159" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1159" s="3">
+        <v>59</v>
+      </c>
+      <c r="J1159" s="3">
+        <v>60</v>
+      </c>
+      <c r="K1159" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1159" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1159" s="3" t="s">
+        <v>3661</v>
+      </c>
+      <c r="N1159" s="3"/>
+    </row>
+    <row r="1160" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1160" s="3" t="s">
+        <v>3662</v>
+      </c>
+      <c r="B1160" s="3"/>
+      <c r="C1160" s="3">
+        <v>375</v>
+      </c>
+      <c r="D1160" s="3">
+        <v>1561953304</v>
+      </c>
+      <c r="E1160" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1160" s="3" t="s">
+        <v>3663</v>
+      </c>
+      <c r="G1160" s="3" t="s">
+        <v>3664</v>
+      </c>
+      <c r="H1160" s="3"/>
+      <c r="I1160" s="3">
+        <v>70</v>
+      </c>
+      <c r="J1160" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1160" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1160" s="3"/>
+      <c r="M1160" s="3"/>
+      <c r="N1160" s="3"/>
+    </row>
+    <row r="1161" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1161" s="3" t="s">
+        <v>3665</v>
+      </c>
+      <c r="B1161" s="3"/>
+      <c r="C1161" s="3">
+        <v>339</v>
+      </c>
+      <c r="D1161" s="3">
+        <v>1562043198</v>
+      </c>
+      <c r="E1161" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1161" s="3" t="s">
+        <v>3666</v>
+      </c>
+      <c r="G1161" s="3" t="s">
+        <v>3667</v>
+      </c>
+      <c r="H1161" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1161" s="3">
+        <v>21</v>
+      </c>
+      <c r="J1161" s="3"/>
+      <c r="K1161" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1161" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1161" s="3" t="s">
+        <v>3668</v>
+      </c>
+      <c r="N1161" s="3"/>
+    </row>
+    <row r="1162" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1162" s="3" t="s">
+        <v>3669</v>
+      </c>
+      <c r="B1162" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="C1162" s="3">
+        <v>63</v>
+      </c>
+      <c r="D1162" s="3">
+        <v>1562241262</v>
+      </c>
+      <c r="E1162" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1162" s="3" t="s">
+        <v>3670</v>
+      </c>
+      <c r="G1162" s="3" t="s">
+        <v>3671</v>
+      </c>
+      <c r="H1162" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1162" s="3">
+        <v>59</v>
+      </c>
+      <c r="J1162" s="3"/>
+      <c r="K1162" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1162" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1162" s="3" t="s">
+        <v>3652</v>
+      </c>
+      <c r="N1162" s="3"/>
+    </row>
+    <row r="1163" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1163" s="3" t="s">
+        <v>3672</v>
+      </c>
+      <c r="B1163" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="C1163" s="3">
+        <v>63</v>
+      </c>
+      <c r="D1163" s="3">
+        <v>1562326779</v>
+      </c>
+      <c r="E1163" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1163" s="3" t="s">
+        <v>3673</v>
+      </c>
+      <c r="G1163" s="3" t="s">
+        <v>3674</v>
+      </c>
+      <c r="H1163" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1163" s="3">
+        <v>14</v>
+      </c>
+      <c r="J1163" s="3"/>
+      <c r="K1163" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1163" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1163" s="3" t="s">
+        <v>3675</v>
+      </c>
+      <c r="N1163" s="3"/>
+    </row>
+    <row r="1164" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1164" s="3" t="s">
+        <v>3676</v>
+      </c>
+      <c r="B1164" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1164" s="3">
+        <v>336</v>
+      </c>
+      <c r="D1164" s="3">
+        <v>1562453658</v>
+      </c>
+      <c r="E1164" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1164" s="3" t="s">
+        <v>3677</v>
+      </c>
+      <c r="G1164" s="3" t="s">
+        <v>3678</v>
+      </c>
+      <c r="H1164" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1164" s="3">
+        <v>66</v>
+      </c>
+      <c r="J1164" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1164" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1164" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1164" s="3" t="s">
+        <v>3679</v>
+      </c>
+      <c r="N1164" s="3"/>
+    </row>
+    <row r="1165" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1165" s="3" t="s">
+        <v>3680</v>
+      </c>
+      <c r="B1165" s="3"/>
+      <c r="C1165" s="3">
+        <v>729</v>
+      </c>
+      <c r="D1165" s="3">
+        <v>1562493152</v>
+      </c>
+      <c r="E1165" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1165" s="3" t="s">
+        <v>3681</v>
+      </c>
+      <c r="G1165" s="3" t="s">
+        <v>3682</v>
+      </c>
+      <c r="H1165" s="3"/>
+      <c r="I1165" s="3">
+        <v>68</v>
+      </c>
+      <c r="J1165" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1165" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1165" s="3"/>
+      <c r="M1165" s="3"/>
+      <c r="N1165" s="3"/>
+    </row>
+    <row r="1166" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1166" s="3" t="s">
+        <v>3683</v>
+      </c>
+      <c r="B1166" s="3"/>
+      <c r="C1166" s="3">
+        <v>729</v>
+      </c>
+      <c r="D1166" s="3">
+        <v>1562495242</v>
+      </c>
+      <c r="E1166" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1166" s="3" t="s">
+        <v>3684</v>
+      </c>
+      <c r="G1166" s="3" t="s">
+        <v>3685</v>
+      </c>
+      <c r="H1166" s="3"/>
+      <c r="I1166" s="3">
+        <v>64</v>
+      </c>
+      <c r="J1166" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1166" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1166" s="3"/>
+      <c r="M1166" s="3"/>
+      <c r="N1166" s="3"/>
+    </row>
+    <row r="1167" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1167" s="3" t="s">
+        <v>3686</v>
+      </c>
+      <c r="B1167" s="3"/>
+      <c r="C1167" s="3">
+        <v>338</v>
+      </c>
+      <c r="D1167" s="3">
+        <v>1562672033</v>
+      </c>
+      <c r="E1167" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1167" s="3" t="s">
+        <v>3687</v>
+      </c>
+      <c r="G1167" s="3" t="s">
+        <v>3688</v>
+      </c>
+      <c r="H1167" s="3"/>
+      <c r="I1167" s="3">
+        <v>52</v>
+      </c>
+      <c r="J1167" s="3">
+        <v>45</v>
+      </c>
+      <c r="K1167" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1167" s="3"/>
+      <c r="M1167" s="3"/>
+      <c r="N1167" s="3"/>
+    </row>
+    <row r="1168" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1168" s="3" t="s">
+        <v>3689</v>
+      </c>
+      <c r="B1168" s="3"/>
+      <c r="C1168" s="3">
+        <v>375</v>
+      </c>
+      <c r="D1168" s="3">
+        <v>1562712364</v>
+      </c>
+      <c r="E1168" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1168" s="3" t="s">
+        <v>3690</v>
+      </c>
+      <c r="G1168" s="3" t="s">
+        <v>3691</v>
+      </c>
+      <c r="H1168" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1168" s="3">
+        <v>67</v>
+      </c>
+      <c r="J1168" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1168" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1168" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1168" s="3" t="s">
+        <v>3692</v>
+      </c>
+      <c r="N1168" s="3"/>
+    </row>
+    <row r="1169" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1169" s="3" t="s">
+        <v>3693</v>
+      </c>
+      <c r="B1169" s="3"/>
+      <c r="C1169" s="3">
+        <v>338</v>
+      </c>
+      <c r="D1169" s="3">
+        <v>1563144884</v>
+      </c>
+      <c r="E1169" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1169" s="3" t="s">
+        <v>902</v>
+      </c>
+      <c r="G1169" s="3" t="s">
+        <v>3694</v>
+      </c>
+      <c r="H1169" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1169" s="3">
+        <v>15</v>
+      </c>
+      <c r="J1169" s="3"/>
+      <c r="K1169" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1169" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1169" s="3" t="s">
+        <v>3692</v>
+      </c>
+      <c r="N1169" s="3"/>
+    </row>
+    <row r="1170" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1170" s="3" t="s">
+        <v>3695</v>
+      </c>
+      <c r="B1170" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="C1170" s="3">
+        <v>208</v>
+      </c>
+      <c r="D1170" s="3">
+        <v>1563360598</v>
+      </c>
+      <c r="E1170" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1170" s="3" t="s">
+        <v>3696</v>
+      </c>
+      <c r="G1170" s="3" t="s">
+        <v>3697</v>
+      </c>
+      <c r="H1170" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1170" s="3">
+        <v>77</v>
+      </c>
+      <c r="J1170" s="3">
+        <v>80</v>
+      </c>
+      <c r="K1170" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1170" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1170" s="3" t="s">
+        <v>3698</v>
+      </c>
+      <c r="N1170" s="3"/>
+    </row>
+    <row r="1171" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1171" s="3" t="s">
+        <v>3699</v>
+      </c>
+      <c r="B1171" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="C1171" s="3">
+        <v>208</v>
+      </c>
+      <c r="D1171" s="3">
+        <v>1563363589</v>
+      </c>
+      <c r="E1171" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1171" s="3" t="s">
+        <v>3700</v>
+      </c>
+      <c r="G1171" s="3" t="s">
+        <v>3701</v>
+      </c>
+      <c r="H1171" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1171" s="3">
+        <v>72</v>
+      </c>
+      <c r="J1171" s="3"/>
+      <c r="K1171" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1171" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1171" s="3" t="s">
+        <v>3698</v>
+      </c>
+      <c r="N1171" s="3"/>
+    </row>
+    <row r="1172" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1172" s="3" t="s">
+        <v>3702</v>
+      </c>
+      <c r="B1172" s="3"/>
+      <c r="C1172" s="3">
+        <v>459</v>
+      </c>
+      <c r="D1172" s="3">
+        <v>1563459540</v>
+      </c>
+      <c r="E1172" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1172" s="3" t="s">
+        <v>3703</v>
+      </c>
+      <c r="G1172" s="3" t="s">
+        <v>3704</v>
+      </c>
+      <c r="H1172" s="3"/>
+      <c r="I1172" s="3">
+        <v>65</v>
+      </c>
+      <c r="J1172" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1172" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1172" s="3"/>
+      <c r="M1172" s="3"/>
+      <c r="N1172" s="3"/>
+    </row>
+    <row r="1173" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1173" s="3" t="s">
+        <v>3705</v>
+      </c>
+      <c r="B1173" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1173" s="3">
+        <v>375</v>
+      </c>
+      <c r="D1173" s="3">
+        <v>1563719833</v>
+      </c>
+      <c r="E1173" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1173" s="3" t="s">
+        <v>1253</v>
+      </c>
+      <c r="G1173" s="3" t="s">
+        <v>3706</v>
+      </c>
+      <c r="H1173" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1173" s="3">
+        <v>70</v>
+      </c>
+      <c r="J1173" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1173" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1173" s="3"/>
+      <c r="M1173" s="3"/>
+      <c r="N1173" s="3"/>
+    </row>
+    <row r="1174" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1174" s="3" t="s">
+        <v>3707</v>
+      </c>
+      <c r="B1174" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1174" s="3">
+        <v>375</v>
+      </c>
+      <c r="D1174" s="3">
+        <v>1563805192</v>
+      </c>
+      <c r="E1174" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1174" s="3" t="s">
+        <v>3708</v>
+      </c>
+      <c r="G1174" s="3" t="s">
+        <v>3709</v>
+      </c>
+      <c r="H1174" s="3"/>
+      <c r="I1174" s="3">
+        <v>67</v>
+      </c>
+      <c r="J1174" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1174" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1174" s="3"/>
+      <c r="M1174" s="3"/>
+      <c r="N1174" s="3"/>
+    </row>
+    <row r="1175" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1175" s="3" t="s">
+        <v>3710</v>
+      </c>
+      <c r="B1175" s="3"/>
+      <c r="C1175" s="3">
+        <v>342</v>
+      </c>
+      <c r="D1175" s="3">
+        <v>1563925496</v>
+      </c>
+      <c r="E1175" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1175" s="3" t="s">
+        <v>2723</v>
+      </c>
+      <c r="G1175" s="3" t="s">
+        <v>3711</v>
+      </c>
+      <c r="H1175" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1175" s="3">
+        <v>75</v>
+      </c>
+      <c r="J1175" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1175" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1175" s="3"/>
+      <c r="M1175" s="3"/>
+      <c r="N1175" s="3"/>
+    </row>
+    <row r="1176" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1176" s="3" t="s">
+        <v>3710</v>
+      </c>
+      <c r="B1176" s="3"/>
+      <c r="C1176" s="3">
+        <v>342</v>
+      </c>
+      <c r="D1176" s="3">
+        <v>1563925509</v>
+      </c>
+      <c r="E1176" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1176" s="3" t="s">
+        <v>3712</v>
+      </c>
+      <c r="G1176" s="3" t="s">
+        <v>3713</v>
+      </c>
+      <c r="H1176" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1176" s="3">
+        <v>75</v>
+      </c>
+      <c r="J1176" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1176" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1176" s="3"/>
+      <c r="M1176" s="3"/>
+      <c r="N1176" s="3"/>
+    </row>
+    <row r="1177" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1177" s="3" t="s">
+        <v>3714</v>
+      </c>
+      <c r="B1177" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1177" s="3">
+        <v>336</v>
+      </c>
+      <c r="D1177" s="3">
+        <v>1563994356</v>
+      </c>
+      <c r="E1177" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1177" s="3" t="s">
+        <v>3715</v>
+      </c>
+      <c r="G1177" s="3" t="s">
+        <v>3716</v>
+      </c>
+      <c r="H1177" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1177" s="3">
+        <v>66</v>
+      </c>
+      <c r="J1177" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1177" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1177" s="3"/>
+      <c r="M1177" s="3"/>
+      <c r="N1177" s="3"/>
+    </row>
+    <row r="1178" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1178" s="3" t="s">
+        <v>3717</v>
+      </c>
+      <c r="B1178" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1178" s="3">
+        <v>336</v>
+      </c>
+      <c r="D1178" s="3">
+        <v>1564049614</v>
+      </c>
+      <c r="E1178" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1178" s="3" t="s">
+        <v>3718</v>
+      </c>
+      <c r="G1178" s="3" t="s">
+        <v>3719</v>
+      </c>
+      <c r="H1178" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1178" s="3">
+        <v>27</v>
+      </c>
+      <c r="J1178" s="3"/>
+      <c r="K1178" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1178" s="3"/>
+      <c r="M1178" s="3"/>
+      <c r="N1178" s="3"/>
+    </row>
+    <row r="1179" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1179" s="3" t="s">
+        <v>3720</v>
+      </c>
+      <c r="B1179" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="C1179" s="3">
+        <v>838</v>
+      </c>
+      <c r="D1179" s="3">
+        <v>1564063745</v>
+      </c>
+      <c r="E1179" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1179" s="3" t="s">
+        <v>3721</v>
+      </c>
+      <c r="G1179" s="3" t="s">
+        <v>3722</v>
+      </c>
+      <c r="H1179" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1179" s="3">
+        <v>62</v>
+      </c>
+      <c r="J1179" s="3"/>
+      <c r="K1179" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1179" s="3"/>
+      <c r="M1179" s="3"/>
+      <c r="N1179" s="3"/>
+    </row>
+    <row r="1180" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1180" s="3" t="s">
+        <v>3723</v>
+      </c>
+      <c r="B1180" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C1180" s="3">
+        <v>731</v>
+      </c>
+      <c r="D1180" s="3">
+        <v>1564072540</v>
+      </c>
+      <c r="E1180" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1180" s="3" t="s">
+        <v>3724</v>
+      </c>
+      <c r="G1180" s="3" t="s">
+        <v>3725</v>
+      </c>
+      <c r="H1180" s="3"/>
+      <c r="I1180" s="3">
+        <v>72</v>
+      </c>
+      <c r="J1180" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1180" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1180" s="3"/>
+      <c r="M1180" s="3"/>
+      <c r="N1180" s="3"/>
+    </row>
+    <row r="1181" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1181" s="3" t="s">
+        <v>3726</v>
+      </c>
+      <c r="B1181" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1181" s="3">
+        <v>375</v>
+      </c>
+      <c r="D1181" s="3">
+        <v>1564128793</v>
+      </c>
+      <c r="E1181" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1181" s="3" t="s">
+        <v>3727</v>
+      </c>
+      <c r="G1181" s="3" t="s">
+        <v>3728</v>
+      </c>
+      <c r="H1181" s="3"/>
+      <c r="I1181" s="3">
+        <v>59</v>
+      </c>
+      <c r="J1181" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1181" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1181" s="3"/>
+      <c r="M1181" s="3"/>
+      <c r="N1181" s="3"/>
+    </row>
+    <row r="1182" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1182" s="3" t="s">
+        <v>3729</v>
+      </c>
+      <c r="B1182" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1182" s="3">
+        <v>375</v>
+      </c>
+      <c r="D1182" s="3">
+        <v>1564251553</v>
+      </c>
+      <c r="E1182" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1182" s="3" t="s">
+        <v>3730</v>
+      </c>
+      <c r="G1182" s="3" t="s">
+        <v>3731</v>
+      </c>
+      <c r="H1182" s="3"/>
+      <c r="I1182" s="3">
+        <v>63</v>
+      </c>
+      <c r="J1182" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1182" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1182" s="3"/>
+      <c r="M1182" s="3"/>
+      <c r="N1182" s="3"/>
+    </row>
+    <row r="1183" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1183" s="3" t="s">
+        <v>3732</v>
+      </c>
+      <c r="B1183" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="C1183" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="D1183" s="3">
+        <v>1564264070</v>
+      </c>
+      <c r="E1183" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1183" s="3" t="s">
+        <v>3733</v>
+      </c>
+      <c r="G1183" s="3" t="s">
+        <v>3734</v>
+      </c>
+      <c r="H1183" s="3"/>
+      <c r="I1183" s="3">
+        <v>36</v>
+      </c>
+      <c r="J1183" s="3">
+        <v>45</v>
+      </c>
+      <c r="K1183" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1183" s="3"/>
+      <c r="M1183" s="3"/>
+      <c r="N1183" s="3"/>
+    </row>
+    <row r="1184" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1184" s="3" t="s">
+        <v>3735</v>
+      </c>
+      <c r="B1184" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1184" s="3">
+        <v>375</v>
+      </c>
+      <c r="D1184" s="3">
+        <v>1564273165</v>
+      </c>
+      <c r="E1184" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1184" s="3" t="s">
+        <v>3736</v>
+      </c>
+      <c r="G1184" s="3" t="s">
+        <v>3737</v>
+      </c>
+      <c r="H1184" s="3"/>
+      <c r="I1184" s="3">
+        <v>58</v>
+      </c>
+      <c r="J1184" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1184" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1184" s="3"/>
+      <c r="M1184" s="3"/>
+      <c r="N1184" s="3"/>
+    </row>
+    <row r="1185" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1185" s="3" t="s">
+        <v>3738</v>
+      </c>
+      <c r="B1185" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1185" s="3">
+        <v>672</v>
+      </c>
+      <c r="D1185" s="3">
+        <v>1564632671</v>
+      </c>
+      <c r="E1185" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1185" s="3" t="s">
+        <v>3739</v>
+      </c>
+      <c r="G1185" s="3" t="s">
+        <v>3740</v>
+      </c>
+      <c r="H1185" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1185" s="3">
+        <v>54</v>
+      </c>
+      <c r="J1185" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1185" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1185" s="3"/>
+      <c r="M1185" s="3"/>
+      <c r="N1185" s="3"/>
+    </row>
+    <row r="1186" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1186" s="3" t="s">
+        <v>3741</v>
+      </c>
+      <c r="B1186" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C1186" s="3">
+        <v>731</v>
+      </c>
+      <c r="D1186" s="3">
+        <v>1564682303</v>
+      </c>
+      <c r="E1186" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1186" s="3" t="s">
+        <v>3742</v>
+      </c>
+      <c r="G1186" s="3" t="s">
+        <v>3743</v>
+      </c>
+      <c r="H1186" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1186" s="3">
+        <v>23</v>
+      </c>
+      <c r="J1186" s="3"/>
+      <c r="K1186" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1186" s="3"/>
+      <c r="M1186" s="3"/>
+      <c r="N1186" s="3"/>
+    </row>
+    <row r="1187" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1187" s="3" t="s">
+        <v>3744</v>
+      </c>
+      <c r="B1187" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1187" s="3">
+        <v>210</v>
+      </c>
+      <c r="D1187" s="3">
+        <v>1564685235</v>
+      </c>
+      <c r="E1187" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="F1187" s="3" t="s">
+        <v>3745</v>
+      </c>
+      <c r="G1187" s="3" t="s">
+        <v>3746</v>
+      </c>
+      <c r="H1187" s="3"/>
+      <c r="I1187" s="3">
+        <v>57</v>
+      </c>
+      <c r="J1187" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1187" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1187" s="3"/>
+      <c r="M1187" s="3"/>
+      <c r="N1187" s="3"/>
+    </row>
+    <row r="1188" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1188" s="3" t="s">
+        <v>3747</v>
+      </c>
+      <c r="B1188" s="3"/>
+      <c r="C1188" s="3">
+        <v>459</v>
+      </c>
+      <c r="D1188" s="3">
+        <v>1564764159</v>
+      </c>
+      <c r="E1188" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1188" s="3" t="s">
+        <v>3748</v>
+      </c>
+      <c r="G1188" s="3" t="s">
+        <v>3749</v>
+      </c>
+      <c r="H1188" s="3"/>
+      <c r="I1188" s="3">
+        <v>50</v>
+      </c>
+      <c r="J1188" s="3"/>
+      <c r="K1188" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1188" s="3"/>
+      <c r="M1188" s="3"/>
+      <c r="N1188" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\PCS-Trucking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2D56A0AF-58C1-43D2-ADE9-2A96DB5103FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1FEAFAE0-90F8-475B-94B0-8B38BDD64FBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9232" uniqueCount="3917">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9667" uniqueCount="4082">
   <si>
     <t>DRIVE ALERTS</t>
   </si>
@@ -11620,6 +11620,9 @@
     <t>41.742907, -107.647738</t>
   </si>
   <si>
+    <t>07/06/26 11:26 EDT</t>
+  </si>
+  <si>
     <t>07/02/26 11:45 EDT</t>
   </si>
   <si>
@@ -11674,6 +11677,9 @@
     <t>40.675374, -111.901394</t>
   </si>
   <si>
+    <t>07/06/26 11:27 EDT</t>
+  </si>
+  <si>
     <t>07/02/26 15:18 EDT</t>
   </si>
   <si>
@@ -11716,6 +11722,9 @@
     <t>41.550461, -106.090619</t>
   </si>
   <si>
+    <t>07/06/26 11:28 EDT</t>
+  </si>
+  <si>
     <t>07/03/26 11:04 EDT</t>
   </si>
   <si>
@@ -11764,6 +11773,9 @@
     <t>36.160549, -86.621746</t>
   </si>
   <si>
+    <t>07/06/26 11:29 EDT</t>
+  </si>
+  <si>
     <t>07/04/26 18:36 EDT</t>
   </si>
   <si>
@@ -11771,6 +11783,489 @@
   </si>
   <si>
     <t>40.897270, -96.578262</t>
+  </si>
+  <si>
+    <t>07/06/26 11:30 EDT</t>
+  </si>
+  <si>
+    <t>07/05/26 13:59 EDT</t>
+  </si>
+  <si>
+    <t>2.7mi NW of Salem UT</t>
+  </si>
+  <si>
+    <t>40.085364, -111.701477</t>
+  </si>
+  <si>
+    <t>07/05/26 14:12 EDT</t>
+  </si>
+  <si>
+    <t>22.3mi SW of Muskogee OK</t>
+  </si>
+  <si>
+    <t>35.458726, -95.542907</t>
+  </si>
+  <si>
+    <t>07/05/26 14:56 EDT</t>
+  </si>
+  <si>
+    <t>15.5mi W of DuBois PA</t>
+  </si>
+  <si>
+    <t>41.170353, -79.047269</t>
+  </si>
+  <si>
+    <t>07/05/26 22:07 EDT</t>
+  </si>
+  <si>
+    <t>11.8mi SW of Montgomery PA</t>
+  </si>
+  <si>
+    <t>39.672201, -78.079070</t>
+  </si>
+  <si>
+    <t>07/06/26 11:31 EDT</t>
+  </si>
+  <si>
+    <t>07/06/26 02:50 EDT</t>
+  </si>
+  <si>
+    <t>3.3mi NW of Lamar CO</t>
+  </si>
+  <si>
+    <t>38.111934, -102.653663</t>
+  </si>
+  <si>
+    <t>1mi S of Kaysville UT</t>
+  </si>
+  <si>
+    <t>41.014165, -111.949264</t>
+  </si>
+  <si>
+    <t>07/06/26 15:45 EDT</t>
+  </si>
+  <si>
+    <t>07/06/26 12:08 EDT</t>
+  </si>
+  <si>
+    <t>4mi SE of Decatur TX</t>
+  </si>
+  <si>
+    <t>33.179135, -97.546251</t>
+  </si>
+  <si>
+    <t>07/06/26 19:05 EDT</t>
+  </si>
+  <si>
+    <t>3.9mi SE of Decatur TX</t>
+  </si>
+  <si>
+    <t>33.180967, -97.547871</t>
+  </si>
+  <si>
+    <t>07/06/26 19:06 EDT</t>
+  </si>
+  <si>
+    <t>07/06/26 13:53 EDT</t>
+  </si>
+  <si>
+    <t>40.723265, -112.024807</t>
+  </si>
+  <si>
+    <t>07/06/26 16:23 EDT</t>
+  </si>
+  <si>
+    <t>40.731923, -111.958005</t>
+  </si>
+  <si>
+    <t>07/06/26 17:09 EDT</t>
+  </si>
+  <si>
+    <t>5.4mi NE of Chubbuck ID</t>
+  </si>
+  <si>
+    <t>42.996546, -112.413406</t>
+  </si>
+  <si>
+    <t>07/06/26 17:30 EDT</t>
+  </si>
+  <si>
+    <t>35.514962, -115.432424</t>
+  </si>
+  <si>
+    <t>07/06/26 19:19 EDT</t>
+  </si>
+  <si>
+    <t>9mi W of Moapa Valley NV</t>
+  </si>
+  <si>
+    <t>36.621305, -114.617772</t>
+  </si>
+  <si>
+    <t>07/07/26 07:54 EDT</t>
+  </si>
+  <si>
+    <t>07/06/26 19:34 EDT</t>
+  </si>
+  <si>
+    <t>18.1mi NE of North Las Vegas NV</t>
+  </si>
+  <si>
+    <t>36.456897, -114.838745</t>
+  </si>
+  <si>
+    <t>07/07/26 11:00 EDT</t>
+  </si>
+  <si>
+    <t>36.040751, -115.189245</t>
+  </si>
+  <si>
+    <t>07/07/26 19:25 EDT</t>
+  </si>
+  <si>
+    <t>07/07/26 12:31 EDT</t>
+  </si>
+  <si>
+    <t>2.1mi NW of Draper UT</t>
+  </si>
+  <si>
+    <t>40.514098, -111.891411</t>
+  </si>
+  <si>
+    <t>07/07/26 12:57 EDT</t>
+  </si>
+  <si>
+    <t>0.8mi SW of Brigham City UT</t>
+  </si>
+  <si>
+    <t>41.493191, -112.054191</t>
+  </si>
+  <si>
+    <t>07/07/26 13:00 EDT</t>
+  </si>
+  <si>
+    <t>0.7mi NW of Brigham City UT</t>
+  </si>
+  <si>
+    <t>41.509666, -112.056412</t>
+  </si>
+  <si>
+    <t>07/08/26 08:37 EDT</t>
+  </si>
+  <si>
+    <t>07/07/26 13:25 EDT</t>
+  </si>
+  <si>
+    <t>4.9mi NE of Grove City PA</t>
+  </si>
+  <si>
+    <t>41.201271, -80.016426</t>
+  </si>
+  <si>
+    <t>07/07/26 15:51 EDT</t>
+  </si>
+  <si>
+    <t>67.3mi NE of Rexburg ID</t>
+  </si>
+  <si>
+    <t>44.662229, -111.102936</t>
+  </si>
+  <si>
+    <t>07/07/26 15:58 EDT</t>
+  </si>
+  <si>
+    <t>1mi SW of Salt Lake City UT</t>
+  </si>
+  <si>
+    <t>40.765407, -111.941865</t>
+  </si>
+  <si>
+    <t>07/07/26 16:05 EDT</t>
+  </si>
+  <si>
+    <t>9.1mi NE of Lochbuie CO</t>
+  </si>
+  <si>
+    <t>40.102077, -104.602682</t>
+  </si>
+  <si>
+    <t>07/07/26 16:24 EDT</t>
+  </si>
+  <si>
+    <t>1.5mi N of Spanish Fork UT</t>
+  </si>
+  <si>
+    <t>40.131558, -111.646909</t>
+  </si>
+  <si>
+    <t>07/07/26 19:26 EDT</t>
+  </si>
+  <si>
+    <t>07/08/26 08:47 EDT</t>
+  </si>
+  <si>
+    <t>40.776239, -111.949369</t>
+  </si>
+  <si>
+    <t>07/09/26 07:39 EDT</t>
+  </si>
+  <si>
+    <t>07/08/26 13:56 EDT</t>
+  </si>
+  <si>
+    <t>1.9mi SE of Taylorsville UT</t>
+  </si>
+  <si>
+    <t>40.638526, -111.921921</t>
+  </si>
+  <si>
+    <t>07/09/26 07:41 EDT</t>
+  </si>
+  <si>
+    <t>07/08/26 13:57 EDT</t>
+  </si>
+  <si>
+    <t>40.637892, -111.920762</t>
+  </si>
+  <si>
+    <t>07/08/26 14:27 EDT</t>
+  </si>
+  <si>
+    <t>2.1mi SW of Springville UT</t>
+  </si>
+  <si>
+    <t>40.141712, -111.646605</t>
+  </si>
+  <si>
+    <t>07/09/26 07:42 EDT</t>
+  </si>
+  <si>
+    <t>07/08/26 14:29 EDT</t>
+  </si>
+  <si>
+    <t>2mi N of Payson UT</t>
+  </si>
+  <si>
+    <t>40.064648, -111.732240</t>
+  </si>
+  <si>
+    <t>07/08/26 14:49 EDT</t>
+  </si>
+  <si>
+    <t>3mi S of Cedar Falls IA</t>
+  </si>
+  <si>
+    <t>42.478498, -92.471007</t>
+  </si>
+  <si>
+    <t>07/08/26 16:12 EDT</t>
+  </si>
+  <si>
+    <t>1.9mi S of Santaquin UT</t>
+  </si>
+  <si>
+    <t>39.945031, -111.807568</t>
+  </si>
+  <si>
+    <t>07/08/26 16:24 EDT</t>
+  </si>
+  <si>
+    <t>40.754243, -111.972096</t>
+  </si>
+  <si>
+    <t>07/08/26 18:44 EDT</t>
+  </si>
+  <si>
+    <t>40.743328, -111.988384</t>
+  </si>
+  <si>
+    <t>07/08/26 19:28 EDT</t>
+  </si>
+  <si>
+    <t>42.478150, -92.472906</t>
+  </si>
+  <si>
+    <t>07/09/26 01:11 EDT</t>
+  </si>
+  <si>
+    <t>19mi NE of North Las Vegas NV</t>
+  </si>
+  <si>
+    <t>36.466216, -114.828636</t>
+  </si>
+  <si>
+    <t>07/09/26 18:08 EDT</t>
+  </si>
+  <si>
+    <t>07/09/26 02:06 EDT</t>
+  </si>
+  <si>
+    <t>36.317646, -114.986958</t>
+  </si>
+  <si>
+    <t>07/09/26 02:18 EDT</t>
+  </si>
+  <si>
+    <t>8.8mi SW of St. George UT</t>
+  </si>
+  <si>
+    <t>36.976487, -113.676391</t>
+  </si>
+  <si>
+    <t>07/09/26 12:41 EDT</t>
+  </si>
+  <si>
+    <t>2.3mi W of Provo UT</t>
+  </si>
+  <si>
+    <t>40.237298, -111.688404</t>
+  </si>
+  <si>
+    <t>07/09/26 18:59 EDT</t>
+  </si>
+  <si>
+    <t>07/09/26 12:59 EDT</t>
+  </si>
+  <si>
+    <t>3.4mi N of Winchester NV</t>
+  </si>
+  <si>
+    <t>36.185898, -115.143787</t>
+  </si>
+  <si>
+    <t>07/09/26 19:00 EDT</t>
+  </si>
+  <si>
+    <t>07/09/26 14:56 EDT</t>
+  </si>
+  <si>
+    <t>1.8mi W of Nibley UT</t>
+  </si>
+  <si>
+    <t>41.677080, -111.881368</t>
+  </si>
+  <si>
+    <t>07/09/26 18:09 EDT</t>
+  </si>
+  <si>
+    <t>07/09/26 17:03 EDT</t>
+  </si>
+  <si>
+    <t>24.7mi NE of Enoch UT</t>
+  </si>
+  <si>
+    <t>38.015524, -112.719335</t>
+  </si>
+  <si>
+    <t>07/09/26 17:17 EDT</t>
+  </si>
+  <si>
+    <t>41.204128, -111.994200</t>
+  </si>
+  <si>
+    <t>07/09/26 18:38 EDT</t>
+  </si>
+  <si>
+    <t>4mi NE of Washington UT</t>
+  </si>
+  <si>
+    <t>37.172651, -113.438274</t>
+  </si>
+  <si>
+    <t>07/10/26 00:56 EDT</t>
+  </si>
+  <si>
+    <t>13.7mi N of McPherson KS</t>
+  </si>
+  <si>
+    <t>38.566836, -97.621016</t>
+  </si>
+  <si>
+    <t>07/10/26 01:43 EDT</t>
+  </si>
+  <si>
+    <t>32.3mi W of Salina KS</t>
+  </si>
+  <si>
+    <t>38.848263, -98.213231</t>
+  </si>
+  <si>
+    <t>07/10/26 10:05 EDT</t>
+  </si>
+  <si>
+    <t>0.8mi NW of Centerville UT</t>
+  </si>
+  <si>
+    <t>40.939181, -111.891164</t>
+  </si>
+  <si>
+    <t>07/10/26 12:21 EDT</t>
+  </si>
+  <si>
+    <t>3.3mi SW of Salt Lake City UT</t>
+  </si>
+  <si>
+    <t>40.741371, -111.972204</t>
+  </si>
+  <si>
+    <t>07/10/26 13:22 EDT</t>
+  </si>
+  <si>
+    <t>3.3mi NE of West Valley City UT</t>
+  </si>
+  <si>
+    <t>40.731945, -111.987756</t>
+  </si>
+  <si>
+    <t>07/10/26 15:57 EDT</t>
+  </si>
+  <si>
+    <t>39.261806, -103.646742</t>
+  </si>
+  <si>
+    <t>07/11/26 11:20 EDT</t>
+  </si>
+  <si>
+    <t>40.709732, -111.903691</t>
+  </si>
+  <si>
+    <t>07/11/26 11:22 EDT</t>
+  </si>
+  <si>
+    <t>3mi S of Clovis NM</t>
+  </si>
+  <si>
+    <t>34.396184, -103.176717</t>
+  </si>
+  <si>
+    <t>07/11/26 12:56 EDT</t>
+  </si>
+  <si>
+    <t>13.4mi NE of Roswell NM</t>
+  </si>
+  <si>
+    <t>33.542981, -104.416921</t>
+  </si>
+  <si>
+    <t>07/11/26 18:18 EDT</t>
+  </si>
+  <si>
+    <t>12.3mi E of Albuquerque NM</t>
+  </si>
+  <si>
+    <t>35.064446, -106.435359</t>
+  </si>
+  <si>
+    <t>35.064383, -106.435731</t>
+  </si>
+  <si>
+    <t>07/12/26 04:49 EDT</t>
+  </si>
+  <si>
+    <t>1.3mi N of Ontario OR</t>
+  </si>
+  <si>
+    <t>44.044652, -116.977298</t>
   </si>
 </sst>
 </file>
@@ -12132,7 +12627,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N1243"/>
+  <dimension ref="A1:N1297"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="14" width="15" customWidth="1"/>
@@ -58656,15 +59151,19 @@
         <v>75</v>
       </c>
       <c r="K1225" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1225" s="3"/>
-      <c r="M1225" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L1225" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1225" s="3" t="s">
+        <v>3866</v>
+      </c>
       <c r="N1225" s="3"/>
     </row>
     <row r="1226" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1226" s="3" t="s">
-        <v>3866</v>
+        <v>3867</v>
       </c>
       <c r="B1226" s="3"/>
       <c r="C1226" s="3">
@@ -58677,13 +59176,13 @@
         <v>47</v>
       </c>
       <c r="F1226" s="3" t="s">
-        <v>3867</v>
+        <v>3868</v>
       </c>
       <c r="G1226" s="3" t="s">
-        <v>3868</v>
+        <v>3869</v>
       </c>
       <c r="H1226" s="3" t="s">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="I1226" s="3">
         <v>67</v>
@@ -58692,15 +59191,19 @@
         <v>55</v>
       </c>
       <c r="K1226" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1226" s="3"/>
-      <c r="M1226" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L1226" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1226" s="3" t="s">
+        <v>3866</v>
+      </c>
       <c r="N1226" s="3"/>
     </row>
     <row r="1227" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1227" s="3" t="s">
-        <v>3869</v>
+        <v>3870</v>
       </c>
       <c r="B1227" s="3" t="s">
         <v>372</v>
@@ -58715,10 +59218,10 @@
         <v>24</v>
       </c>
       <c r="F1227" s="3" t="s">
-        <v>3870</v>
+        <v>3871</v>
       </c>
       <c r="G1227" s="3" t="s">
-        <v>3871</v>
+        <v>3872</v>
       </c>
       <c r="H1227" s="3"/>
       <c r="I1227" s="3">
@@ -58736,7 +59239,7 @@
     </row>
     <row r="1228" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1228" s="3" t="s">
-        <v>3872</v>
+        <v>3873</v>
       </c>
       <c r="B1228" s="3" t="s">
         <v>81</v>
@@ -58751,10 +59254,10 @@
         <v>47</v>
       </c>
       <c r="F1228" s="3" t="s">
-        <v>3873</v>
+        <v>3874</v>
       </c>
       <c r="G1228" s="3" t="s">
-        <v>3874</v>
+        <v>3875</v>
       </c>
       <c r="H1228" s="3"/>
       <c r="I1228" s="3">
@@ -58772,7 +59275,7 @@
     </row>
     <row r="1229" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1229" s="3" t="s">
-        <v>3875</v>
+        <v>3876</v>
       </c>
       <c r="B1229" s="3"/>
       <c r="C1229" s="3">
@@ -58785,13 +59288,13 @@
         <v>43</v>
       </c>
       <c r="F1229" s="3" t="s">
-        <v>3876</v>
+        <v>3877</v>
       </c>
       <c r="G1229" s="3" t="s">
-        <v>3877</v>
+        <v>3878</v>
       </c>
       <c r="H1229" s="3" t="s">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="I1229" s="3">
         <v>65</v>
@@ -58800,15 +59303,19 @@
         <v>75</v>
       </c>
       <c r="K1229" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1229" s="3"/>
-      <c r="M1229" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L1229" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1229" s="3" t="s">
+        <v>3866</v>
+      </c>
       <c r="N1229" s="3"/>
     </row>
     <row r="1230" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1230" s="3" t="s">
-        <v>3878</v>
+        <v>3879</v>
       </c>
       <c r="B1230" s="3" t="s">
         <v>81</v>
@@ -58823,10 +59330,10 @@
         <v>47</v>
       </c>
       <c r="F1230" s="3" t="s">
-        <v>3879</v>
+        <v>3880</v>
       </c>
       <c r="G1230" s="3" t="s">
-        <v>3880</v>
+        <v>3881</v>
       </c>
       <c r="H1230" s="3"/>
       <c r="I1230" s="3">
@@ -58844,7 +59351,7 @@
     </row>
     <row r="1231" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1231" s="3" t="s">
-        <v>3881</v>
+        <v>3882</v>
       </c>
       <c r="B1231" s="3" t="s">
         <v>74</v>
@@ -58859,10 +59366,10 @@
         <v>47</v>
       </c>
       <c r="F1231" s="3" t="s">
-        <v>3882</v>
+        <v>3883</v>
       </c>
       <c r="G1231" s="3" t="s">
-        <v>3883</v>
+        <v>3884</v>
       </c>
       <c r="H1231" s="3" t="s">
         <v>98</v>
@@ -58874,15 +59381,19 @@
         <v>70</v>
       </c>
       <c r="K1231" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1231" s="3"/>
-      <c r="M1231" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L1231" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1231" s="3" t="s">
+        <v>3885</v>
+      </c>
       <c r="N1231" s="3"/>
     </row>
     <row r="1232" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1232" s="3" t="s">
-        <v>3884</v>
+        <v>3886</v>
       </c>
       <c r="B1232" s="3" t="s">
         <v>74</v>
@@ -58897,10 +59408,10 @@
         <v>47</v>
       </c>
       <c r="F1232" s="3" t="s">
-        <v>3885</v>
+        <v>3887</v>
       </c>
       <c r="G1232" s="3" t="s">
-        <v>3886</v>
+        <v>3888</v>
       </c>
       <c r="H1232" s="3"/>
       <c r="I1232" s="3">
@@ -58916,7 +59427,7 @@
     </row>
     <row r="1233" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1233" s="3" t="s">
-        <v>3887</v>
+        <v>3889</v>
       </c>
       <c r="B1233" s="3" t="s">
         <v>81</v>
@@ -58931,13 +59442,13 @@
         <v>43</v>
       </c>
       <c r="F1233" s="3" t="s">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="G1233" s="3" t="s">
-        <v>3889</v>
+        <v>3891</v>
       </c>
       <c r="H1233" s="3" t="s">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="I1233" s="3">
         <v>65</v>
@@ -58946,15 +59457,19 @@
         <v>75</v>
       </c>
       <c r="K1233" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1233" s="3"/>
-      <c r="M1233" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L1233" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1233" s="3" t="s">
+        <v>3885</v>
+      </c>
       <c r="N1233" s="3"/>
     </row>
     <row r="1234" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1234" s="3" t="s">
-        <v>3890</v>
+        <v>3892</v>
       </c>
       <c r="B1234" s="3" t="s">
         <v>74</v>
@@ -58972,7 +59487,7 @@
         <v>1192</v>
       </c>
       <c r="G1234" s="3" t="s">
-        <v>3891</v>
+        <v>3893</v>
       </c>
       <c r="H1234" s="3"/>
       <c r="I1234" s="3">
@@ -58990,7 +59505,7 @@
     </row>
     <row r="1235" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1235" s="3" t="s">
-        <v>3892</v>
+        <v>3894</v>
       </c>
       <c r="B1235" s="3"/>
       <c r="C1235" s="3">
@@ -59003,13 +59518,13 @@
         <v>43</v>
       </c>
       <c r="F1235" s="3" t="s">
-        <v>3893</v>
+        <v>3895</v>
       </c>
       <c r="G1235" s="3" t="s">
-        <v>3894</v>
+        <v>3896</v>
       </c>
       <c r="H1235" s="3" t="s">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="I1235" s="3">
         <v>64</v>
@@ -59018,15 +59533,19 @@
         <v>65</v>
       </c>
       <c r="K1235" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1235" s="3"/>
-      <c r="M1235" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L1235" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1235" s="3" t="s">
+        <v>3885</v>
+      </c>
       <c r="N1235" s="3"/>
     </row>
     <row r="1236" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1236" s="3" t="s">
-        <v>3895</v>
+        <v>3897</v>
       </c>
       <c r="B1236" s="3" t="s">
         <v>339</v>
@@ -59041,13 +59560,13 @@
         <v>43</v>
       </c>
       <c r="F1236" s="3" t="s">
-        <v>3896</v>
+        <v>3898</v>
       </c>
       <c r="G1236" s="3" t="s">
-        <v>3897</v>
+        <v>3899</v>
       </c>
       <c r="H1236" s="3" t="s">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="I1236" s="3">
         <v>79</v>
@@ -59056,15 +59575,19 @@
         <v>75</v>
       </c>
       <c r="K1236" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1236" s="3"/>
-      <c r="M1236" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L1236" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1236" s="3" t="s">
+        <v>3900</v>
+      </c>
       <c r="N1236" s="3"/>
     </row>
     <row r="1237" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1237" s="3" t="s">
-        <v>3898</v>
+        <v>3901</v>
       </c>
       <c r="B1237" s="3" t="s">
         <v>81</v>
@@ -59079,13 +59602,13 @@
         <v>47</v>
       </c>
       <c r="F1237" s="3" t="s">
-        <v>3899</v>
+        <v>3902</v>
       </c>
       <c r="G1237" s="3" t="s">
-        <v>3900</v>
+        <v>3903</v>
       </c>
       <c r="H1237" s="3" t="s">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="I1237" s="3">
         <v>72</v>
@@ -59094,15 +59617,19 @@
         <v>75</v>
       </c>
       <c r="K1237" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1237" s="3"/>
-      <c r="M1237" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L1237" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1237" s="3" t="s">
+        <v>3900</v>
+      </c>
       <c r="N1237" s="3"/>
     </row>
     <row r="1238" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1238" s="3" t="s">
-        <v>3898</v>
+        <v>3901</v>
       </c>
       <c r="B1238" s="3" t="s">
         <v>81</v>
@@ -59117,13 +59644,13 @@
         <v>43</v>
       </c>
       <c r="F1238" s="3" t="s">
-        <v>3901</v>
+        <v>3904</v>
       </c>
       <c r="G1238" s="3" t="s">
-        <v>3902</v>
+        <v>3905</v>
       </c>
       <c r="H1238" s="3" t="s">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="I1238" s="3">
         <v>72</v>
@@ -59132,15 +59659,19 @@
         <v>75</v>
       </c>
       <c r="K1238" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1238" s="3"/>
-      <c r="M1238" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L1238" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1238" s="3" t="s">
+        <v>3900</v>
+      </c>
       <c r="N1238" s="3"/>
     </row>
     <row r="1239" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1239" s="3" t="s">
-        <v>3903</v>
+        <v>3906</v>
       </c>
       <c r="B1239" s="3"/>
       <c r="C1239" s="3">
@@ -59153,26 +59684,32 @@
         <v>24</v>
       </c>
       <c r="F1239" s="3" t="s">
-        <v>3904</v>
+        <v>3907</v>
       </c>
       <c r="G1239" s="3" t="s">
-        <v>3905</v>
-      </c>
-      <c r="H1239" s="3"/>
+        <v>3908</v>
+      </c>
+      <c r="H1239" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="I1239" s="3">
         <v>66</v>
       </c>
       <c r="J1239" s="3"/>
       <c r="K1239" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1239" s="3"/>
-      <c r="M1239" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L1239" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1239" s="3" t="s">
+        <v>3900</v>
+      </c>
       <c r="N1239" s="3"/>
     </row>
     <row r="1240" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1240" s="3" t="s">
-        <v>3906</v>
+        <v>3909</v>
       </c>
       <c r="B1240" s="3"/>
       <c r="C1240" s="3">
@@ -59185,26 +59722,32 @@
         <v>65</v>
       </c>
       <c r="F1240" s="3" t="s">
-        <v>3907</v>
+        <v>3910</v>
       </c>
       <c r="G1240" s="3" t="s">
-        <v>3908</v>
-      </c>
-      <c r="H1240" s="3"/>
+        <v>3911</v>
+      </c>
+      <c r="H1240" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="I1240" s="3">
         <v>24</v>
       </c>
       <c r="J1240" s="3"/>
       <c r="K1240" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1240" s="3"/>
-      <c r="M1240" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L1240" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1240" s="3" t="s">
+        <v>3900</v>
+      </c>
       <c r="N1240" s="3"/>
     </row>
     <row r="1241" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1241" s="3" t="s">
-        <v>3909</v>
+        <v>3912</v>
       </c>
       <c r="B1241" s="3" t="s">
         <v>872</v>
@@ -59222,25 +59765,29 @@
         <v>1309</v>
       </c>
       <c r="G1241" s="3" t="s">
-        <v>3910</v>
+        <v>3913</v>
       </c>
       <c r="H1241" s="3" t="s">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="I1241" s="3">
         <v>46</v>
       </c>
       <c r="J1241" s="3"/>
       <c r="K1241" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1241" s="3"/>
-      <c r="M1241" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L1241" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1241" s="3" t="s">
+        <v>3900</v>
+      </c>
       <c r="N1241" s="3"/>
     </row>
     <row r="1242" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1242" s="3" t="s">
-        <v>3911</v>
+        <v>3914</v>
       </c>
       <c r="B1242" s="3" t="s">
         <v>324</v>
@@ -59255,10 +59802,10 @@
         <v>47</v>
       </c>
       <c r="F1242" s="3" t="s">
-        <v>3912</v>
+        <v>3915</v>
       </c>
       <c r="G1242" s="3" t="s">
-        <v>3913</v>
+        <v>3916</v>
       </c>
       <c r="H1242" s="3" t="s">
         <v>98</v>
@@ -59268,15 +59815,19 @@
       </c>
       <c r="J1242" s="3"/>
       <c r="K1242" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1242" s="3"/>
-      <c r="M1242" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L1242" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1242" s="3" t="s">
+        <v>3917</v>
+      </c>
       <c r="N1242" s="3"/>
     </row>
     <row r="1243" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1243" s="3" t="s">
-        <v>3914</v>
+        <v>3918</v>
       </c>
       <c r="B1243" s="3" t="s">
         <v>23</v>
@@ -59291,10 +59842,10 @@
         <v>47</v>
       </c>
       <c r="F1243" s="3" t="s">
-        <v>3915</v>
+        <v>3919</v>
       </c>
       <c r="G1243" s="3" t="s">
-        <v>3916</v>
+        <v>3920</v>
       </c>
       <c r="H1243" s="3" t="s">
         <v>98</v>
@@ -59306,11 +59857,2075 @@
         <v>75</v>
       </c>
       <c r="K1243" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1243" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1243" s="3" t="s">
+        <v>3921</v>
+      </c>
+      <c r="N1243" s="3"/>
+    </row>
+    <row r="1244" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1244" s="3" t="s">
+        <v>3922</v>
+      </c>
+      <c r="B1244" s="3"/>
+      <c r="C1244" s="3">
+        <v>837</v>
+      </c>
+      <c r="D1244" s="3">
+        <v>1569716224</v>
+      </c>
+      <c r="E1244" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1244" s="3" t="s">
+        <v>3923</v>
+      </c>
+      <c r="G1244" s="3" t="s">
+        <v>3924</v>
+      </c>
+      <c r="H1244" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1244" s="3">
+        <v>37</v>
+      </c>
+      <c r="J1244" s="3">
+        <v>55</v>
+      </c>
+      <c r="K1244" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1244" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1244" s="3" t="s">
+        <v>3921</v>
+      </c>
+      <c r="N1244" s="3"/>
+    </row>
+    <row r="1245" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1245" s="3" t="s">
+        <v>3925</v>
+      </c>
+      <c r="B1245" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C1245" s="3">
+        <v>731</v>
+      </c>
+      <c r="D1245" s="3">
+        <v>1569719732</v>
+      </c>
+      <c r="E1245" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1245" s="3" t="s">
+        <v>3926</v>
+      </c>
+      <c r="G1245" s="3" t="s">
+        <v>3927</v>
+      </c>
+      <c r="H1245" s="3"/>
+      <c r="I1245" s="3">
+        <v>67</v>
+      </c>
+      <c r="J1245" s="3"/>
+      <c r="K1245" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L1243" s="3"/>
-      <c r="M1243" s="3"/>
-      <c r="N1243" s="3"/>
+      <c r="L1245" s="3"/>
+      <c r="M1245" s="3"/>
+      <c r="N1245" s="3"/>
+    </row>
+    <row r="1246" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1246" s="3" t="s">
+        <v>3928</v>
+      </c>
+      <c r="B1246" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1246" s="3">
+        <v>336</v>
+      </c>
+      <c r="D1246" s="3">
+        <v>1569731810</v>
+      </c>
+      <c r="E1246" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1246" s="3" t="s">
+        <v>3929</v>
+      </c>
+      <c r="G1246" s="3" t="s">
+        <v>3930</v>
+      </c>
+      <c r="H1246" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1246" s="3">
+        <v>16</v>
+      </c>
+      <c r="J1246" s="3"/>
+      <c r="K1246" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1246" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1246" s="3" t="s">
+        <v>3921</v>
+      </c>
+      <c r="N1246" s="3"/>
+    </row>
+    <row r="1247" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1247" s="3" t="s">
+        <v>3931</v>
+      </c>
+      <c r="B1247" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1247" s="3">
+        <v>839</v>
+      </c>
+      <c r="D1247" s="3">
+        <v>1569838371</v>
+      </c>
+      <c r="E1247" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="F1247" s="3" t="s">
+        <v>3932</v>
+      </c>
+      <c r="G1247" s="3" t="s">
+        <v>3933</v>
+      </c>
+      <c r="H1247" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1247" s="3">
+        <v>65</v>
+      </c>
+      <c r="J1247" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1247" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1247" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1247" s="3" t="s">
+        <v>3934</v>
+      </c>
+      <c r="N1247" s="3"/>
+    </row>
+    <row r="1248" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1248" s="3" t="s">
+        <v>3935</v>
+      </c>
+      <c r="B1248" s="3"/>
+      <c r="C1248" s="3">
+        <v>209</v>
+      </c>
+      <c r="D1248" s="3">
+        <v>1569873260</v>
+      </c>
+      <c r="E1248" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1248" s="3" t="s">
+        <v>3936</v>
+      </c>
+      <c r="G1248" s="3" t="s">
+        <v>3937</v>
+      </c>
+      <c r="H1248" s="3"/>
+      <c r="I1248" s="3">
+        <v>63</v>
+      </c>
+      <c r="J1248" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1248" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1248" s="3"/>
+      <c r="M1248" s="3"/>
+      <c r="N1248" s="3"/>
+    </row>
+    <row r="1249" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1249" s="3" t="s">
+        <v>3900</v>
+      </c>
+      <c r="B1249" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C1249" s="3">
+        <v>96</v>
+      </c>
+      <c r="D1249" s="3">
+        <v>1570160915</v>
+      </c>
+      <c r="E1249" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="F1249" s="3" t="s">
+        <v>3938</v>
+      </c>
+      <c r="G1249" s="3" t="s">
+        <v>3939</v>
+      </c>
+      <c r="H1249" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1249" s="3"/>
+      <c r="J1249" s="3"/>
+      <c r="K1249" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1249" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1249" s="3" t="s">
+        <v>3940</v>
+      </c>
+      <c r="N1249" s="3"/>
+    </row>
+    <row r="1250" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1250" s="3" t="s">
+        <v>3941</v>
+      </c>
+      <c r="B1250" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1250" s="3">
+        <v>672</v>
+      </c>
+      <c r="D1250" s="3">
+        <v>1570200659</v>
+      </c>
+      <c r="E1250" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1250" s="3" t="s">
+        <v>3942</v>
+      </c>
+      <c r="G1250" s="3" t="s">
+        <v>3943</v>
+      </c>
+      <c r="H1250" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1250" s="3">
+        <v>64</v>
+      </c>
+      <c r="J1250" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1250" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1250" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1250" s="3" t="s">
+        <v>3944</v>
+      </c>
+      <c r="N1250" s="3"/>
+    </row>
+    <row r="1251" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1251" s="3" t="s">
+        <v>3941</v>
+      </c>
+      <c r="B1251" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1251" s="3">
+        <v>672</v>
+      </c>
+      <c r="D1251" s="3">
+        <v>1570200652</v>
+      </c>
+      <c r="E1251" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1251" s="3" t="s">
+        <v>3945</v>
+      </c>
+      <c r="G1251" s="3" t="s">
+        <v>3946</v>
+      </c>
+      <c r="H1251" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1251" s="3">
+        <v>60</v>
+      </c>
+      <c r="J1251" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1251" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1251" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1251" s="3" t="s">
+        <v>3947</v>
+      </c>
+      <c r="N1251" s="3"/>
+    </row>
+    <row r="1252" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1252" s="3" t="s">
+        <v>3948</v>
+      </c>
+      <c r="B1252" s="3"/>
+      <c r="C1252" s="3">
+        <v>340</v>
+      </c>
+      <c r="D1252" s="3">
+        <v>1570303684</v>
+      </c>
+      <c r="E1252" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1252" s="3" t="s">
+        <v>2187</v>
+      </c>
+      <c r="G1252" s="3" t="s">
+        <v>3949</v>
+      </c>
+      <c r="H1252" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1252" s="3">
+        <v>45</v>
+      </c>
+      <c r="J1252" s="3">
+        <v>45</v>
+      </c>
+      <c r="K1252" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1252" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1252" s="3" t="s">
+        <v>3940</v>
+      </c>
+      <c r="N1252" s="3"/>
+    </row>
+    <row r="1253" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1253" s="3" t="s">
+        <v>3950</v>
+      </c>
+      <c r="B1253" s="3"/>
+      <c r="C1253" s="3">
+        <v>340</v>
+      </c>
+      <c r="D1253" s="3">
+        <v>1570454797</v>
+      </c>
+      <c r="E1253" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1253" s="3" t="s">
+        <v>802</v>
+      </c>
+      <c r="G1253" s="3" t="s">
+        <v>3951</v>
+      </c>
+      <c r="H1253" s="3"/>
+      <c r="I1253" s="3">
+        <v>31</v>
+      </c>
+      <c r="J1253" s="3"/>
+      <c r="K1253" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1253" s="3"/>
+      <c r="M1253" s="3"/>
+      <c r="N1253" s="3"/>
+    </row>
+    <row r="1254" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1254" s="3" t="s">
+        <v>3952</v>
+      </c>
+      <c r="B1254" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1254" s="3">
+        <v>86</v>
+      </c>
+      <c r="D1254" s="3">
+        <v>1570492146</v>
+      </c>
+      <c r="E1254" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1254" s="3" t="s">
+        <v>3953</v>
+      </c>
+      <c r="G1254" s="3" t="s">
+        <v>3954</v>
+      </c>
+      <c r="H1254" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1254" s="3">
+        <v>70</v>
+      </c>
+      <c r="J1254" s="3"/>
+      <c r="K1254" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1254" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1254" s="3" t="s">
+        <v>3947</v>
+      </c>
+      <c r="N1254" s="3"/>
+    </row>
+    <row r="1255" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1255" s="3" t="s">
+        <v>3955</v>
+      </c>
+      <c r="B1255" s="3"/>
+      <c r="C1255" s="3">
+        <v>840</v>
+      </c>
+      <c r="D1255" s="3">
+        <v>1570509658</v>
+      </c>
+      <c r="E1255" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1255" s="3" t="s">
+        <v>3180</v>
+      </c>
+      <c r="G1255" s="3" t="s">
+        <v>3956</v>
+      </c>
+      <c r="H1255" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1255" s="3">
+        <v>20</v>
+      </c>
+      <c r="J1255" s="3">
+        <v>35</v>
+      </c>
+      <c r="K1255" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1255" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1255" s="3" t="s">
+        <v>3947</v>
+      </c>
+      <c r="N1255" s="3"/>
+    </row>
+    <row r="1256" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1256" s="3" t="s">
+        <v>3957</v>
+      </c>
+      <c r="B1256" s="3"/>
+      <c r="C1256" s="3">
+        <v>375</v>
+      </c>
+      <c r="D1256" s="3">
+        <v>1570587480</v>
+      </c>
+      <c r="E1256" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1256" s="3" t="s">
+        <v>3958</v>
+      </c>
+      <c r="G1256" s="3" t="s">
+        <v>3959</v>
+      </c>
+      <c r="H1256" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1256" s="3">
+        <v>74</v>
+      </c>
+      <c r="J1256" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1256" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1256" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1256" s="3" t="s">
+        <v>3960</v>
+      </c>
+      <c r="N1256" s="3"/>
+    </row>
+    <row r="1257" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1257" s="3" t="s">
+        <v>3961</v>
+      </c>
+      <c r="B1257" s="3"/>
+      <c r="C1257" s="3">
+        <v>375</v>
+      </c>
+      <c r="D1257" s="3">
+        <v>1570595582</v>
+      </c>
+      <c r="E1257" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1257" s="3" t="s">
+        <v>3962</v>
+      </c>
+      <c r="G1257" s="3" t="s">
+        <v>3963</v>
+      </c>
+      <c r="H1257" s="3"/>
+      <c r="I1257" s="3">
+        <v>74</v>
+      </c>
+      <c r="J1257" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1257" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1257" s="3"/>
+      <c r="M1257" s="3"/>
+      <c r="N1257" s="3"/>
+    </row>
+    <row r="1258" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1258" s="3" t="s">
+        <v>3964</v>
+      </c>
+      <c r="B1258" s="3"/>
+      <c r="C1258" s="3">
+        <v>673</v>
+      </c>
+      <c r="D1258" s="3">
+        <v>1571023319</v>
+      </c>
+      <c r="E1258" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1258" s="3" t="s">
+        <v>832</v>
+      </c>
+      <c r="G1258" s="3" t="s">
+        <v>3965</v>
+      </c>
+      <c r="H1258" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1258" s="3">
+        <v>37</v>
+      </c>
+      <c r="J1258" s="3">
+        <v>55</v>
+      </c>
+      <c r="K1258" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1258" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1258" s="3" t="s">
+        <v>3966</v>
+      </c>
+      <c r="N1258" s="3"/>
+    </row>
+    <row r="1259" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1259" s="3" t="s">
+        <v>3967</v>
+      </c>
+      <c r="B1259" s="3"/>
+      <c r="C1259" s="3">
+        <v>342</v>
+      </c>
+      <c r="D1259" s="3">
+        <v>1571122135</v>
+      </c>
+      <c r="E1259" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1259" s="3" t="s">
+        <v>3968</v>
+      </c>
+      <c r="G1259" s="3" t="s">
+        <v>3969</v>
+      </c>
+      <c r="H1259" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1259" s="3">
+        <v>73</v>
+      </c>
+      <c r="J1259" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1259" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1259" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1259" s="3" t="s">
+        <v>3966</v>
+      </c>
+      <c r="N1259" s="3"/>
+    </row>
+    <row r="1260" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1260" s="3" t="s">
+        <v>3970</v>
+      </c>
+      <c r="B1260" s="3"/>
+      <c r="C1260" s="3">
+        <v>333</v>
+      </c>
+      <c r="D1260" s="3">
+        <v>1571150156</v>
+      </c>
+      <c r="E1260" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1260" s="3" t="s">
+        <v>3971</v>
+      </c>
+      <c r="G1260" s="3" t="s">
+        <v>3972</v>
+      </c>
+      <c r="H1260" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1260" s="3">
+        <v>64</v>
+      </c>
+      <c r="J1260" s="3"/>
+      <c r="K1260" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1260" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1260" s="3" t="s">
+        <v>3966</v>
+      </c>
+      <c r="N1260" s="3"/>
+    </row>
+    <row r="1261" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1261" s="3" t="s">
+        <v>3973</v>
+      </c>
+      <c r="B1261" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="C1261" s="3">
+        <v>208</v>
+      </c>
+      <c r="D1261" s="3">
+        <v>1571153495</v>
+      </c>
+      <c r="E1261" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1261" s="3" t="s">
+        <v>3974</v>
+      </c>
+      <c r="G1261" s="3" t="s">
+        <v>3975</v>
+      </c>
+      <c r="H1261" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1261" s="3">
+        <v>46</v>
+      </c>
+      <c r="J1261" s="3"/>
+      <c r="K1261" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1261" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1261" s="3" t="s">
+        <v>3976</v>
+      </c>
+      <c r="N1261" s="3"/>
+    </row>
+    <row r="1262" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1262" s="3" t="s">
+        <v>3977</v>
+      </c>
+      <c r="B1262" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1262" s="3">
+        <v>336</v>
+      </c>
+      <c r="D1262" s="3">
+        <v>1571180019</v>
+      </c>
+      <c r="E1262" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1262" s="3" t="s">
+        <v>3978</v>
+      </c>
+      <c r="G1262" s="3" t="s">
+        <v>3979</v>
+      </c>
+      <c r="H1262" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1262" s="3">
+        <v>65</v>
+      </c>
+      <c r="J1262" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1262" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1262" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1262" s="3" t="s">
+        <v>3966</v>
+      </c>
+      <c r="N1262" s="3"/>
+    </row>
+    <row r="1263" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1263" s="3" t="s">
+        <v>3980</v>
+      </c>
+      <c r="B1263" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="C1263" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="D1263" s="3">
+        <v>1571341310</v>
+      </c>
+      <c r="E1263" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1263" s="3" t="s">
+        <v>3981</v>
+      </c>
+      <c r="G1263" s="3" t="s">
+        <v>3982</v>
+      </c>
+      <c r="H1263" s="3"/>
+      <c r="I1263" s="3">
+        <v>27</v>
+      </c>
+      <c r="J1263" s="3">
+        <v>25</v>
+      </c>
+      <c r="K1263" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1263" s="3"/>
+      <c r="M1263" s="3"/>
+      <c r="N1263" s="3"/>
+    </row>
+    <row r="1264" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1264" s="3" t="s">
+        <v>3983</v>
+      </c>
+      <c r="B1264" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="C1264" s="3">
+        <v>838</v>
+      </c>
+      <c r="D1264" s="3">
+        <v>1571349156</v>
+      </c>
+      <c r="E1264" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1264" s="3" t="s">
+        <v>3984</v>
+      </c>
+      <c r="G1264" s="3" t="s">
+        <v>3985</v>
+      </c>
+      <c r="H1264" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1264" s="3">
+        <v>46</v>
+      </c>
+      <c r="J1264" s="3"/>
+      <c r="K1264" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1264" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1264" s="3" t="s">
+        <v>3966</v>
+      </c>
+      <c r="N1264" s="3"/>
+    </row>
+    <row r="1265" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1265" s="3" t="s">
+        <v>3986</v>
+      </c>
+      <c r="B1265" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C1265" s="3">
+        <v>96</v>
+      </c>
+      <c r="D1265" s="3">
+        <v>1571356436</v>
+      </c>
+      <c r="E1265" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1265" s="3" t="s">
+        <v>3987</v>
+      </c>
+      <c r="G1265" s="3" t="s">
+        <v>3988</v>
+      </c>
+      <c r="H1265" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1265" s="3">
+        <v>25</v>
+      </c>
+      <c r="J1265" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1265" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1265" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1265" s="3" t="s">
+        <v>3966</v>
+      </c>
+      <c r="N1265" s="3"/>
+    </row>
+    <row r="1266" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1266" s="3" t="s">
+        <v>3989</v>
+      </c>
+      <c r="B1266" s="3"/>
+      <c r="C1266" s="3">
+        <v>340</v>
+      </c>
+      <c r="D1266" s="3">
+        <v>1571380489</v>
+      </c>
+      <c r="E1266" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1266" s="3" t="s">
+        <v>3990</v>
+      </c>
+      <c r="G1266" s="3" t="s">
+        <v>3991</v>
+      </c>
+      <c r="H1266" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1266" s="3">
+        <v>63</v>
+      </c>
+      <c r="J1266" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1266" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1266" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1266" s="3" t="s">
+        <v>3992</v>
+      </c>
+      <c r="N1266" s="3"/>
+    </row>
+    <row r="1267" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1267" s="3" t="s">
+        <v>3993</v>
+      </c>
+      <c r="B1267" s="3"/>
+      <c r="C1267" s="3">
+        <v>338</v>
+      </c>
+      <c r="D1267" s="3">
+        <v>1571840035</v>
+      </c>
+      <c r="E1267" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1267" s="3" t="s">
+        <v>1057</v>
+      </c>
+      <c r="G1267" s="3" t="s">
+        <v>3994</v>
+      </c>
+      <c r="H1267" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1267" s="3">
+        <v>60</v>
+      </c>
+      <c r="J1267" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1267" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1267" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1267" s="3" t="s">
+        <v>3995</v>
+      </c>
+      <c r="N1267" s="3"/>
+    </row>
+    <row r="1268" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1268" s="3" t="s">
+        <v>3996</v>
+      </c>
+      <c r="B1268" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1268" s="3">
+        <v>672</v>
+      </c>
+      <c r="D1268" s="3">
+        <v>1572169440</v>
+      </c>
+      <c r="E1268" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1268" s="3" t="s">
+        <v>3997</v>
+      </c>
+      <c r="G1268" s="3" t="s">
+        <v>3998</v>
+      </c>
+      <c r="H1268" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1268" s="3">
+        <v>67</v>
+      </c>
+      <c r="J1268" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1268" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1268" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1268" s="3" t="s">
+        <v>3999</v>
+      </c>
+      <c r="N1268" s="3"/>
+    </row>
+    <row r="1269" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1269" s="3" t="s">
+        <v>4000</v>
+      </c>
+      <c r="B1269" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1269" s="3">
+        <v>672</v>
+      </c>
+      <c r="D1269" s="3">
+        <v>1572169426</v>
+      </c>
+      <c r="E1269" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1269" s="3" t="s">
+        <v>2521</v>
+      </c>
+      <c r="G1269" s="3" t="s">
+        <v>4001</v>
+      </c>
+      <c r="H1269" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1269" s="3">
+        <v>67</v>
+      </c>
+      <c r="J1269" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1269" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1269" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1269" s="3" t="s">
+        <v>3999</v>
+      </c>
+      <c r="N1269" s="3"/>
+    </row>
+    <row r="1270" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1270" s="3" t="s">
+        <v>4002</v>
+      </c>
+      <c r="B1270" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C1270" s="3">
+        <v>459</v>
+      </c>
+      <c r="D1270" s="3">
+        <v>1572201989</v>
+      </c>
+      <c r="E1270" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1270" s="3" t="s">
+        <v>4003</v>
+      </c>
+      <c r="G1270" s="3" t="s">
+        <v>4004</v>
+      </c>
+      <c r="H1270" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1270" s="3">
+        <v>64</v>
+      </c>
+      <c r="J1270" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1270" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1270" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1270" s="3" t="s">
+        <v>4005</v>
+      </c>
+      <c r="N1270" s="3"/>
+    </row>
+    <row r="1271" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1271" s="3" t="s">
+        <v>4006</v>
+      </c>
+      <c r="B1271" s="3"/>
+      <c r="C1271" s="3">
+        <v>840</v>
+      </c>
+      <c r="D1271" s="3">
+        <v>1572204453</v>
+      </c>
+      <c r="E1271" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1271" s="3" t="s">
+        <v>4007</v>
+      </c>
+      <c r="G1271" s="3" t="s">
+        <v>4008</v>
+      </c>
+      <c r="H1271" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1271" s="3">
+        <v>27</v>
+      </c>
+      <c r="J1271" s="3"/>
+      <c r="K1271" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1271" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1271" s="3" t="s">
+        <v>4005</v>
+      </c>
+      <c r="N1271" s="3"/>
+    </row>
+    <row r="1272" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1272" s="3" t="s">
+        <v>4009</v>
+      </c>
+      <c r="B1272" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1272" s="3">
+        <v>336</v>
+      </c>
+      <c r="D1272" s="3">
+        <v>1572226957</v>
+      </c>
+      <c r="E1272" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1272" s="3" t="s">
+        <v>4010</v>
+      </c>
+      <c r="G1272" s="3" t="s">
+        <v>4011</v>
+      </c>
+      <c r="H1272" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1272" s="3">
+        <v>21</v>
+      </c>
+      <c r="J1272" s="3"/>
+      <c r="K1272" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1272" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1272" s="3" t="s">
+        <v>4005</v>
+      </c>
+      <c r="N1272" s="3"/>
+    </row>
+    <row r="1273" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1273" s="3" t="s">
+        <v>4012</v>
+      </c>
+      <c r="B1273" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C1273" s="3">
+        <v>459</v>
+      </c>
+      <c r="D1273" s="3">
+        <v>1572315904</v>
+      </c>
+      <c r="E1273" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1273" s="3" t="s">
+        <v>4013</v>
+      </c>
+      <c r="G1273" s="3" t="s">
+        <v>4014</v>
+      </c>
+      <c r="H1273" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1273" s="3">
+        <v>64</v>
+      </c>
+      <c r="J1273" s="3"/>
+      <c r="K1273" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1273" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1273" s="3" t="s">
+        <v>4005</v>
+      </c>
+      <c r="N1273" s="3"/>
+    </row>
+    <row r="1274" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1274" s="3" t="s">
+        <v>4015</v>
+      </c>
+      <c r="B1274" s="3"/>
+      <c r="C1274" s="3">
+        <v>340</v>
+      </c>
+      <c r="D1274" s="3">
+        <v>1572326131</v>
+      </c>
+      <c r="E1274" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1274" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="G1274" s="3" t="s">
+        <v>4016</v>
+      </c>
+      <c r="H1274" s="3"/>
+      <c r="I1274" s="3">
+        <v>32</v>
+      </c>
+      <c r="J1274" s="3"/>
+      <c r="K1274" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1274" s="3"/>
+      <c r="M1274" s="3"/>
+      <c r="N1274" s="3"/>
+    </row>
+    <row r="1275" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1275" s="3" t="s">
+        <v>4017</v>
+      </c>
+      <c r="B1275" s="3"/>
+      <c r="C1275" s="3">
+        <v>338</v>
+      </c>
+      <c r="D1275" s="3">
+        <v>1572450828</v>
+      </c>
+      <c r="E1275" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1275" s="3" t="s">
+        <v>3042</v>
+      </c>
+      <c r="G1275" s="3" t="s">
+        <v>4018</v>
+      </c>
+      <c r="H1275" s="3"/>
+      <c r="I1275" s="3">
+        <v>37</v>
+      </c>
+      <c r="J1275" s="3"/>
+      <c r="K1275" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1275" s="3"/>
+      <c r="M1275" s="3"/>
+      <c r="N1275" s="3"/>
+    </row>
+    <row r="1276" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1276" s="3" t="s">
+        <v>4019</v>
+      </c>
+      <c r="B1276" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1276" s="3">
+        <v>336</v>
+      </c>
+      <c r="D1276" s="3">
+        <v>1572480058</v>
+      </c>
+      <c r="E1276" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1276" s="3" t="s">
+        <v>4010</v>
+      </c>
+      <c r="G1276" s="3" t="s">
+        <v>4020</v>
+      </c>
+      <c r="H1276" s="3"/>
+      <c r="I1276" s="3">
+        <v>15</v>
+      </c>
+      <c r="J1276" s="3"/>
+      <c r="K1276" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1276" s="3"/>
+      <c r="M1276" s="3"/>
+      <c r="N1276" s="3"/>
+    </row>
+    <row r="1277" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1277" s="3" t="s">
+        <v>4021</v>
+      </c>
+      <c r="B1277" s="3"/>
+      <c r="C1277" s="3">
+        <v>375</v>
+      </c>
+      <c r="D1277" s="3">
+        <v>1572605284</v>
+      </c>
+      <c r="E1277" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1277" s="3" t="s">
+        <v>4022</v>
+      </c>
+      <c r="G1277" s="3" t="s">
+        <v>4023</v>
+      </c>
+      <c r="H1277" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1277" s="3">
+        <v>75</v>
+      </c>
+      <c r="J1277" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1277" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1277" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1277" s="3" t="s">
+        <v>4024</v>
+      </c>
+      <c r="N1277" s="3"/>
+    </row>
+    <row r="1278" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1278" s="3" t="s">
+        <v>4025</v>
+      </c>
+      <c r="B1278" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C1278" s="3">
+        <v>459</v>
+      </c>
+      <c r="D1278" s="3">
+        <v>1572612094</v>
+      </c>
+      <c r="E1278" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1278" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="G1278" s="3" t="s">
+        <v>4026</v>
+      </c>
+      <c r="H1278" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1278" s="3">
+        <v>23</v>
+      </c>
+      <c r="J1278" s="3"/>
+      <c r="K1278" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1278" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1278" s="3" t="s">
+        <v>4024</v>
+      </c>
+      <c r="N1278" s="3"/>
+    </row>
+    <row r="1279" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1279" s="3" t="s">
+        <v>4027</v>
+      </c>
+      <c r="B1279" s="3"/>
+      <c r="C1279" s="3">
+        <v>375</v>
+      </c>
+      <c r="D1279" s="3">
+        <v>1572614117</v>
+      </c>
+      <c r="E1279" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1279" s="3" t="s">
+        <v>4028</v>
+      </c>
+      <c r="G1279" s="3" t="s">
+        <v>4029</v>
+      </c>
+      <c r="H1279" s="3"/>
+      <c r="I1279" s="3">
+        <v>67</v>
+      </c>
+      <c r="J1279" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1279" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1279" s="3"/>
+      <c r="M1279" s="3"/>
+      <c r="N1279" s="3"/>
+    </row>
+    <row r="1280" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1280" s="3" t="s">
+        <v>4030</v>
+      </c>
+      <c r="B1280" s="3"/>
+      <c r="C1280" s="3">
+        <v>342</v>
+      </c>
+      <c r="D1280" s="3">
+        <v>1573040023</v>
+      </c>
+      <c r="E1280" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1280" s="3" t="s">
+        <v>4031</v>
+      </c>
+      <c r="G1280" s="3" t="s">
+        <v>4032</v>
+      </c>
+      <c r="H1280" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1280" s="3">
+        <v>70</v>
+      </c>
+      <c r="J1280" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1280" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1280" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1280" s="3" t="s">
+        <v>4033</v>
+      </c>
+      <c r="N1280" s="3"/>
+    </row>
+    <row r="1281" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1281" s="3" t="s">
+        <v>4034</v>
+      </c>
+      <c r="B1281" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C1281" s="3">
+        <v>459</v>
+      </c>
+      <c r="D1281" s="3">
+        <v>1573058959</v>
+      </c>
+      <c r="E1281" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1281" s="3" t="s">
+        <v>4035</v>
+      </c>
+      <c r="G1281" s="3" t="s">
+        <v>4036</v>
+      </c>
+      <c r="H1281" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1281" s="3">
+        <v>62</v>
+      </c>
+      <c r="J1281" s="3"/>
+      <c r="K1281" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1281" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1281" s="3" t="s">
+        <v>4037</v>
+      </c>
+      <c r="N1281" s="3"/>
+    </row>
+    <row r="1282" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1282" s="3" t="s">
+        <v>4038</v>
+      </c>
+      <c r="B1282" s="3"/>
+      <c r="C1282" s="3">
+        <v>333</v>
+      </c>
+      <c r="D1282" s="3">
+        <v>1573185781</v>
+      </c>
+      <c r="E1282" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1282" s="3" t="s">
+        <v>4039</v>
+      </c>
+      <c r="G1282" s="3" t="s">
+        <v>4040</v>
+      </c>
+      <c r="H1282" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1282" s="3">
+        <v>55</v>
+      </c>
+      <c r="J1282" s="3">
+        <v>60</v>
+      </c>
+      <c r="K1282" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1282" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1282" s="3" t="s">
+        <v>4041</v>
+      </c>
+      <c r="N1282" s="3"/>
+    </row>
+    <row r="1283" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1283" s="3" t="s">
+        <v>4042</v>
+      </c>
+      <c r="B1283" s="3"/>
+      <c r="C1283" s="3">
+        <v>237</v>
+      </c>
+      <c r="D1283" s="3">
+        <v>1573314241</v>
+      </c>
+      <c r="E1283" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1283" s="3" t="s">
+        <v>4043</v>
+      </c>
+      <c r="G1283" s="3" t="s">
+        <v>4044</v>
+      </c>
+      <c r="H1283" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1283" s="3">
+        <v>67</v>
+      </c>
+      <c r="J1283" s="3">
+        <v>80</v>
+      </c>
+      <c r="K1283" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1283" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1283" s="3" t="s">
+        <v>4041</v>
+      </c>
+      <c r="N1283" s="3"/>
+    </row>
+    <row r="1284" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1284" s="3" t="s">
+        <v>4045</v>
+      </c>
+      <c r="B1284" s="3" t="s">
+        <v>872</v>
+      </c>
+      <c r="C1284" s="3">
+        <v>339</v>
+      </c>
+      <c r="D1284" s="3">
+        <v>1573325994</v>
+      </c>
+      <c r="E1284" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1284" s="3" t="s">
+        <v>3163</v>
+      </c>
+      <c r="G1284" s="3" t="s">
+        <v>4046</v>
+      </c>
+      <c r="H1284" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1284" s="3">
+        <v>69</v>
+      </c>
+      <c r="J1284" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1284" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1284" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1284" s="3" t="s">
+        <v>4041</v>
+      </c>
+      <c r="N1284" s="3"/>
+    </row>
+    <row r="1285" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1285" s="3" t="s">
+        <v>4047</v>
+      </c>
+      <c r="B1285" s="3"/>
+      <c r="C1285" s="3">
+        <v>237</v>
+      </c>
+      <c r="D1285" s="3">
+        <v>1573392792</v>
+      </c>
+      <c r="E1285" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1285" s="3" t="s">
+        <v>4048</v>
+      </c>
+      <c r="G1285" s="3" t="s">
+        <v>4049</v>
+      </c>
+      <c r="H1285" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1285" s="3">
+        <v>74</v>
+      </c>
+      <c r="J1285" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1285" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1285" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1285" s="3" t="s">
+        <v>4037</v>
+      </c>
+      <c r="N1285" s="3"/>
+    </row>
+    <row r="1286" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1286" s="3" t="s">
+        <v>4050</v>
+      </c>
+      <c r="B1286" s="3"/>
+      <c r="C1286" s="3">
+        <v>837</v>
+      </c>
+      <c r="D1286" s="3">
+        <v>1573543498</v>
+      </c>
+      <c r="E1286" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1286" s="3" t="s">
+        <v>4051</v>
+      </c>
+      <c r="G1286" s="3" t="s">
+        <v>4052</v>
+      </c>
+      <c r="H1286" s="3"/>
+      <c r="I1286" s="3">
+        <v>74</v>
+      </c>
+      <c r="J1286" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1286" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1286" s="3"/>
+      <c r="M1286" s="3"/>
+      <c r="N1286" s="3"/>
+    </row>
+    <row r="1287" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1287" s="3" t="s">
+        <v>4053</v>
+      </c>
+      <c r="B1287" s="3"/>
+      <c r="C1287" s="3">
+        <v>837</v>
+      </c>
+      <c r="D1287" s="3">
+        <v>1573551071</v>
+      </c>
+      <c r="E1287" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1287" s="3" t="s">
+        <v>4054</v>
+      </c>
+      <c r="G1287" s="3" t="s">
+        <v>4055</v>
+      </c>
+      <c r="H1287" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1287" s="3">
+        <v>54</v>
+      </c>
+      <c r="J1287" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1287" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1287" s="3"/>
+      <c r="M1287" s="3"/>
+      <c r="N1287" s="3"/>
+    </row>
+    <row r="1288" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1288" s="3" t="s">
+        <v>4056</v>
+      </c>
+      <c r="B1288" s="3"/>
+      <c r="C1288" s="3">
+        <v>333</v>
+      </c>
+      <c r="D1288" s="3">
+        <v>1573797331</v>
+      </c>
+      <c r="E1288" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1288" s="3" t="s">
+        <v>4057</v>
+      </c>
+      <c r="G1288" s="3" t="s">
+        <v>4058</v>
+      </c>
+      <c r="H1288" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1288" s="3">
+        <v>72</v>
+      </c>
+      <c r="J1288" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1288" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1288" s="3"/>
+      <c r="M1288" s="3"/>
+      <c r="N1288" s="3"/>
+    </row>
+    <row r="1289" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1289" s="3" t="s">
+        <v>4059</v>
+      </c>
+      <c r="B1289" s="3"/>
+      <c r="C1289" s="3">
+        <v>340</v>
+      </c>
+      <c r="D1289" s="3">
+        <v>1573935296</v>
+      </c>
+      <c r="E1289" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1289" s="3" t="s">
+        <v>4060</v>
+      </c>
+      <c r="G1289" s="3" t="s">
+        <v>4061</v>
+      </c>
+      <c r="H1289" s="3"/>
+      <c r="I1289" s="3">
+        <v>30</v>
+      </c>
+      <c r="J1289" s="3"/>
+      <c r="K1289" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1289" s="3"/>
+      <c r="M1289" s="3"/>
+      <c r="N1289" s="3"/>
+    </row>
+    <row r="1290" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1290" s="3" t="s">
+        <v>4062</v>
+      </c>
+      <c r="B1290" s="3"/>
+      <c r="C1290" s="3">
+        <v>338</v>
+      </c>
+      <c r="D1290" s="3">
+        <v>1573998843</v>
+      </c>
+      <c r="E1290" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1290" s="3" t="s">
+        <v>4063</v>
+      </c>
+      <c r="G1290" s="3" t="s">
+        <v>4064</v>
+      </c>
+      <c r="H1290" s="3"/>
+      <c r="I1290" s="3">
+        <v>45</v>
+      </c>
+      <c r="J1290" s="3">
+        <v>50</v>
+      </c>
+      <c r="K1290" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1290" s="3"/>
+      <c r="M1290" s="3"/>
+      <c r="N1290" s="3"/>
+    </row>
+    <row r="1291" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1291" s="3" t="s">
+        <v>4065</v>
+      </c>
+      <c r="B1291" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1291" s="3">
+        <v>336</v>
+      </c>
+      <c r="D1291" s="3">
+        <v>1574156297</v>
+      </c>
+      <c r="E1291" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1291" s="3" t="s">
+        <v>913</v>
+      </c>
+      <c r="G1291" s="3" t="s">
+        <v>4066</v>
+      </c>
+      <c r="H1291" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1291" s="3">
+        <v>33</v>
+      </c>
+      <c r="J1291" s="3"/>
+      <c r="K1291" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1291" s="3"/>
+      <c r="M1291" s="3"/>
+      <c r="N1291" s="3"/>
+    </row>
+    <row r="1292" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1292" s="3" t="s">
+        <v>4067</v>
+      </c>
+      <c r="B1292" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="C1292" s="3">
+        <v>208</v>
+      </c>
+      <c r="D1292" s="3">
+        <v>1574568335</v>
+      </c>
+      <c r="E1292" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1292" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="G1292" s="3" t="s">
+        <v>4068</v>
+      </c>
+      <c r="H1292" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1292" s="3">
+        <v>69</v>
+      </c>
+      <c r="J1292" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1292" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1292" s="3"/>
+      <c r="M1292" s="3"/>
+      <c r="N1292" s="3"/>
+    </row>
+    <row r="1293" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1293" s="3" t="s">
+        <v>4069</v>
+      </c>
+      <c r="B1293" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C1293" s="3">
+        <v>731</v>
+      </c>
+      <c r="D1293" s="3">
+        <v>1574569027</v>
+      </c>
+      <c r="E1293" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1293" s="3" t="s">
+        <v>4070</v>
+      </c>
+      <c r="G1293" s="3" t="s">
+        <v>4071</v>
+      </c>
+      <c r="H1293" s="3"/>
+      <c r="I1293" s="3">
+        <v>45</v>
+      </c>
+      <c r="J1293" s="3"/>
+      <c r="K1293" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1293" s="3"/>
+      <c r="M1293" s="3"/>
+      <c r="N1293" s="3"/>
+    </row>
+    <row r="1294" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1294" s="3" t="s">
+        <v>4072</v>
+      </c>
+      <c r="B1294" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C1294" s="3">
+        <v>731</v>
+      </c>
+      <c r="D1294" s="3">
+        <v>1574610863</v>
+      </c>
+      <c r="E1294" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1294" s="3" t="s">
+        <v>4073</v>
+      </c>
+      <c r="G1294" s="3" t="s">
+        <v>4074</v>
+      </c>
+      <c r="H1294" s="3"/>
+      <c r="I1294" s="3">
+        <v>69</v>
+      </c>
+      <c r="J1294" s="3"/>
+      <c r="K1294" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1294" s="3"/>
+      <c r="M1294" s="3"/>
+      <c r="N1294" s="3"/>
+    </row>
+    <row r="1295" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1295" s="3" t="s">
+        <v>4075</v>
+      </c>
+      <c r="B1295" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1295" s="3">
+        <v>336</v>
+      </c>
+      <c r="D1295" s="3">
+        <v>1574738210</v>
+      </c>
+      <c r="E1295" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1295" s="3" t="s">
+        <v>4076</v>
+      </c>
+      <c r="G1295" s="3" t="s">
+        <v>4077</v>
+      </c>
+      <c r="H1295" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1295" s="3">
+        <v>81</v>
+      </c>
+      <c r="J1295" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1295" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1295" s="3"/>
+      <c r="M1295" s="3"/>
+      <c r="N1295" s="3"/>
+    </row>
+    <row r="1296" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1296" s="3" t="s">
+        <v>4075</v>
+      </c>
+      <c r="B1296" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1296" s="3">
+        <v>336</v>
+      </c>
+      <c r="D1296" s="3">
+        <v>1574738216</v>
+      </c>
+      <c r="E1296" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1296" s="3" t="s">
+        <v>4076</v>
+      </c>
+      <c r="G1296" s="3" t="s">
+        <v>4078</v>
+      </c>
+      <c r="H1296" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1296" s="3">
+        <v>81</v>
+      </c>
+      <c r="J1296" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1296" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1296" s="3"/>
+      <c r="M1296" s="3"/>
+      <c r="N1296" s="3"/>
+    </row>
+    <row r="1297" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1297" s="3" t="s">
+        <v>4079</v>
+      </c>
+      <c r="B1297" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1297" s="3">
+        <v>839</v>
+      </c>
+      <c r="D1297" s="3">
+        <v>1574843120</v>
+      </c>
+      <c r="E1297" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1297" s="3" t="s">
+        <v>4080</v>
+      </c>
+      <c r="G1297" s="3" t="s">
+        <v>4081</v>
+      </c>
+      <c r="H1297" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1297" s="3">
+        <v>13</v>
+      </c>
+      <c r="J1297" s="3"/>
+      <c r="K1297" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1297" s="3"/>
+      <c r="M1297" s="3"/>
+      <c r="N1297" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\PCS-Trucking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1FEAFAE0-90F8-475B-94B0-8B38BDD64FBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3D8024B2-8B49-45BA-9257-232F0201AD7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9667" uniqueCount="4082">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9897" uniqueCount="4182">
   <si>
     <t>DRIVE ALERTS</t>
   </si>
@@ -12190,6 +12190,9 @@
     <t>38.848263, -98.213231</t>
   </si>
   <si>
+    <t>07/12/26 10:42 EDT</t>
+  </si>
+  <si>
     <t>07/10/26 10:05 EDT</t>
   </si>
   <si>
@@ -12223,6 +12226,9 @@
     <t>39.261806, -103.646742</t>
   </si>
   <si>
+    <t>07/12/26 10:43 EDT</t>
+  </si>
+  <si>
     <t>07/11/26 11:20 EDT</t>
   </si>
   <si>
@@ -12259,6 +12265,9 @@
     <t>35.064383, -106.435731</t>
   </si>
   <si>
+    <t>07/12/26 20:31 EDT</t>
+  </si>
+  <si>
     <t>07/12/26 04:49 EDT</t>
   </si>
   <si>
@@ -12266,6 +12275,297 @@
   </si>
   <si>
     <t>44.044652, -116.977298</t>
+  </si>
+  <si>
+    <t>07/12/26 13:41 EDT</t>
+  </si>
+  <si>
+    <t>22.8mi NW of Abilene TX</t>
+  </si>
+  <si>
+    <t>32.756257, -99.897187</t>
+  </si>
+  <si>
+    <t>07/12/26 20:32 EDT</t>
+  </si>
+  <si>
+    <t>07/13/26 13:13 EDT</t>
+  </si>
+  <si>
+    <t>4.6mi E of Albuquerque NM</t>
+  </si>
+  <si>
+    <t>35.096023, -106.565673</t>
+  </si>
+  <si>
+    <t>07/14/26 11:51 EDT</t>
+  </si>
+  <si>
+    <t>07/13/26 13:22 EDT</t>
+  </si>
+  <si>
+    <t>40.744333, -111.989225</t>
+  </si>
+  <si>
+    <t>07/13/26 14:44 EDT</t>
+  </si>
+  <si>
+    <t>7.6mi N of Nephi UT</t>
+  </si>
+  <si>
+    <t>39.816904, -111.833954</t>
+  </si>
+  <si>
+    <t>07/14/26 12:08 EDT</t>
+  </si>
+  <si>
+    <t>07/13/26 14:58 EDT</t>
+  </si>
+  <si>
+    <t>1.4mi N of Taylorsville UT</t>
+  </si>
+  <si>
+    <t>40.676596, -111.952764</t>
+  </si>
+  <si>
+    <t>07/13/26 15:58 EDT</t>
+  </si>
+  <si>
+    <t>40.747921, -112.022280</t>
+  </si>
+  <si>
+    <t>07/13/26 16:32 EDT</t>
+  </si>
+  <si>
+    <t>40.188917, -111.648801</t>
+  </si>
+  <si>
+    <t>07/13/26 16:51 EDT</t>
+  </si>
+  <si>
+    <t>40.747873, -112.022306</t>
+  </si>
+  <si>
+    <t>07/13/26 19:14 EDT</t>
+  </si>
+  <si>
+    <t>40.736471, -111.969090</t>
+  </si>
+  <si>
+    <t>07/14/26 03:04 EDT</t>
+  </si>
+  <si>
+    <t>33.9mi NE of Enoch UT</t>
+  </si>
+  <si>
+    <t>38.130648, -112.626944</t>
+  </si>
+  <si>
+    <t>07/14/26 04:30 EDT</t>
+  </si>
+  <si>
+    <t>18.9mi SW of Nephi UT</t>
+  </si>
+  <si>
+    <t>39.465153, -111.999093</t>
+  </si>
+  <si>
+    <t>07/14/26 12:13 EDT</t>
+  </si>
+  <si>
+    <t>1mi S of American Fork UT</t>
+  </si>
+  <si>
+    <t>40.364739, -111.791640</t>
+  </si>
+  <si>
+    <t>07/15/26 08:02 EDT</t>
+  </si>
+  <si>
+    <t>07/14/26 14:02 EDT</t>
+  </si>
+  <si>
+    <t>4.1mi E of Commerce City CO</t>
+  </si>
+  <si>
+    <t>39.842720, -104.771875</t>
+  </si>
+  <si>
+    <t>07/14/26 21:19 EDT</t>
+  </si>
+  <si>
+    <t>07/14/26 14:45 EDT</t>
+  </si>
+  <si>
+    <t>40.187890, -111.646728</t>
+  </si>
+  <si>
+    <t>07/14/26 17:12 EDT</t>
+  </si>
+  <si>
+    <t>22.9mi N of Stephenville TX</t>
+  </si>
+  <si>
+    <t>32.536634, -98.311869</t>
+  </si>
+  <si>
+    <t>07/15/26 10:52 EDT</t>
+  </si>
+  <si>
+    <t>2.1mi S of Fultondale AL</t>
+  </si>
+  <si>
+    <t>33.587273, -86.805205</t>
+  </si>
+  <si>
+    <t>07/15/26 11:02 EDT</t>
+  </si>
+  <si>
+    <t>07/15/26 11:07 EDT</t>
+  </si>
+  <si>
+    <t>40.751526, -112.020275</t>
+  </si>
+  <si>
+    <t>07/15/26 16:05 EDT</t>
+  </si>
+  <si>
+    <t>07/15/26 14:49 EDT</t>
+  </si>
+  <si>
+    <t>5mi SE of Tuscaloosa AL</t>
+  </si>
+  <si>
+    <t>33.174838, -87.479365</t>
+  </si>
+  <si>
+    <t>07/15/26 18:51 EDT</t>
+  </si>
+  <si>
+    <t>36.1mi W of Rawlins WY</t>
+  </si>
+  <si>
+    <t>41.698129, -107.917694</t>
+  </si>
+  <si>
+    <t>07/16/26 08:38 EDT</t>
+  </si>
+  <si>
+    <t>07/15/26 22:02 EDT</t>
+  </si>
+  <si>
+    <t>35.514790, -115.432528</t>
+  </si>
+  <si>
+    <t>07/16/26 08:39 EDT</t>
+  </si>
+  <si>
+    <t>07/16/26 16:37 EDT</t>
+  </si>
+  <si>
+    <t>31.2mi SW of Richfield UT</t>
+  </si>
+  <si>
+    <t>38.553523, -112.607084</t>
+  </si>
+  <si>
+    <t>07/16/26 21:15 EDT</t>
+  </si>
+  <si>
+    <t>07/16/26 17:19 EDT</t>
+  </si>
+  <si>
+    <t>36.209420, -115.129886</t>
+  </si>
+  <si>
+    <t>07/17/26 14:04 EDT</t>
+  </si>
+  <si>
+    <t>1.9mi W of Springville UT</t>
+  </si>
+  <si>
+    <t>40.161375, -111.655700</t>
+  </si>
+  <si>
+    <t>07/17/26 16:52 EDT</t>
+  </si>
+  <si>
+    <t>12.2mi W of Forrest City AR</t>
+  </si>
+  <si>
+    <t>34.959540, -90.998392</t>
+  </si>
+  <si>
+    <t>07/17/26 18:23 EDT</t>
+  </si>
+  <si>
+    <t>1.7mi NE of Cedar City UT</t>
+  </si>
+  <si>
+    <t>37.700915, -113.074937</t>
+  </si>
+  <si>
+    <t>07/17/26 18:39 EDT</t>
+  </si>
+  <si>
+    <t>48.8mi N of Lamar CO</t>
+  </si>
+  <si>
+    <t>38.763966, -102.809076</t>
+  </si>
+  <si>
+    <t>07/17/26 22:49 EDT</t>
+  </si>
+  <si>
+    <t>40.2mi S of Enterprise NV</t>
+  </si>
+  <si>
+    <t>35.466791, -115.485017</t>
+  </si>
+  <si>
+    <t>07/18/26 03:00 EDT</t>
+  </si>
+  <si>
+    <t>2.6mi E of Layton UT</t>
+  </si>
+  <si>
+    <t>41.078245, -111.911222</t>
+  </si>
+  <si>
+    <t>07/18/26 08:34 EDT</t>
+  </si>
+  <si>
+    <t>7mi E of Kearney NE</t>
+  </si>
+  <si>
+    <t>40.688249, -98.949936</t>
+  </si>
+  <si>
+    <t>07/18/26 11:53 EDT</t>
+  </si>
+  <si>
+    <t>3mi N of West Valley City UT</t>
+  </si>
+  <si>
+    <t>40.730357, -112.024750</t>
+  </si>
+  <si>
+    <t>07/18/26 13:36 EDT</t>
+  </si>
+  <si>
+    <t>9.6mi E of Amarillo TX</t>
+  </si>
+  <si>
+    <t>35.206388, -101.662328</t>
+  </si>
+  <si>
+    <t>07/18/26 23:40 EDT</t>
+  </si>
+  <si>
+    <t>6.9mi E of Barstow CA</t>
+  </si>
+  <si>
+    <t>34.903384, -116.934257</t>
   </si>
 </sst>
 </file>
@@ -12627,7 +12927,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N1297"/>
+  <dimension ref="A1:N1329"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="14" width="15" customWidth="1"/>
@@ -61556,7 +61856,7 @@
         <v>4055</v>
       </c>
       <c r="H1287" s="3" t="s">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="I1287" s="3">
         <v>54</v>
@@ -61565,15 +61865,19 @@
         <v>75</v>
       </c>
       <c r="K1287" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1287" s="3"/>
-      <c r="M1287" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L1287" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1287" s="3" t="s">
+        <v>4056</v>
+      </c>
       <c r="N1287" s="3"/>
     </row>
     <row r="1288" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1288" s="3" t="s">
-        <v>4056</v>
+        <v>4057</v>
       </c>
       <c r="B1288" s="3"/>
       <c r="C1288" s="3">
@@ -61586,13 +61890,13 @@
         <v>47</v>
       </c>
       <c r="F1288" s="3" t="s">
-        <v>4057</v>
+        <v>4058</v>
       </c>
       <c r="G1288" s="3" t="s">
-        <v>4058</v>
+        <v>4059</v>
       </c>
       <c r="H1288" s="3" t="s">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="I1288" s="3">
         <v>72</v>
@@ -61601,15 +61905,19 @@
         <v>70</v>
       </c>
       <c r="K1288" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1288" s="3"/>
-      <c r="M1288" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L1288" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1288" s="3" t="s">
+        <v>4056</v>
+      </c>
       <c r="N1288" s="3"/>
     </row>
     <row r="1289" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1289" s="3" t="s">
-        <v>4059</v>
+        <v>4060</v>
       </c>
       <c r="B1289" s="3"/>
       <c r="C1289" s="3">
@@ -61622,10 +61930,10 @@
         <v>24</v>
       </c>
       <c r="F1289" s="3" t="s">
-        <v>4060</v>
+        <v>4061</v>
       </c>
       <c r="G1289" s="3" t="s">
-        <v>4061</v>
+        <v>4062</v>
       </c>
       <c r="H1289" s="3"/>
       <c r="I1289" s="3">
@@ -61641,7 +61949,7 @@
     </row>
     <row r="1290" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1290" s="3" t="s">
-        <v>4062</v>
+        <v>4063</v>
       </c>
       <c r="B1290" s="3"/>
       <c r="C1290" s="3">
@@ -61654,10 +61962,10 @@
         <v>24</v>
       </c>
       <c r="F1290" s="3" t="s">
-        <v>4063</v>
+        <v>4064</v>
       </c>
       <c r="G1290" s="3" t="s">
-        <v>4064</v>
+        <v>4065</v>
       </c>
       <c r="H1290" s="3"/>
       <c r="I1290" s="3">
@@ -61675,7 +61983,7 @@
     </row>
     <row r="1291" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1291" s="3" t="s">
-        <v>4065</v>
+        <v>4066</v>
       </c>
       <c r="B1291" s="3" t="s">
         <v>81</v>
@@ -61693,25 +62001,29 @@
         <v>913</v>
       </c>
       <c r="G1291" s="3" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
       <c r="H1291" s="3" t="s">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="I1291" s="3">
         <v>33</v>
       </c>
       <c r="J1291" s="3"/>
       <c r="K1291" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1291" s="3"/>
-      <c r="M1291" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L1291" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1291" s="3" t="s">
+        <v>4068</v>
+      </c>
       <c r="N1291" s="3"/>
     </row>
     <row r="1292" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1292" s="3" t="s">
-        <v>4067</v>
+        <v>4069</v>
       </c>
       <c r="B1292" s="3" t="s">
         <v>291</v>
@@ -61729,10 +62041,10 @@
         <v>1099</v>
       </c>
       <c r="G1292" s="3" t="s">
-        <v>4068</v>
+        <v>4070</v>
       </c>
       <c r="H1292" s="3" t="s">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="I1292" s="3">
         <v>69</v>
@@ -61741,15 +62053,19 @@
         <v>70</v>
       </c>
       <c r="K1292" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1292" s="3"/>
-      <c r="M1292" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L1292" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1292" s="3" t="s">
+        <v>4068</v>
+      </c>
       <c r="N1292" s="3"/>
     </row>
     <row r="1293" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1293" s="3" t="s">
-        <v>4069</v>
+        <v>4071</v>
       </c>
       <c r="B1293" s="3" t="s">
         <v>324</v>
@@ -61764,10 +62080,10 @@
         <v>24</v>
       </c>
       <c r="F1293" s="3" t="s">
-        <v>4070</v>
+        <v>4072</v>
       </c>
       <c r="G1293" s="3" t="s">
-        <v>4071</v>
+        <v>4073</v>
       </c>
       <c r="H1293" s="3"/>
       <c r="I1293" s="3">
@@ -61783,7 +62099,7 @@
     </row>
     <row r="1294" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1294" s="3" t="s">
-        <v>4072</v>
+        <v>4074</v>
       </c>
       <c r="B1294" s="3" t="s">
         <v>324</v>
@@ -61798,10 +62114,10 @@
         <v>24</v>
       </c>
       <c r="F1294" s="3" t="s">
-        <v>4073</v>
+        <v>4075</v>
       </c>
       <c r="G1294" s="3" t="s">
-        <v>4074</v>
+        <v>4076</v>
       </c>
       <c r="H1294" s="3"/>
       <c r="I1294" s="3">
@@ -61817,7 +62133,7 @@
     </row>
     <row r="1295" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1295" s="3" t="s">
-        <v>4075</v>
+        <v>4077</v>
       </c>
       <c r="B1295" s="3" t="s">
         <v>81</v>
@@ -61832,13 +62148,13 @@
         <v>43</v>
       </c>
       <c r="F1295" s="3" t="s">
-        <v>4076</v>
+        <v>4078</v>
       </c>
       <c r="G1295" s="3" t="s">
-        <v>4077</v>
+        <v>4079</v>
       </c>
       <c r="H1295" s="3" t="s">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="I1295" s="3">
         <v>81</v>
@@ -61847,15 +62163,19 @@
         <v>65</v>
       </c>
       <c r="K1295" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1295" s="3"/>
-      <c r="M1295" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L1295" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1295" s="3" t="s">
+        <v>4068</v>
+      </c>
       <c r="N1295" s="3"/>
     </row>
     <row r="1296" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1296" s="3" t="s">
-        <v>4075</v>
+        <v>4077</v>
       </c>
       <c r="B1296" s="3" t="s">
         <v>81</v>
@@ -61870,10 +62190,10 @@
         <v>47</v>
       </c>
       <c r="F1296" s="3" t="s">
-        <v>4076</v>
+        <v>4078</v>
       </c>
       <c r="G1296" s="3" t="s">
-        <v>4078</v>
+        <v>4080</v>
       </c>
       <c r="H1296" s="3" t="s">
         <v>98</v>
@@ -61885,15 +62205,19 @@
         <v>65</v>
       </c>
       <c r="K1296" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1296" s="3"/>
-      <c r="M1296" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L1296" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1296" s="3" t="s">
+        <v>4081</v>
+      </c>
       <c r="N1296" s="3"/>
     </row>
     <row r="1297" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1297" s="3" t="s">
-        <v>4079</v>
+        <v>4082</v>
       </c>
       <c r="B1297" s="3" t="s">
         <v>17</v>
@@ -61908,24 +62232,1194 @@
         <v>65</v>
       </c>
       <c r="F1297" s="3" t="s">
-        <v>4080</v>
+        <v>4083</v>
       </c>
       <c r="G1297" s="3" t="s">
-        <v>4081</v>
+        <v>4084</v>
       </c>
       <c r="H1297" s="3" t="s">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="I1297" s="3">
         <v>13</v>
       </c>
       <c r="J1297" s="3"/>
       <c r="K1297" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1297" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1297" s="3" t="s">
+        <v>4068</v>
+      </c>
+      <c r="N1297" s="3"/>
+    </row>
+    <row r="1298" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1298" s="3" t="s">
+        <v>4085</v>
+      </c>
+      <c r="B1298" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1298" s="3">
+        <v>210</v>
+      </c>
+      <c r="D1298" s="3">
+        <v>1574944429</v>
+      </c>
+      <c r="E1298" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1298" s="3" t="s">
+        <v>4086</v>
+      </c>
+      <c r="G1298" s="3" t="s">
+        <v>4087</v>
+      </c>
+      <c r="H1298" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1298" s="3">
+        <v>22</v>
+      </c>
+      <c r="J1298" s="3"/>
+      <c r="K1298" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1298" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1298" s="3" t="s">
+        <v>4088</v>
+      </c>
+      <c r="N1298" s="3"/>
+    </row>
+    <row r="1299" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1299" s="3" t="s">
+        <v>4089</v>
+      </c>
+      <c r="B1299" s="3"/>
+      <c r="C1299" s="3">
+        <v>375</v>
+      </c>
+      <c r="D1299" s="3">
+        <v>1575533091</v>
+      </c>
+      <c r="E1299" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1299" s="3" t="s">
+        <v>4090</v>
+      </c>
+      <c r="G1299" s="3" t="s">
+        <v>4091</v>
+      </c>
+      <c r="H1299" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1299" s="3">
+        <v>64</v>
+      </c>
+      <c r="J1299" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1299" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1299" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1299" s="3" t="s">
+        <v>4092</v>
+      </c>
+      <c r="N1299" s="3"/>
+    </row>
+    <row r="1300" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1300" s="3" t="s">
+        <v>4093</v>
+      </c>
+      <c r="B1300" s="3"/>
+      <c r="C1300" s="3">
+        <v>338</v>
+      </c>
+      <c r="D1300" s="3">
+        <v>1575541792</v>
+      </c>
+      <c r="E1300" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1300" s="3" t="s">
+        <v>3042</v>
+      </c>
+      <c r="G1300" s="3" t="s">
+        <v>4094</v>
+      </c>
+      <c r="H1300" s="3"/>
+      <c r="I1300" s="3">
+        <v>39</v>
+      </c>
+      <c r="J1300" s="3"/>
+      <c r="K1300" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L1297" s="3"/>
-      <c r="M1297" s="3"/>
-      <c r="N1297" s="3"/>
+      <c r="L1300" s="3"/>
+      <c r="M1300" s="3"/>
+      <c r="N1300" s="3"/>
+    </row>
+    <row r="1301" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1301" s="3" t="s">
+        <v>4095</v>
+      </c>
+      <c r="B1301" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="C1301" s="3">
+        <v>342</v>
+      </c>
+      <c r="D1301" s="3">
+        <v>1575624680</v>
+      </c>
+      <c r="E1301" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1301" s="3" t="s">
+        <v>4096</v>
+      </c>
+      <c r="G1301" s="3" t="s">
+        <v>4097</v>
+      </c>
+      <c r="H1301" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1301" s="3">
+        <v>74</v>
+      </c>
+      <c r="J1301" s="3">
+        <v>80</v>
+      </c>
+      <c r="K1301" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1301" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1301" s="3" t="s">
+        <v>4098</v>
+      </c>
+      <c r="N1301" s="3"/>
+    </row>
+    <row r="1302" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1302" s="3" t="s">
+        <v>4099</v>
+      </c>
+      <c r="B1302" s="3" t="s">
+        <v>872</v>
+      </c>
+      <c r="C1302" s="3">
+        <v>344</v>
+      </c>
+      <c r="D1302" s="3">
+        <v>1575638914</v>
+      </c>
+      <c r="E1302" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1302" s="3" t="s">
+        <v>4100</v>
+      </c>
+      <c r="G1302" s="3" t="s">
+        <v>4101</v>
+      </c>
+      <c r="H1302" s="3"/>
+      <c r="I1302" s="3">
+        <v>55</v>
+      </c>
+      <c r="J1302" s="3"/>
+      <c r="K1302" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1302" s="3"/>
+      <c r="M1302" s="3"/>
+      <c r="N1302" s="3"/>
+    </row>
+    <row r="1303" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1303" s="3" t="s">
+        <v>4102</v>
+      </c>
+      <c r="B1303" s="3"/>
+      <c r="C1303" s="3">
+        <v>340</v>
+      </c>
+      <c r="D1303" s="3">
+        <v>1575697392</v>
+      </c>
+      <c r="E1303" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1303" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="G1303" s="3" t="s">
+        <v>4103</v>
+      </c>
+      <c r="H1303" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1303" s="3">
+        <v>21</v>
+      </c>
+      <c r="J1303" s="3"/>
+      <c r="K1303" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1303" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1303" s="3" t="s">
+        <v>4098</v>
+      </c>
+      <c r="N1303" s="3"/>
+    </row>
+    <row r="1304" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1304" s="3" t="s">
+        <v>4104</v>
+      </c>
+      <c r="B1304" s="3"/>
+      <c r="C1304" s="3">
+        <v>840</v>
+      </c>
+      <c r="D1304" s="3">
+        <v>1575729195</v>
+      </c>
+      <c r="E1304" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1304" s="3" t="s">
+        <v>2437</v>
+      </c>
+      <c r="G1304" s="3" t="s">
+        <v>4105</v>
+      </c>
+      <c r="H1304" s="3"/>
+      <c r="I1304" s="3">
+        <v>38</v>
+      </c>
+      <c r="J1304" s="3"/>
+      <c r="K1304" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1304" s="3"/>
+      <c r="M1304" s="3"/>
+      <c r="N1304" s="3"/>
+    </row>
+    <row r="1305" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1305" s="3" t="s">
+        <v>4106</v>
+      </c>
+      <c r="B1305" s="3"/>
+      <c r="C1305" s="3">
+        <v>340</v>
+      </c>
+      <c r="D1305" s="3">
+        <v>1575747565</v>
+      </c>
+      <c r="E1305" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1305" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="G1305" s="3" t="s">
+        <v>4107</v>
+      </c>
+      <c r="H1305" s="3"/>
+      <c r="I1305" s="3">
+        <v>16</v>
+      </c>
+      <c r="J1305" s="3"/>
+      <c r="K1305" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1305" s="3"/>
+      <c r="M1305" s="3"/>
+      <c r="N1305" s="3"/>
+    </row>
+    <row r="1306" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1306" s="3" t="s">
+        <v>4108</v>
+      </c>
+      <c r="B1306" s="3"/>
+      <c r="C1306" s="3">
+        <v>340</v>
+      </c>
+      <c r="D1306" s="3">
+        <v>1575854632</v>
+      </c>
+      <c r="E1306" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1306" s="3" t="s">
+        <v>802</v>
+      </c>
+      <c r="G1306" s="3" t="s">
+        <v>4109</v>
+      </c>
+      <c r="H1306" s="3"/>
+      <c r="I1306" s="3">
+        <v>21</v>
+      </c>
+      <c r="J1306" s="3"/>
+      <c r="K1306" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1306" s="3"/>
+      <c r="M1306" s="3"/>
+      <c r="N1306" s="3"/>
+    </row>
+    <row r="1307" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1307" s="3" t="s">
+        <v>4110</v>
+      </c>
+      <c r="B1307" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="C1307" s="3">
+        <v>342</v>
+      </c>
+      <c r="D1307" s="3">
+        <v>1575991177</v>
+      </c>
+      <c r="E1307" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1307" s="3" t="s">
+        <v>4111</v>
+      </c>
+      <c r="G1307" s="3" t="s">
+        <v>4112</v>
+      </c>
+      <c r="H1307" s="3"/>
+      <c r="I1307" s="3">
+        <v>68</v>
+      </c>
+      <c r="J1307" s="3">
+        <v>80</v>
+      </c>
+      <c r="K1307" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1307" s="3"/>
+      <c r="M1307" s="3"/>
+      <c r="N1307" s="3"/>
+    </row>
+    <row r="1308" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1308" s="3" t="s">
+        <v>4113</v>
+      </c>
+      <c r="B1308" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="C1308" s="3">
+        <v>342</v>
+      </c>
+      <c r="D1308" s="3">
+        <v>1576004652</v>
+      </c>
+      <c r="E1308" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1308" s="3" t="s">
+        <v>4114</v>
+      </c>
+      <c r="G1308" s="3" t="s">
+        <v>4115</v>
+      </c>
+      <c r="H1308" s="3"/>
+      <c r="I1308" s="3">
+        <v>65</v>
+      </c>
+      <c r="J1308" s="3">
+        <v>80</v>
+      </c>
+      <c r="K1308" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1308" s="3"/>
+      <c r="M1308" s="3"/>
+      <c r="N1308" s="3"/>
+    </row>
+    <row r="1309" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1309" s="3" t="s">
+        <v>4116</v>
+      </c>
+      <c r="B1309" s="3"/>
+      <c r="C1309" s="3">
+        <v>340</v>
+      </c>
+      <c r="D1309" s="3">
+        <v>1576371667</v>
+      </c>
+      <c r="E1309" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1309" s="3" t="s">
+        <v>4117</v>
+      </c>
+      <c r="G1309" s="3" t="s">
+        <v>4118</v>
+      </c>
+      <c r="H1309" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1309" s="3">
+        <v>65</v>
+      </c>
+      <c r="J1309" s="3"/>
+      <c r="K1309" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1309" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1309" s="3" t="s">
+        <v>4119</v>
+      </c>
+      <c r="N1309" s="3"/>
+    </row>
+    <row r="1310" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1310" s="3" t="s">
+        <v>4120</v>
+      </c>
+      <c r="B1310" s="3"/>
+      <c r="C1310" s="3">
+        <v>237</v>
+      </c>
+      <c r="D1310" s="3">
+        <v>1576491327</v>
+      </c>
+      <c r="E1310" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1310" s="3" t="s">
+        <v>4121</v>
+      </c>
+      <c r="G1310" s="3" t="s">
+        <v>4122</v>
+      </c>
+      <c r="H1310" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1310" s="3">
+        <v>48</v>
+      </c>
+      <c r="J1310" s="3"/>
+      <c r="K1310" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1310" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1310" s="3" t="s">
+        <v>4123</v>
+      </c>
+      <c r="N1310" s="3"/>
+    </row>
+    <row r="1311" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1311" s="3" t="s">
+        <v>4124</v>
+      </c>
+      <c r="B1311" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="C1311" s="3">
+        <v>342</v>
+      </c>
+      <c r="D1311" s="3">
+        <v>1576539125</v>
+      </c>
+      <c r="E1311" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1311" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="G1311" s="3" t="s">
+        <v>4125</v>
+      </c>
+      <c r="H1311" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1311" s="3">
+        <v>74</v>
+      </c>
+      <c r="J1311" s="3"/>
+      <c r="K1311" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1311" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1311" s="3" t="s">
+        <v>4123</v>
+      </c>
+      <c r="N1311" s="3"/>
+    </row>
+    <row r="1312" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1312" s="3" t="s">
+        <v>4126</v>
+      </c>
+      <c r="B1312" s="3"/>
+      <c r="C1312" s="3">
+        <v>375</v>
+      </c>
+      <c r="D1312" s="3">
+        <v>1576692348</v>
+      </c>
+      <c r="E1312" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1312" s="3" t="s">
+        <v>4127</v>
+      </c>
+      <c r="G1312" s="3" t="s">
+        <v>4128</v>
+      </c>
+      <c r="H1312" s="3"/>
+      <c r="I1312" s="3">
+        <v>72</v>
+      </c>
+      <c r="J1312" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1312" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1312" s="3"/>
+      <c r="M1312" s="3"/>
+      <c r="N1312" s="3"/>
+    </row>
+    <row r="1313" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1313" s="3" t="s">
+        <v>4129</v>
+      </c>
+      <c r="B1313" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C1313" s="3">
+        <v>731</v>
+      </c>
+      <c r="D1313" s="3">
+        <v>1577232076</v>
+      </c>
+      <c r="E1313" s="3" t="s">
+        <v>765</v>
+      </c>
+      <c r="F1313" s="3" t="s">
+        <v>4130</v>
+      </c>
+      <c r="G1313" s="3" t="s">
+        <v>4131</v>
+      </c>
+      <c r="H1313" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1313" s="3">
+        <v>50</v>
+      </c>
+      <c r="J1313" s="3"/>
+      <c r="K1313" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1313" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1313" s="3" t="s">
+        <v>4132</v>
+      </c>
+      <c r="N1313" s="3"/>
+    </row>
+    <row r="1314" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1314" s="3" t="s">
+        <v>4133</v>
+      </c>
+      <c r="B1314" s="3"/>
+      <c r="C1314" s="3">
+        <v>338</v>
+      </c>
+      <c r="D1314" s="3">
+        <v>1577249350</v>
+      </c>
+      <c r="E1314" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1314" s="3" t="s">
+        <v>1818</v>
+      </c>
+      <c r="G1314" s="3" t="s">
+        <v>4134</v>
+      </c>
+      <c r="H1314" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1314" s="3">
+        <v>18</v>
+      </c>
+      <c r="J1314" s="3"/>
+      <c r="K1314" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1314" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1314" s="3" t="s">
+        <v>4135</v>
+      </c>
+      <c r="N1314" s="3"/>
+    </row>
+    <row r="1315" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1315" s="3" t="s">
+        <v>4136</v>
+      </c>
+      <c r="B1315" s="3"/>
+      <c r="C1315" s="3">
+        <v>375</v>
+      </c>
+      <c r="D1315" s="3">
+        <v>1577493439</v>
+      </c>
+      <c r="E1315" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1315" s="3" t="s">
+        <v>4137</v>
+      </c>
+      <c r="G1315" s="3" t="s">
+        <v>4138</v>
+      </c>
+      <c r="H1315" s="3"/>
+      <c r="I1315" s="3">
+        <v>76</v>
+      </c>
+      <c r="J1315" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1315" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1315" s="3"/>
+      <c r="M1315" s="3"/>
+      <c r="N1315" s="3"/>
+    </row>
+    <row r="1316" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1316" s="3" t="s">
+        <v>4139</v>
+      </c>
+      <c r="B1316" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="C1316" s="3">
+        <v>63</v>
+      </c>
+      <c r="D1316" s="3">
+        <v>1577722864</v>
+      </c>
+      <c r="E1316" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1316" s="3" t="s">
+        <v>4140</v>
+      </c>
+      <c r="G1316" s="3" t="s">
+        <v>4141</v>
+      </c>
+      <c r="H1316" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1316" s="3">
+        <v>76</v>
+      </c>
+      <c r="J1316" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1316" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1316" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1316" s="3" t="s">
+        <v>4142</v>
+      </c>
+      <c r="N1316" s="3"/>
+    </row>
+    <row r="1317" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1317" s="3" t="s">
+        <v>4143</v>
+      </c>
+      <c r="B1317" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1317" s="3">
+        <v>839</v>
+      </c>
+      <c r="D1317" s="3">
+        <v>1577821250</v>
+      </c>
+      <c r="E1317" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1317" s="3" t="s">
+        <v>3180</v>
+      </c>
+      <c r="G1317" s="3" t="s">
+        <v>4144</v>
+      </c>
+      <c r="H1317" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1317" s="3">
+        <v>18</v>
+      </c>
+      <c r="J1317" s="3">
+        <v>35</v>
+      </c>
+      <c r="K1317" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1317" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1317" s="3" t="s">
+        <v>4145</v>
+      </c>
+      <c r="N1317" s="3"/>
+    </row>
+    <row r="1318" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1318" s="3" t="s">
+        <v>4146</v>
+      </c>
+      <c r="B1318" s="3"/>
+      <c r="C1318" s="3">
+        <v>237</v>
+      </c>
+      <c r="D1318" s="3">
+        <v>1578558770</v>
+      </c>
+      <c r="E1318" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1318" s="3" t="s">
+        <v>4147</v>
+      </c>
+      <c r="G1318" s="3" t="s">
+        <v>4148</v>
+      </c>
+      <c r="H1318" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1318" s="3">
+        <v>66</v>
+      </c>
+      <c r="J1318" s="3">
+        <v>80</v>
+      </c>
+      <c r="K1318" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1318" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1318" s="3" t="s">
+        <v>4149</v>
+      </c>
+      <c r="N1318" s="3"/>
+    </row>
+    <row r="1319" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1319" s="3" t="s">
+        <v>4150</v>
+      </c>
+      <c r="B1319" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1319" s="3">
+        <v>336</v>
+      </c>
+      <c r="D1319" s="3">
+        <v>1578597872</v>
+      </c>
+      <c r="E1319" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1319" s="3" t="s">
+        <v>2983</v>
+      </c>
+      <c r="G1319" s="3" t="s">
+        <v>4151</v>
+      </c>
+      <c r="H1319" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1319" s="3">
+        <v>55</v>
+      </c>
+      <c r="J1319" s="3"/>
+      <c r="K1319" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1319" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1319" s="3" t="s">
+        <v>4149</v>
+      </c>
+      <c r="N1319" s="3"/>
+    </row>
+    <row r="1320" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1320" s="3" t="s">
+        <v>4152</v>
+      </c>
+      <c r="B1320" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="C1320" s="3">
+        <v>673</v>
+      </c>
+      <c r="D1320" s="3">
+        <v>1579317633</v>
+      </c>
+      <c r="E1320" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1320" s="3" t="s">
+        <v>4153</v>
+      </c>
+      <c r="G1320" s="3" t="s">
+        <v>4154</v>
+      </c>
+      <c r="H1320" s="3"/>
+      <c r="I1320" s="3">
+        <v>41</v>
+      </c>
+      <c r="J1320" s="3"/>
+      <c r="K1320" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1320" s="3"/>
+      <c r="M1320" s="3"/>
+      <c r="N1320" s="3"/>
+    </row>
+    <row r="1321" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1321" s="3" t="s">
+        <v>4155</v>
+      </c>
+      <c r="B1321" s="3"/>
+      <c r="C1321" s="3">
+        <v>375</v>
+      </c>
+      <c r="D1321" s="3">
+        <v>1579482521</v>
+      </c>
+      <c r="E1321" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1321" s="3" t="s">
+        <v>4156</v>
+      </c>
+      <c r="G1321" s="3" t="s">
+        <v>4157</v>
+      </c>
+      <c r="H1321" s="3"/>
+      <c r="I1321" s="3">
+        <v>72</v>
+      </c>
+      <c r="J1321" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1321" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1321" s="3"/>
+      <c r="M1321" s="3"/>
+      <c r="N1321" s="3"/>
+    </row>
+    <row r="1322" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1322" s="3" t="s">
+        <v>4158</v>
+      </c>
+      <c r="B1322" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="C1322" s="3">
+        <v>108</v>
+      </c>
+      <c r="D1322" s="3">
+        <v>1579551813</v>
+      </c>
+      <c r="E1322" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1322" s="3" t="s">
+        <v>4159</v>
+      </c>
+      <c r="G1322" s="3" t="s">
+        <v>4160</v>
+      </c>
+      <c r="H1322" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1322" s="3">
+        <v>76</v>
+      </c>
+      <c r="J1322" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1322" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1322" s="3"/>
+      <c r="M1322" s="3"/>
+      <c r="N1322" s="3"/>
+    </row>
+    <row r="1323" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1323" s="3" t="s">
+        <v>4161</v>
+      </c>
+      <c r="B1323" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C1323" s="3">
+        <v>729</v>
+      </c>
+      <c r="D1323" s="3">
+        <v>1579562263</v>
+      </c>
+      <c r="E1323" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1323" s="3" t="s">
+        <v>4162</v>
+      </c>
+      <c r="G1323" s="3" t="s">
+        <v>4163</v>
+      </c>
+      <c r="H1323" s="3"/>
+      <c r="I1323" s="3">
+        <v>53</v>
+      </c>
+      <c r="J1323" s="3"/>
+      <c r="K1323" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1323" s="3"/>
+      <c r="M1323" s="3"/>
+      <c r="N1323" s="3"/>
+    </row>
+    <row r="1324" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1324" s="3" t="s">
+        <v>4164</v>
+      </c>
+      <c r="B1324" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1324" s="3">
+        <v>672</v>
+      </c>
+      <c r="D1324" s="3">
+        <v>1579669474</v>
+      </c>
+      <c r="E1324" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1324" s="3" t="s">
+        <v>4165</v>
+      </c>
+      <c r="G1324" s="3" t="s">
+        <v>4166</v>
+      </c>
+      <c r="H1324" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1324" s="3">
+        <v>70</v>
+      </c>
+      <c r="J1324" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1324" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1324" s="3"/>
+      <c r="M1324" s="3"/>
+      <c r="N1324" s="3"/>
+    </row>
+    <row r="1325" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1325" s="3" t="s">
+        <v>4167</v>
+      </c>
+      <c r="B1325" s="3"/>
+      <c r="C1325" s="3">
+        <v>209</v>
+      </c>
+      <c r="D1325" s="3">
+        <v>1579710167</v>
+      </c>
+      <c r="E1325" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1325" s="3" t="s">
+        <v>4168</v>
+      </c>
+      <c r="G1325" s="3" t="s">
+        <v>4169</v>
+      </c>
+      <c r="H1325" s="3"/>
+      <c r="I1325" s="3">
+        <v>73</v>
+      </c>
+      <c r="J1325" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1325" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1325" s="3"/>
+      <c r="M1325" s="3"/>
+      <c r="N1325" s="3"/>
+    </row>
+    <row r="1326" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1326" s="3" t="s">
+        <v>4170</v>
+      </c>
+      <c r="B1326" s="3"/>
+      <c r="C1326" s="3">
+        <v>840</v>
+      </c>
+      <c r="D1326" s="3">
+        <v>1579773571</v>
+      </c>
+      <c r="E1326" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1326" s="3" t="s">
+        <v>4171</v>
+      </c>
+      <c r="G1326" s="3" t="s">
+        <v>4172</v>
+      </c>
+      <c r="H1326" s="3"/>
+      <c r="I1326" s="3">
+        <v>35</v>
+      </c>
+      <c r="J1326" s="3"/>
+      <c r="K1326" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1326" s="3"/>
+      <c r="M1326" s="3"/>
+      <c r="N1326" s="3"/>
+    </row>
+    <row r="1327" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1327" s="3" t="s">
+        <v>4173</v>
+      </c>
+      <c r="B1327" s="3"/>
+      <c r="C1327" s="3">
+        <v>333</v>
+      </c>
+      <c r="D1327" s="3">
+        <v>1579852497</v>
+      </c>
+      <c r="E1327" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1327" s="3" t="s">
+        <v>4174</v>
+      </c>
+      <c r="G1327" s="3" t="s">
+        <v>4175</v>
+      </c>
+      <c r="H1327" s="3"/>
+      <c r="I1327" s="3">
+        <v>49</v>
+      </c>
+      <c r="J1327" s="3"/>
+      <c r="K1327" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1327" s="3"/>
+      <c r="M1327" s="3"/>
+      <c r="N1327" s="3"/>
+    </row>
+    <row r="1328" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1328" s="3" t="s">
+        <v>4176</v>
+      </c>
+      <c r="B1328" s="3"/>
+      <c r="C1328" s="3">
+        <v>375</v>
+      </c>
+      <c r="D1328" s="3">
+        <v>1579897288</v>
+      </c>
+      <c r="E1328" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1328" s="3" t="s">
+        <v>4177</v>
+      </c>
+      <c r="G1328" s="3" t="s">
+        <v>4178</v>
+      </c>
+      <c r="H1328" s="3"/>
+      <c r="I1328" s="3">
+        <v>74</v>
+      </c>
+      <c r="J1328" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1328" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1328" s="3"/>
+      <c r="M1328" s="3"/>
+      <c r="N1328" s="3"/>
+    </row>
+    <row r="1329" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1329" s="3" t="s">
+        <v>4179</v>
+      </c>
+      <c r="B1329" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1329" s="3">
+        <v>839</v>
+      </c>
+      <c r="D1329" s="3">
+        <v>1580086005</v>
+      </c>
+      <c r="E1329" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1329" s="3" t="s">
+        <v>4180</v>
+      </c>
+      <c r="G1329" s="3" t="s">
+        <v>4181</v>
+      </c>
+      <c r="H1329" s="3"/>
+      <c r="I1329" s="3">
+        <v>64</v>
+      </c>
+      <c r="J1329" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1329" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1329" s="3"/>
+      <c r="M1329" s="3"/>
+      <c r="N1329" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\PCS-Trucking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{99DA518C-25C9-45F8-98D5-6C38DA602A9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F50B69B1-9578-4987-8B48-CBDFE15C1398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10189" uniqueCount="4295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10402" uniqueCount="4375">
   <si>
     <t>DRIVE ALERTS</t>
   </si>
@@ -12898,6 +12898,9 @@
     <t>36.317738, -114.986931</t>
   </si>
   <si>
+    <t>07/27/26 19:11 EDT</t>
+  </si>
+  <si>
     <t>07/26/26 22:54 EDT</t>
   </si>
   <si>
@@ -12905,6 +12908,243 @@
   </si>
   <si>
     <t>44.451594, -111.361689</t>
+  </si>
+  <si>
+    <t>07/27/26 16:32 EDT</t>
+  </si>
+  <si>
+    <t>0.3mi W of South Salt Lake UT</t>
+  </si>
+  <si>
+    <t>40.707228, -111.903970</t>
+  </si>
+  <si>
+    <t>07/27/26 19:12 EDT</t>
+  </si>
+  <si>
+    <t>40.706478, -111.903947</t>
+  </si>
+  <si>
+    <t>07/27/26 19:13 EDT</t>
+  </si>
+  <si>
+    <t>07/28/26 11:02 EDT</t>
+  </si>
+  <si>
+    <t>2.4mi S of El Reno OK</t>
+  </si>
+  <si>
+    <t>35.508401, -97.974580</t>
+  </si>
+  <si>
+    <t>07/29/26 09:38 EDT</t>
+  </si>
+  <si>
+    <t>07/28/26 13:29 EDT</t>
+  </si>
+  <si>
+    <t>2.4mi SE of Bluffdale UT</t>
+  </si>
+  <si>
+    <t>40.446636, -111.909460</t>
+  </si>
+  <si>
+    <t>07/29/26 01:32 EDT</t>
+  </si>
+  <si>
+    <t>25.2mi W of Fruita CO</t>
+  </si>
+  <si>
+    <t>39.104124, -109.195980</t>
+  </si>
+  <si>
+    <t>1.8mi NE of St. George UT</t>
+  </si>
+  <si>
+    <t>37.099086, -113.562711</t>
+  </si>
+  <si>
+    <t>07/30/26 08:34 EDT</t>
+  </si>
+  <si>
+    <t>07/29/26 13:48 EDT</t>
+  </si>
+  <si>
+    <t>40.463701, -111.913318</t>
+  </si>
+  <si>
+    <t>07/29/26 16:43 EDT</t>
+  </si>
+  <si>
+    <t>40.757268, -112.025071</t>
+  </si>
+  <si>
+    <t>07/29/26 19:06 EDT</t>
+  </si>
+  <si>
+    <t>1mi SE of Mesquite NV</t>
+  </si>
+  <si>
+    <t>36.797386, -114.116859</t>
+  </si>
+  <si>
+    <t>07/30/26 00:06 EDT</t>
+  </si>
+  <si>
+    <t>35.514930, -115.432452</t>
+  </si>
+  <si>
+    <t>07/30/26 10:13 EDT</t>
+  </si>
+  <si>
+    <t>18.8mi E of Rock Springs WY</t>
+  </si>
+  <si>
+    <t>41.690990, -108.881187</t>
+  </si>
+  <si>
+    <t>07/30/26 11:01 EDT</t>
+  </si>
+  <si>
+    <t>31.6mi W of Rawlins WY</t>
+  </si>
+  <si>
+    <t>41.705007, -107.829800</t>
+  </si>
+  <si>
+    <t>07/30/26 15:26 EDT</t>
+  </si>
+  <si>
+    <t>40.114339, -111.703746</t>
+  </si>
+  <si>
+    <t>07/31/26 06:51 EDT</t>
+  </si>
+  <si>
+    <t>07/30/26 15:27 EDT</t>
+  </si>
+  <si>
+    <t>07/30/26 15:28 EDT</t>
+  </si>
+  <si>
+    <t>07/30/26 16:49 EDT</t>
+  </si>
+  <si>
+    <t>29mi NE of Enoch UT</t>
+  </si>
+  <si>
+    <t>38.076109, -112.686040</t>
+  </si>
+  <si>
+    <t>07/30/26 18:10 EDT</t>
+  </si>
+  <si>
+    <t>7.6mi E of Tolleson AZ</t>
+  </si>
+  <si>
+    <t>33.461794, -112.125512</t>
+  </si>
+  <si>
+    <t>07/31/26 06:52 EDT</t>
+  </si>
+  <si>
+    <t>07/30/26 18:52 EDT</t>
+  </si>
+  <si>
+    <t>6.3mi W of Mesquite NV</t>
+  </si>
+  <si>
+    <t>36.772238, -114.239251</t>
+  </si>
+  <si>
+    <t>07/31/26 08:00 EDT</t>
+  </si>
+  <si>
+    <t>1.8mi S of Norfolk NE</t>
+  </si>
+  <si>
+    <t>42.006210, -97.426505</t>
+  </si>
+  <si>
+    <t>07/31/26 08:48 EDT</t>
+  </si>
+  <si>
+    <t>36.708235, -101.445742</t>
+  </si>
+  <si>
+    <t>07/31/26 15:44 EDT</t>
+  </si>
+  <si>
+    <t>0.9mi NE of Oak Hills CA</t>
+  </si>
+  <si>
+    <t>34.400023, -117.401391</t>
+  </si>
+  <si>
+    <t>07/31/26 16:35 EDT</t>
+  </si>
+  <si>
+    <t>7.5mi NE of Benson AZ</t>
+  </si>
+  <si>
+    <t>31.979198, -110.221110</t>
+  </si>
+  <si>
+    <t>07/31/26 18:34 EDT</t>
+  </si>
+  <si>
+    <t>3.9mi W of Springville UT</t>
+  </si>
+  <si>
+    <t>40.158454, -111.694012</t>
+  </si>
+  <si>
+    <t>07/31/26 19:51 EDT</t>
+  </si>
+  <si>
+    <t>21.6mi S of Arvin CA</t>
+  </si>
+  <si>
+    <t>34.888821, -118.908549</t>
+  </si>
+  <si>
+    <t>08/01/26 17:23 EDT</t>
+  </si>
+  <si>
+    <t>41.234221, -112.013768</t>
+  </si>
+  <si>
+    <t>08/02/26 13:11 EDT</t>
+  </si>
+  <si>
+    <t>1.5mi NE of Santaquin UT</t>
+  </si>
+  <si>
+    <t>39.981058, -111.768076</t>
+  </si>
+  <si>
+    <t>08/02/26 16:19 EDT</t>
+  </si>
+  <si>
+    <t>3.9mi W of Battlement Mesa CO</t>
+  </si>
+  <si>
+    <t>39.430354, -108.073520</t>
+  </si>
+  <si>
+    <t>08/02/26 18:11 EDT</t>
+  </si>
+  <si>
+    <t>40.757895, -111.950696</t>
+  </si>
+  <si>
+    <t>08/02/26 20:58 EDT</t>
+  </si>
+  <si>
+    <t>1.3mi NW of Spanish Fork UT</t>
+  </si>
+  <si>
+    <t>40.126398, -111.653211</t>
   </si>
 </sst>
 </file>
@@ -13266,7 +13506,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N1364"/>
+  <dimension ref="A1:N1393"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="14" width="15" customWidth="1"/>
@@ -65101,22 +65341,26 @@
         <v>4291</v>
       </c>
       <c r="H1363" s="3" t="s">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="I1363" s="3">
         <v>26</v>
       </c>
       <c r="J1363" s="3"/>
       <c r="K1363" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1363" s="3"/>
-      <c r="M1363" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L1363" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1363" s="3" t="s">
+        <v>4292</v>
+      </c>
       <c r="N1363" s="3"/>
     </row>
     <row r="1364" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1364" s="3" t="s">
-        <v>4292</v>
+        <v>4293</v>
       </c>
       <c r="B1364" s="3" t="s">
         <v>372</v>
@@ -65131,13 +65375,13 @@
         <v>24</v>
       </c>
       <c r="F1364" s="3" t="s">
-        <v>4293</v>
+        <v>4294</v>
       </c>
       <c r="G1364" s="3" t="s">
-        <v>4294</v>
+        <v>4295</v>
       </c>
       <c r="H1364" s="3" t="s">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="I1364" s="3">
         <v>47</v>
@@ -65146,11 +65390,1105 @@
         <v>45</v>
       </c>
       <c r="K1364" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1364" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1364" s="3" t="s">
+        <v>4292</v>
+      </c>
+      <c r="N1364" s="3"/>
+    </row>
+    <row r="1365" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1365" s="3" t="s">
+        <v>4296</v>
+      </c>
+      <c r="B1365" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C1365" s="3">
+        <v>342</v>
+      </c>
+      <c r="D1365" s="3">
+        <v>1586207491</v>
+      </c>
+      <c r="E1365" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1365" s="3" t="s">
+        <v>4297</v>
+      </c>
+      <c r="G1365" s="3" t="s">
+        <v>4298</v>
+      </c>
+      <c r="H1365" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1365" s="3">
+        <v>65</v>
+      </c>
+      <c r="J1365" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1365" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1365" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1365" s="3" t="s">
+        <v>4299</v>
+      </c>
+      <c r="N1365" s="3"/>
+    </row>
+    <row r="1366" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1366" s="3" t="s">
+        <v>4296</v>
+      </c>
+      <c r="B1366" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C1366" s="3">
+        <v>342</v>
+      </c>
+      <c r="D1366" s="3">
+        <v>1586207489</v>
+      </c>
+      <c r="E1366" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1366" s="3" t="s">
+        <v>4297</v>
+      </c>
+      <c r="G1366" s="3" t="s">
+        <v>4300</v>
+      </c>
+      <c r="H1366" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1366" s="3">
+        <v>65</v>
+      </c>
+      <c r="J1366" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1366" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1366" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1366" s="3" t="s">
+        <v>4301</v>
+      </c>
+      <c r="N1366" s="3"/>
+    </row>
+    <row r="1367" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1367" s="3" t="s">
+        <v>4302</v>
+      </c>
+      <c r="B1367" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C1367" s="3">
+        <v>731</v>
+      </c>
+      <c r="D1367" s="3">
+        <v>1586766402</v>
+      </c>
+      <c r="E1367" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1367" s="3" t="s">
+        <v>4303</v>
+      </c>
+      <c r="G1367" s="3" t="s">
+        <v>4304</v>
+      </c>
+      <c r="H1367" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1367" s="3">
+        <v>72</v>
+      </c>
+      <c r="J1367" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1367" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1367" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1367" s="3" t="s">
+        <v>4305</v>
+      </c>
+      <c r="N1367" s="3"/>
+    </row>
+    <row r="1368" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1368" s="3" t="s">
+        <v>4306</v>
+      </c>
+      <c r="B1368" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C1368" s="3">
+        <v>342</v>
+      </c>
+      <c r="D1368" s="3">
+        <v>1586921665</v>
+      </c>
+      <c r="E1368" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1368" s="3" t="s">
+        <v>4307</v>
+      </c>
+      <c r="G1368" s="3" t="s">
+        <v>4308</v>
+      </c>
+      <c r="H1368" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1368" s="3">
+        <v>70</v>
+      </c>
+      <c r="J1368" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1368" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1368" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1368" s="3" t="s">
+        <v>4305</v>
+      </c>
+      <c r="N1368" s="3"/>
+    </row>
+    <row r="1369" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1369" s="3" t="s">
+        <v>4309</v>
+      </c>
+      <c r="B1369" s="3"/>
+      <c r="C1369" s="3">
+        <v>837</v>
+      </c>
+      <c r="D1369" s="3">
+        <v>1587372519</v>
+      </c>
+      <c r="E1369" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1369" s="3" t="s">
+        <v>4310</v>
+      </c>
+      <c r="G1369" s="3" t="s">
+        <v>4311</v>
+      </c>
+      <c r="H1369" s="3"/>
+      <c r="I1369" s="3">
+        <v>68</v>
+      </c>
+      <c r="J1369" s="3">
+        <v>80</v>
+      </c>
+      <c r="K1369" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L1364" s="3"/>
-      <c r="M1364" s="3"/>
-      <c r="N1364" s="3"/>
+      <c r="L1369" s="3"/>
+      <c r="M1369" s="3"/>
+      <c r="N1369" s="3"/>
+    </row>
+    <row r="1370" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1370" s="3" t="s">
+        <v>4305</v>
+      </c>
+      <c r="B1370" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1370" s="3">
+        <v>672</v>
+      </c>
+      <c r="D1370" s="3">
+        <v>1587600382</v>
+      </c>
+      <c r="E1370" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1370" s="3" t="s">
+        <v>4312</v>
+      </c>
+      <c r="G1370" s="3" t="s">
+        <v>4313</v>
+      </c>
+      <c r="H1370" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1370" s="3">
+        <v>66</v>
+      </c>
+      <c r="J1370" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1370" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1370" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1370" s="3" t="s">
+        <v>4314</v>
+      </c>
+      <c r="N1370" s="3"/>
+    </row>
+    <row r="1371" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1371" s="3" t="s">
+        <v>4315</v>
+      </c>
+      <c r="B1371" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1371" s="3">
+        <v>672</v>
+      </c>
+      <c r="D1371" s="3">
+        <v>1587864217</v>
+      </c>
+      <c r="E1371" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1371" s="3" t="s">
+        <v>3814</v>
+      </c>
+      <c r="G1371" s="3" t="s">
+        <v>4316</v>
+      </c>
+      <c r="H1371" s="3"/>
+      <c r="I1371" s="3">
+        <v>76</v>
+      </c>
+      <c r="J1371" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1371" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1371" s="3"/>
+      <c r="M1371" s="3"/>
+      <c r="N1371" s="3"/>
+    </row>
+    <row r="1372" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1372" s="3" t="s">
+        <v>4317</v>
+      </c>
+      <c r="B1372" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1372" s="3">
+        <v>672</v>
+      </c>
+      <c r="D1372" s="3">
+        <v>1588046063</v>
+      </c>
+      <c r="E1372" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1372" s="3" t="s">
+        <v>2221</v>
+      </c>
+      <c r="G1372" s="3" t="s">
+        <v>4318</v>
+      </c>
+      <c r="H1372" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1372" s="3">
+        <v>44</v>
+      </c>
+      <c r="J1372" s="3">
+        <v>50</v>
+      </c>
+      <c r="K1372" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1372" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1372" s="3" t="s">
+        <v>4314</v>
+      </c>
+      <c r="N1372" s="3"/>
+    </row>
+    <row r="1373" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1373" s="3" t="s">
+        <v>4319</v>
+      </c>
+      <c r="B1373" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="C1373" s="3">
+        <v>63</v>
+      </c>
+      <c r="D1373" s="3">
+        <v>1588163857</v>
+      </c>
+      <c r="E1373" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1373" s="3" t="s">
+        <v>4320</v>
+      </c>
+      <c r="G1373" s="3" t="s">
+        <v>4321</v>
+      </c>
+      <c r="H1373" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1373" s="3">
+        <v>80</v>
+      </c>
+      <c r="J1373" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1373" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1373" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1373" s="3" t="s">
+        <v>4314</v>
+      </c>
+      <c r="N1373" s="3"/>
+    </row>
+    <row r="1374" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1374" s="3" t="s">
+        <v>4322</v>
+      </c>
+      <c r="B1374" s="3"/>
+      <c r="C1374" s="3">
+        <v>375</v>
+      </c>
+      <c r="D1374" s="3">
+        <v>1588284710</v>
+      </c>
+      <c r="E1374" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1374" s="3" t="s">
+        <v>3180</v>
+      </c>
+      <c r="G1374" s="3" t="s">
+        <v>4323</v>
+      </c>
+      <c r="H1374" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1374" s="3">
+        <v>17</v>
+      </c>
+      <c r="J1374" s="3">
+        <v>35</v>
+      </c>
+      <c r="K1374" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1374" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1374" s="3" t="s">
+        <v>4314</v>
+      </c>
+      <c r="N1374" s="3"/>
+    </row>
+    <row r="1375" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1375" s="3" t="s">
+        <v>4324</v>
+      </c>
+      <c r="B1375" s="3"/>
+      <c r="C1375" s="3">
+        <v>459</v>
+      </c>
+      <c r="D1375" s="3">
+        <v>1588567290</v>
+      </c>
+      <c r="E1375" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1375" s="3" t="s">
+        <v>4325</v>
+      </c>
+      <c r="G1375" s="3" t="s">
+        <v>4326</v>
+      </c>
+      <c r="H1375" s="3"/>
+      <c r="I1375" s="3">
+        <v>72</v>
+      </c>
+      <c r="J1375" s="3">
+        <v>80</v>
+      </c>
+      <c r="K1375" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1375" s="3"/>
+      <c r="M1375" s="3"/>
+      <c r="N1375" s="3"/>
+    </row>
+    <row r="1376" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1376" s="3" t="s">
+        <v>4327</v>
+      </c>
+      <c r="B1376" s="3"/>
+      <c r="C1376" s="3">
+        <v>459</v>
+      </c>
+      <c r="D1376" s="3">
+        <v>1588617444</v>
+      </c>
+      <c r="E1376" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1376" s="3" t="s">
+        <v>4328</v>
+      </c>
+      <c r="G1376" s="3" t="s">
+        <v>4329</v>
+      </c>
+      <c r="H1376" s="3"/>
+      <c r="I1376" s="3">
+        <v>72</v>
+      </c>
+      <c r="J1376" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1376" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1376" s="3"/>
+      <c r="M1376" s="3"/>
+      <c r="N1376" s="3"/>
+    </row>
+    <row r="1377" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1377" s="3" t="s">
+        <v>4330</v>
+      </c>
+      <c r="B1377" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1377" s="3">
+        <v>336</v>
+      </c>
+      <c r="D1377" s="3">
+        <v>1588898670</v>
+      </c>
+      <c r="E1377" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="F1377" s="3" t="s">
+        <v>683</v>
+      </c>
+      <c r="G1377" s="3" t="s">
+        <v>4331</v>
+      </c>
+      <c r="H1377" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1377" s="3"/>
+      <c r="J1377" s="3"/>
+      <c r="K1377" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1377" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1377" s="3" t="s">
+        <v>4332</v>
+      </c>
+      <c r="N1377" s="3"/>
+    </row>
+    <row r="1378" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1378" s="3" t="s">
+        <v>4333</v>
+      </c>
+      <c r="B1378" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1378" s="3">
+        <v>336</v>
+      </c>
+      <c r="D1378" s="3">
+        <v>1588898673</v>
+      </c>
+      <c r="E1378" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="F1378" s="3" t="s">
+        <v>683</v>
+      </c>
+      <c r="G1378" s="3" t="s">
+        <v>4331</v>
+      </c>
+      <c r="H1378" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1378" s="3"/>
+      <c r="J1378" s="3"/>
+      <c r="K1378" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1378" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1378" s="3" t="s">
+        <v>4332</v>
+      </c>
+      <c r="N1378" s="3"/>
+    </row>
+    <row r="1379" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1379" s="3" t="s">
+        <v>4334</v>
+      </c>
+      <c r="B1379" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1379" s="3">
+        <v>336</v>
+      </c>
+      <c r="D1379" s="3">
+        <v>1588898683</v>
+      </c>
+      <c r="E1379" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="F1379" s="3" t="s">
+        <v>683</v>
+      </c>
+      <c r="G1379" s="3" t="s">
+        <v>4331</v>
+      </c>
+      <c r="H1379" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1379" s="3"/>
+      <c r="J1379" s="3"/>
+      <c r="K1379" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1379" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1379" s="3" t="s">
+        <v>4332</v>
+      </c>
+      <c r="N1379" s="3"/>
+    </row>
+    <row r="1380" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1380" s="3" t="s">
+        <v>4335</v>
+      </c>
+      <c r="B1380" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1380" s="3">
+        <v>208</v>
+      </c>
+      <c r="D1380" s="3">
+        <v>1588979486</v>
+      </c>
+      <c r="E1380" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1380" s="3" t="s">
+        <v>4336</v>
+      </c>
+      <c r="G1380" s="3" t="s">
+        <v>4337</v>
+      </c>
+      <c r="H1380" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1380" s="3">
+        <v>76</v>
+      </c>
+      <c r="J1380" s="3">
+        <v>80</v>
+      </c>
+      <c r="K1380" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1380" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1380" s="3" t="s">
+        <v>4332</v>
+      </c>
+      <c r="N1380" s="3"/>
+    </row>
+    <row r="1381" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1381" s="3" t="s">
+        <v>4338</v>
+      </c>
+      <c r="B1381" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="C1381" s="3">
+        <v>63</v>
+      </c>
+      <c r="D1381" s="3">
+        <v>1589048477</v>
+      </c>
+      <c r="E1381" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1381" s="3" t="s">
+        <v>4339</v>
+      </c>
+      <c r="G1381" s="3" t="s">
+        <v>4340</v>
+      </c>
+      <c r="H1381" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1381" s="3">
+        <v>55</v>
+      </c>
+      <c r="J1381" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1381" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1381" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1381" s="3" t="s">
+        <v>4341</v>
+      </c>
+      <c r="N1381" s="3"/>
+    </row>
+    <row r="1382" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1382" s="3" t="s">
+        <v>4342</v>
+      </c>
+      <c r="B1382" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1382" s="3">
+        <v>208</v>
+      </c>
+      <c r="D1382" s="3">
+        <v>1589079932</v>
+      </c>
+      <c r="E1382" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1382" s="3" t="s">
+        <v>4343</v>
+      </c>
+      <c r="G1382" s="3" t="s">
+        <v>4344</v>
+      </c>
+      <c r="H1382" s="3"/>
+      <c r="I1382" s="3">
+        <v>60</v>
+      </c>
+      <c r="J1382" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1382" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1382" s="3"/>
+      <c r="M1382" s="3"/>
+      <c r="N1382" s="3"/>
+    </row>
+    <row r="1383" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1383" s="3" t="s">
+        <v>4345</v>
+      </c>
+      <c r="B1383" s="3"/>
+      <c r="C1383" s="3">
+        <v>459</v>
+      </c>
+      <c r="D1383" s="3">
+        <v>1589351404</v>
+      </c>
+      <c r="E1383" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1383" s="3" t="s">
+        <v>4346</v>
+      </c>
+      <c r="G1383" s="3" t="s">
+        <v>4347</v>
+      </c>
+      <c r="H1383" s="3"/>
+      <c r="I1383" s="3">
+        <v>45</v>
+      </c>
+      <c r="J1383" s="3"/>
+      <c r="K1383" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1383" s="3"/>
+      <c r="M1383" s="3"/>
+      <c r="N1383" s="3"/>
+    </row>
+    <row r="1384" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1384" s="3" t="s">
+        <v>4348</v>
+      </c>
+      <c r="B1384" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1384" s="3">
+        <v>839</v>
+      </c>
+      <c r="D1384" s="3">
+        <v>1589391722</v>
+      </c>
+      <c r="E1384" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1384" s="3" t="s">
+        <v>1507</v>
+      </c>
+      <c r="G1384" s="3" t="s">
+        <v>4349</v>
+      </c>
+      <c r="H1384" s="3"/>
+      <c r="I1384" s="3">
+        <v>14</v>
+      </c>
+      <c r="J1384" s="3"/>
+      <c r="K1384" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1384" s="3"/>
+      <c r="M1384" s="3"/>
+      <c r="N1384" s="3"/>
+    </row>
+    <row r="1385" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1385" s="3" t="s">
+        <v>4350</v>
+      </c>
+      <c r="B1385" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1385" s="3">
+        <v>336</v>
+      </c>
+      <c r="D1385" s="3">
+        <v>1589801414</v>
+      </c>
+      <c r="E1385" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="F1385" s="3" t="s">
+        <v>4351</v>
+      </c>
+      <c r="G1385" s="3" t="s">
+        <v>4352</v>
+      </c>
+      <c r="H1385" s="3"/>
+      <c r="I1385" s="3">
+        <v>56</v>
+      </c>
+      <c r="J1385" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1385" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1385" s="3"/>
+      <c r="M1385" s="3"/>
+      <c r="N1385" s="3"/>
+    </row>
+    <row r="1386" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1386" s="3" t="s">
+        <v>4353</v>
+      </c>
+      <c r="B1386" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="C1386" s="3">
+        <v>63</v>
+      </c>
+      <c r="D1386" s="3">
+        <v>1589846943</v>
+      </c>
+      <c r="E1386" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1386" s="3" t="s">
+        <v>4354</v>
+      </c>
+      <c r="G1386" s="3" t="s">
+        <v>4355</v>
+      </c>
+      <c r="H1386" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1386" s="3">
+        <v>78</v>
+      </c>
+      <c r="J1386" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1386" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1386" s="3"/>
+      <c r="M1386" s="3"/>
+      <c r="N1386" s="3"/>
+    </row>
+    <row r="1387" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1387" s="3" t="s">
+        <v>4356</v>
+      </c>
+      <c r="B1387" s="3"/>
+      <c r="C1387" s="3">
+        <v>375</v>
+      </c>
+      <c r="D1387" s="3">
+        <v>1589936955</v>
+      </c>
+      <c r="E1387" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1387" s="3" t="s">
+        <v>4357</v>
+      </c>
+      <c r="G1387" s="3" t="s">
+        <v>4358</v>
+      </c>
+      <c r="H1387" s="3"/>
+      <c r="I1387" s="3">
+        <v>42</v>
+      </c>
+      <c r="J1387" s="3"/>
+      <c r="K1387" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1387" s="3"/>
+      <c r="M1387" s="3"/>
+      <c r="N1387" s="3"/>
+    </row>
+    <row r="1388" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1388" s="3" t="s">
+        <v>4359</v>
+      </c>
+      <c r="B1388" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1388" s="3">
+        <v>336</v>
+      </c>
+      <c r="D1388" s="3">
+        <v>1589980533</v>
+      </c>
+      <c r="E1388" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="F1388" s="3" t="s">
+        <v>4360</v>
+      </c>
+      <c r="G1388" s="3" t="s">
+        <v>4361</v>
+      </c>
+      <c r="H1388" s="3"/>
+      <c r="I1388" s="3">
+        <v>65</v>
+      </c>
+      <c r="J1388" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1388" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1388" s="3"/>
+      <c r="M1388" s="3"/>
+      <c r="N1388" s="3"/>
+    </row>
+    <row r="1389" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1389" s="3" t="s">
+        <v>4362</v>
+      </c>
+      <c r="B1389" s="3"/>
+      <c r="C1389" s="3">
+        <v>459</v>
+      </c>
+      <c r="D1389" s="3">
+        <v>1590349391</v>
+      </c>
+      <c r="E1389" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1389" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="G1389" s="3" t="s">
+        <v>4363</v>
+      </c>
+      <c r="H1389" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1389" s="3">
+        <v>72</v>
+      </c>
+      <c r="J1389" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1389" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1389" s="3"/>
+      <c r="M1389" s="3"/>
+      <c r="N1389" s="3"/>
+    </row>
+    <row r="1390" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1390" s="3" t="s">
+        <v>4364</v>
+      </c>
+      <c r="B1390" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C1390" s="3">
+        <v>731</v>
+      </c>
+      <c r="D1390" s="3">
+        <v>1590558704</v>
+      </c>
+      <c r="E1390" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1390" s="3" t="s">
+        <v>4365</v>
+      </c>
+      <c r="G1390" s="3" t="s">
+        <v>4366</v>
+      </c>
+      <c r="H1390" s="3"/>
+      <c r="I1390" s="3">
+        <v>59</v>
+      </c>
+      <c r="J1390" s="3"/>
+      <c r="K1390" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1390" s="3"/>
+      <c r="M1390" s="3"/>
+      <c r="N1390" s="3"/>
+    </row>
+    <row r="1391" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1391" s="3" t="s">
+        <v>4367</v>
+      </c>
+      <c r="B1391" s="3"/>
+      <c r="C1391" s="3">
+        <v>837</v>
+      </c>
+      <c r="D1391" s="3">
+        <v>1590614236</v>
+      </c>
+      <c r="E1391" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1391" s="3" t="s">
+        <v>4368</v>
+      </c>
+      <c r="G1391" s="3" t="s">
+        <v>4369</v>
+      </c>
+      <c r="H1391" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1391" s="3">
+        <v>75</v>
+      </c>
+      <c r="J1391" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1391" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1391" s="3"/>
+      <c r="M1391" s="3"/>
+      <c r="N1391" s="3"/>
+    </row>
+    <row r="1392" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1392" s="3" t="s">
+        <v>4370</v>
+      </c>
+      <c r="B1392" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1392" s="3">
+        <v>839</v>
+      </c>
+      <c r="D1392" s="3">
+        <v>1590647432</v>
+      </c>
+      <c r="E1392" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1392" s="3" t="s">
+        <v>1956</v>
+      </c>
+      <c r="G1392" s="3" t="s">
+        <v>4371</v>
+      </c>
+      <c r="H1392" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1392" s="3">
+        <v>59</v>
+      </c>
+      <c r="J1392" s="3"/>
+      <c r="K1392" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1392" s="3"/>
+      <c r="M1392" s="3"/>
+      <c r="N1392" s="3"/>
+    </row>
+    <row r="1393" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1393" s="3" t="s">
+        <v>4372</v>
+      </c>
+      <c r="B1393" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1393" s="3">
+        <v>839</v>
+      </c>
+      <c r="D1393" s="3">
+        <v>1590691668</v>
+      </c>
+      <c r="E1393" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1393" s="3" t="s">
+        <v>4373</v>
+      </c>
+      <c r="G1393" s="3" t="s">
+        <v>4374</v>
+      </c>
+      <c r="H1393" s="3"/>
+      <c r="I1393" s="3">
+        <v>45</v>
+      </c>
+      <c r="J1393" s="3"/>
+      <c r="K1393" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1393" s="3"/>
+      <c r="M1393" s="3"/>
+      <c r="N1393" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\PCS-Trucking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F50B69B1-9578-4987-8B48-CBDFE15C1398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B0625955-0DFA-45AB-9CDD-D13F02646C46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1860" yWindow="1860" windowWidth="43200" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRIVE-ALERTS" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10402" uniqueCount="4375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10565" uniqueCount="4442">
   <si>
     <t>DRIVE ALERTS</t>
   </si>
@@ -13066,6 +13066,9 @@
     <t>42.006210, -97.426505</t>
   </si>
   <si>
+    <t>08/03/26 13:24 EDT</t>
+  </si>
+  <si>
     <t>07/31/26 08:48 EDT</t>
   </si>
   <si>
@@ -13099,6 +13102,9 @@
     <t>40.158454, -111.694012</t>
   </si>
   <si>
+    <t>08/03/26 13:25 EDT</t>
+  </si>
+  <si>
     <t>07/31/26 19:51 EDT</t>
   </si>
   <si>
@@ -13114,6 +13120,9 @@
     <t>41.234221, -112.013768</t>
   </si>
   <si>
+    <t>08/03/26 13:26 EDT</t>
+  </si>
+  <si>
     <t>08/02/26 13:11 EDT</t>
   </si>
   <si>
@@ -13145,6 +13154,198 @@
   </si>
   <si>
     <t>40.126398, -111.653211</t>
+  </si>
+  <si>
+    <t>08/03/26 11:06 EDT</t>
+  </si>
+  <si>
+    <t>40.744604, -111.989136</t>
+  </si>
+  <si>
+    <t>08/03/26 17:49 EDT</t>
+  </si>
+  <si>
+    <t>2.4mi W of Rawlins WY</t>
+  </si>
+  <si>
+    <t>41.780702, -107.272159</t>
+  </si>
+  <si>
+    <t>08/05/26 09:22 EDT</t>
+  </si>
+  <si>
+    <t>3.7mi NE of Enterprise NV</t>
+  </si>
+  <si>
+    <t>36.045138, -115.180004</t>
+  </si>
+  <si>
+    <t>08/06/26 08:43 EDT</t>
+  </si>
+  <si>
+    <t>08/06/26 10:10 EDT</t>
+  </si>
+  <si>
+    <t>16.3mi SW of Santa Clara UT</t>
+  </si>
+  <si>
+    <t>36.937274, -113.825748</t>
+  </si>
+  <si>
+    <t>08/07/26 10:22 EDT</t>
+  </si>
+  <si>
+    <t>08/06/26 10:31 EDT</t>
+  </si>
+  <si>
+    <t>2.8mi W of Washington UT</t>
+  </si>
+  <si>
+    <t>37.122001, -113.537708</t>
+  </si>
+  <si>
+    <t>08/07/26 10:23 EDT</t>
+  </si>
+  <si>
+    <t>08/06/26 18:31 EDT</t>
+  </si>
+  <si>
+    <t>36.5mi NE of Enoch UT</t>
+  </si>
+  <si>
+    <t>38.184399, -112.635034</t>
+  </si>
+  <si>
+    <t>08/06/26 20:11 EDT</t>
+  </si>
+  <si>
+    <t>6.5mi NE of Dalhart TX</t>
+  </si>
+  <si>
+    <t>36.122183, -102.427857</t>
+  </si>
+  <si>
+    <t>08/06/26 20:36 EDT</t>
+  </si>
+  <si>
+    <t>6.5mi W of Mesquite NV</t>
+  </si>
+  <si>
+    <t>36.773687, -114.243770</t>
+  </si>
+  <si>
+    <t>08/07/26 05:06 EDT</t>
+  </si>
+  <si>
+    <t>2.6mi NW of Winchester NV</t>
+  </si>
+  <si>
+    <t>36.170544, -115.158230</t>
+  </si>
+  <si>
+    <t>08/07/26 08:10 EDT</t>
+  </si>
+  <si>
+    <t>2.6mi SE of Victorville CA</t>
+  </si>
+  <si>
+    <t>34.495669, -117.329068</t>
+  </si>
+  <si>
+    <t>08/07/26 08:15 EDT</t>
+  </si>
+  <si>
+    <t>2.9mi NE of Oak Hills CA</t>
+  </si>
+  <si>
+    <t>34.425188, -117.381725</t>
+  </si>
+  <si>
+    <t>08/07/26 12:43 EDT</t>
+  </si>
+  <si>
+    <t>2.6mi W of Pomona CA</t>
+  </si>
+  <si>
+    <t>34.067974, -117.806764</t>
+  </si>
+  <si>
+    <t>08/07/26 14:32 EDT</t>
+  </si>
+  <si>
+    <t>4.9mi N of San Diego CA</t>
+  </si>
+  <si>
+    <t>32.902036, -117.116692</t>
+  </si>
+  <si>
+    <t>08/07/26 15:37 EDT</t>
+  </si>
+  <si>
+    <t>39.749445, -111.835073</t>
+  </si>
+  <si>
+    <t>08/07/26 15:40 EDT</t>
+  </si>
+  <si>
+    <t>6.7mi N of Aurora CO</t>
+  </si>
+  <si>
+    <t>39.799210, -104.678116</t>
+  </si>
+  <si>
+    <t>08/07/26 16:06 EDT</t>
+  </si>
+  <si>
+    <t>19.6mi SW of Nephi UT</t>
+  </si>
+  <si>
+    <t>39.457588, -112.008392</t>
+  </si>
+  <si>
+    <t>08/07/26 18:47 EDT</t>
+  </si>
+  <si>
+    <t>1.2mi N of Enterprise NV</t>
+  </si>
+  <si>
+    <t>36.025873, -115.224110</t>
+  </si>
+  <si>
+    <t>08/08/26 12:12 EDT</t>
+  </si>
+  <si>
+    <t>4.9mi W of Spanish Fork UT</t>
+  </si>
+  <si>
+    <t>40.114597, -111.732428</t>
+  </si>
+  <si>
+    <t>08/08/26 13:03 EDT</t>
+  </si>
+  <si>
+    <t>2.1mi W of Washington UT</t>
+  </si>
+  <si>
+    <t>37.127824, -113.525792</t>
+  </si>
+  <si>
+    <t>08/08/26 13:18 EDT</t>
+  </si>
+  <si>
+    <t>1.3mi S of Brigham City UT</t>
+  </si>
+  <si>
+    <t>41.485679, -112.052804</t>
+  </si>
+  <si>
+    <t>08/08/26 18:16 EDT</t>
+  </si>
+  <si>
+    <t>14.8mi SE of Price UT</t>
+  </si>
+  <si>
+    <t>39.514995, -110.548489</t>
   </si>
 </sst>
 </file>
@@ -13506,7 +13707,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N1393"/>
+  <dimension ref="A1:N1414"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="14" width="15" customWidth="1"/>
@@ -66126,21 +66327,27 @@
       <c r="G1383" s="3" t="s">
         <v>4347</v>
       </c>
-      <c r="H1383" s="3"/>
+      <c r="H1383" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="I1383" s="3">
         <v>45</v>
       </c>
       <c r="J1383" s="3"/>
       <c r="K1383" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1383" s="3"/>
-      <c r="M1383" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L1383" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1383" s="3" t="s">
+        <v>4348</v>
+      </c>
       <c r="N1383" s="3"/>
     </row>
     <row r="1384" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1384" s="3" t="s">
-        <v>4348</v>
+        <v>4349</v>
       </c>
       <c r="B1384" s="3" t="s">
         <v>17</v>
@@ -66158,23 +66365,29 @@
         <v>1507</v>
       </c>
       <c r="G1384" s="3" t="s">
-        <v>4349</v>
-      </c>
-      <c r="H1384" s="3"/>
+        <v>4350</v>
+      </c>
+      <c r="H1384" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="I1384" s="3">
         <v>14</v>
       </c>
       <c r="J1384" s="3"/>
       <c r="K1384" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1384" s="3"/>
-      <c r="M1384" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L1384" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1384" s="3" t="s">
+        <v>4348</v>
+      </c>
       <c r="N1384" s="3"/>
     </row>
     <row r="1385" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1385" s="3" t="s">
-        <v>4350</v>
+        <v>4351</v>
       </c>
       <c r="B1385" s="3" t="s">
         <v>81</v>
@@ -66189,12 +66402,14 @@
         <v>382</v>
       </c>
       <c r="F1385" s="3" t="s">
-        <v>4351</v>
+        <v>4352</v>
       </c>
       <c r="G1385" s="3" t="s">
-        <v>4352</v>
-      </c>
-      <c r="H1385" s="3"/>
+        <v>4353</v>
+      </c>
+      <c r="H1385" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="I1385" s="3">
         <v>56</v>
       </c>
@@ -66202,15 +66417,19 @@
         <v>70</v>
       </c>
       <c r="K1385" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1385" s="3"/>
-      <c r="M1385" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L1385" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1385" s="3" t="s">
+        <v>4348</v>
+      </c>
       <c r="N1385" s="3"/>
     </row>
     <row r="1386" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1386" s="3" t="s">
-        <v>4353</v>
+        <v>4354</v>
       </c>
       <c r="B1386" s="3" t="s">
         <v>339</v>
@@ -66225,13 +66444,13 @@
         <v>47</v>
       </c>
       <c r="F1386" s="3" t="s">
-        <v>4354</v>
+        <v>4355</v>
       </c>
       <c r="G1386" s="3" t="s">
-        <v>4355</v>
+        <v>4356</v>
       </c>
       <c r="H1386" s="3" t="s">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="I1386" s="3">
         <v>78</v>
@@ -66240,15 +66459,19 @@
         <v>75</v>
       </c>
       <c r="K1386" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1386" s="3"/>
-      <c r="M1386" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L1386" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1386" s="3" t="s">
+        <v>4348</v>
+      </c>
       <c r="N1386" s="3"/>
     </row>
     <row r="1387" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1387" s="3" t="s">
-        <v>4356</v>
+        <v>4357</v>
       </c>
       <c r="B1387" s="3"/>
       <c r="C1387" s="3">
@@ -66261,26 +66484,32 @@
         <v>24</v>
       </c>
       <c r="F1387" s="3" t="s">
-        <v>4357</v>
+        <v>4358</v>
       </c>
       <c r="G1387" s="3" t="s">
-        <v>4358</v>
-      </c>
-      <c r="H1387" s="3"/>
+        <v>4359</v>
+      </c>
+      <c r="H1387" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="I1387" s="3">
         <v>42</v>
       </c>
       <c r="J1387" s="3"/>
       <c r="K1387" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1387" s="3"/>
-      <c r="M1387" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L1387" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1387" s="3" t="s">
+        <v>4360</v>
+      </c>
       <c r="N1387" s="3"/>
     </row>
     <row r="1388" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1388" s="3" t="s">
-        <v>4359</v>
+        <v>4361</v>
       </c>
       <c r="B1388" s="3" t="s">
         <v>81</v>
@@ -66295,12 +66524,14 @@
         <v>382</v>
       </c>
       <c r="F1388" s="3" t="s">
-        <v>4360</v>
+        <v>4362</v>
       </c>
       <c r="G1388" s="3" t="s">
-        <v>4361</v>
-      </c>
-      <c r="H1388" s="3"/>
+        <v>4363</v>
+      </c>
+      <c r="H1388" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="I1388" s="3">
         <v>65</v>
       </c>
@@ -66308,15 +66539,19 @@
         <v>65</v>
       </c>
       <c r="K1388" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1388" s="3"/>
-      <c r="M1388" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L1388" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1388" s="3" t="s">
+        <v>4360</v>
+      </c>
       <c r="N1388" s="3"/>
     </row>
     <row r="1389" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1389" s="3" t="s">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="B1389" s="3"/>
       <c r="C1389" s="3">
@@ -66332,7 +66567,7 @@
         <v>411</v>
       </c>
       <c r="G1389" s="3" t="s">
-        <v>4363</v>
+        <v>4365</v>
       </c>
       <c r="H1389" s="3" t="s">
         <v>98</v>
@@ -66344,15 +66579,19 @@
         <v>70</v>
       </c>
       <c r="K1389" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1389" s="3"/>
-      <c r="M1389" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L1389" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1389" s="3" t="s">
+        <v>4366</v>
+      </c>
       <c r="N1389" s="3"/>
     </row>
     <row r="1390" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1390" s="3" t="s">
-        <v>4364</v>
+        <v>4367</v>
       </c>
       <c r="B1390" s="3" t="s">
         <v>324</v>
@@ -66367,10 +66606,10 @@
         <v>24</v>
       </c>
       <c r="F1390" s="3" t="s">
-        <v>4365</v>
+        <v>4368</v>
       </c>
       <c r="G1390" s="3" t="s">
-        <v>4366</v>
+        <v>4369</v>
       </c>
       <c r="H1390" s="3"/>
       <c r="I1390" s="3">
@@ -66386,7 +66625,7 @@
     </row>
     <row r="1391" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1391" s="3" t="s">
-        <v>4367</v>
+        <v>4370</v>
       </c>
       <c r="B1391" s="3"/>
       <c r="C1391" s="3">
@@ -66399,13 +66638,13 @@
         <v>24</v>
       </c>
       <c r="F1391" s="3" t="s">
-        <v>4368</v>
+        <v>4371</v>
       </c>
       <c r="G1391" s="3" t="s">
-        <v>4369</v>
+        <v>4372</v>
       </c>
       <c r="H1391" s="3" t="s">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="I1391" s="3">
         <v>75</v>
@@ -66414,15 +66653,19 @@
         <v>75</v>
       </c>
       <c r="K1391" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1391" s="3"/>
-      <c r="M1391" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L1391" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1391" s="3" t="s">
+        <v>4366</v>
+      </c>
       <c r="N1391" s="3"/>
     </row>
     <row r="1392" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1392" s="3" t="s">
-        <v>4370</v>
+        <v>4373</v>
       </c>
       <c r="B1392" s="3" t="s">
         <v>17</v>
@@ -66440,28 +66683,32 @@
         <v>1956</v>
       </c>
       <c r="G1392" s="3" t="s">
-        <v>4371</v>
+        <v>4374</v>
       </c>
       <c r="H1392" s="3" t="s">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="I1392" s="3">
         <v>59</v>
       </c>
       <c r="J1392" s="3"/>
       <c r="K1392" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1392" s="3"/>
-      <c r="M1392" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L1392" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1392" s="3" t="s">
+        <v>4366</v>
+      </c>
       <c r="N1392" s="3"/>
     </row>
     <row r="1393" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1393" s="3" t="s">
-        <v>4372</v>
+        <v>4375</v>
       </c>
       <c r="B1393" s="3" t="s">
-        <v>17</v>
+        <v>557</v>
       </c>
       <c r="C1393" s="3">
         <v>839</v>
@@ -66473,10 +66720,10 @@
         <v>24</v>
       </c>
       <c r="F1393" s="3" t="s">
-        <v>4373</v>
+        <v>4376</v>
       </c>
       <c r="G1393" s="3" t="s">
-        <v>4374</v>
+        <v>4377</v>
       </c>
       <c r="H1393" s="3"/>
       <c r="I1393" s="3">
@@ -66489,6 +66736,774 @@
       <c r="L1393" s="3"/>
       <c r="M1393" s="3"/>
       <c r="N1393" s="3"/>
+    </row>
+    <row r="1394" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1394" s="3" t="s">
+        <v>4378</v>
+      </c>
+      <c r="B1394" s="3"/>
+      <c r="C1394" s="3">
+        <v>338</v>
+      </c>
+      <c r="D1394" s="3">
+        <v>1591003766</v>
+      </c>
+      <c r="E1394" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1394" s="3" t="s">
+        <v>3042</v>
+      </c>
+      <c r="G1394" s="3" t="s">
+        <v>4379</v>
+      </c>
+      <c r="H1394" s="3"/>
+      <c r="I1394" s="3">
+        <v>44</v>
+      </c>
+      <c r="J1394" s="3"/>
+      <c r="K1394" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1394" s="3"/>
+      <c r="M1394" s="3"/>
+      <c r="N1394" s="3"/>
+    </row>
+    <row r="1395" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1395" s="3" t="s">
+        <v>4380</v>
+      </c>
+      <c r="B1395" s="3" t="s">
+        <v>1742</v>
+      </c>
+      <c r="C1395" s="3">
+        <v>22</v>
+      </c>
+      <c r="D1395" s="3">
+        <v>1591372417</v>
+      </c>
+      <c r="E1395" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1395" s="3" t="s">
+        <v>4381</v>
+      </c>
+      <c r="G1395" s="3" t="s">
+        <v>4382</v>
+      </c>
+      <c r="H1395" s="3"/>
+      <c r="I1395" s="3">
+        <v>69</v>
+      </c>
+      <c r="J1395" s="3"/>
+      <c r="K1395" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1395" s="3"/>
+      <c r="M1395" s="3"/>
+      <c r="N1395" s="3"/>
+    </row>
+    <row r="1396" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1396" s="3" t="s">
+        <v>4383</v>
+      </c>
+      <c r="B1396" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1396" s="3">
+        <v>208</v>
+      </c>
+      <c r="D1396" s="3">
+        <v>1592649953</v>
+      </c>
+      <c r="E1396" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1396" s="3" t="s">
+        <v>4384</v>
+      </c>
+      <c r="G1396" s="3" t="s">
+        <v>4385</v>
+      </c>
+      <c r="H1396" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1396" s="3">
+        <v>61</v>
+      </c>
+      <c r="J1396" s="3"/>
+      <c r="K1396" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1396" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1396" s="3" t="s">
+        <v>4386</v>
+      </c>
+      <c r="N1396" s="3"/>
+    </row>
+    <row r="1397" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1397" s="3" t="s">
+        <v>4387</v>
+      </c>
+      <c r="B1397" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1397" s="3">
+        <v>208</v>
+      </c>
+      <c r="D1397" s="3">
+        <v>1593611919</v>
+      </c>
+      <c r="E1397" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1397" s="3" t="s">
+        <v>4388</v>
+      </c>
+      <c r="G1397" s="3" t="s">
+        <v>4389</v>
+      </c>
+      <c r="H1397" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1397" s="3">
+        <v>70</v>
+      </c>
+      <c r="J1397" s="3">
+        <v>55</v>
+      </c>
+      <c r="K1397" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1397" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1397" s="3" t="s">
+        <v>4390</v>
+      </c>
+      <c r="N1397" s="3"/>
+    </row>
+    <row r="1398" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1398" s="3" t="s">
+        <v>4391</v>
+      </c>
+      <c r="B1398" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1398" s="3">
+        <v>208</v>
+      </c>
+      <c r="D1398" s="3">
+        <v>1593624680</v>
+      </c>
+      <c r="E1398" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1398" s="3" t="s">
+        <v>4392</v>
+      </c>
+      <c r="G1398" s="3" t="s">
+        <v>4393</v>
+      </c>
+      <c r="H1398" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1398" s="3">
+        <v>74</v>
+      </c>
+      <c r="J1398" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1398" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1398" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1398" s="3" t="s">
+        <v>4394</v>
+      </c>
+      <c r="N1398" s="3"/>
+    </row>
+    <row r="1399" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1399" s="3" t="s">
+        <v>4395</v>
+      </c>
+      <c r="B1399" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1399" s="3">
+        <v>208</v>
+      </c>
+      <c r="D1399" s="3">
+        <v>1594095946</v>
+      </c>
+      <c r="E1399" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1399" s="3" t="s">
+        <v>4396</v>
+      </c>
+      <c r="G1399" s="3" t="s">
+        <v>4397</v>
+      </c>
+      <c r="H1399" s="3"/>
+      <c r="I1399" s="3">
+        <v>59</v>
+      </c>
+      <c r="J1399" s="3">
+        <v>80</v>
+      </c>
+      <c r="K1399" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1399" s="3"/>
+      <c r="M1399" s="3"/>
+      <c r="N1399" s="3"/>
+    </row>
+    <row r="1400" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1400" s="3" t="s">
+        <v>4398</v>
+      </c>
+      <c r="B1400" s="3"/>
+      <c r="C1400" s="3">
+        <v>375</v>
+      </c>
+      <c r="D1400" s="3">
+        <v>1594156857</v>
+      </c>
+      <c r="E1400" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1400" s="3" t="s">
+        <v>4399</v>
+      </c>
+      <c r="G1400" s="3" t="s">
+        <v>4400</v>
+      </c>
+      <c r="H1400" s="3"/>
+      <c r="I1400" s="3">
+        <v>64</v>
+      </c>
+      <c r="J1400" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1400" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1400" s="3"/>
+      <c r="M1400" s="3"/>
+      <c r="N1400" s="3"/>
+    </row>
+    <row r="1401" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1401" s="3" t="s">
+        <v>4401</v>
+      </c>
+      <c r="B1401" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1401" s="3">
+        <v>208</v>
+      </c>
+      <c r="D1401" s="3">
+        <v>1594168678</v>
+      </c>
+      <c r="E1401" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1401" s="3" t="s">
+        <v>4402</v>
+      </c>
+      <c r="G1401" s="3" t="s">
+        <v>4403</v>
+      </c>
+      <c r="H1401" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1401" s="3">
+        <v>57</v>
+      </c>
+      <c r="J1401" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1401" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1401" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1401" s="3" t="s">
+        <v>4394</v>
+      </c>
+      <c r="N1401" s="3"/>
+    </row>
+    <row r="1402" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1402" s="3" t="s">
+        <v>4404</v>
+      </c>
+      <c r="B1402" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1402" s="3">
+        <v>208</v>
+      </c>
+      <c r="D1402" s="3">
+        <v>1594283233</v>
+      </c>
+      <c r="E1402" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1402" s="3" t="s">
+        <v>4405</v>
+      </c>
+      <c r="G1402" s="3" t="s">
+        <v>4406</v>
+      </c>
+      <c r="H1402" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1402" s="3">
+        <v>71</v>
+      </c>
+      <c r="J1402" s="3"/>
+      <c r="K1402" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1402" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1402" s="3" t="s">
+        <v>4394</v>
+      </c>
+      <c r="N1402" s="3"/>
+    </row>
+    <row r="1403" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1403" s="3" t="s">
+        <v>4407</v>
+      </c>
+      <c r="B1403" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1403" s="3">
+        <v>208</v>
+      </c>
+      <c r="D1403" s="3">
+        <v>1594383101</v>
+      </c>
+      <c r="E1403" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1403" s="3" t="s">
+        <v>4408</v>
+      </c>
+      <c r="G1403" s="3" t="s">
+        <v>4409</v>
+      </c>
+      <c r="H1403" s="3"/>
+      <c r="I1403" s="3">
+        <v>63</v>
+      </c>
+      <c r="J1403" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1403" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1403" s="3"/>
+      <c r="M1403" s="3"/>
+      <c r="N1403" s="3"/>
+    </row>
+    <row r="1404" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1404" s="3" t="s">
+        <v>4410</v>
+      </c>
+      <c r="B1404" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1404" s="3">
+        <v>208</v>
+      </c>
+      <c r="D1404" s="3">
+        <v>1594388091</v>
+      </c>
+      <c r="E1404" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1404" s="3" t="s">
+        <v>4411</v>
+      </c>
+      <c r="G1404" s="3" t="s">
+        <v>4412</v>
+      </c>
+      <c r="H1404" s="3"/>
+      <c r="I1404" s="3">
+        <v>51</v>
+      </c>
+      <c r="J1404" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1404" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1404" s="3"/>
+      <c r="M1404" s="3"/>
+      <c r="N1404" s="3"/>
+    </row>
+    <row r="1405" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1405" s="3" t="s">
+        <v>4413</v>
+      </c>
+      <c r="B1405" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1405" s="3">
+        <v>208</v>
+      </c>
+      <c r="D1405" s="3">
+        <v>1594643120</v>
+      </c>
+      <c r="E1405" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1405" s="3" t="s">
+        <v>4414</v>
+      </c>
+      <c r="G1405" s="3" t="s">
+        <v>4415</v>
+      </c>
+      <c r="H1405" s="3"/>
+      <c r="I1405" s="3">
+        <v>61</v>
+      </c>
+      <c r="J1405" s="3"/>
+      <c r="K1405" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1405" s="3"/>
+      <c r="M1405" s="3"/>
+      <c r="N1405" s="3"/>
+    </row>
+    <row r="1406" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1406" s="3" t="s">
+        <v>4416</v>
+      </c>
+      <c r="B1406" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1406" s="3">
+        <v>208</v>
+      </c>
+      <c r="D1406" s="3">
+        <v>1594752938</v>
+      </c>
+      <c r="E1406" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1406" s="3" t="s">
+        <v>4417</v>
+      </c>
+      <c r="G1406" s="3" t="s">
+        <v>4418</v>
+      </c>
+      <c r="H1406" s="3"/>
+      <c r="I1406" s="3">
+        <v>68</v>
+      </c>
+      <c r="J1406" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1406" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1406" s="3"/>
+      <c r="M1406" s="3"/>
+      <c r="N1406" s="3"/>
+    </row>
+    <row r="1407" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1407" s="3" t="s">
+        <v>4419</v>
+      </c>
+      <c r="B1407" s="3"/>
+      <c r="C1407" s="3">
+        <v>339</v>
+      </c>
+      <c r="D1407" s="3">
+        <v>1594815382</v>
+      </c>
+      <c r="E1407" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1407" s="3" t="s">
+        <v>2897</v>
+      </c>
+      <c r="G1407" s="3" t="s">
+        <v>4420</v>
+      </c>
+      <c r="H1407" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1407" s="3">
+        <v>74</v>
+      </c>
+      <c r="J1407" s="3">
+        <v>80</v>
+      </c>
+      <c r="K1407" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1407" s="3"/>
+      <c r="M1407" s="3"/>
+      <c r="N1407" s="3"/>
+    </row>
+    <row r="1408" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1408" s="3" t="s">
+        <v>4421</v>
+      </c>
+      <c r="B1408" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C1408" s="3">
+        <v>731</v>
+      </c>
+      <c r="D1408" s="3">
+        <v>1594818005</v>
+      </c>
+      <c r="E1408" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1408" s="3" t="s">
+        <v>4422</v>
+      </c>
+      <c r="G1408" s="3" t="s">
+        <v>4423</v>
+      </c>
+      <c r="H1408" s="3"/>
+      <c r="I1408" s="3">
+        <v>40</v>
+      </c>
+      <c r="J1408" s="3"/>
+      <c r="K1408" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1408" s="3"/>
+      <c r="M1408" s="3"/>
+      <c r="N1408" s="3"/>
+    </row>
+    <row r="1409" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1409" s="3" t="s">
+        <v>4424</v>
+      </c>
+      <c r="B1409" s="3"/>
+      <c r="C1409" s="3">
+        <v>840</v>
+      </c>
+      <c r="D1409" s="3">
+        <v>1594842618</v>
+      </c>
+      <c r="E1409" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1409" s="3" t="s">
+        <v>4425</v>
+      </c>
+      <c r="G1409" s="3" t="s">
+        <v>4426</v>
+      </c>
+      <c r="H1409" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1409" s="3">
+        <v>73</v>
+      </c>
+      <c r="J1409" s="3">
+        <v>80</v>
+      </c>
+      <c r="K1409" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1409" s="3"/>
+      <c r="M1409" s="3"/>
+      <c r="N1409" s="3"/>
+    </row>
+    <row r="1410" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1410" s="3" t="s">
+        <v>4427</v>
+      </c>
+      <c r="B1410" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1410" s="3">
+        <v>729</v>
+      </c>
+      <c r="D1410" s="3">
+        <v>1594964373</v>
+      </c>
+      <c r="E1410" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1410" s="3" t="s">
+        <v>4428</v>
+      </c>
+      <c r="G1410" s="3" t="s">
+        <v>4429</v>
+      </c>
+      <c r="H1410" s="3"/>
+      <c r="I1410" s="3">
+        <v>52</v>
+      </c>
+      <c r="J1410" s="3">
+        <v>55</v>
+      </c>
+      <c r="K1410" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1410" s="3"/>
+      <c r="M1410" s="3"/>
+      <c r="N1410" s="3"/>
+    </row>
+    <row r="1411" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1411" s="3" t="s">
+        <v>4430</v>
+      </c>
+      <c r="B1411" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="C1411" s="3">
+        <v>838</v>
+      </c>
+      <c r="D1411" s="3">
+        <v>1595248961</v>
+      </c>
+      <c r="E1411" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1411" s="3" t="s">
+        <v>4431</v>
+      </c>
+      <c r="G1411" s="3" t="s">
+        <v>4432</v>
+      </c>
+      <c r="H1411" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1411" s="3">
+        <v>40</v>
+      </c>
+      <c r="J1411" s="3"/>
+      <c r="K1411" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1411" s="3"/>
+      <c r="M1411" s="3"/>
+      <c r="N1411" s="3"/>
+    </row>
+    <row r="1412" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1412" s="3" t="s">
+        <v>4433</v>
+      </c>
+      <c r="B1412" s="3"/>
+      <c r="C1412" s="3">
+        <v>840</v>
+      </c>
+      <c r="D1412" s="3">
+        <v>1595271132</v>
+      </c>
+      <c r="E1412" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1412" s="3" t="s">
+        <v>4434</v>
+      </c>
+      <c r="G1412" s="3" t="s">
+        <v>4435</v>
+      </c>
+      <c r="H1412" s="3"/>
+      <c r="I1412" s="3">
+        <v>31</v>
+      </c>
+      <c r="J1412" s="3"/>
+      <c r="K1412" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1412" s="3"/>
+      <c r="M1412" s="3"/>
+      <c r="N1412" s="3"/>
+    </row>
+    <row r="1413" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1413" s="3" t="s">
+        <v>4436</v>
+      </c>
+      <c r="B1413" s="3" t="s">
+        <v>1742</v>
+      </c>
+      <c r="C1413" s="3">
+        <v>22</v>
+      </c>
+      <c r="D1413" s="3">
+        <v>1595277987</v>
+      </c>
+      <c r="E1413" s="3" t="s">
+        <v>765</v>
+      </c>
+      <c r="F1413" s="3" t="s">
+        <v>4437</v>
+      </c>
+      <c r="G1413" s="3" t="s">
+        <v>4438</v>
+      </c>
+      <c r="H1413" s="3"/>
+      <c r="I1413" s="3">
+        <v>49</v>
+      </c>
+      <c r="J1413" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1413" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1413" s="3"/>
+      <c r="M1413" s="3"/>
+      <c r="N1413" s="3"/>
+    </row>
+    <row r="1414" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1414" s="3" t="s">
+        <v>4439</v>
+      </c>
+      <c r="B1414" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C1414" s="3">
+        <v>731</v>
+      </c>
+      <c r="D1414" s="3">
+        <v>1595391660</v>
+      </c>
+      <c r="E1414" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1414" s="3" t="s">
+        <v>4440</v>
+      </c>
+      <c r="G1414" s="3" t="s">
+        <v>4441</v>
+      </c>
+      <c r="H1414" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1414" s="3">
+        <v>72</v>
+      </c>
+      <c r="J1414" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1414" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1414" s="3"/>
+      <c r="M1414" s="3"/>
+      <c r="N1414" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\PCS-Trucking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B0625955-0DFA-45AB-9CDD-D13F02646C46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4B607618-D22A-4DF3-A986-3544A3F1B0C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1860" yWindow="1860" windowWidth="43200" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRIVE-ALERTS" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10565" uniqueCount="4442">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10997" uniqueCount="4617">
   <si>
     <t>DRIVE ALERTS</t>
   </si>
@@ -13285,6 +13285,9 @@
     <t>39.749445, -111.835073</t>
   </si>
   <si>
+    <t>08/10/26 09:31 EDT</t>
+  </si>
+  <si>
     <t>08/07/26 15:40 EDT</t>
   </si>
   <si>
@@ -13303,6 +13306,9 @@
     <t>39.457588, -112.008392</t>
   </si>
   <si>
+    <t>08/10/26 09:32 EDT</t>
+  </si>
+  <si>
     <t>08/07/26 18:47 EDT</t>
   </si>
   <si>
@@ -13312,6 +13318,9 @@
     <t>36.025873, -115.224110</t>
   </si>
   <si>
+    <t>08/10/26 09:33 EDT</t>
+  </si>
+  <si>
     <t>08/08/26 12:12 EDT</t>
   </si>
   <si>
@@ -13346,6 +13355,522 @@
   </si>
   <si>
     <t>39.514995, -110.548489</t>
+  </si>
+  <si>
+    <t>08/09/26 10:35 EDT</t>
+  </si>
+  <si>
+    <t>10mi E of Rock Springs WY</t>
+  </si>
+  <si>
+    <t>41.639114, -109.035824</t>
+  </si>
+  <si>
+    <t>08/09/26 11:23 EDT</t>
+  </si>
+  <si>
+    <t>40.5mi W of Rawlins WY</t>
+  </si>
+  <si>
+    <t>41.669958, -107.997117</t>
+  </si>
+  <si>
+    <t>08/09/26 14:52 EDT</t>
+  </si>
+  <si>
+    <t>2.6mi W of Grants NM</t>
+  </si>
+  <si>
+    <t>35.156728, -107.880091</t>
+  </si>
+  <si>
+    <t>08/10/26 09:34 EDT</t>
+  </si>
+  <si>
+    <t>08/09/26 16:12 EDT</t>
+  </si>
+  <si>
+    <t>7.9mi E of Sidney NE</t>
+  </si>
+  <si>
+    <t>41.112770, -102.818758</t>
+  </si>
+  <si>
+    <t>08/09/26 16:36 EDT</t>
+  </si>
+  <si>
+    <t>36.1mi E of Sidney NE</t>
+  </si>
+  <si>
+    <t>41.044940, -102.285498</t>
+  </si>
+  <si>
+    <t>08/10/26 01:38 EDT</t>
+  </si>
+  <si>
+    <t>1.9mi NE of Golden CO</t>
+  </si>
+  <si>
+    <t>39.765080, -105.195393</t>
+  </si>
+  <si>
+    <t>08/10/26 16:27 EDT</t>
+  </si>
+  <si>
+    <t>3.1mi S of Golden CO</t>
+  </si>
+  <si>
+    <t>39.698528, -105.232243</t>
+  </si>
+  <si>
+    <t>08/10/26 18:03 EDT</t>
+  </si>
+  <si>
+    <t>12.2mi NE of Enoch UT</t>
+  </si>
+  <si>
+    <t>37.847875, -112.846132</t>
+  </si>
+  <si>
+    <t>08/11/26 08:17 EDT</t>
+  </si>
+  <si>
+    <t>08/10/26 18:09 EDT</t>
+  </si>
+  <si>
+    <t>3.7mi E of Gallup NM</t>
+  </si>
+  <si>
+    <t>35.534406, -108.680927</t>
+  </si>
+  <si>
+    <t>08/10/26 18:30 EDT</t>
+  </si>
+  <si>
+    <t>7.4mi E of Avon CO</t>
+  </si>
+  <si>
+    <t>39.643504, -106.374123</t>
+  </si>
+  <si>
+    <t>08/10/26 21:07 EDT</t>
+  </si>
+  <si>
+    <t>16.8mi NE of Fruitvale CO</t>
+  </si>
+  <si>
+    <t>39.263476, -108.255768</t>
+  </si>
+  <si>
+    <t>08/10/26 21:34 EDT</t>
+  </si>
+  <si>
+    <t>08/11/26 01:22 EDT</t>
+  </si>
+  <si>
+    <t>35.514889, -115.432450</t>
+  </si>
+  <si>
+    <t>08/11/26 14:46 EDT</t>
+  </si>
+  <si>
+    <t>33.4mi W of Green River WY</t>
+  </si>
+  <si>
+    <t>41.433566, -110.107768</t>
+  </si>
+  <si>
+    <t>08/12/26 03:48 EDT</t>
+  </si>
+  <si>
+    <t>40.114783, -111.706158</t>
+  </si>
+  <si>
+    <t>08/12/26 16:31 EDT</t>
+  </si>
+  <si>
+    <t>41mi NE of Enoch UT</t>
+  </si>
+  <si>
+    <t>38.271859, -112.650214</t>
+  </si>
+  <si>
+    <t>08/13/26 08:49 EDT</t>
+  </si>
+  <si>
+    <t>41.1mi NE of Enoch UT</t>
+  </si>
+  <si>
+    <t>38.274135, -112.650251</t>
+  </si>
+  <si>
+    <t>08/13/26 08:50 EDT</t>
+  </si>
+  <si>
+    <t>08/12/26 17:09 EDT</t>
+  </si>
+  <si>
+    <t>4.3mi E of Denver CO</t>
+  </si>
+  <si>
+    <t>39.767533, -104.795671</t>
+  </si>
+  <si>
+    <t>08/13/26 15:55 EDT</t>
+  </si>
+  <si>
+    <t>1.9mi NE of Nampa ID</t>
+  </si>
+  <si>
+    <t>43.598487, -116.530660</t>
+  </si>
+  <si>
+    <t>08/14/26 08:16 EDT</t>
+  </si>
+  <si>
+    <t>08/13/26 20:02 EDT</t>
+  </si>
+  <si>
+    <t>42mi SW of Richfield UT</t>
+  </si>
+  <si>
+    <t>38.344550, -112.659112</t>
+  </si>
+  <si>
+    <t>08/14/26 08:17 EDT</t>
+  </si>
+  <si>
+    <t>08/13/26 23:12 EDT</t>
+  </si>
+  <si>
+    <t>54.1mi W of Tucumcari NM</t>
+  </si>
+  <si>
+    <t>34.955150, -104.623869</t>
+  </si>
+  <si>
+    <t>08/14/26 05:01 EDT</t>
+  </si>
+  <si>
+    <t>35.514836, -115.432455</t>
+  </si>
+  <si>
+    <t>08/14/26 10:51 EDT</t>
+  </si>
+  <si>
+    <t>40.725815, -111.996117</t>
+  </si>
+  <si>
+    <t>08/17/26 08:19 EDT</t>
+  </si>
+  <si>
+    <t>08/14/26 19:08 EDT</t>
+  </si>
+  <si>
+    <t>46.4mi N of Dalhart TX</t>
+  </si>
+  <si>
+    <t>36.728991, -102.491366</t>
+  </si>
+  <si>
+    <t>08/14/26 21:08 EDT</t>
+  </si>
+  <si>
+    <t>6.5mi E of Green River WY</t>
+  </si>
+  <si>
+    <t>41.541600, -109.351086</t>
+  </si>
+  <si>
+    <t>08/15/26 04:38 EDT</t>
+  </si>
+  <si>
+    <t>1.1mi S of Brigham City UT</t>
+  </si>
+  <si>
+    <t>41.488114, -112.053124</t>
+  </si>
+  <si>
+    <t>08/15/26 09:58 EDT</t>
+  </si>
+  <si>
+    <t>3.3mi E of Rock Springs WY</t>
+  </si>
+  <si>
+    <t>41.598017, -109.157212</t>
+  </si>
+  <si>
+    <t>08/17/26 08:20 EDT</t>
+  </si>
+  <si>
+    <t>08/15/26 13:03 EDT</t>
+  </si>
+  <si>
+    <t>2.1mi N of Millcreek UT</t>
+  </si>
+  <si>
+    <t>40.718379, -111.839884</t>
+  </si>
+  <si>
+    <t>08/15/26 17:02 EDT</t>
+  </si>
+  <si>
+    <t>3.1mi E of Green River WY</t>
+  </si>
+  <si>
+    <t>41.526919, -109.414852</t>
+  </si>
+  <si>
+    <t>08/15/26 19:11 EDT</t>
+  </si>
+  <si>
+    <t>20.4mi E of Rawlins WY</t>
+  </si>
+  <si>
+    <t>41.741301, -106.834786</t>
+  </si>
+  <si>
+    <t>08/15/26 20:40 EDT</t>
+  </si>
+  <si>
+    <t>29.4mi E of Aurora CO</t>
+  </si>
+  <si>
+    <t>39.700781, -104.171612</t>
+  </si>
+  <si>
+    <t>08/17/26 08:21 EDT</t>
+  </si>
+  <si>
+    <t>08/17/26 11:58 EDT</t>
+  </si>
+  <si>
+    <t>3.8mi N of Pampa TX</t>
+  </si>
+  <si>
+    <t>35.602468, -100.954328</t>
+  </si>
+  <si>
+    <t>08/17/26 16:08 EDT</t>
+  </si>
+  <si>
+    <t>7.2mi NE of Platteville WI</t>
+  </si>
+  <si>
+    <t>42.805957, -90.373665</t>
+  </si>
+  <si>
+    <t>08/18/26 09:01 EDT</t>
+  </si>
+  <si>
+    <t>08/17/26 19:08 EDT</t>
+  </si>
+  <si>
+    <t>13.4mi SW of Cedar City UT</t>
+  </si>
+  <si>
+    <t>37.512512, -113.212665</t>
+  </si>
+  <si>
+    <t>08/18/26 09:02 EDT</t>
+  </si>
+  <si>
+    <t>13.6mi SW of Cedar City UT</t>
+  </si>
+  <si>
+    <t>37.510560, -113.213167</t>
+  </si>
+  <si>
+    <t>08/17/26 21:41 EDT</t>
+  </si>
+  <si>
+    <t>7.5mi S of Enterprise NV</t>
+  </si>
+  <si>
+    <t>35.901320, -115.213872</t>
+  </si>
+  <si>
+    <t>08/18/26 01:16 EDT</t>
+  </si>
+  <si>
+    <t>1mi E of Albuquerque NM</t>
+  </si>
+  <si>
+    <t>35.107015, -106.629561</t>
+  </si>
+  <si>
+    <t>08/18/26 09:03 EDT</t>
+  </si>
+  <si>
+    <t>08/18/26 02:11 EDT</t>
+  </si>
+  <si>
+    <t>34.2mi E of Rock Springs WY</t>
+  </si>
+  <si>
+    <t>41.644460, -108.562348</t>
+  </si>
+  <si>
+    <t>08/18/26 09:04 EDT</t>
+  </si>
+  <si>
+    <t>08/18/26 14:19 EDT</t>
+  </si>
+  <si>
+    <t>4.6mi N of Fontana CA</t>
+  </si>
+  <si>
+    <t>34.162631, -117.463929</t>
+  </si>
+  <si>
+    <t>34.163585, -117.462770</t>
+  </si>
+  <si>
+    <t>08/19/26 07:29 EDT</t>
+  </si>
+  <si>
+    <t>08/18/26 15:39 EDT</t>
+  </si>
+  <si>
+    <t>40.603003, -111.904666</t>
+  </si>
+  <si>
+    <t>08/19/26 07:30 EDT</t>
+  </si>
+  <si>
+    <t>08/18/26 23:14 EDT</t>
+  </si>
+  <si>
+    <t>5.9mi N of Borger TX</t>
+  </si>
+  <si>
+    <t>35.743826, -101.417786</t>
+  </si>
+  <si>
+    <t>08/19/26 07:32 EDT</t>
+  </si>
+  <si>
+    <t>5.5mi NE of Amarillo TX</t>
+  </si>
+  <si>
+    <t>35.228204, -101.741753</t>
+  </si>
+  <si>
+    <t>08/19/26 19:00 EDT</t>
+  </si>
+  <si>
+    <t>3.6mi SE of Moab UT</t>
+  </si>
+  <si>
+    <t>38.529632, -109.504817</t>
+  </si>
+  <si>
+    <t>08/20/26 09:26 EDT</t>
+  </si>
+  <si>
+    <t>08/20/26 13:55 EDT</t>
+  </si>
+  <si>
+    <t>4.9mi E of Shafter CA</t>
+  </si>
+  <si>
+    <t>35.462827, -119.115772</t>
+  </si>
+  <si>
+    <t>08/20/26 16:56 EDT</t>
+  </si>
+  <si>
+    <t>08/20/26 14:15 EDT</t>
+  </si>
+  <si>
+    <t>2.8mi NW of Springville UT</t>
+  </si>
+  <si>
+    <t>40.197470, -111.650693</t>
+  </si>
+  <si>
+    <t>08/20/26 18:44 EDT</t>
+  </si>
+  <si>
+    <t>2.7mi SW of Paradise NV</t>
+  </si>
+  <si>
+    <t>36.071609, -115.180606</t>
+  </si>
+  <si>
+    <t>08/21/26 07:25 EDT</t>
+  </si>
+  <si>
+    <t>08/21/26 08:34 EDT</t>
+  </si>
+  <si>
+    <t>5.9mi NW of Muscoy CA</t>
+  </si>
+  <si>
+    <t>34.223295, -117.410310</t>
+  </si>
+  <si>
+    <t>08/21/26 08:35 EDT</t>
+  </si>
+  <si>
+    <t>34.222583, -117.410233</t>
+  </si>
+  <si>
+    <t>08/21/26 08:39 EDT</t>
+  </si>
+  <si>
+    <t>40.565093, -111.899249</t>
+  </si>
+  <si>
+    <t>08/21/26 12:07 EDT</t>
+  </si>
+  <si>
+    <t>40.371033, -111.802371</t>
+  </si>
+  <si>
+    <t>08/21/26 14:09 EDT</t>
+  </si>
+  <si>
+    <t>1.2mi NE of South Monrovia Island CA</t>
+  </si>
+  <si>
+    <t>34.135531, -117.981033</t>
+  </si>
+  <si>
+    <t>08/21/26 20:42 EDT</t>
+  </si>
+  <si>
+    <t>7.2mi E of Evanston WY</t>
+  </si>
+  <si>
+    <t>41.270726, -110.826477</t>
+  </si>
+  <si>
+    <t>08/23/26 00:24 EDT</t>
+  </si>
+  <si>
+    <t>36.032931, -115.180599</t>
+  </si>
+  <si>
+    <t>36.034797, -115.180599</t>
+  </si>
+  <si>
+    <t>08/23/26 02:31 EDT</t>
+  </si>
+  <si>
+    <t>35.4mi E of Aurora CO</t>
+  </si>
+  <si>
+    <t>39.642922, -104.064511</t>
+  </si>
+  <si>
+    <t>08/23/26 22:38 EDT</t>
+  </si>
+  <si>
+    <t>2.6mi S of North Las Vegas NV</t>
+  </si>
+  <si>
+    <t>36.251343, -115.088480</t>
   </si>
 </sst>
 </file>
@@ -13707,7 +14232,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N1414"/>
+  <dimension ref="A1:N1470"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="14" width="15" customWidth="1"/>
@@ -67251,15 +67776,19 @@
         <v>80</v>
       </c>
       <c r="K1407" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1407" s="3"/>
-      <c r="M1407" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L1407" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1407" s="3" t="s">
+        <v>4421</v>
+      </c>
       <c r="N1407" s="3"/>
     </row>
     <row r="1408" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1408" s="3" t="s">
-        <v>4421</v>
+        <v>4422</v>
       </c>
       <c r="B1408" s="3" t="s">
         <v>324</v>
@@ -67274,10 +67803,10 @@
         <v>24</v>
       </c>
       <c r="F1408" s="3" t="s">
-        <v>4422</v>
+        <v>4423</v>
       </c>
       <c r="G1408" s="3" t="s">
-        <v>4423</v>
+        <v>4424</v>
       </c>
       <c r="H1408" s="3"/>
       <c r="I1408" s="3">
@@ -67293,7 +67822,7 @@
     </row>
     <row r="1409" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1409" s="3" t="s">
-        <v>4424</v>
+        <v>4425</v>
       </c>
       <c r="B1409" s="3"/>
       <c r="C1409" s="3">
@@ -67306,10 +67835,10 @@
         <v>47</v>
       </c>
       <c r="F1409" s="3" t="s">
-        <v>4425</v>
+        <v>4426</v>
       </c>
       <c r="G1409" s="3" t="s">
-        <v>4426</v>
+        <v>4427</v>
       </c>
       <c r="H1409" s="3" t="s">
         <v>98</v>
@@ -67321,15 +67850,19 @@
         <v>80</v>
       </c>
       <c r="K1409" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1409" s="3"/>
-      <c r="M1409" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L1409" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1409" s="3" t="s">
+        <v>4428</v>
+      </c>
       <c r="N1409" s="3"/>
     </row>
     <row r="1410" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1410" s="3" t="s">
-        <v>4427</v>
+        <v>4429</v>
       </c>
       <c r="B1410" s="3" t="s">
         <v>42</v>
@@ -67344,12 +67877,14 @@
         <v>24</v>
       </c>
       <c r="F1410" s="3" t="s">
-        <v>4428</v>
+        <v>4430</v>
       </c>
       <c r="G1410" s="3" t="s">
-        <v>4429</v>
-      </c>
-      <c r="H1410" s="3"/>
+        <v>4431</v>
+      </c>
+      <c r="H1410" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="I1410" s="3">
         <v>52</v>
       </c>
@@ -67357,15 +67892,19 @@
         <v>55</v>
       </c>
       <c r="K1410" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1410" s="3"/>
-      <c r="M1410" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L1410" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1410" s="3" t="s">
+        <v>4432</v>
+      </c>
       <c r="N1410" s="3"/>
     </row>
     <row r="1411" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1411" s="3" t="s">
-        <v>4430</v>
+        <v>4433</v>
       </c>
       <c r="B1411" s="3" t="s">
         <v>392</v>
@@ -67380,28 +67919,32 @@
         <v>24</v>
       </c>
       <c r="F1411" s="3" t="s">
-        <v>4431</v>
+        <v>4434</v>
       </c>
       <c r="G1411" s="3" t="s">
-        <v>4432</v>
+        <v>4435</v>
       </c>
       <c r="H1411" s="3" t="s">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="I1411" s="3">
         <v>40</v>
       </c>
       <c r="J1411" s="3"/>
       <c r="K1411" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1411" s="3"/>
-      <c r="M1411" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L1411" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1411" s="3" t="s">
+        <v>4432</v>
+      </c>
       <c r="N1411" s="3"/>
     </row>
     <row r="1412" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1412" s="3" t="s">
-        <v>4433</v>
+        <v>4436</v>
       </c>
       <c r="B1412" s="3"/>
       <c r="C1412" s="3">
@@ -67414,26 +67957,32 @@
         <v>24</v>
       </c>
       <c r="F1412" s="3" t="s">
-        <v>4434</v>
+        <v>4437</v>
       </c>
       <c r="G1412" s="3" t="s">
-        <v>4435</v>
-      </c>
-      <c r="H1412" s="3"/>
+        <v>4438</v>
+      </c>
+      <c r="H1412" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="I1412" s="3">
         <v>31</v>
       </c>
       <c r="J1412" s="3"/>
       <c r="K1412" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1412" s="3"/>
-      <c r="M1412" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L1412" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1412" s="3" t="s">
+        <v>4432</v>
+      </c>
       <c r="N1412" s="3"/>
     </row>
     <row r="1413" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1413" s="3" t="s">
-        <v>4436</v>
+        <v>4439</v>
       </c>
       <c r="B1413" s="3" t="s">
         <v>1742</v>
@@ -67448,10 +67997,10 @@
         <v>765</v>
       </c>
       <c r="F1413" s="3" t="s">
-        <v>4437</v>
+        <v>4440</v>
       </c>
       <c r="G1413" s="3" t="s">
-        <v>4438</v>
+        <v>4441</v>
       </c>
       <c r="H1413" s="3"/>
       <c r="I1413" s="3">
@@ -67469,7 +68018,7 @@
     </row>
     <row r="1414" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1414" s="3" t="s">
-        <v>4439</v>
+        <v>4442</v>
       </c>
       <c r="B1414" s="3" t="s">
         <v>324</v>
@@ -67484,13 +68033,13 @@
         <v>43</v>
       </c>
       <c r="F1414" s="3" t="s">
-        <v>4440</v>
+        <v>4443</v>
       </c>
       <c r="G1414" s="3" t="s">
-        <v>4441</v>
+        <v>4444</v>
       </c>
       <c r="H1414" s="3" t="s">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="I1414" s="3">
         <v>72</v>
@@ -67499,11 +68048,2179 @@
         <v>65</v>
       </c>
       <c r="K1414" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1414" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1414" s="3" t="s">
+        <v>4432</v>
+      </c>
+      <c r="N1414" s="3"/>
+    </row>
+    <row r="1415" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1415" s="3" t="s">
+        <v>4445</v>
+      </c>
+      <c r="B1415" s="3"/>
+      <c r="C1415" s="3">
+        <v>459</v>
+      </c>
+      <c r="D1415" s="3">
+        <v>1595542951</v>
+      </c>
+      <c r="E1415" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1415" s="3" t="s">
+        <v>4446</v>
+      </c>
+      <c r="G1415" s="3" t="s">
+        <v>4447</v>
+      </c>
+      <c r="H1415" s="3"/>
+      <c r="I1415" s="3">
+        <v>72</v>
+      </c>
+      <c r="J1415" s="3">
+        <v>80</v>
+      </c>
+      <c r="K1415" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L1414" s="3"/>
-      <c r="M1414" s="3"/>
-      <c r="N1414" s="3"/>
+      <c r="L1415" s="3"/>
+      <c r="M1415" s="3"/>
+      <c r="N1415" s="3"/>
+    </row>
+    <row r="1416" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1416" s="3" t="s">
+        <v>4448</v>
+      </c>
+      <c r="B1416" s="3"/>
+      <c r="C1416" s="3">
+        <v>459</v>
+      </c>
+      <c r="D1416" s="3">
+        <v>1595554437</v>
+      </c>
+      <c r="E1416" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1416" s="3" t="s">
+        <v>4449</v>
+      </c>
+      <c r="G1416" s="3" t="s">
+        <v>4450</v>
+      </c>
+      <c r="H1416" s="3"/>
+      <c r="I1416" s="3">
+        <v>72</v>
+      </c>
+      <c r="J1416" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1416" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1416" s="3"/>
+      <c r="M1416" s="3"/>
+      <c r="N1416" s="3"/>
+    </row>
+    <row r="1417" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1417" s="3" t="s">
+        <v>4451</v>
+      </c>
+      <c r="B1417" s="3"/>
+      <c r="C1417" s="3">
+        <v>209</v>
+      </c>
+      <c r="D1417" s="3">
+        <v>1595614244</v>
+      </c>
+      <c r="E1417" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1417" s="3" t="s">
+        <v>4452</v>
+      </c>
+      <c r="G1417" s="3" t="s">
+        <v>4453</v>
+      </c>
+      <c r="H1417" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1417" s="3">
+        <v>70</v>
+      </c>
+      <c r="J1417" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1417" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1417" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1417" s="3" t="s">
+        <v>4454</v>
+      </c>
+      <c r="N1417" s="3"/>
+    </row>
+    <row r="1418" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1418" s="3" t="s">
+        <v>4455</v>
+      </c>
+      <c r="B1418" s="3"/>
+      <c r="C1418" s="3">
+        <v>459</v>
+      </c>
+      <c r="D1418" s="3">
+        <v>1595639638</v>
+      </c>
+      <c r="E1418" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1418" s="3" t="s">
+        <v>4456</v>
+      </c>
+      <c r="G1418" s="3" t="s">
+        <v>4457</v>
+      </c>
+      <c r="H1418" s="3"/>
+      <c r="I1418" s="3">
+        <v>68</v>
+      </c>
+      <c r="J1418" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1418" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1418" s="3"/>
+      <c r="M1418" s="3"/>
+      <c r="N1418" s="3"/>
+    </row>
+    <row r="1419" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1419" s="3" t="s">
+        <v>4458</v>
+      </c>
+      <c r="B1419" s="3"/>
+      <c r="C1419" s="3">
+        <v>459</v>
+      </c>
+      <c r="D1419" s="3">
+        <v>1595647286</v>
+      </c>
+      <c r="E1419" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1419" s="3" t="s">
+        <v>4459</v>
+      </c>
+      <c r="G1419" s="3" t="s">
+        <v>4460</v>
+      </c>
+      <c r="H1419" s="3"/>
+      <c r="I1419" s="3">
+        <v>72</v>
+      </c>
+      <c r="J1419" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1419" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1419" s="3"/>
+      <c r="M1419" s="3"/>
+      <c r="N1419" s="3"/>
+    </row>
+    <row r="1420" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1420" s="3" t="s">
+        <v>4461</v>
+      </c>
+      <c r="B1420" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1420" s="3">
+        <v>336</v>
+      </c>
+      <c r="D1420" s="3">
+        <v>1595765078</v>
+      </c>
+      <c r="E1420" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1420" s="3" t="s">
+        <v>4462</v>
+      </c>
+      <c r="G1420" s="3" t="s">
+        <v>4463</v>
+      </c>
+      <c r="H1420" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1420" s="3">
+        <v>42</v>
+      </c>
+      <c r="J1420" s="3"/>
+      <c r="K1420" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1420" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1420" s="3" t="s">
+        <v>4454</v>
+      </c>
+      <c r="N1420" s="3"/>
+    </row>
+    <row r="1421" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1421" s="3" t="s">
+        <v>4464</v>
+      </c>
+      <c r="B1421" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1421" s="3">
+        <v>336</v>
+      </c>
+      <c r="D1421" s="3">
+        <v>1596363554</v>
+      </c>
+      <c r="E1421" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1421" s="3" t="s">
+        <v>4465</v>
+      </c>
+      <c r="G1421" s="3" t="s">
+        <v>4466</v>
+      </c>
+      <c r="H1421" s="3"/>
+      <c r="I1421" s="3">
+        <v>65</v>
+      </c>
+      <c r="J1421" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1421" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1421" s="3"/>
+      <c r="M1421" s="3"/>
+      <c r="N1421" s="3"/>
+    </row>
+    <row r="1422" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1422" s="3" t="s">
+        <v>4467</v>
+      </c>
+      <c r="B1422" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="C1422" s="3">
+        <v>108</v>
+      </c>
+      <c r="D1422" s="3">
+        <v>1596445162</v>
+      </c>
+      <c r="E1422" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1422" s="3" t="s">
+        <v>4468</v>
+      </c>
+      <c r="G1422" s="3" t="s">
+        <v>4469</v>
+      </c>
+      <c r="H1422" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1422" s="3">
+        <v>77</v>
+      </c>
+      <c r="J1422" s="3">
+        <v>80</v>
+      </c>
+      <c r="K1422" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1422" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1422" s="3" t="s">
+        <v>4470</v>
+      </c>
+      <c r="N1422" s="3"/>
+    </row>
+    <row r="1423" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1423" s="3" t="s">
+        <v>4471</v>
+      </c>
+      <c r="B1423" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1423" s="3">
+        <v>729</v>
+      </c>
+      <c r="D1423" s="3">
+        <v>1596449847</v>
+      </c>
+      <c r="E1423" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1423" s="3" t="s">
+        <v>4472</v>
+      </c>
+      <c r="G1423" s="3" t="s">
+        <v>4473</v>
+      </c>
+      <c r="H1423" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1423" s="3">
+        <v>64</v>
+      </c>
+      <c r="J1423" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1423" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1423" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1423" s="3" t="s">
+        <v>4470</v>
+      </c>
+      <c r="N1423" s="3"/>
+    </row>
+    <row r="1424" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1424" s="3" t="s">
+        <v>4474</v>
+      </c>
+      <c r="B1424" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1424" s="3">
+        <v>336</v>
+      </c>
+      <c r="D1424" s="3">
+        <v>1596465614</v>
+      </c>
+      <c r="E1424" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1424" s="3" t="s">
+        <v>4475</v>
+      </c>
+      <c r="G1424" s="3" t="s">
+        <v>4476</v>
+      </c>
+      <c r="H1424" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1424" s="3">
+        <v>65</v>
+      </c>
+      <c r="J1424" s="3"/>
+      <c r="K1424" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1424" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1424" s="3" t="s">
+        <v>4470</v>
+      </c>
+      <c r="N1424" s="3"/>
+    </row>
+    <row r="1425" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1425" s="3" t="s">
+        <v>4477</v>
+      </c>
+      <c r="B1425" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1425" s="3">
+        <v>336</v>
+      </c>
+      <c r="D1425" s="3">
+        <v>1596551078</v>
+      </c>
+      <c r="E1425" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1425" s="3" t="s">
+        <v>4478</v>
+      </c>
+      <c r="G1425" s="3" t="s">
+        <v>4479</v>
+      </c>
+      <c r="H1425" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1425" s="3">
+        <v>56</v>
+      </c>
+      <c r="J1425" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1425" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1425" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1425" s="3" t="s">
+        <v>4480</v>
+      </c>
+      <c r="N1425" s="3"/>
+    </row>
+    <row r="1426" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1426" s="3" t="s">
+        <v>4481</v>
+      </c>
+      <c r="B1426" s="3"/>
+      <c r="C1426" s="3">
+        <v>339</v>
+      </c>
+      <c r="D1426" s="3">
+        <v>1596614264</v>
+      </c>
+      <c r="E1426" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1426" s="3" t="s">
+        <v>3180</v>
+      </c>
+      <c r="G1426" s="3" t="s">
+        <v>4482</v>
+      </c>
+      <c r="H1426" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1426" s="3">
+        <v>27</v>
+      </c>
+      <c r="J1426" s="3">
+        <v>35</v>
+      </c>
+      <c r="K1426" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1426" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1426" s="3" t="s">
+        <v>4470</v>
+      </c>
+      <c r="N1426" s="3"/>
+    </row>
+    <row r="1427" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1427" s="3" t="s">
+        <v>4483</v>
+      </c>
+      <c r="B1427" s="3"/>
+      <c r="C1427" s="3">
+        <v>459</v>
+      </c>
+      <c r="D1427" s="3">
+        <v>1597158133</v>
+      </c>
+      <c r="E1427" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1427" s="3" t="s">
+        <v>4484</v>
+      </c>
+      <c r="G1427" s="3" t="s">
+        <v>4485</v>
+      </c>
+      <c r="H1427" s="3"/>
+      <c r="I1427" s="3">
+        <v>71</v>
+      </c>
+      <c r="J1427" s="3">
+        <v>80</v>
+      </c>
+      <c r="K1427" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1427" s="3"/>
+      <c r="M1427" s="3"/>
+      <c r="N1427" s="3"/>
+    </row>
+    <row r="1428" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1428" s="3" t="s">
+        <v>4486</v>
+      </c>
+      <c r="B1428" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1428" s="3">
+        <v>336</v>
+      </c>
+      <c r="D1428" s="3">
+        <v>1597545412</v>
+      </c>
+      <c r="E1428" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1428" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="G1428" s="3" t="s">
+        <v>4487</v>
+      </c>
+      <c r="H1428" s="3"/>
+      <c r="I1428" s="3">
+        <v>51</v>
+      </c>
+      <c r="J1428" s="3"/>
+      <c r="K1428" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1428" s="3"/>
+      <c r="M1428" s="3"/>
+      <c r="N1428" s="3"/>
+    </row>
+    <row r="1429" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1429" s="3" t="s">
+        <v>4488</v>
+      </c>
+      <c r="B1429" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="C1429" s="3">
+        <v>838</v>
+      </c>
+      <c r="D1429" s="3">
+        <v>1598180575</v>
+      </c>
+      <c r="E1429" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1429" s="3" t="s">
+        <v>4489</v>
+      </c>
+      <c r="G1429" s="3" t="s">
+        <v>4490</v>
+      </c>
+      <c r="H1429" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1429" s="3">
+        <v>65</v>
+      </c>
+      <c r="J1429" s="3">
+        <v>80</v>
+      </c>
+      <c r="K1429" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1429" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1429" s="3" t="s">
+        <v>4491</v>
+      </c>
+      <c r="N1429" s="3"/>
+    </row>
+    <row r="1430" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1430" s="3" t="s">
+        <v>4488</v>
+      </c>
+      <c r="B1430" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="C1430" s="3">
+        <v>838</v>
+      </c>
+      <c r="D1430" s="3">
+        <v>1598180540</v>
+      </c>
+      <c r="E1430" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1430" s="3" t="s">
+        <v>4492</v>
+      </c>
+      <c r="G1430" s="3" t="s">
+        <v>4493</v>
+      </c>
+      <c r="H1430" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1430" s="3">
+        <v>65</v>
+      </c>
+      <c r="J1430" s="3">
+        <v>80</v>
+      </c>
+      <c r="K1430" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1430" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1430" s="3" t="s">
+        <v>4494</v>
+      </c>
+      <c r="N1430" s="3"/>
+    </row>
+    <row r="1431" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1431" s="3" t="s">
+        <v>4495</v>
+      </c>
+      <c r="B1431" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C1431" s="3">
+        <v>731</v>
+      </c>
+      <c r="D1431" s="3">
+        <v>1598216446</v>
+      </c>
+      <c r="E1431" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1431" s="3" t="s">
+        <v>4496</v>
+      </c>
+      <c r="G1431" s="3" t="s">
+        <v>4497</v>
+      </c>
+      <c r="H1431" s="3"/>
+      <c r="I1431" s="3">
+        <v>57</v>
+      </c>
+      <c r="J1431" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1431" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1431" s="3"/>
+      <c r="M1431" s="3"/>
+      <c r="N1431" s="3"/>
+    </row>
+    <row r="1432" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1432" s="3" t="s">
+        <v>4498</v>
+      </c>
+      <c r="B1432" s="3"/>
+      <c r="C1432" s="3">
+        <v>673</v>
+      </c>
+      <c r="D1432" s="3">
+        <v>1599066062</v>
+      </c>
+      <c r="E1432" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1432" s="3" t="s">
+        <v>4499</v>
+      </c>
+      <c r="G1432" s="3" t="s">
+        <v>4500</v>
+      </c>
+      <c r="H1432" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1432" s="3">
+        <v>63</v>
+      </c>
+      <c r="J1432" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1432" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1432" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1432" s="3" t="s">
+        <v>4501</v>
+      </c>
+      <c r="N1432" s="3"/>
+    </row>
+    <row r="1433" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1433" s="3" t="s">
+        <v>4502</v>
+      </c>
+      <c r="B1433" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C1433" s="3">
+        <v>342</v>
+      </c>
+      <c r="D1433" s="3">
+        <v>1599262086</v>
+      </c>
+      <c r="E1433" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1433" s="3" t="s">
+        <v>4503</v>
+      </c>
+      <c r="G1433" s="3" t="s">
+        <v>4504</v>
+      </c>
+      <c r="H1433" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1433" s="3">
+        <v>75</v>
+      </c>
+      <c r="J1433" s="3">
+        <v>80</v>
+      </c>
+      <c r="K1433" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1433" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1433" s="3" t="s">
+        <v>4505</v>
+      </c>
+      <c r="N1433" s="3"/>
+    </row>
+    <row r="1434" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1434" s="3" t="s">
+        <v>4506</v>
+      </c>
+      <c r="B1434" s="3"/>
+      <c r="C1434" s="3">
+        <v>837</v>
+      </c>
+      <c r="D1434" s="3">
+        <v>1599336155</v>
+      </c>
+      <c r="E1434" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1434" s="3" t="s">
+        <v>4507</v>
+      </c>
+      <c r="G1434" s="3" t="s">
+        <v>4508</v>
+      </c>
+      <c r="H1434" s="3"/>
+      <c r="I1434" s="3">
+        <v>54</v>
+      </c>
+      <c r="J1434" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1434" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1434" s="3"/>
+      <c r="M1434" s="3"/>
+      <c r="N1434" s="3"/>
+    </row>
+    <row r="1435" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1435" s="3" t="s">
+        <v>4509</v>
+      </c>
+      <c r="B1435" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="C1435" s="3">
+        <v>63</v>
+      </c>
+      <c r="D1435" s="3">
+        <v>1599397050</v>
+      </c>
+      <c r="E1435" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1435" s="3" t="s">
+        <v>3180</v>
+      </c>
+      <c r="G1435" s="3" t="s">
+        <v>4510</v>
+      </c>
+      <c r="H1435" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1435" s="3">
+        <v>29</v>
+      </c>
+      <c r="J1435" s="3">
+        <v>35</v>
+      </c>
+      <c r="K1435" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1435" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1435" s="3" t="s">
+        <v>4505</v>
+      </c>
+      <c r="N1435" s="3"/>
+    </row>
+    <row r="1436" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1436" s="3" t="s">
+        <v>4511</v>
+      </c>
+      <c r="B1436" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C1436" s="3">
+        <v>672</v>
+      </c>
+      <c r="D1436" s="3">
+        <v>1599647891</v>
+      </c>
+      <c r="E1436" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1436" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="G1436" s="3" t="s">
+        <v>4512</v>
+      </c>
+      <c r="H1436" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1436" s="3">
+        <v>72</v>
+      </c>
+      <c r="J1436" s="3"/>
+      <c r="K1436" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1436" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1436" s="3" t="s">
+        <v>4513</v>
+      </c>
+      <c r="N1436" s="3"/>
+    </row>
+    <row r="1437" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1437" s="3" t="s">
+        <v>4514</v>
+      </c>
+      <c r="B1437" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C1437" s="3">
+        <v>731</v>
+      </c>
+      <c r="D1437" s="3">
+        <v>1600104555</v>
+      </c>
+      <c r="E1437" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1437" s="3" t="s">
+        <v>4515</v>
+      </c>
+      <c r="G1437" s="3" t="s">
+        <v>4516</v>
+      </c>
+      <c r="H1437" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1437" s="3">
+        <v>27</v>
+      </c>
+      <c r="J1437" s="3">
+        <v>55</v>
+      </c>
+      <c r="K1437" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1437" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1437" s="3" t="s">
+        <v>4513</v>
+      </c>
+      <c r="N1437" s="3"/>
+    </row>
+    <row r="1438" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1438" s="3" t="s">
+        <v>4517</v>
+      </c>
+      <c r="B1438" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1438" s="3">
+        <v>336</v>
+      </c>
+      <c r="D1438" s="3">
+        <v>1600162074</v>
+      </c>
+      <c r="E1438" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1438" s="3" t="s">
+        <v>4518</v>
+      </c>
+      <c r="G1438" s="3" t="s">
+        <v>4519</v>
+      </c>
+      <c r="H1438" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1438" s="3">
+        <v>65</v>
+      </c>
+      <c r="J1438" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1438" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1438" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1438" s="3" t="s">
+        <v>4513</v>
+      </c>
+      <c r="N1438" s="3"/>
+    </row>
+    <row r="1439" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1439" s="3" t="s">
+        <v>4520</v>
+      </c>
+      <c r="B1439" s="3"/>
+      <c r="C1439" s="3">
+        <v>673</v>
+      </c>
+      <c r="D1439" s="3">
+        <v>1600244081</v>
+      </c>
+      <c r="E1439" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1439" s="3" t="s">
+        <v>4521</v>
+      </c>
+      <c r="G1439" s="3" t="s">
+        <v>4522</v>
+      </c>
+      <c r="H1439" s="3"/>
+      <c r="I1439" s="3">
+        <v>65</v>
+      </c>
+      <c r="J1439" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1439" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1439" s="3"/>
+      <c r="M1439" s="3"/>
+      <c r="N1439" s="3"/>
+    </row>
+    <row r="1440" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1440" s="3" t="s">
+        <v>4523</v>
+      </c>
+      <c r="B1440" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1440" s="3">
+        <v>729</v>
+      </c>
+      <c r="D1440" s="3">
+        <v>1600326572</v>
+      </c>
+      <c r="E1440" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1440" s="3" t="s">
+        <v>4524</v>
+      </c>
+      <c r="G1440" s="3" t="s">
+        <v>4525</v>
+      </c>
+      <c r="H1440" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1440" s="3">
+        <v>68</v>
+      </c>
+      <c r="J1440" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1440" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1440" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1440" s="3" t="s">
+        <v>4526</v>
+      </c>
+      <c r="N1440" s="3"/>
+    </row>
+    <row r="1441" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1441" s="3" t="s">
+        <v>4527</v>
+      </c>
+      <c r="B1441" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1441" s="3">
+        <v>729</v>
+      </c>
+      <c r="D1441" s="3">
+        <v>1600404530</v>
+      </c>
+      <c r="E1441" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1441" s="3" t="s">
+        <v>4528</v>
+      </c>
+      <c r="G1441" s="3" t="s">
+        <v>4529</v>
+      </c>
+      <c r="H1441" s="3"/>
+      <c r="I1441" s="3">
+        <v>68</v>
+      </c>
+      <c r="J1441" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1441" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1441" s="3"/>
+      <c r="M1441" s="3"/>
+      <c r="N1441" s="3"/>
+    </row>
+    <row r="1442" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1442" s="3" t="s">
+        <v>4530</v>
+      </c>
+      <c r="B1442" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1442" s="3">
+        <v>210</v>
+      </c>
+      <c r="D1442" s="3">
+        <v>1600501488</v>
+      </c>
+      <c r="E1442" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1442" s="3" t="s">
+        <v>4531</v>
+      </c>
+      <c r="G1442" s="3" t="s">
+        <v>4532</v>
+      </c>
+      <c r="H1442" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1442" s="3">
+        <v>73</v>
+      </c>
+      <c r="J1442" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1442" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1442" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1442" s="3" t="s">
+        <v>4526</v>
+      </c>
+      <c r="N1442" s="3"/>
+    </row>
+    <row r="1443" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1443" s="3" t="s">
+        <v>4533</v>
+      </c>
+      <c r="B1443" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1443" s="3">
+        <v>210</v>
+      </c>
+      <c r="D1443" s="3">
+        <v>1600545427</v>
+      </c>
+      <c r="E1443" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1443" s="3" t="s">
+        <v>4534</v>
+      </c>
+      <c r="G1443" s="3" t="s">
+        <v>4535</v>
+      </c>
+      <c r="H1443" s="3"/>
+      <c r="I1443" s="3">
+        <v>70</v>
+      </c>
+      <c r="J1443" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1443" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1443" s="3"/>
+      <c r="M1443" s="3"/>
+      <c r="N1443" s="3"/>
+    </row>
+    <row r="1444" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1444" s="3" t="s">
+        <v>4536</v>
+      </c>
+      <c r="B1444" s="3"/>
+      <c r="C1444" s="3">
+        <v>339</v>
+      </c>
+      <c r="D1444" s="3">
+        <v>1600569818</v>
+      </c>
+      <c r="E1444" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1444" s="3" t="s">
+        <v>4537</v>
+      </c>
+      <c r="G1444" s="3" t="s">
+        <v>4538</v>
+      </c>
+      <c r="H1444" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1444" s="3">
+        <v>69</v>
+      </c>
+      <c r="J1444" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1444" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1444" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1444" s="3" t="s">
+        <v>4539</v>
+      </c>
+      <c r="N1444" s="3"/>
+    </row>
+    <row r="1445" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1445" s="3" t="s">
+        <v>4540</v>
+      </c>
+      <c r="B1445" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1445" s="3">
+        <v>839</v>
+      </c>
+      <c r="D1445" s="3">
+        <v>1601243245</v>
+      </c>
+      <c r="E1445" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1445" s="3" t="s">
+        <v>4541</v>
+      </c>
+      <c r="G1445" s="3" t="s">
+        <v>4542</v>
+      </c>
+      <c r="H1445" s="3"/>
+      <c r="I1445" s="3">
+        <v>64</v>
+      </c>
+      <c r="J1445" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1445" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1445" s="3"/>
+      <c r="M1445" s="3"/>
+      <c r="N1445" s="3"/>
+    </row>
+    <row r="1446" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1446" s="3" t="s">
+        <v>4543</v>
+      </c>
+      <c r="B1446" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1446" s="3">
+        <v>210</v>
+      </c>
+      <c r="D1446" s="3">
+        <v>1601492520</v>
+      </c>
+      <c r="E1446" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1446" s="3" t="s">
+        <v>4544</v>
+      </c>
+      <c r="G1446" s="3" t="s">
+        <v>4545</v>
+      </c>
+      <c r="H1446" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1446" s="3">
+        <v>34</v>
+      </c>
+      <c r="J1446" s="3"/>
+      <c r="K1446" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1446" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1446" s="3" t="s">
+        <v>4546</v>
+      </c>
+      <c r="N1446" s="3"/>
+    </row>
+    <row r="1447" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1447" s="3" t="s">
+        <v>4547</v>
+      </c>
+      <c r="B1447" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1447" s="3">
+        <v>208</v>
+      </c>
+      <c r="D1447" s="3">
+        <v>1601637282</v>
+      </c>
+      <c r="E1447" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1447" s="3" t="s">
+        <v>4548</v>
+      </c>
+      <c r="G1447" s="3" t="s">
+        <v>4549</v>
+      </c>
+      <c r="H1447" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1447" s="3">
+        <v>70</v>
+      </c>
+      <c r="J1447" s="3">
+        <v>80</v>
+      </c>
+      <c r="K1447" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1447" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1447" s="3" t="s">
+        <v>4550</v>
+      </c>
+      <c r="N1447" s="3"/>
+    </row>
+    <row r="1448" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1448" s="3" t="s">
+        <v>4547</v>
+      </c>
+      <c r="B1448" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1448" s="3">
+        <v>208</v>
+      </c>
+      <c r="D1448" s="3">
+        <v>1601637287</v>
+      </c>
+      <c r="E1448" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1448" s="3" t="s">
+        <v>4551</v>
+      </c>
+      <c r="G1448" s="3" t="s">
+        <v>4552</v>
+      </c>
+      <c r="H1448" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1448" s="3">
+        <v>75</v>
+      </c>
+      <c r="J1448" s="3">
+        <v>80</v>
+      </c>
+      <c r="K1448" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1448" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1448" s="3" t="s">
+        <v>4550</v>
+      </c>
+      <c r="N1448" s="3"/>
+    </row>
+    <row r="1449" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1449" s="3" t="s">
+        <v>4553</v>
+      </c>
+      <c r="B1449" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1449" s="3">
+        <v>208</v>
+      </c>
+      <c r="D1449" s="3">
+        <v>1601711104</v>
+      </c>
+      <c r="E1449" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1449" s="3" t="s">
+        <v>4554</v>
+      </c>
+      <c r="G1449" s="3" t="s">
+        <v>4555</v>
+      </c>
+      <c r="H1449" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1449" s="3">
+        <v>70</v>
+      </c>
+      <c r="J1449" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1449" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1449" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1449" s="3" t="s">
+        <v>4550</v>
+      </c>
+      <c r="N1449" s="3"/>
+    </row>
+    <row r="1450" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1450" s="3" t="s">
+        <v>4556</v>
+      </c>
+      <c r="B1450" s="3"/>
+      <c r="C1450" s="3">
+        <v>673</v>
+      </c>
+      <c r="D1450" s="3">
+        <v>1601759507</v>
+      </c>
+      <c r="E1450" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1450" s="3" t="s">
+        <v>4557</v>
+      </c>
+      <c r="G1450" s="3" t="s">
+        <v>4558</v>
+      </c>
+      <c r="H1450" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1450" s="3">
+        <v>62</v>
+      </c>
+      <c r="J1450" s="3"/>
+      <c r="K1450" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1450" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1450" s="3" t="s">
+        <v>4559</v>
+      </c>
+      <c r="N1450" s="3"/>
+    </row>
+    <row r="1451" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1451" s="3" t="s">
+        <v>4560</v>
+      </c>
+      <c r="B1451" s="3"/>
+      <c r="C1451" s="3">
+        <v>209</v>
+      </c>
+      <c r="D1451" s="3">
+        <v>1601767417</v>
+      </c>
+      <c r="E1451" s="3" t="s">
+        <v>867</v>
+      </c>
+      <c r="F1451" s="3" t="s">
+        <v>4561</v>
+      </c>
+      <c r="G1451" s="3" t="s">
+        <v>4562</v>
+      </c>
+      <c r="H1451" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1451" s="3">
+        <v>43</v>
+      </c>
+      <c r="J1451" s="3"/>
+      <c r="K1451" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1451" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1451" s="3" t="s">
+        <v>4563</v>
+      </c>
+      <c r="N1451" s="3"/>
+    </row>
+    <row r="1452" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1452" s="3" t="s">
+        <v>4564</v>
+      </c>
+      <c r="B1452" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1452" s="3">
+        <v>208</v>
+      </c>
+      <c r="D1452" s="3">
+        <v>1602284173</v>
+      </c>
+      <c r="E1452" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1452" s="3" t="s">
+        <v>4565</v>
+      </c>
+      <c r="G1452" s="3" t="s">
+        <v>4566</v>
+      </c>
+      <c r="H1452" s="3"/>
+      <c r="I1452" s="3">
+        <v>53</v>
+      </c>
+      <c r="J1452" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1452" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1452" s="3"/>
+      <c r="M1452" s="3"/>
+      <c r="N1452" s="3"/>
+    </row>
+    <row r="1453" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1453" s="3" t="s">
+        <v>4564</v>
+      </c>
+      <c r="B1453" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1453" s="3">
+        <v>208</v>
+      </c>
+      <c r="D1453" s="3">
+        <v>1602284167</v>
+      </c>
+      <c r="E1453" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1453" s="3" t="s">
+        <v>4565</v>
+      </c>
+      <c r="G1453" s="3" t="s">
+        <v>4567</v>
+      </c>
+      <c r="H1453" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1453" s="3">
+        <v>54</v>
+      </c>
+      <c r="J1453" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1453" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1453" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1453" s="3" t="s">
+        <v>4568</v>
+      </c>
+      <c r="N1453" s="3"/>
+    </row>
+    <row r="1454" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1454" s="3" t="s">
+        <v>4569</v>
+      </c>
+      <c r="B1454" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C1454" s="3">
+        <v>342</v>
+      </c>
+      <c r="D1454" s="3">
+        <v>1602373292</v>
+      </c>
+      <c r="E1454" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1454" s="3" t="s">
+        <v>3803</v>
+      </c>
+      <c r="G1454" s="3" t="s">
+        <v>4570</v>
+      </c>
+      <c r="H1454" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1454" s="3">
+        <v>66</v>
+      </c>
+      <c r="J1454" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1454" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1454" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1454" s="3" t="s">
+        <v>4571</v>
+      </c>
+      <c r="N1454" s="3"/>
+    </row>
+    <row r="1455" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1455" s="3" t="s">
+        <v>4572</v>
+      </c>
+      <c r="B1455" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="C1455" s="3">
+        <v>838</v>
+      </c>
+      <c r="D1455" s="3">
+        <v>1602665849</v>
+      </c>
+      <c r="E1455" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1455" s="3" t="s">
+        <v>4573</v>
+      </c>
+      <c r="G1455" s="3" t="s">
+        <v>4574</v>
+      </c>
+      <c r="H1455" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1455" s="3">
+        <v>53</v>
+      </c>
+      <c r="J1455" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1455" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1455" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1455" s="3" t="s">
+        <v>4571</v>
+      </c>
+      <c r="N1455" s="3"/>
+    </row>
+    <row r="1456" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1456" s="3" t="s">
+        <v>4575</v>
+      </c>
+      <c r="B1456" s="3"/>
+      <c r="C1456" s="3">
+        <v>673</v>
+      </c>
+      <c r="D1456" s="3">
+        <v>1602803552</v>
+      </c>
+      <c r="E1456" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1456" s="3" t="s">
+        <v>4576</v>
+      </c>
+      <c r="G1456" s="3" t="s">
+        <v>4577</v>
+      </c>
+      <c r="H1456" s="3"/>
+      <c r="I1456" s="3">
+        <v>51</v>
+      </c>
+      <c r="J1456" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1456" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1456" s="3"/>
+      <c r="M1456" s="3"/>
+      <c r="N1456" s="3"/>
+    </row>
+    <row r="1457" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1457" s="3" t="s">
+        <v>4578</v>
+      </c>
+      <c r="B1457" s="3"/>
+      <c r="C1457" s="3">
+        <v>339</v>
+      </c>
+      <c r="D1457" s="3">
+        <v>1603485633</v>
+      </c>
+      <c r="E1457" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1457" s="3" t="s">
+        <v>4579</v>
+      </c>
+      <c r="G1457" s="3" t="s">
+        <v>4580</v>
+      </c>
+      <c r="H1457" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1457" s="3">
+        <v>50</v>
+      </c>
+      <c r="J1457" s="3">
+        <v>55</v>
+      </c>
+      <c r="K1457" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1457" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1457" s="3" t="s">
+        <v>4581</v>
+      </c>
+      <c r="N1457" s="3"/>
+    </row>
+    <row r="1458" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1458" s="3" t="s">
+        <v>4582</v>
+      </c>
+      <c r="B1458" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1458" s="3">
+        <v>208</v>
+      </c>
+      <c r="D1458" s="3">
+        <v>1604123282</v>
+      </c>
+      <c r="E1458" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1458" s="3" t="s">
+        <v>4583</v>
+      </c>
+      <c r="G1458" s="3" t="s">
+        <v>4584</v>
+      </c>
+      <c r="H1458" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1458" s="3">
+        <v>66</v>
+      </c>
+      <c r="J1458" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1458" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1458" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1458" s="3" t="s">
+        <v>4585</v>
+      </c>
+      <c r="N1458" s="3"/>
+    </row>
+    <row r="1459" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1459" s="3" t="s">
+        <v>4586</v>
+      </c>
+      <c r="B1459" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C1459" s="3">
+        <v>342</v>
+      </c>
+      <c r="D1459" s="3">
+        <v>1604144411</v>
+      </c>
+      <c r="E1459" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1459" s="3" t="s">
+        <v>4587</v>
+      </c>
+      <c r="G1459" s="3" t="s">
+        <v>4588</v>
+      </c>
+      <c r="H1459" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1459" s="3">
+        <v>73</v>
+      </c>
+      <c r="J1459" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1459" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1459" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1459" s="3" t="s">
+        <v>4585</v>
+      </c>
+      <c r="N1459" s="3"/>
+    </row>
+    <row r="1460" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1460" s="3" t="s">
+        <v>4589</v>
+      </c>
+      <c r="B1460" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1460" s="3">
+        <v>208</v>
+      </c>
+      <c r="D1460" s="3">
+        <v>1604399527</v>
+      </c>
+      <c r="E1460" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1460" s="3" t="s">
+        <v>4590</v>
+      </c>
+      <c r="G1460" s="3" t="s">
+        <v>4591</v>
+      </c>
+      <c r="H1460" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1460" s="3">
+        <v>66</v>
+      </c>
+      <c r="J1460" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1460" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1460" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1460" s="3" t="s">
+        <v>4592</v>
+      </c>
+      <c r="N1460" s="3"/>
+    </row>
+    <row r="1461" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1461" s="3" t="s">
+        <v>4593</v>
+      </c>
+      <c r="B1461" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1461" s="3">
+        <v>208</v>
+      </c>
+      <c r="D1461" s="3">
+        <v>1604705003</v>
+      </c>
+      <c r="E1461" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1461" s="3" t="s">
+        <v>4594</v>
+      </c>
+      <c r="G1461" s="3" t="s">
+        <v>4595</v>
+      </c>
+      <c r="H1461" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1461" s="3">
+        <v>67</v>
+      </c>
+      <c r="J1461" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1461" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1461" s="3"/>
+      <c r="M1461" s="3"/>
+      <c r="N1461" s="3"/>
+    </row>
+    <row r="1462" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1462" s="3" t="s">
+        <v>4596</v>
+      </c>
+      <c r="B1462" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1462" s="3">
+        <v>208</v>
+      </c>
+      <c r="D1462" s="3">
+        <v>1604704991</v>
+      </c>
+      <c r="E1462" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1462" s="3" t="s">
+        <v>4594</v>
+      </c>
+      <c r="G1462" s="3" t="s">
+        <v>4597</v>
+      </c>
+      <c r="H1462" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1462" s="3">
+        <v>66</v>
+      </c>
+      <c r="J1462" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1462" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1462" s="3"/>
+      <c r="M1462" s="3"/>
+      <c r="N1462" s="3"/>
+    </row>
+    <row r="1463" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1463" s="3" t="s">
+        <v>4598</v>
+      </c>
+      <c r="B1463" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C1463" s="3">
+        <v>342</v>
+      </c>
+      <c r="D1463" s="3">
+        <v>1604709323</v>
+      </c>
+      <c r="E1463" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1463" s="3" t="s">
+        <v>1469</v>
+      </c>
+      <c r="G1463" s="3" t="s">
+        <v>4599</v>
+      </c>
+      <c r="H1463" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1463" s="3">
+        <v>73</v>
+      </c>
+      <c r="J1463" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1463" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1463" s="3"/>
+      <c r="M1463" s="3"/>
+      <c r="N1463" s="3"/>
+    </row>
+    <row r="1464" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1464" s="3" t="s">
+        <v>4600</v>
+      </c>
+      <c r="B1464" s="3"/>
+      <c r="C1464" s="3">
+        <v>459</v>
+      </c>
+      <c r="D1464" s="3">
+        <v>1604914847</v>
+      </c>
+      <c r="E1464" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1464" s="3" t="s">
+        <v>3625</v>
+      </c>
+      <c r="G1464" s="3" t="s">
+        <v>4601</v>
+      </c>
+      <c r="H1464" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1464" s="3">
+        <v>69</v>
+      </c>
+      <c r="J1464" s="3"/>
+      <c r="K1464" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1464" s="3"/>
+      <c r="M1464" s="3"/>
+      <c r="N1464" s="3"/>
+    </row>
+    <row r="1465" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1465" s="3" t="s">
+        <v>4602</v>
+      </c>
+      <c r="B1465" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1465" s="3">
+        <v>208</v>
+      </c>
+      <c r="D1465" s="3">
+        <v>1605040230</v>
+      </c>
+      <c r="E1465" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1465" s="3" t="s">
+        <v>4603</v>
+      </c>
+      <c r="G1465" s="3" t="s">
+        <v>4604</v>
+      </c>
+      <c r="H1465" s="3"/>
+      <c r="I1465" s="3">
+        <v>57</v>
+      </c>
+      <c r="J1465" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1465" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1465" s="3"/>
+      <c r="M1465" s="3"/>
+      <c r="N1465" s="3"/>
+    </row>
+    <row r="1466" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1466" s="3" t="s">
+        <v>4605</v>
+      </c>
+      <c r="B1466" s="3"/>
+      <c r="C1466" s="3">
+        <v>209</v>
+      </c>
+      <c r="D1466" s="3">
+        <v>1605343325</v>
+      </c>
+      <c r="E1466" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1466" s="3" t="s">
+        <v>4606</v>
+      </c>
+      <c r="G1466" s="3" t="s">
+        <v>4607</v>
+      </c>
+      <c r="H1466" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1466" s="3">
+        <v>71</v>
+      </c>
+      <c r="J1466" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1466" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1466" s="3"/>
+      <c r="M1466" s="3"/>
+      <c r="N1466" s="3"/>
+    </row>
+    <row r="1467" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1467" s="3" t="s">
+        <v>4608</v>
+      </c>
+      <c r="B1467" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1467" s="3">
+        <v>208</v>
+      </c>
+      <c r="D1467" s="3">
+        <v>1605794943</v>
+      </c>
+      <c r="E1467" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1467" s="3" t="s">
+        <v>832</v>
+      </c>
+      <c r="G1467" s="3" t="s">
+        <v>4609</v>
+      </c>
+      <c r="H1467" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1467" s="3">
+        <v>68</v>
+      </c>
+      <c r="J1467" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1467" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1467" s="3"/>
+      <c r="M1467" s="3"/>
+      <c r="N1467" s="3"/>
+    </row>
+    <row r="1468" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1468" s="3" t="s">
+        <v>4608</v>
+      </c>
+      <c r="B1468" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1468" s="3">
+        <v>208</v>
+      </c>
+      <c r="D1468" s="3">
+        <v>1605794941</v>
+      </c>
+      <c r="E1468" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1468" s="3" t="s">
+        <v>2979</v>
+      </c>
+      <c r="G1468" s="3" t="s">
+        <v>4610</v>
+      </c>
+      <c r="H1468" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1468" s="3">
+        <v>68</v>
+      </c>
+      <c r="J1468" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1468" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1468" s="3"/>
+      <c r="M1468" s="3"/>
+      <c r="N1468" s="3"/>
+    </row>
+    <row r="1469" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1469" s="3" t="s">
+        <v>4611</v>
+      </c>
+      <c r="B1469" s="3"/>
+      <c r="C1469" s="3">
+        <v>837</v>
+      </c>
+      <c r="D1469" s="3">
+        <v>1605807303</v>
+      </c>
+      <c r="E1469" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1469" s="3" t="s">
+        <v>4612</v>
+      </c>
+      <c r="G1469" s="3" t="s">
+        <v>4613</v>
+      </c>
+      <c r="H1469" s="3"/>
+      <c r="I1469" s="3">
+        <v>62</v>
+      </c>
+      <c r="J1469" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1469" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1469" s="3"/>
+      <c r="M1469" s="3"/>
+      <c r="N1469" s="3"/>
+    </row>
+    <row r="1470" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1470" s="3" t="s">
+        <v>4614</v>
+      </c>
+      <c r="B1470" s="3"/>
+      <c r="C1470" s="3">
+        <v>209</v>
+      </c>
+      <c r="D1470" s="3">
+        <v>1606064974</v>
+      </c>
+      <c r="E1470" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1470" s="3" t="s">
+        <v>4615</v>
+      </c>
+      <c r="G1470" s="3" t="s">
+        <v>4616</v>
+      </c>
+      <c r="H1470" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1470" s="3">
+        <v>70</v>
+      </c>
+      <c r="J1470" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1470" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1470" s="3"/>
+      <c r="M1470" s="3"/>
+      <c r="N1470" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\PCS-Trucking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4B607618-D22A-4DF3-A986-3544A3F1B0C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8F5C79CF-87D3-4D03-921B-8641C9782C6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,12 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10997" uniqueCount="4617">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11222" uniqueCount="4704">
   <si>
     <t>DRIVE ALERTS</t>
   </si>
   <si>
-    <t>Period: 01/01/26 00:00 EST - 12/31/26 23:59 EST</t>
+    <t>Period: 01/01/26 02:00 EST - 01/01/27 23:59 EST</t>
   </si>
   <si>
     <t>Datetime</t>
@@ -13810,12 +13810,18 @@
     <t>34.223295, -117.410310</t>
   </si>
   <si>
+    <t>08/24/26 10:11 EDT</t>
+  </si>
+  <si>
     <t>08/21/26 08:35 EDT</t>
   </si>
   <si>
     <t>34.222583, -117.410233</t>
   </si>
   <si>
+    <t>08/24/26 10:12 EDT</t>
+  </si>
+  <si>
     <t>08/21/26 08:39 EDT</t>
   </si>
   <si>
@@ -13828,6 +13834,9 @@
     <t>40.371033, -111.802371</t>
   </si>
   <si>
+    <t>08/24/26 10:13 EDT</t>
+  </si>
+  <si>
     <t>08/21/26 14:09 EDT</t>
   </si>
   <si>
@@ -13846,6 +13855,9 @@
     <t>41.270726, -110.826477</t>
   </si>
   <si>
+    <t>08/24/26 10:14 EDT</t>
+  </si>
+  <si>
     <t>08/23/26 00:24 EDT</t>
   </si>
   <si>
@@ -13871,6 +13883,255 @@
   </si>
   <si>
     <t>36.251343, -115.088480</t>
+  </si>
+  <si>
+    <t>08/24/26 18:10 EDT</t>
+  </si>
+  <si>
+    <t>35.514796, -115.432494</t>
+  </si>
+  <si>
+    <t>08/24/26 18:28 EDT</t>
+  </si>
+  <si>
+    <t>08/24/26 19:20 EDT</t>
+  </si>
+  <si>
+    <t>3mi SW of Winchester NV</t>
+  </si>
+  <si>
+    <t>36.111976, -115.180557</t>
+  </si>
+  <si>
+    <t>08/25/26 08:18 EDT</t>
+  </si>
+  <si>
+    <t>08/24/26 21:12 EDT</t>
+  </si>
+  <si>
+    <t>17.1mi S of Twin Falls ID</t>
+  </si>
+  <si>
+    <t>42.332405, -114.574842</t>
+  </si>
+  <si>
+    <t>08/25/26 08:19 EDT</t>
+  </si>
+  <si>
+    <t>08/24/26 21:40 EDT</t>
+  </si>
+  <si>
+    <t>2.9mi SW of Orem UT</t>
+  </si>
+  <si>
+    <t>40.260833, -111.722742</t>
+  </si>
+  <si>
+    <t>08/25/26 10:04 EDT</t>
+  </si>
+  <si>
+    <t>69.9mi SE of Spring Creek NV</t>
+  </si>
+  <si>
+    <t>40.065473, -114.614102</t>
+  </si>
+  <si>
+    <t>08/25/26 16:03 EDT</t>
+  </si>
+  <si>
+    <t>08/25/26 13:39 EDT</t>
+  </si>
+  <si>
+    <t>2.1mi SE of Upland CA</t>
+  </si>
+  <si>
+    <t>34.103925, -117.628533</t>
+  </si>
+  <si>
+    <t>08/25/26 16:20 EDT</t>
+  </si>
+  <si>
+    <t>15.5mi SE of Colby KS</t>
+  </si>
+  <si>
+    <t>39.199620, -100.880582</t>
+  </si>
+  <si>
+    <t>08/25/26 17:20 EDT</t>
+  </si>
+  <si>
+    <t>39.3mi E of Edgewood NM</t>
+  </si>
+  <si>
+    <t>35.005940, -105.537116</t>
+  </si>
+  <si>
+    <t>08/26/26 07:38 EDT</t>
+  </si>
+  <si>
+    <t>08/25/26 17:32 EDT</t>
+  </si>
+  <si>
+    <t>19.9mi SE of Fort Irwin CA</t>
+  </si>
+  <si>
+    <t>35.079376, -116.397514</t>
+  </si>
+  <si>
+    <t>08/26/26 12:35 EDT</t>
+  </si>
+  <si>
+    <t>40.706208, -111.903520</t>
+  </si>
+  <si>
+    <t>08/26/26 22:01 EDT</t>
+  </si>
+  <si>
+    <t>08/26/26 19:16 EDT</t>
+  </si>
+  <si>
+    <t>14.1mi NE of Mesquite NV</t>
+  </si>
+  <si>
+    <t>36.897877, -113.907821</t>
+  </si>
+  <si>
+    <t>08/26/26 22:21 EDT</t>
+  </si>
+  <si>
+    <t>1.4mi SW of Azusa CA</t>
+  </si>
+  <si>
+    <t>34.129752, -117.934636</t>
+  </si>
+  <si>
+    <t>08/27/26 12:42 EDT</t>
+  </si>
+  <si>
+    <t>61.3mi W of Guymon OK</t>
+  </si>
+  <si>
+    <t>36.980645, -102.523966</t>
+  </si>
+  <si>
+    <t>08/28/26 09:37 EDT</t>
+  </si>
+  <si>
+    <t>08/27/26 12:47 EDT</t>
+  </si>
+  <si>
+    <t>64.3mi W of Guymon OK</t>
+  </si>
+  <si>
+    <t>37.050750, -102.549580</t>
+  </si>
+  <si>
+    <t>08/28/26 09:38 EDT</t>
+  </si>
+  <si>
+    <t>08/27/26 15:03 EDT</t>
+  </si>
+  <si>
+    <t>2.6mi NW of Burbank CA</t>
+  </si>
+  <si>
+    <t>34.216232, -118.353068</t>
+  </si>
+  <si>
+    <t>08/31/26 07:53 EDT</t>
+  </si>
+  <si>
+    <t>08/27/26 16:33 EDT</t>
+  </si>
+  <si>
+    <t>2mi NW of Springville UT</t>
+  </si>
+  <si>
+    <t>40.184462, -111.646710</t>
+  </si>
+  <si>
+    <t>08/28/26 11:10 EDT</t>
+  </si>
+  <si>
+    <t>10.9mi W of Cheyenne WY</t>
+  </si>
+  <si>
+    <t>41.106086, -104.996261</t>
+  </si>
+  <si>
+    <t>08/31/26 07:54 EDT</t>
+  </si>
+  <si>
+    <t>08/28/26 13:30 EDT</t>
+  </si>
+  <si>
+    <t>1.7mi SW of Pleasant Grove UT</t>
+  </si>
+  <si>
+    <t>40.350842, -111.757599</t>
+  </si>
+  <si>
+    <t>08/28/26 14:58 EDT</t>
+  </si>
+  <si>
+    <t>2.3mi NW of Denver CO</t>
+  </si>
+  <si>
+    <t>39.787989, -104.904248</t>
+  </si>
+  <si>
+    <t>08/28/26 16:23 EDT</t>
+  </si>
+  <si>
+    <t>1.5mi W of American Fork UT</t>
+  </si>
+  <si>
+    <t>40.379446, -111.823612</t>
+  </si>
+  <si>
+    <t>1.4mi W of American Fork UT</t>
+  </si>
+  <si>
+    <t>40.378113, -111.821356</t>
+  </si>
+  <si>
+    <t>08/28/26 16:34 EDT</t>
+  </si>
+  <si>
+    <t>40.242905, -111.694188</t>
+  </si>
+  <si>
+    <t>08/29/26 09:25 EDT</t>
+  </si>
+  <si>
+    <t>18.1mi SW of Nephi UT</t>
+  </si>
+  <si>
+    <t>39.474310, -111.988708</t>
+  </si>
+  <si>
+    <t>08/31/26 07:55 EDT</t>
+  </si>
+  <si>
+    <t>08/30/26 18:15 EDT</t>
+  </si>
+  <si>
+    <t>17.7mi SW of Cedar City UT</t>
+  </si>
+  <si>
+    <t>37.449796, -113.229621</t>
+  </si>
+  <si>
+    <t>17.8mi SW of Cedar City UT</t>
+  </si>
+  <si>
+    <t>37.449280, -113.229763</t>
+  </si>
+  <si>
+    <t>08/30/26 18:59 EDT</t>
+  </si>
+  <si>
+    <t>36.950970, -113.801678</t>
   </si>
 </sst>
 </file>
@@ -14232,7 +14493,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N1470"/>
+  <dimension ref="A1:N1496"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="14" width="15" customWidth="1"/>
@@ -69888,15 +70149,19 @@
         <v>70</v>
       </c>
       <c r="K1461" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1461" s="3"/>
-      <c r="M1461" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L1461" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1461" s="3" t="s">
+        <v>4596</v>
+      </c>
       <c r="N1461" s="3"/>
     </row>
     <row r="1462" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1462" s="3" t="s">
-        <v>4596</v>
+        <v>4597</v>
       </c>
       <c r="B1462" s="3" t="s">
         <v>74</v>
@@ -69914,10 +70179,10 @@
         <v>4594</v>
       </c>
       <c r="G1462" s="3" t="s">
-        <v>4597</v>
+        <v>4598</v>
       </c>
       <c r="H1462" s="3" t="s">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="I1462" s="3">
         <v>66</v>
@@ -69926,15 +70191,19 @@
         <v>70</v>
       </c>
       <c r="K1462" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1462" s="3"/>
-      <c r="M1462" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L1462" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1462" s="3" t="s">
+        <v>4599</v>
+      </c>
       <c r="N1462" s="3"/>
     </row>
     <row r="1463" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1463" s="3" t="s">
-        <v>4598</v>
+        <v>4600</v>
       </c>
       <c r="B1463" s="3" t="s">
         <v>113</v>
@@ -69952,7 +70221,7 @@
         <v>1469</v>
       </c>
       <c r="G1463" s="3" t="s">
-        <v>4599</v>
+        <v>4601</v>
       </c>
       <c r="H1463" s="3" t="s">
         <v>98</v>
@@ -69964,15 +70233,19 @@
         <v>70</v>
       </c>
       <c r="K1463" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1463" s="3"/>
-      <c r="M1463" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L1463" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1463" s="3" t="s">
+        <v>4599</v>
+      </c>
       <c r="N1463" s="3"/>
     </row>
     <row r="1464" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1464" s="3" t="s">
-        <v>4600</v>
+        <v>4602</v>
       </c>
       <c r="B1464" s="3"/>
       <c r="C1464" s="3">
@@ -69988,25 +70261,29 @@
         <v>3625</v>
       </c>
       <c r="G1464" s="3" t="s">
-        <v>4601</v>
+        <v>4603</v>
       </c>
       <c r="H1464" s="3" t="s">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="I1464" s="3">
         <v>69</v>
       </c>
       <c r="J1464" s="3"/>
       <c r="K1464" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1464" s="3"/>
-      <c r="M1464" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L1464" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1464" s="3" t="s">
+        <v>4604</v>
+      </c>
       <c r="N1464" s="3"/>
     </row>
     <row r="1465" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1465" s="3" t="s">
-        <v>4602</v>
+        <v>4605</v>
       </c>
       <c r="B1465" s="3" t="s">
         <v>74</v>
@@ -70021,10 +70298,10 @@
         <v>47</v>
       </c>
       <c r="F1465" s="3" t="s">
-        <v>4603</v>
+        <v>4606</v>
       </c>
       <c r="G1465" s="3" t="s">
-        <v>4604</v>
+        <v>4607</v>
       </c>
       <c r="H1465" s="3"/>
       <c r="I1465" s="3">
@@ -70042,7 +70319,7 @@
     </row>
     <row r="1466" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1466" s="3" t="s">
-        <v>4605</v>
+        <v>4608</v>
       </c>
       <c r="B1466" s="3"/>
       <c r="C1466" s="3">
@@ -70055,10 +70332,10 @@
         <v>47</v>
       </c>
       <c r="F1466" s="3" t="s">
-        <v>4606</v>
+        <v>4609</v>
       </c>
       <c r="G1466" s="3" t="s">
-        <v>4607</v>
+        <v>4610</v>
       </c>
       <c r="H1466" s="3" t="s">
         <v>98</v>
@@ -70070,15 +70347,19 @@
         <v>75</v>
       </c>
       <c r="K1466" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1466" s="3"/>
-      <c r="M1466" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L1466" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1466" s="3" t="s">
+        <v>4611</v>
+      </c>
       <c r="N1466" s="3"/>
     </row>
     <row r="1467" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1467" s="3" t="s">
-        <v>4608</v>
+        <v>4612</v>
       </c>
       <c r="B1467" s="3" t="s">
         <v>74</v>
@@ -70096,10 +70377,10 @@
         <v>832</v>
       </c>
       <c r="G1467" s="3" t="s">
-        <v>4609</v>
+        <v>4613</v>
       </c>
       <c r="H1467" s="3" t="s">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="I1467" s="3">
         <v>68</v>
@@ -70108,15 +70389,19 @@
         <v>65</v>
       </c>
       <c r="K1467" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1467" s="3"/>
-      <c r="M1467" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L1467" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1467" s="3" t="s">
+        <v>4611</v>
+      </c>
       <c r="N1467" s="3"/>
     </row>
     <row r="1468" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1468" s="3" t="s">
-        <v>4608</v>
+        <v>4612</v>
       </c>
       <c r="B1468" s="3" t="s">
         <v>74</v>
@@ -70134,10 +70419,10 @@
         <v>2979</v>
       </c>
       <c r="G1468" s="3" t="s">
-        <v>4610</v>
+        <v>4614</v>
       </c>
       <c r="H1468" s="3" t="s">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="I1468" s="3">
         <v>68</v>
@@ -70146,15 +70431,19 @@
         <v>65</v>
       </c>
       <c r="K1468" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1468" s="3"/>
-      <c r="M1468" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L1468" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1468" s="3" t="s">
+        <v>4611</v>
+      </c>
       <c r="N1468" s="3"/>
     </row>
     <row r="1469" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1469" s="3" t="s">
-        <v>4611</v>
+        <v>4615</v>
       </c>
       <c r="B1469" s="3"/>
       <c r="C1469" s="3">
@@ -70167,10 +70456,10 @@
         <v>18</v>
       </c>
       <c r="F1469" s="3" t="s">
-        <v>4612</v>
+        <v>4616</v>
       </c>
       <c r="G1469" s="3" t="s">
-        <v>4613</v>
+        <v>4617</v>
       </c>
       <c r="H1469" s="3"/>
       <c r="I1469" s="3">
@@ -70188,7 +70477,7 @@
     </row>
     <row r="1470" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1470" s="3" t="s">
-        <v>4614</v>
+        <v>4618</v>
       </c>
       <c r="B1470" s="3"/>
       <c r="C1470" s="3">
@@ -70201,13 +70490,13 @@
         <v>47</v>
       </c>
       <c r="F1470" s="3" t="s">
-        <v>4615</v>
+        <v>4619</v>
       </c>
       <c r="G1470" s="3" t="s">
-        <v>4616</v>
+        <v>4620</v>
       </c>
       <c r="H1470" s="3" t="s">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="I1470" s="3">
         <v>70</v>
@@ -70216,11 +70505,1045 @@
         <v>65</v>
       </c>
       <c r="K1470" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1470" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1470" s="3" t="s">
+        <v>4611</v>
+      </c>
+      <c r="N1470" s="3"/>
+    </row>
+    <row r="1471" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1471" s="3" t="s">
+        <v>4621</v>
+      </c>
+      <c r="B1471" s="3"/>
+      <c r="C1471" s="3">
+        <v>840</v>
+      </c>
+      <c r="D1471" s="3">
+        <v>1606783439</v>
+      </c>
+      <c r="E1471" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1471" s="3" t="s">
+        <v>3180</v>
+      </c>
+      <c r="G1471" s="3" t="s">
+        <v>4622</v>
+      </c>
+      <c r="H1471" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1471" s="3">
+        <v>20</v>
+      </c>
+      <c r="J1471" s="3">
+        <v>35</v>
+      </c>
+      <c r="K1471" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1471" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1471" s="3" t="s">
+        <v>4623</v>
+      </c>
+      <c r="N1471" s="3"/>
+    </row>
+    <row r="1472" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1472" s="3" t="s">
+        <v>4624</v>
+      </c>
+      <c r="B1472" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="C1472" s="3">
+        <v>63</v>
+      </c>
+      <c r="D1472" s="3">
+        <v>1606828928</v>
+      </c>
+      <c r="E1472" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1472" s="3" t="s">
+        <v>4625</v>
+      </c>
+      <c r="G1472" s="3" t="s">
+        <v>4626</v>
+      </c>
+      <c r="H1472" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1472" s="3">
+        <v>55</v>
+      </c>
+      <c r="J1472" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1472" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1472" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1472" s="3" t="s">
+        <v>4627</v>
+      </c>
+      <c r="N1472" s="3"/>
+    </row>
+    <row r="1473" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1473" s="3" t="s">
+        <v>4628</v>
+      </c>
+      <c r="B1473" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1473" s="3">
+        <v>208</v>
+      </c>
+      <c r="D1473" s="3">
+        <v>1606885421</v>
+      </c>
+      <c r="E1473" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1473" s="3" t="s">
+        <v>4629</v>
+      </c>
+      <c r="G1473" s="3" t="s">
+        <v>4630</v>
+      </c>
+      <c r="H1473" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1473" s="3">
+        <v>56</v>
+      </c>
+      <c r="J1473" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1473" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1473" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1473" s="3" t="s">
+        <v>4631</v>
+      </c>
+      <c r="N1473" s="3"/>
+    </row>
+    <row r="1474" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1474" s="3" t="s">
+        <v>4632</v>
+      </c>
+      <c r="B1474" s="3"/>
+      <c r="C1474" s="3">
+        <v>673</v>
+      </c>
+      <c r="D1474" s="3">
+        <v>1606894751</v>
+      </c>
+      <c r="E1474" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1474" s="3" t="s">
+        <v>4633</v>
+      </c>
+      <c r="G1474" s="3" t="s">
+        <v>4634</v>
+      </c>
+      <c r="H1474" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1474" s="3">
+        <v>27</v>
+      </c>
+      <c r="J1474" s="3"/>
+      <c r="K1474" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1474" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1474" s="3" t="s">
+        <v>4631</v>
+      </c>
+      <c r="N1474" s="3"/>
+    </row>
+    <row r="1475" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1475" s="3" t="s">
+        <v>4635</v>
+      </c>
+      <c r="B1475" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1475" s="3">
+        <v>208</v>
+      </c>
+      <c r="D1475" s="3">
+        <v>1607198594</v>
+      </c>
+      <c r="E1475" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1475" s="3" t="s">
+        <v>4636</v>
+      </c>
+      <c r="G1475" s="3" t="s">
+        <v>4637</v>
+      </c>
+      <c r="H1475" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1475" s="3">
         <v>21</v>
       </c>
-      <c r="L1470" s="3"/>
-      <c r="M1470" s="3"/>
-      <c r="N1470" s="3"/>
+      <c r="J1475" s="3"/>
+      <c r="K1475" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1475" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1475" s="3" t="s">
+        <v>4638</v>
+      </c>
+      <c r="N1475" s="3"/>
+    </row>
+    <row r="1476" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1476" s="3" t="s">
+        <v>4639</v>
+      </c>
+      <c r="B1476" s="3"/>
+      <c r="C1476" s="3">
+        <v>339</v>
+      </c>
+      <c r="D1476" s="3">
+        <v>1607426625</v>
+      </c>
+      <c r="E1476" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1476" s="3" t="s">
+        <v>4640</v>
+      </c>
+      <c r="G1476" s="3" t="s">
+        <v>4641</v>
+      </c>
+      <c r="H1476" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1476" s="3">
+        <v>31</v>
+      </c>
+      <c r="J1476" s="3"/>
+      <c r="K1476" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1476" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1476" s="3" t="s">
+        <v>4638</v>
+      </c>
+      <c r="N1476" s="3"/>
+    </row>
+    <row r="1477" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1477" s="3" t="s">
+        <v>4642</v>
+      </c>
+      <c r="B1477" s="3"/>
+      <c r="C1477" s="3">
+        <v>837</v>
+      </c>
+      <c r="D1477" s="3">
+        <v>1607599408</v>
+      </c>
+      <c r="E1477" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1477" s="3" t="s">
+        <v>4643</v>
+      </c>
+      <c r="G1477" s="3" t="s">
+        <v>4644</v>
+      </c>
+      <c r="H1477" s="3"/>
+      <c r="I1477" s="3">
+        <v>73</v>
+      </c>
+      <c r="J1477" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1477" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1477" s="3"/>
+      <c r="M1477" s="3"/>
+      <c r="N1477" s="3"/>
+    </row>
+    <row r="1478" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1478" s="3" t="s">
+        <v>4645</v>
+      </c>
+      <c r="B1478" s="3"/>
+      <c r="C1478" s="3">
+        <v>459</v>
+      </c>
+      <c r="D1478" s="3">
+        <v>1607656610</v>
+      </c>
+      <c r="E1478" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1478" s="3" t="s">
+        <v>4646</v>
+      </c>
+      <c r="G1478" s="3" t="s">
+        <v>4647</v>
+      </c>
+      <c r="H1478" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1478" s="3">
+        <v>74</v>
+      </c>
+      <c r="J1478" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1478" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1478" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1478" s="3" t="s">
+        <v>4648</v>
+      </c>
+      <c r="N1478" s="3"/>
+    </row>
+    <row r="1479" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1479" s="3" t="s">
+        <v>4649</v>
+      </c>
+      <c r="B1479" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1479" s="3">
+        <v>208</v>
+      </c>
+      <c r="D1479" s="3">
+        <v>1607666700</v>
+      </c>
+      <c r="E1479" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1479" s="3" t="s">
+        <v>4650</v>
+      </c>
+      <c r="G1479" s="3" t="s">
+        <v>4651</v>
+      </c>
+      <c r="H1479" s="3"/>
+      <c r="I1479" s="3">
+        <v>69</v>
+      </c>
+      <c r="J1479" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1479" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1479" s="3"/>
+      <c r="M1479" s="3"/>
+      <c r="N1479" s="3"/>
+    </row>
+    <row r="1480" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1480" s="3" t="s">
+        <v>4652</v>
+      </c>
+      <c r="B1480" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C1480" s="3">
+        <v>342</v>
+      </c>
+      <c r="D1480" s="3">
+        <v>1608283259</v>
+      </c>
+      <c r="E1480" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="F1480" s="3" t="s">
+        <v>4297</v>
+      </c>
+      <c r="G1480" s="3" t="s">
+        <v>4653</v>
+      </c>
+      <c r="H1480" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1480" s="3">
+        <v>65</v>
+      </c>
+      <c r="J1480" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1480" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1480" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1480" s="3" t="s">
+        <v>4654</v>
+      </c>
+      <c r="N1480" s="3"/>
+    </row>
+    <row r="1481" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1481" s="3" t="s">
+        <v>4655</v>
+      </c>
+      <c r="B1481" s="3"/>
+      <c r="C1481" s="3">
+        <v>840</v>
+      </c>
+      <c r="D1481" s="3">
+        <v>1608670180</v>
+      </c>
+      <c r="E1481" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1481" s="3" t="s">
+        <v>4656</v>
+      </c>
+      <c r="G1481" s="3" t="s">
+        <v>4657</v>
+      </c>
+      <c r="H1481" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1481" s="3">
+        <v>49</v>
+      </c>
+      <c r="J1481" s="3"/>
+      <c r="K1481" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1481" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1481" s="3" t="s">
+        <v>4654</v>
+      </c>
+      <c r="N1481" s="3"/>
+    </row>
+    <row r="1482" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1482" s="3" t="s">
+        <v>4658</v>
+      </c>
+      <c r="B1482" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1482" s="3">
+        <v>208</v>
+      </c>
+      <c r="D1482" s="3">
+        <v>1608757867</v>
+      </c>
+      <c r="E1482" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1482" s="3" t="s">
+        <v>4659</v>
+      </c>
+      <c r="G1482" s="3" t="s">
+        <v>4660</v>
+      </c>
+      <c r="H1482" s="3"/>
+      <c r="I1482" s="3">
+        <v>57</v>
+      </c>
+      <c r="J1482" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1482" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1482" s="3"/>
+      <c r="M1482" s="3"/>
+      <c r="N1482" s="3"/>
+    </row>
+    <row r="1483" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1483" s="3" t="s">
+        <v>4661</v>
+      </c>
+      <c r="B1483" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1483" s="3">
+        <v>210</v>
+      </c>
+      <c r="D1483" s="3">
+        <v>1609214751</v>
+      </c>
+      <c r="E1483" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="F1483" s="3" t="s">
+        <v>4662</v>
+      </c>
+      <c r="G1483" s="3" t="s">
+        <v>4663</v>
+      </c>
+      <c r="H1483" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1483" s="3">
+        <v>69</v>
+      </c>
+      <c r="J1483" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1483" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1483" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1483" s="3" t="s">
+        <v>4664</v>
+      </c>
+      <c r="N1483" s="3"/>
+    </row>
+    <row r="1484" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1484" s="3" t="s">
+        <v>4665</v>
+      </c>
+      <c r="B1484" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C1484" s="3">
+        <v>731</v>
+      </c>
+      <c r="D1484" s="3">
+        <v>1609221089</v>
+      </c>
+      <c r="E1484" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1484" s="3" t="s">
+        <v>4666</v>
+      </c>
+      <c r="G1484" s="3" t="s">
+        <v>4667</v>
+      </c>
+      <c r="H1484" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1484" s="3">
+        <v>63</v>
+      </c>
+      <c r="J1484" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1484" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1484" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1484" s="3" t="s">
+        <v>4668</v>
+      </c>
+      <c r="N1484" s="3"/>
+    </row>
+    <row r="1485" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1485" s="3" t="s">
+        <v>4669</v>
+      </c>
+      <c r="B1485" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1485" s="3">
+        <v>208</v>
+      </c>
+      <c r="D1485" s="3">
+        <v>1609366946</v>
+      </c>
+      <c r="E1485" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1485" s="3" t="s">
+        <v>4670</v>
+      </c>
+      <c r="G1485" s="3" t="s">
+        <v>4671</v>
+      </c>
+      <c r="H1485" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1485" s="3">
+        <v>59</v>
+      </c>
+      <c r="J1485" s="3"/>
+      <c r="K1485" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1485" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1485" s="3" t="s">
+        <v>4672</v>
+      </c>
+      <c r="N1485" s="3"/>
+    </row>
+    <row r="1486" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1486" s="3" t="s">
+        <v>4673</v>
+      </c>
+      <c r="B1486" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C1486" s="3">
+        <v>342</v>
+      </c>
+      <c r="D1486" s="3">
+        <v>1609462382</v>
+      </c>
+      <c r="E1486" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1486" s="3" t="s">
+        <v>4674</v>
+      </c>
+      <c r="G1486" s="3" t="s">
+        <v>4675</v>
+      </c>
+      <c r="H1486" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1486" s="3">
+        <v>69</v>
+      </c>
+      <c r="J1486" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1486" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1486" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1486" s="3" t="s">
+        <v>4672</v>
+      </c>
+      <c r="N1486" s="3"/>
+    </row>
+    <row r="1487" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1487" s="3" t="s">
+        <v>4676</v>
+      </c>
+      <c r="B1487" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C1487" s="3">
+        <v>731</v>
+      </c>
+      <c r="D1487" s="3">
+        <v>1610024194</v>
+      </c>
+      <c r="E1487" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1487" s="3" t="s">
+        <v>4677</v>
+      </c>
+      <c r="G1487" s="3" t="s">
+        <v>4678</v>
+      </c>
+      <c r="H1487" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1487" s="3">
+        <v>66</v>
+      </c>
+      <c r="J1487" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1487" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1487" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1487" s="3" t="s">
+        <v>4679</v>
+      </c>
+      <c r="N1487" s="3"/>
+    </row>
+    <row r="1488" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1488" s="3" t="s">
+        <v>4680</v>
+      </c>
+      <c r="B1488" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C1488" s="3">
+        <v>729</v>
+      </c>
+      <c r="D1488" s="3">
+        <v>1610166418</v>
+      </c>
+      <c r="E1488" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1488" s="3" t="s">
+        <v>4681</v>
+      </c>
+      <c r="G1488" s="3" t="s">
+        <v>4682</v>
+      </c>
+      <c r="H1488" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1488" s="3">
+        <v>31</v>
+      </c>
+      <c r="J1488" s="3"/>
+      <c r="K1488" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1488" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1488" s="3" t="s">
+        <v>4679</v>
+      </c>
+      <c r="N1488" s="3"/>
+    </row>
+    <row r="1489" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1489" s="3" t="s">
+        <v>4683</v>
+      </c>
+      <c r="B1489" s="3"/>
+      <c r="C1489" s="3">
+        <v>673</v>
+      </c>
+      <c r="D1489" s="3">
+        <v>1610256836</v>
+      </c>
+      <c r="E1489" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1489" s="3" t="s">
+        <v>4684</v>
+      </c>
+      <c r="G1489" s="3" t="s">
+        <v>4685</v>
+      </c>
+      <c r="H1489" s="3"/>
+      <c r="I1489" s="3">
+        <v>54</v>
+      </c>
+      <c r="J1489" s="3">
+        <v>55</v>
+      </c>
+      <c r="K1489" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1489" s="3"/>
+      <c r="M1489" s="3"/>
+      <c r="N1489" s="3"/>
+    </row>
+    <row r="1490" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1490" s="3" t="s">
+        <v>4686</v>
+      </c>
+      <c r="B1490" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C1490" s="3">
+        <v>342</v>
+      </c>
+      <c r="D1490" s="3">
+        <v>1610341065</v>
+      </c>
+      <c r="E1490" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1490" s="3" t="s">
+        <v>4687</v>
+      </c>
+      <c r="G1490" s="3" t="s">
+        <v>4688</v>
+      </c>
+      <c r="H1490" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1490" s="3">
+        <v>72</v>
+      </c>
+      <c r="J1490" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1490" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1490" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1490" s="3" t="s">
+        <v>4679</v>
+      </c>
+      <c r="N1490" s="3"/>
+    </row>
+    <row r="1491" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1491" s="3" t="s">
+        <v>4686</v>
+      </c>
+      <c r="B1491" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C1491" s="3">
+        <v>342</v>
+      </c>
+      <c r="D1491" s="3">
+        <v>1610341059</v>
+      </c>
+      <c r="E1491" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1491" s="3" t="s">
+        <v>4689</v>
+      </c>
+      <c r="G1491" s="3" t="s">
+        <v>4690</v>
+      </c>
+      <c r="H1491" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1491" s="3">
+        <v>70</v>
+      </c>
+      <c r="J1491" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1491" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1491" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1491" s="3" t="s">
+        <v>4679</v>
+      </c>
+      <c r="N1491" s="3"/>
+    </row>
+    <row r="1492" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1492" s="3" t="s">
+        <v>4691</v>
+      </c>
+      <c r="B1492" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C1492" s="3">
+        <v>342</v>
+      </c>
+      <c r="D1492" s="3">
+        <v>1610350229</v>
+      </c>
+      <c r="E1492" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1492" s="3" t="s">
+        <v>798</v>
+      </c>
+      <c r="G1492" s="3" t="s">
+        <v>4692</v>
+      </c>
+      <c r="H1492" s="3"/>
+      <c r="I1492" s="3">
+        <v>70</v>
+      </c>
+      <c r="J1492" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1492" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1492" s="3"/>
+      <c r="M1492" s="3"/>
+      <c r="N1492" s="3"/>
+    </row>
+    <row r="1493" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1493" s="3" t="s">
+        <v>4693</v>
+      </c>
+      <c r="B1493" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1493" s="3">
+        <v>208</v>
+      </c>
+      <c r="D1493" s="3">
+        <v>1610670385</v>
+      </c>
+      <c r="E1493" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1493" s="3" t="s">
+        <v>4694</v>
+      </c>
+      <c r="G1493" s="3" t="s">
+        <v>4695</v>
+      </c>
+      <c r="H1493" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1493" s="3">
+        <v>78</v>
+      </c>
+      <c r="J1493" s="3">
+        <v>80</v>
+      </c>
+      <c r="K1493" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1493" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1493" s="3" t="s">
+        <v>4696</v>
+      </c>
+      <c r="N1493" s="3"/>
+    </row>
+    <row r="1494" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1494" s="3" t="s">
+        <v>4697</v>
+      </c>
+      <c r="B1494" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1494" s="3">
+        <v>208</v>
+      </c>
+      <c r="D1494" s="3">
+        <v>1611168947</v>
+      </c>
+      <c r="E1494" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1494" s="3" t="s">
+        <v>4698</v>
+      </c>
+      <c r="G1494" s="3" t="s">
+        <v>4699</v>
+      </c>
+      <c r="H1494" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1494" s="3">
+        <v>72</v>
+      </c>
+      <c r="J1494" s="3">
+        <v>80</v>
+      </c>
+      <c r="K1494" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1494" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1494" s="3" t="s">
+        <v>4696</v>
+      </c>
+      <c r="N1494" s="3"/>
+    </row>
+    <row r="1495" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1495" s="3" t="s">
+        <v>4697</v>
+      </c>
+      <c r="B1495" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1495" s="3">
+        <v>208</v>
+      </c>
+      <c r="D1495" s="3">
+        <v>1611168952</v>
+      </c>
+      <c r="E1495" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1495" s="3" t="s">
+        <v>4700</v>
+      </c>
+      <c r="G1495" s="3" t="s">
+        <v>4701</v>
+      </c>
+      <c r="H1495" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1495" s="3">
+        <v>73</v>
+      </c>
+      <c r="J1495" s="3">
+        <v>80</v>
+      </c>
+      <c r="K1495" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1495" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1495" s="3" t="s">
+        <v>4696</v>
+      </c>
+      <c r="N1495" s="3"/>
+    </row>
+    <row r="1496" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1496" s="3" t="s">
+        <v>4702</v>
+      </c>
+      <c r="B1496" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1496" s="3">
+        <v>208</v>
+      </c>
+      <c r="D1496" s="3">
+        <v>1611182700</v>
+      </c>
+      <c r="E1496" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1496" s="3" t="s">
+        <v>1124</v>
+      </c>
+      <c r="G1496" s="3" t="s">
+        <v>4703</v>
+      </c>
+      <c r="H1496" s="3"/>
+      <c r="I1496" s="3">
+        <v>64</v>
+      </c>
+      <c r="J1496" s="3">
+        <v>55</v>
+      </c>
+      <c r="K1496" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1496" s="3"/>
+      <c r="M1496" s="3"/>
+      <c r="N1496" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
